--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446674346924</t>
+    <t xml:space="preserve">3.78446745872498</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277425765991</t>
+    <t xml:space="preserve">3.73277473449707</t>
   </si>
   <si>
     <t xml:space="preserve">3.49607563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41445469856262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901398658752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43349933624268</t>
+    <t xml:space="preserve">3.41445422172546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901231765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4334990978241</t>
   </si>
   <si>
     <t xml:space="preserve">3.53144335746765</t>
@@ -65,238 +65,238 @@
     <t xml:space="preserve">3.53688549995422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28658223152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920241355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157608985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040320396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41989588737488</t>
+    <t xml:space="preserve">3.28658246994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937581062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29202389717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040368080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41989541053772</t>
   </si>
   <si>
     <t xml:space="preserve">3.42805814743042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43077826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276125907898</t>
+    <t xml:space="preserve">3.43077802658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187888145447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276173591614</t>
   </si>
   <si>
     <t xml:space="preserve">3.22672772407532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1396656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18863821029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30562782287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03083848953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89208436012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15599036216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393438339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31378984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40357136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36548256874084</t>
+    <t xml:space="preserve">3.13966631889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18863725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30562710762024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03083896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8920841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1559898853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393462181091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31379008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40357184410095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36548233032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.36820316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46614694595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43622016906738</t>
+    <t xml:space="preserve">3.46614670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43622040748596</t>
   </si>
   <si>
     <t xml:space="preserve">3.36004161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49063420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56681227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409215927124</t>
+    <t xml:space="preserve">3.49063348770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56681323051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409168243408</t>
   </si>
   <si>
     <t xml:space="preserve">3.6919641494751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71100902557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61850547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652319908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380188941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093675613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623173713684</t>
+    <t xml:space="preserve">3.71100807189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61850571632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380212783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623316764832</t>
   </si>
   <si>
     <t xml:space="preserve">3.7926287651062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76542234420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70284676551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181913375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72189092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6946849822998</t>
+    <t xml:space="preserve">3.76542139053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70284724235535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7518196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72189164161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69468450546265</t>
   </si>
   <si>
     <t xml:space="preserve">3.65387439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81439518928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432196617126</t>
+    <t xml:space="preserve">3.81439447402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84432220458984</t>
   </si>
   <si>
     <t xml:space="preserve">3.86608791351318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71372890472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63482999801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5423264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74637722969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77630424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821520805359</t>
+    <t xml:space="preserve">3.7137291431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54232668876648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74637770652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77630496025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73821568489075</t>
   </si>
   <si>
     <t xml:space="preserve">3.8796911239624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91778063774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85248374938965</t>
+    <t xml:space="preserve">3.91778016090393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85248398780823</t>
   </si>
   <si>
     <t xml:space="preserve">3.94407820701599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88579106330872</t>
+    <t xml:space="preserve">3.88579058647156</t>
   </si>
   <si>
     <t xml:space="preserve">3.94962859153748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97460865974426</t>
+    <t xml:space="preserve">3.97460913658142</t>
   </si>
   <si>
     <t xml:space="preserve">3.96628260612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88023996353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92464852333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88856649398804</t>
+    <t xml:space="preserve">3.88023948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92464900016785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88856601715088</t>
   </si>
   <si>
     <t xml:space="preserve">4.00236463546753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98848724365234</t>
+    <t xml:space="preserve">3.98848628997803</t>
   </si>
   <si>
     <t xml:space="preserve">4.04122257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93020009994507</t>
+    <t xml:space="preserve">3.93020057678223</t>
   </si>
   <si>
     <t xml:space="preserve">4.07730531692505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99681401252747</t>
+    <t xml:space="preserve">3.99681282043457</t>
   </si>
   <si>
     <t xml:space="preserve">3.96905755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0606517791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742419242859</t>
+    <t xml:space="preserve">4.06065082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742466926575</t>
   </si>
   <si>
     <t xml:space="preserve">3.93575119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92187309265137</t>
+    <t xml:space="preserve">3.92187356948853</t>
   </si>
   <si>
     <t xml:space="preserve">3.95240473747253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9190981388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130253791809</t>
+    <t xml:space="preserve">3.91909718513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130158424377</t>
   </si>
   <si>
     <t xml:space="preserve">4.08008050918579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29102468490601</t>
+    <t xml:space="preserve">4.29102373123169</t>
   </si>
   <si>
     <t xml:space="preserve">4.23551273345947</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">4.16334772109985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18832731246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21608304977417</t>
+    <t xml:space="preserve">4.18832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21608352661133</t>
   </si>
   <si>
     <t xml:space="preserve">4.182776927948</t>
@@ -317,16 +317,16 @@
     <t xml:space="preserve">4.13559198379517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15502071380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03289556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0523247718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09673357009888</t>
+    <t xml:space="preserve">4.15502023696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03289604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05232524871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09673404693604</t>
   </si>
   <si>
     <t xml:space="preserve">4.06342744827271</t>
@@ -335,232 +335,232 @@
     <t xml:space="preserve">3.69427752494812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53051900863647</t>
+    <t xml:space="preserve">3.53051853179932</t>
   </si>
   <si>
     <t xml:space="preserve">3.55272340774536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48888564109802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60268306732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78587079048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82472920417786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80529975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685316085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288190841675</t>
+    <t xml:space="preserve">3.48888492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60268259048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78586983680725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8247287273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80530047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288238525391</t>
   </si>
   <si>
     <t xml:space="preserve">3.13916373252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26961541175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23630905151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40561842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41394472122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19189977645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410393714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39174032211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47778296470642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59713220596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49721217155457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941657066345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53884530067444</t>
+    <t xml:space="preserve">3.26961517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23630833625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40561819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41394448280334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904414176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1919002532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410441398621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39174056053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47778272628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59713244438171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5388457775116</t>
   </si>
   <si>
     <t xml:space="preserve">3.55827379226685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54162120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63598966598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58047842979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64154148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39451575279236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34455561637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4194962978363</t>
+    <t xml:space="preserve">3.5416202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386475563049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63599038124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58047938346863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64154076576233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39451599121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34455585479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949605941772</t>
   </si>
   <si>
     <t xml:space="preserve">3.54717183113098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56937718391418</t>
+    <t xml:space="preserve">3.56937646865845</t>
   </si>
   <si>
     <t xml:space="preserve">3.4694561958313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41116905212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280313491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231206893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48055839538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51664066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45002794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47500777244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51108932495117</t>
+    <t xml:space="preserve">3.41116952896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280289649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4805588722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51664042472839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45002770423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47500824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51108980178833</t>
   </si>
   <si>
     <t xml:space="preserve">3.56660175323486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58325362205505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994630813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215261459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264344215393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59990787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49166083335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52219176292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50831389427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31402492523193</t>
+    <t xml:space="preserve">3.58325386047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994750022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215189933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264296531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59990811347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49166107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52219200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50831413269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31402397155762</t>
   </si>
   <si>
     <t xml:space="preserve">3.37786269187927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30847382545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36120915412903</t>
+    <t xml:space="preserve">3.30847406387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36120867729187</t>
   </si>
   <si>
     <t xml:space="preserve">3.38896441459656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29737091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1974515914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23075795173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29182076454163</t>
+    <t xml:space="preserve">3.29737114906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19745111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23075771331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29182052612305</t>
   </si>
   <si>
     <t xml:space="preserve">3.2668399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27516627311707</t>
+    <t xml:space="preserve">3.27516722679138</t>
   </si>
   <si>
     <t xml:space="preserve">3.43337368965149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39729166030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46390438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839409828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46112942695618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32235169410706</t>
+    <t xml:space="preserve">3.39729070663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4639048576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4083936214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46112966537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32235193252563</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43059778213501</t>
+    <t xml:space="preserve">3.43059849739075</t>
   </si>
   <si>
     <t xml:space="preserve">3.43614959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50276255607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56382513046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398434638977</t>
+    <t xml:space="preserve">3.50276279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5638256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398506164551</t>
   </si>
   <si>
     <t xml:space="preserve">3.33900475502014</t>
@@ -569,49 +569,49 @@
     <t xml:space="preserve">3.45835447311401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54439640045166</t>
+    <t xml:space="preserve">3.54439687728882</t>
   </si>
   <si>
     <t xml:space="preserve">3.42227149009705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38341403007507</t>
+    <t xml:space="preserve">3.38341283798218</t>
   </si>
   <si>
     <t xml:space="preserve">3.30014681816101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2830331325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37145495414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39142179489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3771595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41423988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45702481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48554825782776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256127357483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73370146751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930472373962</t>
+    <t xml:space="preserve">3.28303265571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37145471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39142155647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37715983390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41424012184143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4570255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48554849624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118586540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79930424690247</t>
   </si>
   <si>
     <t xml:space="preserve">4.09309482574463</t>
@@ -620,37 +620,37 @@
     <t xml:space="preserve">3.95047855377197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89343190193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95333003997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93906903266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93051171302795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92480635643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90483951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93621730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94192051887512</t>
+    <t xml:space="preserve">3.8934314250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332956314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93906855583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93051218986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635089874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92480683326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90484094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93621587753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94192099571228</t>
   </si>
   <si>
     <t xml:space="preserve">3.92195463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89628386497498</t>
+    <t xml:space="preserve">3.89628434181213</t>
   </si>
   <si>
     <t xml:space="preserve">3.94477391242981</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">4.10735654830933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12446975708008</t>
+    <t xml:space="preserve">4.12447023391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.04175329208374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426746368408</t>
+    <t xml:space="preserve">4.07883405685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2442684173584</t>
   </si>
   <si>
     <t xml:space="preserve">4.15014171600342</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">4.30131530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21574401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20433521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26708650588989</t>
+    <t xml:space="preserve">4.215744972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2043342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26708698272705</t>
   </si>
   <si>
     <t xml:space="preserve">4.21289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20718765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09879922866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23571109771729</t>
+    <t xml:space="preserve">4.20718812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09879875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23571062088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.18151712417603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17010736465454</t>
+    <t xml:space="preserve">4.17010688781738</t>
   </si>
   <si>
     <t xml:space="preserve">4.17581224441528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03319501876831</t>
+    <t xml:space="preserve">4.03319549560547</t>
   </si>
   <si>
     <t xml:space="preserve">4.03890085220337</t>
@@ -722,73 +722,73 @@
     <t xml:space="preserve">4.07027626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97044396400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99326276779175</t>
+    <t xml:space="preserve">3.97044491767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99326229095459</t>
   </si>
   <si>
     <t xml:space="preserve">3.98185396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05886650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11306095123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06171941757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04745769500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02749061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75651955604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105060577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51977610588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53689002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692461967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68235898017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64242672920227</t>
+    <t xml:space="preserve">4.05886745452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11305999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06171894073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04745721817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02749109268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75651979446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105036735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51977634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53689026832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386940956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68235850334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64242625236511</t>
   </si>
   <si>
     <t xml:space="preserve">3.6509838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69091582298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71943998336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73084855079651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81641840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78789520263672</t>
+    <t xml:space="preserve">3.69091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7194390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73084902763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81641864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7878954410553</t>
   </si>
   <si>
     <t xml:space="preserve">3.81071400642395</t>
@@ -797,43 +797,43 @@
     <t xml:space="preserve">3.84779453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76792883872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78219103813171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80215740203857</t>
+    <t xml:space="preserve">3.76792931556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7821900844574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80215668678284</t>
   </si>
   <si>
     <t xml:space="preserve">3.83353233337402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85064673423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90769386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91625022888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94762468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97614908218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92765927314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89057970046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349869728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212400436401</t>
+    <t xml:space="preserve">3.85064578056335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9162495136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9476261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.976149559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92765974998474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89057922363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349893569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212257385254</t>
   </si>
   <si>
     <t xml:space="preserve">3.87346506118774</t>
@@ -845,31 +845,31 @@
     <t xml:space="preserve">4.10869359970093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17076826095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11460542678833</t>
+    <t xml:space="preserve">4.17076778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11460638046265</t>
   </si>
   <si>
     <t xml:space="preserve">4.1530327796936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12938499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10573816299438</t>
+    <t xml:space="preserve">4.12938547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10573863983154</t>
   </si>
   <si>
     <t xml:space="preserve">4.16485595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23579835891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875331878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919466018677</t>
+    <t xml:space="preserve">4.23579788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919418334961</t>
   </si>
   <si>
     <t xml:space="preserve">4.34516572952271</t>
@@ -878,130 +878,130 @@
     <t xml:space="preserve">4.35107803344727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36290073394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35994482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39837121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28900337219238</t>
+    <t xml:space="preserve">4.36290121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35994529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39837217330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28900480270386</t>
   </si>
   <si>
     <t xml:space="preserve">4.30082750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3717679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340131759644</t>
+    <t xml:space="preserve">4.37176847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340084075928</t>
   </si>
   <si>
     <t xml:space="preserve">4.5195631980896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46931266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47522449493408</t>
+    <t xml:space="preserve">4.469313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4752254486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.45453357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.368812084198</t>
+    <t xml:space="preserve">4.36881303787231</t>
   </si>
   <si>
     <t xml:space="preserve">4.3333420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41315126419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30673933029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41906309127808</t>
+    <t xml:space="preserve">4.41315174102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30673885345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41906213760376</t>
   </si>
   <si>
     <t xml:space="preserve">4.43384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38654756546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30969381332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28604698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31856203079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39245939254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29491519927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3362979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25353336334229</t>
+    <t xml:space="preserve">4.38654851913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30969476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28604793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31856250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39245986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29491567611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33629751205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25353240966797</t>
   </si>
   <si>
     <t xml:space="preserve">4.32447481155396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37472486495972</t>
+    <t xml:space="preserve">4.37472438812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.3274302482605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33925342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38063621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49296045303345</t>
+    <t xml:space="preserve">4.3392539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3806357383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49295997619629</t>
   </si>
   <si>
     <t xml:space="preserve">4.37768077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40723943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38950395584106</t>
+    <t xml:space="preserve">4.40723991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38950347900391</t>
   </si>
   <si>
     <t xml:space="preserve">4.31560659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27126789093018</t>
+    <t xml:space="preserve">4.27126884460449</t>
   </si>
   <si>
     <t xml:space="preserve">4.21510648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34220933914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3215184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25648880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28309106826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057697296143</t>
+    <t xml:space="preserve">4.342209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32151794433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25648927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28309059143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057744979858</t>
   </si>
   <si>
     <t xml:space="preserve">4.23284196853638</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">4.22101783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16190004348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1973705291748</t>
+    <t xml:space="preserve">4.16189956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19737148284912</t>
   </si>
   <si>
     <t xml:space="preserve">4.24170970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17963457107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22397422790527</t>
+    <t xml:space="preserve">4.17963552474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22397327423096</t>
   </si>
   <si>
     <t xml:space="preserve">4.26831197738647</t>
@@ -1031,73 +1031,73 @@
     <t xml:space="preserve">4.29195976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35403251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43679857254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42201852798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26535606384277</t>
+    <t xml:space="preserve">4.35403347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43679904937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42201900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26535701751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.18850374221802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1737232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16781282424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24762105941772</t>
+    <t xml:space="preserve">4.17372369766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16781234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24762058258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.21806240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23866891860962</t>
+    <t xml:space="preserve">4.28013563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23866939544678</t>
   </si>
   <si>
     <t xml:space="preserve">4.13528633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13832712173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16873359680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1656928062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25083112716675</t>
+    <t xml:space="preserve">4.13832759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16873455047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16569232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25083160400391</t>
   </si>
   <si>
     <t xml:space="preserve">4.25995349884033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27211570739746</t>
+    <t xml:space="preserve">4.27211666107178</t>
   </si>
   <si>
     <t xml:space="preserve">4.36637592315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3694167137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117292404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32988882064819</t>
+    <t xml:space="preserve">4.36941766738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509229660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32988834381104</t>
   </si>
   <si>
     <t xml:space="preserve">4.38157892227173</t>
@@ -1109,49 +1109,49 @@
     <t xml:space="preserve">4.39678239822388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44543218612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5001654624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54577493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4393515586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48800230026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51232719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44847440719604</t>
+    <t xml:space="preserve">4.44543361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50016403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54577445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43935108184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48800277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51232767105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44847345352173</t>
   </si>
   <si>
     <t xml:space="preserve">4.46367692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38766145706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30860424041748</t>
+    <t xml:space="preserve">4.38766050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30860376358032</t>
   </si>
   <si>
     <t xml:space="preserve">4.29340076446533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37245798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46063613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45759630203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718982696533</t>
+    <t xml:space="preserve">4.37245750427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46063709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45759534835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718935012817</t>
   </si>
   <si>
     <t xml:space="preserve">4.55489635467529</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">4.57922172546387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62179040908813</t>
+    <t xml:space="preserve">4.62179088592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.70084762573242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.725172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74037599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73429536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77078294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81639194488525</t>
+    <t xml:space="preserve">4.72517395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7403769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73429489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77078247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81639242172241</t>
   </si>
   <si>
     <t xml:space="preserve">4.81943368911743</t>
@@ -1190,28 +1190,28 @@
     <t xml:space="preserve">4.80423021316528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83463621139526</t>
+    <t xml:space="preserve">4.83463716506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.71301078796387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61571025848389</t>
+    <t xml:space="preserve">4.61570930480957</t>
   </si>
   <si>
     <t xml:space="preserve">4.691725730896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62787246704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53665256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25691270828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29948091506958</t>
+    <t xml:space="preserve">4.62787294387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5366530418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25691223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2994818687439</t>
   </si>
   <si>
     <t xml:space="preserve">4.4059042930603</t>
@@ -1220,856 +1220,856 @@
     <t xml:space="preserve">4.39374208450317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43326950073242</t>
+    <t xml:space="preserve">4.43327045440674</t>
   </si>
   <si>
     <t xml:space="preserve">4.42414855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42110729217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43023061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52448987960815</t>
+    <t xml:space="preserve">4.42110824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43023014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52449035644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50320625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31468439102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27819776535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32076549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38461971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41502666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40894556045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35725450515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33292865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26907539367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29644060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30556297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23562812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29035997390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2660346031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26299381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22650623321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21738386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32380676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38646936416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32702350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20500373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11427021026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14555835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16745901107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24567651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23003339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25506353378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24254846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16120195388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21439027786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17997407913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17058801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08924102783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458636283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83581399917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82329964637756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77636861801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80765604972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81704163551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79826927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73882389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63557577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262639045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8264274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66060590744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72630834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74508118629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6387050151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77011132240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71692228317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379446983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74821019172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69815039634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72318005561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373467445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76072573661804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64183330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60116004943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57925939559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63244724273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68876433372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67624974250793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70440793037415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62931871414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686296463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61993217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6261899471283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84520101547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99537897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88587379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91090297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87022995948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341804504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961649894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84207201004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78575420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79514074325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77324080467224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7075366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698279380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452704429626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80139803886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75446748733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73256635665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82017064094543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75759649276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81391263008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77949738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397314071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8733594417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89213132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9922502040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97660779953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912167549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00163650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47288250923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37276339530945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37589240074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39466428756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39779329299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31018829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24448561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22258472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313815116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18503999710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13498044013977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2069411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26325821876526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31644678115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30706000328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28515887260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25387167930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25074362754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2784378528595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13193368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541566848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890469551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727289199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48354339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44773173332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44122052192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494249343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29146027565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192711830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23351001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28820562362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680676460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4086639881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33378410339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31099462509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3533182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30773854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15537476539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076191902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31425046920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28494930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41517496109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4021532535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36634111404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44447588920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46401023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633406639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48679971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331068992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726560592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45749926567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50958919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47052145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58121347427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71795129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77655267715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70818376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83189868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864332199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87096619606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92305731773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87422180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073325157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88724398612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99142503738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95886898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00770330429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99793696403503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06304979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97189116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01747035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956052780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12165117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09235000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11513996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12816333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09886169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14118528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08583927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11188459396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16071939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13141822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26164484024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24862194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24210977554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23559999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2323431968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3235011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38210296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40489292144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233591079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37569141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2884464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32871341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3320689201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39247035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22804546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23811292648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25153541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751195907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10388851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10724449157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1642894744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12737798690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12402200698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06697702407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07704448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08039999008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04684495925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02671098709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00657749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03342151641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09046649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14415550231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13408899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435598373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15757846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13744497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19784545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21797895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24482488632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34213542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28173542022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28509092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34549188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34884786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47300434112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50991535186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46293783187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45622587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41931390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978185653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48307085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51662683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5367603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4931378364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44280385971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.426025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42267036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4495153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42938089370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5065598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46964836120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40924739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39582490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20120143890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21126747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14080047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38575887680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46629333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595840454102</t>
   </si>
   <si>
     <t xml:space="preserve">4.50320529937744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31468439102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27819681167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32076644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38461923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41502714157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40894556045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35725402832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3329291343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26907634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29644107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3055624961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23562860488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29036045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2660346031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26299381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22650575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21738433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28731966018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32380723953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38646936416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32702398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20500373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11427021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14555740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16745901107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23003339767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2550630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16120147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21438980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17997407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17058801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08924055099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458636283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83581471443176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82330012321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77636861801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80765557289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81704211235046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79826974868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73882341384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63557624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195313453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262615203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82642769813538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66060543060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72630953788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74508166313171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6387050151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77011108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71692252159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379423141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74821019172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69815063476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6825065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72318029403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7607250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60116004943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57925915718079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6324474811554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68876385688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67624926567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70440769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56361603736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62931847572327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686296463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61993288993835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261899471283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84520101547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99537944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88587379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9109034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87023043632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341876029968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961506843567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84207248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78575468063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79514145851135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77324032783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70753645896912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698207855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452656745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81078481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80139803886414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75446748733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73256635665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563508987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82017087936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75759601593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81391334533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77949738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335896492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89213156700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99225091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97660684585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912167549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00163602828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47288250923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37276339530945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37589192390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3946647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098042488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39779281616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31018853187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29141664505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2444863319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22258448600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16313886642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18503975868225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13498044013977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21007037162781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2069411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26325845718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31644678115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30705952644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31331777572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28515887260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25387167930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27843737602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13193440437317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541566848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890445709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48354387283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44773197174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44122004508972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42494249343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41843104362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192711830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23351073265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28820562362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40866422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33378434181213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31099486351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331797599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30773901939392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1553750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076168060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31425023078918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2849497795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41517472267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40215301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36634039878845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44447612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4640097618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633358955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48679995536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331068992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45749878883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50958943367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47052121162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58121371269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71795010566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77655243873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70818448066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83189845085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864308357239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87096619606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92305684089661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87422180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073325157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88724446296692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99142551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95886850357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00770330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99793744087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97189164161682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01746988296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0663046836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956052780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0825834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12165117263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09235000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11513996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1281623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09886169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14118528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08583927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11188459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16071891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13141822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26164388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24862146377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24536561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24210977554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23559856414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23234272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3235011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38210296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4048924446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3788480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233591079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37569189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28844594955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32871389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33206987380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4126033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39246988296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36226940155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22804594039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23811197280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25153541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10388898849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10724401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1642894744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12737798690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12402248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06697750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07704448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08039999008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04684400558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02671003341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00657653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03342199325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09046649932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14415597915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13408899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435693740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15757894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11059999465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13744497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368898391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19784545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21797895431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24482345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34213542938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28173589706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28509092330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33878040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34549140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34884738922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47300338745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50991535186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4629373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41931438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978137969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48307085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51662635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5367603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49313735961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44280338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42602586746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42266988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44951486587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42938137054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5065598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46964836120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40924787521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39582490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20120143890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455646514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21126747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14080047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33542442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38575839996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46629285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595792770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50320482254028</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.52333784103394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722780227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61729431152344</t>
+    <t xml:space="preserve">4.60722732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6172947883606</t>
   </si>
   <si>
     <t xml:space="preserve">4.59716081619263</t>
@@ -2081,10 +2081,10 @@
     <t xml:space="preserve">4.65756177902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67769575119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7246732711792</t>
+    <t xml:space="preserve">4.67769527435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72467279434204</t>
   </si>
   <si>
     <t xml:space="preserve">4.73138475418091</t>
@@ -2093,55 +2093,55 @@
     <t xml:space="preserve">4.69782829284668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61393880844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64078426361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60387229919434</t>
+    <t xml:space="preserve">4.61393928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64078330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60387277603149</t>
   </si>
   <si>
     <t xml:space="preserve">4.62736129760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62400531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62065029144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56024932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66762781143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66427278518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66091775894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6810507774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82534122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86560869216919</t>
+    <t xml:space="preserve">4.62400579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62065076828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56024885177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66762828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66427230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66091728210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68105030059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82534074783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86560773849487</t>
   </si>
   <si>
     <t xml:space="preserve">4.90252017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94278717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98305463790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04345464706421</t>
+    <t xml:space="preserve">4.942786693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98305320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04345512390137</t>
   </si>
   <si>
     <t xml:space="preserve">5.07365465164185</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">5.08707714080811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09714412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11727714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15083312988281</t>
+    <t xml:space="preserve">5.09714365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11727809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15083360671997</t>
   </si>
   <si>
     <t xml:space="preserve">5.16090059280396</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">5.15754461288452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16425609588623</t>
+    <t xml:space="preserve">5.16425561904907</t>
   </si>
   <si>
     <t xml:space="preserve">5.17432260513306</t>
@@ -2174,181 +2174,181 @@
     <t xml:space="preserve">5.16761112213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23472356796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54343795776367</t>
+    <t xml:space="preserve">5.2347240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54343843460083</t>
   </si>
   <si>
     <t xml:space="preserve">5.6340389251709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79175138473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89241933822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7716178894043</t>
+    <t xml:space="preserve">5.79175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89241981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77161836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78504133224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87102508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02923679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17025136947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18400812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26999378204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32846307754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909868240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40069007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878183364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28031206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26311445236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33534240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38349342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33190202713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23216104507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25967597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23559951782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28375148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27687215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24935722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1668119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13585758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1461763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09114503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611516952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91229820251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00860071182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00516080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10490274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03267669677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92949533462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95700883865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90885877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73001050949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8572678565979</t>
   </si>
   <si>
     <t xml:space="preserve">5.78504037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87102556228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02923774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17025136947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18400812149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2699933052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840333938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32846307754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40069103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878135681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28031206130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2631139755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33534145355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3834924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33190250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2321605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25967597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23559999465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30438756942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28375196456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27687168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24935722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16681241989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13585710525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14617586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09114503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11866092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91229820251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0533127784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00860023498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00516080856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10490274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0326771736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92949390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95700931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90885829925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73001050949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8572678565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78504085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60619211196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61651134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249462127686</t>
+    <t xml:space="preserve">5.60619258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61651086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249557495117</t>
   </si>
   <si>
     <t xml:space="preserve">5.66810131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71625232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77816200256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81255626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80567646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80911636352539</t>
+    <t xml:space="preserve">5.71625328063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77816152572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81255531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80567741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80911540985107</t>
   </si>
   <si>
     <t xml:space="preserve">5.87790393829346</t>
@@ -2360,37 +2360,37 @@
     <t xml:space="preserve">6.01547956466675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86758661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70593547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40326881408691</t>
+    <t xml:space="preserve">5.8675856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70593452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40326929092407</t>
   </si>
   <si>
     <t xml:space="preserve">5.35511779785156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37231397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505710601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06277084350586</t>
+    <t xml:space="preserve">5.372314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06277132034302</t>
   </si>
   <si>
     <t xml:space="preserve">5.00430107116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98366498947144</t>
+    <t xml:space="preserve">4.98366403579712</t>
   </si>
   <si>
     <t xml:space="preserve">4.9492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6981954574585</t>
+    <t xml:space="preserve">4.69819641113281</t>
   </si>
   <si>
     <t xml:space="preserve">4.58813571929932</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">4.26483345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75580525398254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71453332901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36509156227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36784267425537</t>
+    <t xml:space="preserve">3.75580477714539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71453285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3650918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36784338951111</t>
   </si>
   <si>
     <t xml:space="preserve">3.08306217193604</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">2.91109299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90283823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25365519523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3513343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53568434715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4159939289093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24815225601196</t>
+    <t xml:space="preserve">2.90283870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25365567207336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35133409500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53568482398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41599416732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24815249443054</t>
   </si>
   <si>
     <t xml:space="preserve">3.1986255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18899488449097</t>
+    <t xml:space="preserve">3.18899512290955</t>
   </si>
   <si>
     <t xml:space="preserve">3.20000076293945</t>
@@ -2453,43 +2453,43 @@
     <t xml:space="preserve">3.14359569549561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25778293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43938255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59415411949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76268362998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44969964027405</t>
+    <t xml:space="preserve">3.25778245925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43938231468201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59415435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76268410682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44970011711121</t>
   </si>
   <si>
     <t xml:space="preserve">3.49097299575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5975935459137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52880644798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48409414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56319952011108</t>
+    <t xml:space="preserve">3.59759402275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52880573272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096405982971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4840943813324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56319975852966</t>
   </si>
   <si>
     <t xml:space="preserve">3.54600310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68013858795166</t>
+    <t xml:space="preserve">3.68013834953308</t>
   </si>
   <si>
     <t xml:space="preserve">3.8555474281311</t>
@@ -2501,55 +2501,55 @@
     <t xml:space="preserve">3.83147144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65950202941895</t>
+    <t xml:space="preserve">3.65950274467468</t>
   </si>
   <si>
     <t xml:space="preserve">3.60447239875793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64574551582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68701815605164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69045686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84866833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019951820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80739545822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81427431106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92089581489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95528936386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03439521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07222747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16853141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12037992477417</t>
+    <t xml:space="preserve">3.64574480056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68701767921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69045662879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84866881370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745638847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421481132507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80739641189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81427526473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92089629173279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95528960227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03439569473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16853094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12037944793701</t>
   </si>
   <si>
     <t xml:space="preserve">4.08598566055298</t>
@@ -2564,37 +2564,37 @@
     <t xml:space="preserve">4.44712114334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65348291397095</t>
+    <t xml:space="preserve">4.65348386764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.76010465621948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57781744003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33018255233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34737920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49183320999146</t>
+    <t xml:space="preserve">4.57781791687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33018207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34737873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4918327331543</t>
   </si>
   <si>
     <t xml:space="preserve">4.44368171691895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42304611206055</t>
+    <t xml:space="preserve">4.42304468154907</t>
   </si>
   <si>
     <t xml:space="preserve">4.46775722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45399904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49527263641357</t>
+    <t xml:space="preserve">4.4539999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49527215957642</t>
   </si>
   <si>
     <t xml:space="preserve">4.30266666412354</t>
@@ -2603,22 +2603,22 @@
     <t xml:space="preserve">4.29234886169434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33706092834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39552974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32330274581909</t>
+    <t xml:space="preserve">4.33706045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37489366531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39553022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32330322265625</t>
   </si>
   <si>
     <t xml:space="preserve">4.52622652053833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41616678237915</t>
+    <t xml:space="preserve">4.41616630554199</t>
   </si>
   <si>
     <t xml:space="preserve">4.52278757095337</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">4.31298494338989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41960668563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47119665145874</t>
+    <t xml:space="preserve">4.41960573196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4711971282959</t>
   </si>
   <si>
     <t xml:space="preserve">4.53310537338257</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">4.53654479980469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55718088150024</t>
+    <t xml:space="preserve">4.5571813583374</t>
   </si>
   <si>
     <t xml:space="preserve">4.66380167007446</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">4.61221075057983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52966594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743989944458</t>
+    <t xml:space="preserve">4.57093858718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52966547012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743942260742</t>
   </si>
   <si>
     <t xml:space="preserve">4.40928745269775</t>
@@ -2666,58 +2666,58 @@
     <t xml:space="preserve">4.39209079742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42648506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26139497756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42992401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43680238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56062078475952</t>
+    <t xml:space="preserve">4.42648410797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26139450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42992353439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43680286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56062126159668</t>
   </si>
   <si>
     <t xml:space="preserve">4.63628721237183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68443822860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60877132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48839330673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56406021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45056056976318</t>
+    <t xml:space="preserve">4.68443775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60877227783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48839378356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5640606880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45056009292603</t>
   </si>
   <si>
     <t xml:space="preserve">4.59501457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51590919494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54686307907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40240907669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27515172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081815719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35425710678101</t>
+    <t xml:space="preserve">4.51590824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54686260223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40240859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35081911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35425806045532</t>
   </si>
   <si>
     <t xml:space="preserve">4.55030250549316</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">4.23043966293335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32674169540405</t>
+    <t xml:space="preserve">4.32674264907837</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636415481567</t>
@@ -2741,82 +2741,82 @@
     <t xml:space="preserve">4.50558996200562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4333643913269</t>
+    <t xml:space="preserve">4.43336296081543</t>
   </si>
   <si>
     <t xml:space="preserve">4.29922771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31986379623413</t>
+    <t xml:space="preserve">4.31986331939697</t>
   </si>
   <si>
     <t xml:space="preserve">4.30610656738281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16165256500244</t>
+    <t xml:space="preserve">4.16165208816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.03783416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98968386650085</t>
+    <t xml:space="preserve">3.98968315124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.03095579147339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25107574462891</t>
+    <t xml:space="preserve">4.25107669830322</t>
   </si>
   <si>
     <t xml:space="preserve">4.73258972167969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81169509887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93207359313965</t>
+    <t xml:space="preserve">4.81169605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93207406997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.81513452529907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.966468334198</t>
+    <t xml:space="preserve">4.96646738052368</t>
   </si>
   <si>
     <t xml:space="preserve">5.20034551620483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1934666633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12467861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22442197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24161815643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37919330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569414138794</t>
+    <t xml:space="preserve">5.19346618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12467956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22442102432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24161911010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3791937828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569366455078</t>
   </si>
   <si>
     <t xml:space="preserve">5.34136056900024</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23129987716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29664850234985</t>
+    <t xml:space="preserve">5.23130035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2966480255127</t>
   </si>
   <si>
     <t xml:space="preserve">5.15563344955444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11092138290405</t>
+    <t xml:space="preserve">5.11092185974121</t>
   </si>
   <si>
     <t xml:space="preserve">5.10404300689697</t>
@@ -2825,31 +2825,31 @@
     <t xml:space="preserve">5.04557371139526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00774049758911</t>
+    <t xml:space="preserve">5.00774002075195</t>
   </si>
   <si>
     <t xml:space="preserve">5.00086164474487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91831588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88736152648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8942403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89767980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8839225769043</t>
+    <t xml:space="preserve">4.91831684112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88736200332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89423990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89768075942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88392210006714</t>
   </si>
   <si>
     <t xml:space="preserve">4.8667254447937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76698350906372</t>
+    <t xml:space="preserve">4.76698303222656</t>
   </si>
   <si>
     <t xml:space="preserve">4.83577108383179</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">4.85296773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89080190658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91487646102905</t>
+    <t xml:space="preserve">4.89080142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91487741470337</t>
   </si>
   <si>
     <t xml:space="preserve">4.85984706878662</t>
@@ -2870,25 +2870,25 @@
     <t xml:space="preserve">4.87016439437866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05933094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03869438171387</t>
+    <t xml:space="preserve">5.05933046340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03869485855103</t>
   </si>
   <si>
     <t xml:space="preserve">5.03181600570679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71539258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59845352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53998422622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61565065383911</t>
+    <t xml:space="preserve">4.71539354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59845447540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53998374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61565160751343</t>
   </si>
   <si>
     <t xml:space="preserve">4.67068099975586</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">5.02837657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12811803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31728506088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25537633895874</t>
+    <t xml:space="preserve">5.12811899185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31728410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25537586212158</t>
   </si>
   <si>
     <t xml:space="preserve">5.27257299423218</t>
@@ -2912,136 +2912,136 @@
     <t xml:space="preserve">5.2588152885437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15219402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07652759552002</t>
+    <t xml:space="preserve">5.15219449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07652854919434</t>
   </si>
   <si>
     <t xml:space="preserve">5.09028577804565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14875459671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493715286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0524525642395</t>
+    <t xml:space="preserve">5.14875555038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493762969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05245208740234</t>
   </si>
   <si>
     <t xml:space="preserve">4.96990728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13499784469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14187574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23817920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29320907592773</t>
+    <t xml:space="preserve">5.1349983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16251277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14187669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23817873001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29320859909058</t>
   </si>
   <si>
     <t xml:space="preserve">5.32760238647461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34479999542236</t>
+    <t xml:space="preserve">5.34480094909668</t>
   </si>
   <si>
     <t xml:space="preserve">5.33104181289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33792018890381</t>
+    <t xml:space="preserve">5.33792066574097</t>
   </si>
   <si>
     <t xml:space="preserve">5.45142078399658</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58899593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44454145431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48237562179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48925352096558</t>
+    <t xml:space="preserve">5.58899641036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50645160675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708673477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44454097747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48237466812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48925447463989</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53740549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51952123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55116271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47824859619141</t>
+    <t xml:space="preserve">5.53740453720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51952028274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5511622428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47824811935425</t>
   </si>
   <si>
     <t xml:space="preserve">5.40258169174194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45898675918579</t>
+    <t xml:space="preserve">5.45898723602295</t>
   </si>
   <si>
     <t xml:space="preserve">5.41221189498901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41496276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36543560028076</t>
+    <t xml:space="preserve">5.41496324539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36543655395508</t>
   </si>
   <si>
     <t xml:space="preserve">5.3833212852478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43972682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39019918441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32553863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37644195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39982938766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37506628036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34617519378662</t>
+    <t xml:space="preserve">5.43972635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39019966125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32554006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37644147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39983034133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37506675720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34617567062378</t>
   </si>
   <si>
     <t xml:space="preserve">5.46036243438721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37369012832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43697500228882</t>
+    <t xml:space="preserve">5.37368965148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43697452545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.51401710510254</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">5.57730197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55528974533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42321729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44247817993164</t>
+    <t xml:space="preserve">5.55529022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44247770309448</t>
   </si>
   <si>
     <t xml:space="preserve">5.39845418930054</t>
@@ -3068,223 +3068,223 @@
     <t xml:space="preserve">5.47484111785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43066692352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42928600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44309091567993</t>
+    <t xml:space="preserve">5.43066644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42928647994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44308996200562</t>
   </si>
   <si>
     <t xml:space="preserve">5.59493923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58113527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56732988357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57837390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55766773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70813608169556</t>
+    <t xml:space="preserve">5.58113574981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5673303604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57837438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55766725540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60046148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70813655853271</t>
   </si>
   <si>
     <t xml:space="preserve">5.74264717102051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63773345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69571113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66948366165161</t>
+    <t xml:space="preserve">5.6377329826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69571208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66948318481445</t>
   </si>
   <si>
     <t xml:space="preserve">5.76473474502563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77715826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291738510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61288499832153</t>
+    <t xml:space="preserve">5.7771577835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6750054359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61288547515869</t>
   </si>
   <si>
     <t xml:space="preserve">5.67914628982544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83927822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66120052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79234409332275</t>
+    <t xml:space="preserve">5.83927774429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66120100021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79234313964844</t>
   </si>
   <si>
     <t xml:space="preserve">5.66258144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328809738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68604898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65015745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55352544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63635349273682</t>
+    <t xml:space="preserve">5.6653413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68466901779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68604850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65015649795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55352640151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63635301589966</t>
   </si>
   <si>
     <t xml:space="preserve">5.72746229171753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6681022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68742895126343</t>
+    <t xml:space="preserve">5.66810321807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68742942810059</t>
   </si>
   <si>
     <t xml:space="preserve">5.60460233688354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59355878829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36164474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40443849563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57975482940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62392854690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362499237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81442928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8199520111084</t>
+    <t xml:space="preserve">5.59355974197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36164426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40443897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57975387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62392902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362546920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81995153427124</t>
   </si>
   <si>
     <t xml:space="preserve">5.79924583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79510354995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73160314559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74540853500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71503782272339</t>
+    <t xml:space="preserve">5.79510450363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73160362243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71503829956055</t>
   </si>
   <si>
     <t xml:space="preserve">5.75507164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80752801895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88069152832031</t>
+    <t xml:space="preserve">5.8075270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88069200515747</t>
   </si>
   <si>
     <t xml:space="preserve">5.95523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04910659790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03115892410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981134414673</t>
+    <t xml:space="preserve">5.96351861953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04910564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0311598777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06981229782104</t>
   </si>
   <si>
     <t xml:space="preserve">6.0325403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07809400558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94695329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92348432540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98284435272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9731822013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99802875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98560571670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03668165206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05048608779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06705141067505</t>
+    <t xml:space="preserve">6.07809448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9469518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92348480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98284482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97318124771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99802827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98560523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03668212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05048561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06705188751221</t>
   </si>
   <si>
     <t xml:space="preserve">6.06567096710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08775758743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09051942825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06014823913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04220390319824</t>
+    <t xml:space="preserve">6.08775663375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09051895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06014919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04220247268677</t>
   </si>
   <si>
     <t xml:space="preserve">6.03944253921509</t>
@@ -3293,16 +3293,16 @@
     <t xml:space="preserve">6.01045322418213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15677976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19681262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15125846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20233535766602</t>
+    <t xml:space="preserve">6.15678071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19681310653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15125799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20233488082886</t>
   </si>
   <si>
     <t xml:space="preserve">6.14573669433594</t>
@@ -3311,19 +3311,19 @@
     <t xml:space="preserve">5.9593768119812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14849805831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3459005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30034637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32519388198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32243299484253</t>
+    <t xml:space="preserve">6.14849710464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34590101242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30034589767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32519340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32243394851685</t>
   </si>
   <si>
     <t xml:space="preserve">6.39835834503174</t>
@@ -3332,67 +3332,67 @@
     <t xml:space="preserve">6.4535756111145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55710935592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57229375839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616344451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71585988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72000074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245759963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80697011947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82739353179932</t>
+    <t xml:space="preserve">6.5571084022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57229328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60542440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72000122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245950698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80696964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.827392578125</t>
   </si>
   <si>
     <t xml:space="preserve">6.70334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70931816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62562084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61366415023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56284618377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66149091720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60917949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56583547592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50605154037476</t>
+    <t xml:space="preserve">6.70931911468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62562131881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61366319656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56284666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66149139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60918045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56583642959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50605297088623</t>
   </si>
   <si>
     <t xml:space="preserve">6.58227634429932</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">6.49708414077759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.553879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68241548538208</t>
+    <t xml:space="preserve">6.55387926101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68241596221924</t>
   </si>
   <si>
     <t xml:space="preserve">6.65850210189819</t>
@@ -3416,103 +3416,103 @@
     <t xml:space="preserve">6.73771667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77657508850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78405046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84532833099365</t>
+    <t xml:space="preserve">6.77657604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78404951095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84532928466797</t>
   </si>
   <si>
     <t xml:space="preserve">6.83187675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7436957359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66298675537109</t>
+    <t xml:space="preserve">6.74369478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66298627853394</t>
   </si>
   <si>
     <t xml:space="preserve">6.56434154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70861291885376</t>
+    <t xml:space="preserve">6.70861196517944</t>
   </si>
   <si>
     <t xml:space="preserve">6.58429384231567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77614307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68865966796875</t>
+    <t xml:space="preserve">6.7761435508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68866014480591</t>
   </si>
   <si>
     <t xml:space="preserve">6.38783931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4384880065918</t>
+    <t xml:space="preserve">6.43848752975464</t>
   </si>
   <si>
     <t xml:space="preserve">6.32951736450195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49373960494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44309234619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47685670852661</t>
+    <t xml:space="preserve">6.49374103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44309186935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47685766220093</t>
   </si>
   <si>
     <t xml:space="preserve">6.5489935874939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68405532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62112903594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56127214431763</t>
+    <t xml:space="preserve">6.68405485153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62112855911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56127166748047</t>
   </si>
   <si>
     <t xml:space="preserve">6.51522731781006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50601863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51062393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52443599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4446268081665</t>
+    <t xml:space="preserve">6.50601816177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51062345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52443647384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44462633132935</t>
   </si>
   <si>
     <t xml:space="preserve">6.2451024055481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42927932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48299694061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58889818191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65335893630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64568614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103410720825</t>
+    <t xml:space="preserve">6.42927980422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48299646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58889865875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65335988998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64568519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103458404541</t>
   </si>
   <si>
     <t xml:space="preserve">6.74391317367554</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">6.7945613861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8528847694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66410303115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78688764572144</t>
+    <t xml:space="preserve">6.85288381576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66410350799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78688812255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.84981393814087</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">6.97566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10612630844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13221645355225</t>
+    <t xml:space="preserve">7.106125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13221740722656</t>
   </si>
   <si>
     <t xml:space="preserve">6.99255132675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96185398101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79763174057007</t>
+    <t xml:space="preserve">6.96185445785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79763031005859</t>
   </si>
   <si>
     <t xml:space="preserve">6.79149198532104</t>
@@ -3557,13 +3557,13 @@
     <t xml:space="preserve">6.70554256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40779209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41700124740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55052804946899</t>
+    <t xml:space="preserve">6.40779161453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41700077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55052852630615</t>
   </si>
   <si>
     <t xml:space="preserve">6.51829719543457</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">6.46611404418945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57201528549194</t>
+    <t xml:space="preserve">6.57201480865479</t>
   </si>
   <si>
     <t xml:space="preserve">6.67177724838257</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76386547088623</t>
+    <t xml:space="preserve">6.76386499404907</t>
   </si>
   <si>
     <t xml:space="preserve">6.69786882400513</t>
@@ -3590,46 +3590,46 @@
     <t xml:space="preserve">6.54438877105713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69940376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79916572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56894540786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5229024887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47225284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38476943969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36328220367432</t>
+    <t xml:space="preserve">6.69940423965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79916524887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56894588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34486436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52290153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47225332260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38476991653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36328268051147</t>
   </si>
   <si>
     <t xml:space="preserve">6.29575157165527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23435878753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2850079536438</t>
+    <t xml:space="preserve">6.23435926437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28500699996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.75089693069458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8874945640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64960050582886</t>
+    <t xml:space="preserve">5.88749408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64959955215454</t>
   </si>
   <si>
     <t xml:space="preserve">5.43933248519897</t>
@@ -3638,13 +3638,13 @@
     <t xml:space="preserve">5.46388912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.336501121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9881010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977952957153</t>
+    <t xml:space="preserve">5.33650064468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98810148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977905273438</t>
   </si>
   <si>
     <t xml:space="preserve">5.07098054885864</t>
@@ -3659,31 +3659,31 @@
     <t xml:space="preserve">5.41938018798828</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50993299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62811326980591</t>
+    <t xml:space="preserve">5.50993394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62811374664307</t>
   </si>
   <si>
     <t xml:space="preserve">5.92125988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88135480880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86447286605835</t>
+    <t xml:space="preserve">5.88135576248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86447238922119</t>
   </si>
   <si>
     <t xml:space="preserve">5.82149791717529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97190856933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90898132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.872145652771</t>
+    <t xml:space="preserve">5.97190809249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90898084640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87214612960815</t>
   </si>
   <si>
     <t xml:space="preserve">5.92586421966553</t>
@@ -3692,82 +3692,82 @@
     <t xml:space="preserve">5.96116495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12538862228394</t>
+    <t xml:space="preserve">6.12538814544678</t>
   </si>
   <si>
     <t xml:space="preserve">6.06860065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95195579528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05325269699097</t>
+    <t xml:space="preserve">5.9519567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05325317382812</t>
   </si>
   <si>
     <t xml:space="preserve">5.98879146575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93353843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72787570953369</t>
+    <t xml:space="preserve">5.93353796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72787523269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.7155966758728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85679769515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82303237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77084970474243</t>
+    <t xml:space="preserve">5.85679864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82303333282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77084922790527</t>
   </si>
   <si>
     <t xml:space="preserve">5.81842851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86293697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79859924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89671564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87098026275635</t>
+    <t xml:space="preserve">5.86293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7985987663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89671611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87098073959351</t>
   </si>
   <si>
     <t xml:space="preserve">5.78090476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65865898132324</t>
+    <t xml:space="preserve">5.65865993499756</t>
   </si>
   <si>
     <t xml:space="preserve">5.56536769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60397100448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55089044570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61040544509888</t>
+    <t xml:space="preserve">5.60397148132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55089139938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61040449142456</t>
   </si>
   <si>
     <t xml:space="preserve">5.56375932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59271192550659</t>
+    <t xml:space="preserve">5.59271144866943</t>
   </si>
   <si>
     <t xml:space="preserve">5.55732488632202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62166500091553</t>
+    <t xml:space="preserve">5.62166404724121</t>
   </si>
   <si>
     <t xml:space="preserve">5.58788633346558</t>
@@ -3779,31 +3779,31 @@
     <t xml:space="preserve">5.56054210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81146574020386</t>
+    <t xml:space="preserve">5.81146621704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.66348505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7085223197937</t>
+    <t xml:space="preserve">5.70852327346802</t>
   </si>
   <si>
     <t xml:space="preserve">5.74069261550903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76321125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68922138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75516891479492</t>
+    <t xml:space="preserve">5.76321172714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6892204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817302703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510774612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75516939163208</t>
   </si>
   <si>
     <t xml:space="preserve">5.76803636550903</t>
@@ -3815,22 +3815,22 @@
     <t xml:space="preserve">5.94175338745117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91280126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84685277938843</t>
+    <t xml:space="preserve">5.91280078887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84685325622559</t>
   </si>
   <si>
     <t xml:space="preserve">5.75034379959106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88706493377686</t>
+    <t xml:space="preserve">5.88706541061401</t>
   </si>
   <si>
     <t xml:space="preserve">5.80503177642822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72299909591675</t>
+    <t xml:space="preserve">5.72299957275391</t>
   </si>
   <si>
     <t xml:space="preserve">5.55249977111816</t>
@@ -3839,115 +3839,115 @@
     <t xml:space="preserve">5.17450475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323230743408</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">5.13107585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20828247070312</t>
+    <t xml:space="preserve">5.20828342437744</t>
   </si>
   <si>
     <t xml:space="preserve">5.01043939590454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05225944519043</t>
+    <t xml:space="preserve">5.05226039886475</t>
   </si>
   <si>
     <t xml:space="preserve">5.11820793151855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11981630325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15198612213135</t>
+    <t xml:space="preserve">5.11981678009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15198659896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.30157566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16807174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17933034896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14876842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04904270172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07156181335449</t>
+    <t xml:space="preserve">5.16807126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17932987213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14876890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04904317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07156133651733</t>
   </si>
   <si>
     <t xml:space="preserve">5.05386829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88819408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03456687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17611312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295850753784</t>
+    <t xml:space="preserve">4.80294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88819456100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03456735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17611360549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03295803070068</t>
   </si>
   <si>
     <t xml:space="preserve">5.10855722427368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0377836227417</t>
+    <t xml:space="preserve">5.03778314590454</t>
   </si>
   <si>
     <t xml:space="preserve">4.85924100875854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98631191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12142515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93484020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01848125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01526498794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96379280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9927453994751</t>
+    <t xml:space="preserve">4.9123215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98631143569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12142467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9348406791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01848173141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0152645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96379327774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99274635314941</t>
   </si>
   <si>
     <t xml:space="preserve">5.18737268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21150016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15842008590698</t>
+    <t xml:space="preserve">5.21150064468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15842056274414</t>
   </si>
   <si>
     <t xml:space="preserve">5.45599031448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59432029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50746154785156</t>
+    <t xml:space="preserve">5.59431982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50746250152588</t>
   </si>
   <si>
     <t xml:space="preserve">5.48976898193359</t>
@@ -3962,13 +3962,13 @@
     <t xml:space="preserve">5.5364146232605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56858491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51067972183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4029107093811</t>
+    <t xml:space="preserve">5.56858396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51067924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40291023254395</t>
   </si>
   <si>
     <t xml:space="preserve">5.44312286376953</t>
@@ -3977,52 +3977,52 @@
     <t xml:space="preserve">5.33374500274658</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19219779968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28388166427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22919321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.163245677948</t>
+    <t xml:space="preserve">5.19219827651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28388261795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22919368743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16324520111084</t>
   </si>
   <si>
     <t xml:space="preserve">5.0410008430481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14394426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12946701049805</t>
+    <t xml:space="preserve">5.14394378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12946653366089</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883054733276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24688720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08121204376221</t>
+    <t xml:space="preserve">5.24688673019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08121252059937</t>
   </si>
   <si>
     <t xml:space="preserve">5.11659955978394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1825475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19863271713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31766033172607</t>
+    <t xml:space="preserve">5.18254709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19863224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31765985488892</t>
   </si>
   <si>
     <t xml:space="preserve">5.53963184356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41577768325806</t>
+    <t xml:space="preserve">5.41577816009521</t>
   </si>
   <si>
     <t xml:space="preserve">5.49459362030029</t>
@@ -4031,76 +4031,76 @@
     <t xml:space="preserve">5.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25653743743896</t>
+    <t xml:space="preserve">5.25653791427612</t>
   </si>
   <si>
     <t xml:space="preserve">5.33052778244019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08925533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15037727355957</t>
+    <t xml:space="preserve">5.08925580978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15037679672241</t>
   </si>
   <si>
     <t xml:space="preserve">5.18898153305054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99596261978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1600284576416</t>
+    <t xml:space="preserve">4.99596309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16002893447876</t>
   </si>
   <si>
     <t xml:space="preserve">5.08603811264038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13590145111084</t>
+    <t xml:space="preserve">5.135901927948</t>
   </si>
   <si>
     <t xml:space="preserve">4.9879207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20345783233643</t>
+    <t xml:space="preserve">5.20345735549927</t>
   </si>
   <si>
     <t xml:space="preserve">5.45920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39808464050293</t>
+    <t xml:space="preserve">5.39808416366577</t>
   </si>
   <si>
     <t xml:space="preserve">5.37878322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32409429550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33696222305298</t>
+    <t xml:space="preserve">5.32409381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33696269989014</t>
   </si>
   <si>
     <t xml:space="preserve">5.28709888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14555215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30961751937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35626411437988</t>
+    <t xml:space="preserve">5.14555168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30961799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35626459121704</t>
   </si>
   <si>
     <t xml:space="preserve">5.47368335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54284906387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61362266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64579200744629</t>
+    <t xml:space="preserve">5.54284858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61362171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64579153060913</t>
   </si>
   <si>
     <t xml:space="preserve">5.67152738571167</t>
@@ -4112,16 +4112,16 @@
     <t xml:space="preserve">5.90315008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92405986785889</t>
+    <t xml:space="preserve">5.9240608215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.04308843612671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11707830429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09616804122925</t>
+    <t xml:space="preserve">6.11707925796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09616851806641</t>
   </si>
   <si>
     <t xml:space="preserve">6.02539491653442</t>
@@ -4133,13 +4133,13 @@
     <t xml:space="preserve">6.08651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21519708633423</t>
+    <t xml:space="preserve">6.21519660949707</t>
   </si>
   <si>
     <t xml:space="preserve">6.27149343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24897480010986</t>
+    <t xml:space="preserve">6.24897432327271</t>
   </si>
   <si>
     <t xml:space="preserve">6.26023387908936</t>
@@ -4154,31 +4154,31 @@
     <t xml:space="preserve">6.45968627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49668216705322</t>
+    <t xml:space="preserve">6.49668169021606</t>
   </si>
   <si>
     <t xml:space="preserve">6.46451234817505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45646953582764</t>
+    <t xml:space="preserve">6.45646905899048</t>
   </si>
   <si>
     <t xml:space="preserve">6.50472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50969743728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290414810181</t>
+    <t xml:space="preserve">6.50969696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290462493896</t>
   </si>
   <si>
     <t xml:space="preserve">6.56108474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47820091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4931206703186</t>
+    <t xml:space="preserve">6.47820138931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49312019348145</t>
   </si>
   <si>
     <t xml:space="preserve">6.52958917617798</t>
@@ -4193,16 +4193,16 @@
     <t xml:space="preserve">6.53124713897705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61413097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57434701919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51301193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47488641738892</t>
+    <t xml:space="preserve">6.61413145065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57434606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47488594055176</t>
   </si>
   <si>
     <t xml:space="preserve">6.52627372741699</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">6.46825551986694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54616546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54948091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4400749206543</t>
+    <t xml:space="preserve">6.54616594314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54948139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44007444381714</t>
   </si>
   <si>
     <t xml:space="preserve">6.39200210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55777025222778</t>
+    <t xml:space="preserve">6.55776977539062</t>
   </si>
   <si>
     <t xml:space="preserve">6.51466989517212</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">6.49146270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46328210830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450845718384</t>
+    <t xml:space="preserve">6.46328258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450798034668</t>
   </si>
   <si>
     <t xml:space="preserve">6.56274271011353</t>
@@ -4244,55 +4244,55 @@
     <t xml:space="preserve">6.68209552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64728450775146</t>
+    <t xml:space="preserve">6.64728498458862</t>
   </si>
   <si>
     <t xml:space="preserve">6.73514175415039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86609840393066</t>
+    <t xml:space="preserve">6.86609792709351</t>
   </si>
   <si>
     <t xml:space="preserve">6.87935924530029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00202751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04015350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11640691757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11806535720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10646200180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97218942642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98545169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07496404647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13464069366455</t>
+    <t xml:space="preserve">7.00202703475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04015398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11640739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11806440353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10646152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9721884727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98545074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0749659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13464164733887</t>
   </si>
   <si>
     <t xml:space="preserve">7.19100189208984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20757865905762</t>
+    <t xml:space="preserve">7.20757913589478</t>
   </si>
   <si>
     <t xml:space="preserve">7.2672553062439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26559782028198</t>
+    <t xml:space="preserve">7.26559734344482</t>
   </si>
   <si>
     <t xml:space="preserve">7.34019327163696</t>
@@ -4304,100 +4304,100 @@
     <t xml:space="preserve">7.40484237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49767160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54077243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54242944717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47446537017822</t>
+    <t xml:space="preserve">7.45788764953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49767255783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54077196121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54242992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47446441650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.58884477615356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62034130096436</t>
+    <t xml:space="preserve">7.6203408241272</t>
   </si>
   <si>
     <t xml:space="preserve">7.64023303985596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67504405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69327783584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52585315704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49435710906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.559006690979</t>
+    <t xml:space="preserve">7.67504453659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69327831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5258526802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46286058425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49435758590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55900573730469</t>
   </si>
   <si>
     <t xml:space="preserve">7.60542154312134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59713363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60210657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66675519943237</t>
+    <t xml:space="preserve">7.59713411331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60210561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66675567626953</t>
   </si>
   <si>
     <t xml:space="preserve">7.71814346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72643041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77781915664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45457410812378</t>
+    <t xml:space="preserve">7.72643232345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77781963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45457315444946</t>
   </si>
   <si>
     <t xml:space="preserve">6.87604331970215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03518104553223</t>
+    <t xml:space="preserve">7.03518009185791</t>
   </si>
   <si>
     <t xml:space="preserve">6.66883373260498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73348331451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51135444641113</t>
+    <t xml:space="preserve">6.73348379135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51135492324829</t>
   </si>
   <si>
     <t xml:space="preserve">6.76166391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00037002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86941289901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76663637161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76000595092773</t>
+    <t xml:space="preserve">7.00036954879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86941337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76663684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76000642776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.67214965820312</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">6.83460235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93406248092651</t>
+    <t xml:space="preserve">6.93406200408936</t>
   </si>
   <si>
     <t xml:space="preserve">6.92743158340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01363039016724</t>
+    <t xml:space="preserve">7.01363086700439</t>
   </si>
   <si>
     <t xml:space="preserve">6.96887397766113</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">7.05341529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06999158859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07993841171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15950679779053</t>
+    <t xml:space="preserve">7.06999206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07993793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15950584411621</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
@@ -4439,25 +4439,25 @@
     <t xml:space="preserve">7.18271398544312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08656930923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1429295539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16344022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05917692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01473617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05746793746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00277233123779</t>
+    <t xml:space="preserve">7.08656883239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14293003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1634407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05917739868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01473665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05746841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00277185440063</t>
   </si>
   <si>
     <t xml:space="preserve">6.7805700302124</t>
@@ -4466,37 +4466,37 @@
     <t xml:space="preserve">6.85406827926636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72245597839355</t>
+    <t xml:space="preserve">6.72245645523071</t>
   </si>
   <si>
     <t xml:space="preserve">6.92414712905884</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92585563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92072820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77031517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65921401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76005887985229</t>
+    <t xml:space="preserve">6.92585611343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92072772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77031469345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65921354293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76005840301514</t>
   </si>
   <si>
     <t xml:space="preserve">6.71049118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71220064163208</t>
+    <t xml:space="preserve">6.71220016479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.79937171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78569841384888</t>
+    <t xml:space="preserve">6.78569746017456</t>
   </si>
   <si>
     <t xml:space="preserve">6.9549126625061</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">6.93782091140747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74638605117798</t>
+    <t xml:space="preserve">6.74638557434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.86774158477783</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">6.73100185394287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84894037246704</t>
+    <t xml:space="preserve">6.84893989562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.0301194190979</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">6.99422550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99593496322632</t>
+    <t xml:space="preserve">6.99593448638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.0232834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06259536743164</t>
+    <t xml:space="preserve">7.06259489059448</t>
   </si>
   <si>
     <t xml:space="preserve">7.09678030014038</t>
@@ -4571,19 +4571,19 @@
     <t xml:space="preserve">7.04208469390869</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98226118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87116050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94636726379395</t>
+    <t xml:space="preserve">6.98226070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87116003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94636678695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.97029638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07797861099243</t>
+    <t xml:space="preserve">7.07797813415527</t>
   </si>
   <si>
     <t xml:space="preserve">7.09165334701538</t>
@@ -4595,28 +4595,28 @@
     <t xml:space="preserve">6.90534496307373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72587442398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88825273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123888015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06088590621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13096523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12925624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14976692199707</t>
+    <t xml:space="preserve">6.72587394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84039354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8882532119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123935699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06088638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13096475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12925577163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14976644515991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30530834197998</t>
@@ -4625,25 +4625,25 @@
     <t xml:space="preserve">7.34291172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3497486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38393306732178</t>
+    <t xml:space="preserve">7.34974813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38393354415894</t>
   </si>
   <si>
     <t xml:space="preserve">7.38564252853394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41982793807983</t>
+    <t xml:space="preserve">7.41982746124268</t>
   </si>
   <si>
     <t xml:space="preserve">7.44033908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46768617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57536888122559</t>
+    <t xml:space="preserve">7.46768569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57536840438843</t>
   </si>
   <si>
     <t xml:space="preserve">7.55485773086548</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">7.27112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21813726425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20446300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788145065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19249773025513</t>
+    <t xml:space="preserve">7.21813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20446348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19249820709229</t>
   </si>
   <si>
     <t xml:space="preserve">6.76347780227661</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">7.03182888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13609313964844</t>
+    <t xml:space="preserve">7.13609266281128</t>
   </si>
   <si>
     <t xml:space="preserve">6.97200536727905</t>
@@ -4682,46 +4682,46 @@
     <t xml:space="preserve">6.91047286987305</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92756462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97371435165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95662212371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94978523254395</t>
+    <t xml:space="preserve">6.92756509780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97371482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95662307739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9497857093811</t>
   </si>
   <si>
     <t xml:space="preserve">7.02157306671143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15318584442139</t>
+    <t xml:space="preserve">7.15318536758423</t>
   </si>
   <si>
     <t xml:space="preserve">7.17027854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21300792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19078826904297</t>
+    <t xml:space="preserve">7.21300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19078874588013</t>
   </si>
   <si>
     <t xml:space="preserve">7.03695678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17882394790649</t>
+    <t xml:space="preserve">7.17882347106934</t>
   </si>
   <si>
     <t xml:space="preserve">7.18737030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1685676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22497367858887</t>
+    <t xml:space="preserve">7.16856813430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22497415542603</t>
   </si>
   <si>
     <t xml:space="preserve">7.08139705657959</t>
@@ -4730,25 +4730,25 @@
     <t xml:space="preserve">7.11558198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19933462142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04037523269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0284104347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97884321212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87799739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83697509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80279016494751</t>
+    <t xml:space="preserve">7.1993350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04037570953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02840995788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97884273529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87799692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83697557449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80279064178467</t>
   </si>
   <si>
     <t xml:space="preserve">6.8916711807251</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">6.88312482833862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76518726348877</t>
+    <t xml:space="preserve">6.76518678665161</t>
   </si>
   <si>
     <t xml:space="preserve">6.78740739822388</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">6.77715110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72416543960571</t>
+    <t xml:space="preserve">6.72416496276855</t>
   </si>
   <si>
     <t xml:space="preserve">6.66946935653687</t>
@@ -4784,22 +4784,22 @@
     <t xml:space="preserve">6.60109949111938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55153131484985</t>
+    <t xml:space="preserve">6.55153179168701</t>
   </si>
   <si>
     <t xml:space="preserve">6.48999834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49854469299316</t>
+    <t xml:space="preserve">6.49854516983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.49341726303101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53443956375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58571577072144</t>
+    <t xml:space="preserve">6.53443908691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58571672439575</t>
   </si>
   <si>
     <t xml:space="preserve">6.61819171905518</t>
@@ -4808,64 +4808,64 @@
     <t xml:space="preserve">6.74980354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88483333587646</t>
+    <t xml:space="preserve">6.88483381271362</t>
   </si>
   <si>
     <t xml:space="preserve">6.80449962615967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82842922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84552145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00789976119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.990807056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1668586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29847097396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28137969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17198705673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19420766830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29675388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26316118240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23487234115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1959753036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24194526672363</t>
+    <t xml:space="preserve">6.82842874526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84552192687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00789928436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99080753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16685914993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29847145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28137874603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17198753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1942081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29675436019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26316070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23487281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19597578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24194478988647</t>
   </si>
   <si>
     <t xml:space="preserve">7.15531015396118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17475938796997</t>
+    <t xml:space="preserve">7.17475891113281</t>
   </si>
   <si>
     <t xml:space="preserve">7.19243907928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21896076202393</t>
+    <t xml:space="preserve">7.21896028518677</t>
   </si>
   <si>
     <t xml:space="preserve">7.26669788360596</t>
@@ -4874,22 +4874,22 @@
     <t xml:space="preserve">7.25785732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24901676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30029058456421</t>
+    <t xml:space="preserve">7.24901628494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30029106140137</t>
   </si>
   <si>
     <t xml:space="preserve">7.2773060798645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31973934173584</t>
+    <t xml:space="preserve">7.31973886489868</t>
   </si>
   <si>
     <t xml:space="preserve">7.40637397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47532796859741</t>
+    <t xml:space="preserve">7.47532749176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.44527053833008</t>
@@ -4898,13 +4898,13 @@
     <t xml:space="preserve">7.551353931427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61853981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5407452583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51952886581421</t>
+    <t xml:space="preserve">7.61854028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54074573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51952791213989</t>
   </si>
   <si>
     <t xml:space="preserve">7.54781818389893</t>
@@ -4913,22 +4913,22 @@
     <t xml:space="preserve">7.48239994049072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47886323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53897762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49654340744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54428195953369</t>
+    <t xml:space="preserve">7.47886371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53897714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49654388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">7.58671474456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58141136169434</t>
+    <t xml:space="preserve">7.58141088485718</t>
   </si>
   <si>
     <t xml:space="preserve">7.67511796951294</t>
@@ -4937,64 +4937,64 @@
     <t xml:space="preserve">7.65390110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7971134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80241727828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81832933425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72815942764282</t>
+    <t xml:space="preserve">7.79711246490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80241775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72815895080566</t>
   </si>
   <si>
     <t xml:space="preserve">7.8625316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04640960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11182689666748</t>
+    <t xml:space="preserve">8.04640865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11182594299316</t>
   </si>
   <si>
     <t xml:space="preserve">8.11005878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21967887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28509616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27625560760498</t>
+    <t xml:space="preserve">8.21967792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28509521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2762565612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.37880229949951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43361282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41946887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26741600036621</t>
+    <t xml:space="preserve">8.43361186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41946792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26741504669189</t>
   </si>
   <si>
     <t xml:space="preserve">8.36642646789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39294815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33106517791748</t>
+    <t xml:space="preserve">8.39294719696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33106422424316</t>
   </si>
   <si>
     <t xml:space="preserve">8.33813762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4636697769165</t>
+    <t xml:space="preserve">8.46366882324219</t>
   </si>
   <si>
     <t xml:space="preserve">8.44952487945557</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">8.5732889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67583656311035</t>
+    <t xml:space="preserve">8.67583560943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.75009346008301</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">8.61572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62456130981445</t>
+    <t xml:space="preserve">8.62456226348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.57152080535889</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">8.59273719787598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.628098487854</t>
+    <t xml:space="preserve">8.62809753417969</t>
   </si>
   <si>
     <t xml:space="preserve">8.737717628479</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">8.79783058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78722190856934</t>
+    <t xml:space="preserve">8.78722286224365</t>
   </si>
   <si>
     <t xml:space="preserve">8.7695426940918</t>
@@ -5048,16 +5048,16 @@
     <t xml:space="preserve">8.79959964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7819185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84026527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88888549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86236381530762</t>
+    <t xml:space="preserve">8.78191947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84026432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88888645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86236476898193</t>
   </si>
   <si>
     <t xml:space="preserve">8.76070213317871</t>
@@ -5066,19 +5066,19 @@
     <t xml:space="preserve">8.73064613342285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62986660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77661609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82258415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97286891937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87120532989502</t>
+    <t xml:space="preserve">8.6298656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77661418914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82258319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97286796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87120628356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.07011127471924</t>
@@ -5087,13 +5087,13 @@
     <t xml:space="preserve">9.10547256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11431312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1496753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13199234008789</t>
+    <t xml:space="preserve">9.11431407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14967441558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13199329376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.06127166748047</t>
@@ -5108,10 +5108,10 @@
     <t xml:space="preserve">9.07895183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03475093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9551887512207</t>
+    <t xml:space="preserve">9.03474998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95518779754639</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910488128662</t>
@@ -5120,16 +5120,16 @@
     <t xml:space="preserve">8.85794544219971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91982650756836</t>
+    <t xml:space="preserve">8.91982746124268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74744129180908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83142375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99054908752441</t>
+    <t xml:space="preserve">8.83142471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9905481338501</t>
   </si>
   <si>
     <t xml:space="preserve">9.00899124145508</t>
@@ -5138,28 +5138,28 @@
     <t xml:space="preserve">9.12886428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24873828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14269733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30406475067139</t>
+    <t xml:space="preserve">9.24873924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14269638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3040657043457</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705539703369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41471862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47926616668701</t>
+    <t xml:space="preserve">9.41471767425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4792652130127</t>
   </si>
   <si>
     <t xml:space="preserve">9.62680244445801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66368770599365</t>
+    <t xml:space="preserve">9.66368675231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.70057201385498</t>
@@ -5168,13 +5168,13 @@
     <t xml:space="preserve">9.94954013824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0601940155029</t>
+    <t xml:space="preserve">10.0601930618286</t>
   </si>
   <si>
     <t xml:space="preserve">10.0509719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99564647674561</t>
+    <t xml:space="preserve">9.99564552307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.95876216888428</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">9.7651195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97720336914062</t>
+    <t xml:space="preserve">9.97720432281494</t>
   </si>
   <si>
     <t xml:space="preserve">10.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98642444610596</t>
+    <t xml:space="preserve">9.98642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901416778564</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">9.49770832061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55303382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79278182983398</t>
+    <t xml:space="preserve">9.55303478240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7927827835083</t>
   </si>
   <si>
     <t xml:space="preserve">9.68212985992432</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">9.57147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50692939758301</t>
+    <t xml:space="preserve">9.50693035125732</t>
   </si>
   <si>
     <t xml:space="preserve">9.69135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667644500732</t>
+    <t xml:space="preserve">9.74667739868164</t>
   </si>
   <si>
     <t xml:space="preserve">9.82044506072998</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">9.86655044555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9126558303833</t>
+    <t xml:space="preserve">9.91265678405762</t>
   </si>
   <si>
     <t xml:space="preserve">9.96798324584961</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">10.0233097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90343570709229</t>
+    <t xml:space="preserve">9.90343475341797</t>
   </si>
   <si>
     <t xml:space="preserve">10.1062994003296</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">10.2077302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48848628997803</t>
+    <t xml:space="preserve">9.48848724365234</t>
   </si>
   <si>
     <t xml:space="preserve">9.25796031951904</t>
@@ -5282,10 +5282,10 @@
     <t xml:space="preserve">8.99515914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96749591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31328678131104</t>
+    <t xml:space="preserve">8.96749687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31328773498535</t>
   </si>
   <si>
     <t xml:space="preserve">9.43315982818604</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">9.58991813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82966613769531</t>
+    <t xml:space="preserve">9.82966709136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.84810924530029</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">10.0878562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1892881393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2446155548096</t>
+    <t xml:space="preserve">10.1892890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2446146011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.014087677002</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">10.0970773696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0694141387939</t>
+    <t xml:space="preserve">10.0694150924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.1247415542603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1800680160522</t>
+    <t xml:space="preserve">10.1800670623779</t>
   </si>
   <si>
     <t xml:space="preserve">10.3737096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198160171509</t>
+    <t xml:space="preserve">10.4198150634766</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907199859619</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">10.3552675247192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183832168579</t>
+    <t xml:space="preserve">10.3183841705322</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765743255615</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">10.2999420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3091621398926</t>
+    <t xml:space="preserve">10.3091630935669</t>
   </si>
   <si>
     <t xml:space="preserve">10.2169523239136</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">10.2722787857056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276052474976</t>
+    <t xml:space="preserve">10.3276042938232</t>
   </si>
   <si>
     <t xml:space="preserve">10.4567003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4935836791992</t>
+    <t xml:space="preserve">10.4935846328735</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042375564575</t>
@@ -5396,22 +5396,22 @@
     <t xml:space="preserve">10.4474792480469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5581312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134586334229</t>
+    <t xml:space="preserve">10.5581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134576797485</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4843635559082</t>
+    <t xml:space="preserve">10.4843626022339</t>
   </si>
   <si>
     <t xml:space="preserve">10.6226797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7517738342285</t>
+    <t xml:space="preserve">10.7517747879028</t>
   </si>
   <si>
     <t xml:space="preserve">10.9177541732788</t>
@@ -71029,7 +71029,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494907407</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>959993</v>
@@ -71050,6 +71050,32 @@
         <v>1996</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6510648148</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>871195</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>17.3299999237061</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>17.0599994659424</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>17.0100002288818</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446745872498</t>
+    <t xml:space="preserve">3.78446698188782</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49607563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41445422172546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901231765747</t>
+    <t xml:space="preserve">3.73277378082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49607491493225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4144549369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901255607605</t>
   </si>
   <si>
     <t xml:space="preserve">3.4334990978241</t>
@@ -62,151 +62,151 @@
     <t xml:space="preserve">3.53144335746765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53688549995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658246994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937581062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29202389717102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040368080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41989541053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805814743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077802658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187888145447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276173591614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22672772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13966631889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18863725662231</t>
+    <t xml:space="preserve">3.53688454627991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658270835876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937485694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2920241355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157656669617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040415763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41989612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077898025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276149749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2267279624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13966608047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">3.30562710762024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8920841217041</t>
+    <t xml:space="preserve">3.03083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89208436012268</t>
   </si>
   <si>
     <t xml:space="preserve">3.1559898853302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25393462181091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31379008293152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40357184410095</t>
+    <t xml:space="preserve">3.25393390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31378960609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40357136726379</t>
   </si>
   <si>
     <t xml:space="preserve">3.36548233032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36820316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46614670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43622040748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36004161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49063348770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56681323051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6919641494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71100807189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61850571632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380212783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623316764832</t>
+    <t xml:space="preserve">3.36820340156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46614742279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43621969223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36004137992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49063420295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56681275367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409215927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69196486473083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71100902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61850619316101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380236625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623173713684</t>
   </si>
   <si>
     <t xml:space="preserve">3.7926287651062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76542139053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70284724235535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7518196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72189164161682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69468450546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387439727783</t>
+    <t xml:space="preserve">3.76542210578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70284605026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181913375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72189235687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6946849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387511253357</t>
   </si>
   <si>
     <t xml:space="preserve">3.81439447402954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84432220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7137291431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63482975959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54232668876648</t>
+    <t xml:space="preserve">3.84432196617126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86608743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71372961997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6348295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54232692718506</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637770652771</t>
@@ -224,313 +224,313 @@
     <t xml:space="preserve">3.91778016090393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85248398780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407820701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88579058647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94962859153748</t>
+    <t xml:space="preserve">3.85248374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407773017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88579130172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94962882995605</t>
   </si>
   <si>
     <t xml:space="preserve">3.97460913658142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96628260612488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88023948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92464900016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88856601715088</t>
+    <t xml:space="preserve">3.96628284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88023996353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92464876174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8885669708252</t>
   </si>
   <si>
     <t xml:space="preserve">4.00236463546753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98848628997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04122257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93020057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07730531692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99681282043457</t>
+    <t xml:space="preserve">3.98848700523376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04122304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93019962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07730436325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99681329727173</t>
   </si>
   <si>
     <t xml:space="preserve">3.96905755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06065082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742466926575</t>
+    <t xml:space="preserve">4.06065130233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742419242859</t>
   </si>
   <si>
     <t xml:space="preserve">3.93575119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92187356948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95240473747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91909718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130158424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08008050918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29102373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23551273345947</t>
+    <t xml:space="preserve">3.92187309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95240449905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91909766197205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130229949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08008146286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29102325439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23551321029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.16334772109985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18832778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21608352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.182776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559198379517</t>
+    <t xml:space="preserve">4.1883282661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21608304977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18277597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559246063232</t>
   </si>
   <si>
     <t xml:space="preserve">4.15502023696899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03289604187012</t>
+    <t xml:space="preserve">4.03289556503296</t>
   </si>
   <si>
     <t xml:space="preserve">4.05232524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09673404693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06342744827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69427752494812</t>
+    <t xml:space="preserve">4.09673357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06342697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69427728652954</t>
   </si>
   <si>
     <t xml:space="preserve">3.53051853179932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55272340774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48888492584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60268259048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78586983680725</t>
+    <t xml:space="preserve">3.55272269248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48888540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6026828289032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78587079048157</t>
   </si>
   <si>
     <t xml:space="preserve">3.8247287273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80530047416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13916373252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26961517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23630833625793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40561819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41394448280334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904414176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463510513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1919002532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410441398621</t>
+    <t xml:space="preserve">3.80529952049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685292243958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288262367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13916444778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26961588859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23630905151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40561842918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41394543647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904438018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463558197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19189953804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410465240479</t>
   </si>
   <si>
     <t xml:space="preserve">3.39174056053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47778272628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59713244438171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49721240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941728591919</t>
+    <t xml:space="preserve">3.47778224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59713220596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721264839172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941657066345</t>
   </si>
   <si>
     <t xml:space="preserve">3.5388457775116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55827379226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5416202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386475563049</t>
+    <t xml:space="preserve">3.558274269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54162073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386547088623</t>
   </si>
   <si>
     <t xml:space="preserve">3.63599038124084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58047938346863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64154076576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39451599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34455585479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949605941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54717183113098</t>
+    <t xml:space="preserve">3.58047842979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64154100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39451503753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34455633163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949582099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54717302322388</t>
   </si>
   <si>
     <t xml:space="preserve">3.56937646865845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4694561958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116952896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280289649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231159210205</t>
+    <t xml:space="preserve">3.46945643424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41116976737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4528021812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231135368347</t>
   </si>
   <si>
     <t xml:space="preserve">3.4805588722229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51664042472839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45002770423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47500824928284</t>
+    <t xml:space="preserve">3.51664090156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45002794265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47500777244568</t>
   </si>
   <si>
     <t xml:space="preserve">3.51108980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56660175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58325386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994750022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215189933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264296531677</t>
+    <t xml:space="preserve">3.56660103797913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58325409889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994797706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264368057251</t>
   </si>
   <si>
     <t xml:space="preserve">3.59990811347961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49166107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52219200134277</t>
+    <t xml:space="preserve">3.49166011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52219128608704</t>
   </si>
   <si>
     <t xml:space="preserve">3.50831413269043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31402397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37786269187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30847406387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36120867729187</t>
+    <t xml:space="preserve">3.31402492523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37786293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30847334861755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36120915412903</t>
   </si>
   <si>
     <t xml:space="preserve">3.38896441459656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29737114906311</t>
+    <t xml:space="preserve">3.29737138748169</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745111465454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23075771331787</t>
+    <t xml:space="preserve">3.23075795173645</t>
   </si>
   <si>
     <t xml:space="preserve">3.29182052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2668399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27516722679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337368965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39729070663452</t>
+    <t xml:space="preserve">3.26684021949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27516746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337392807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39729189872742</t>
   </si>
   <si>
     <t xml:space="preserve">3.4639048576355</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">3.4083936214447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46112966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32235193252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38618922233582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43059849739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43614959716797</t>
+    <t xml:space="preserve">3.46112871170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32235097885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38618898391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43059825897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43614983558655</t>
   </si>
   <si>
     <t xml:space="preserve">3.50276279449463</t>
@@ -560,73 +560,73 @@
     <t xml:space="preserve">3.5638256072998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36398506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33900475502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835447311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54439687728882</t>
+    <t xml:space="preserve">3.36398410797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33900499343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835423469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54439663887024</t>
   </si>
   <si>
     <t xml:space="preserve">3.42227149009705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38341283798218</t>
+    <t xml:space="preserve">3.38341379165649</t>
   </si>
   <si>
     <t xml:space="preserve">3.30014681816101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28303265571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37145471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39142155647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37715983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41424012184143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4570255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48554849624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118586540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930424690247</t>
+    <t xml:space="preserve">3.28303289413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37145519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3914213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37715911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41423988342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45702457427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4855477809906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256055831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73370099067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79930400848389</t>
   </si>
   <si>
     <t xml:space="preserve">4.09309482574463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95047855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8934314250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332956314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93906855583191</t>
+    <t xml:space="preserve">3.95047903060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89343214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95333027839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93906879425049</t>
   </si>
   <si>
     <t xml:space="preserve">3.93051218986511</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.85635089874268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92480683326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90484094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93621587753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94192099571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92195463180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89628434181213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477391242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96473932266235</t>
+    <t xml:space="preserve">3.92480707168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90484023094177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93621611595154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94192123413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.921954870224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89628410339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477343559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96473979949951</t>
   </si>
   <si>
     <t xml:space="preserve">4.10735654830933</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">4.12447023391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04175329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07883405685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2442684173584</t>
+    <t xml:space="preserve">4.04175186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426746368408</t>
   </si>
   <si>
     <t xml:space="preserve">4.15014171600342</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">4.30131530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.215744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2043342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26708698272705</t>
+    <t xml:space="preserve">4.21574449539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20433568954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26708650588989</t>
   </si>
   <si>
     <t xml:space="preserve">4.21289253234863</t>
@@ -698,43 +698,43 @@
     <t xml:space="preserve">4.09879875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23571062088013</t>
+    <t xml:space="preserve">4.23571109771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.18151712417603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17010688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17581224441528</t>
+    <t xml:space="preserve">4.1701078414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17581176757812</t>
   </si>
   <si>
     <t xml:space="preserve">4.03319549560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03890085220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07027626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97044491767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99326229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98185396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05886745452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11305999755859</t>
+    <t xml:space="preserve">4.03889942169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08453845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07027578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97044515609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99326324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.981853723526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05886602401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11306095123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.06171894073486</t>
@@ -746,97 +746,97 @@
     <t xml:space="preserve">4.02749109268188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75651979446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672161102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105036735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51977634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53689026832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386940956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68235850334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64242625236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6509838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091534614563</t>
+    <t xml:space="preserve">3.75651955604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672256469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105108261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5197765827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53689002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386988639832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6823582649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64242672920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65098357200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091582298279</t>
   </si>
   <si>
     <t xml:space="preserve">3.7194390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73084902763367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81641864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7878954410553</t>
+    <t xml:space="preserve">3.73084878921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81641936302185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78789496421814</t>
   </si>
   <si>
     <t xml:space="preserve">3.81071400642395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84779453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76792931556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7821900844574</t>
+    <t xml:space="preserve">3.84779357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76792907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78218984603882</t>
   </si>
   <si>
     <t xml:space="preserve">3.80215668678284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83353233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064578056335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90769290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9162495136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9476261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.976149559021</t>
+    <t xml:space="preserve">3.83353281021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064649581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91625022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94762563705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9761483669281</t>
   </si>
   <si>
     <t xml:space="preserve">3.92765974998474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89057922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349893569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87346506118774</t>
+    <t xml:space="preserve">3.89057993888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349869728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212328910828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8734655380249</t>
   </si>
   <si>
     <t xml:space="preserve">4.10278224945068</t>
@@ -848,22 +848,22 @@
     <t xml:space="preserve">4.17076778411865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11460638046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1530327796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12938547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10573863983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23579788208008</t>
+    <t xml:space="preserve">4.1146068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15303230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12938499450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10573816299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16485691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23579883575439</t>
   </si>
   <si>
     <t xml:space="preserve">4.23875284194946</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">4.20919418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34516572952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35107803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36290121078491</t>
+    <t xml:space="preserve">4.34516525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35107755661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36290073394775</t>
   </si>
   <si>
     <t xml:space="preserve">4.35994529724121</t>
@@ -887,19 +887,19 @@
     <t xml:space="preserve">4.39837217330933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28900480270386</t>
+    <t xml:space="preserve">4.28900384902954</t>
   </si>
   <si>
     <t xml:space="preserve">4.30082750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37176847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5195631980896</t>
+    <t xml:space="preserve">4.37176895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340227127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51956367492676</t>
   </si>
   <si>
     <t xml:space="preserve">4.469313621521</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">4.4752254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45453357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36881303787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3333420753479</t>
+    <t xml:space="preserve">4.45453405380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.368812084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33334255218506</t>
   </si>
   <si>
     <t xml:space="preserve">4.41315174102783</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">4.30673885345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41906213760376</t>
+    <t xml:space="preserve">4.41906261444092</t>
   </si>
   <si>
     <t xml:space="preserve">4.43384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38654851913452</t>
+    <t xml:space="preserve">4.38654756546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.30969476699829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28604793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31856250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39245986938477</t>
+    <t xml:space="preserve">4.28604745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31856298446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39245939254761</t>
   </si>
   <si>
     <t xml:space="preserve">4.29491567611694</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">4.33629751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25353240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32447481155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37472438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3274302482605</t>
+    <t xml:space="preserve">4.25353336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3244743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37472486495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32742977142334</t>
   </si>
   <si>
     <t xml:space="preserve">4.3392539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3806357383728</t>
+    <t xml:space="preserve">4.38063621520996</t>
   </si>
   <si>
     <t xml:space="preserve">4.49295997619629</t>
@@ -974,94 +974,94 @@
     <t xml:space="preserve">4.37768077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40723991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38950347900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31560659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27126884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21510648727417</t>
+    <t xml:space="preserve">4.40723943710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38950395584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31560707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27126789093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21510601043701</t>
   </si>
   <si>
     <t xml:space="preserve">4.342209815979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32151794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25648927688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28309059143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057744979858</t>
+    <t xml:space="preserve">4.3215184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25648880004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28309202194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057697296143</t>
   </si>
   <si>
     <t xml:space="preserve">4.23284196853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22101783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16189956665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19737148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24170970916748</t>
+    <t xml:space="preserve">4.22101831436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16190052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19737100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24170923233032</t>
   </si>
   <si>
     <t xml:space="preserve">4.17963552474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22397327423096</t>
+    <t xml:space="preserve">4.22397422790527</t>
   </si>
   <si>
     <t xml:space="preserve">4.26831197738647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29195976257324</t>
+    <t xml:space="preserve">4.2919602394104</t>
   </si>
   <si>
     <t xml:space="preserve">4.35403347015381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43679904937744</t>
+    <t xml:space="preserve">4.43679857254028</t>
   </si>
   <si>
     <t xml:space="preserve">4.42201900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26535701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18850374221802</t>
+    <t xml:space="preserve">4.26535654067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1885027885437</t>
   </si>
   <si>
     <t xml:space="preserve">4.17372369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16781234741211</t>
+    <t xml:space="preserve">4.16781187057495</t>
   </si>
   <si>
     <t xml:space="preserve">4.24762058258057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21806240081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28013563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23866939544678</t>
+    <t xml:space="preserve">4.21806192398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2801365852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23866844177246</t>
   </si>
   <si>
     <t xml:space="preserve">4.13528633117676</t>
@@ -1076,55 +1076,55 @@
     <t xml:space="preserve">4.16569232940674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25083160400391</t>
+    <t xml:space="preserve">4.25083112716675</t>
   </si>
   <si>
     <t xml:space="preserve">4.25995349884033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27211666107178</t>
+    <t xml:space="preserve">4.27211570739746</t>
   </si>
   <si>
     <t xml:space="preserve">4.36637592315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36941766738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509229660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32988834381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38157892227173</t>
+    <t xml:space="preserve">4.3694167137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117292404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32988882064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38157987594604</t>
   </si>
   <si>
     <t xml:space="preserve">4.3359694480896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39678239822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44543361663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50016403198242</t>
+    <t xml:space="preserve">4.39678287506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44543313980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50016498565674</t>
   </si>
   <si>
     <t xml:space="preserve">4.54577445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43935108184814</t>
+    <t xml:space="preserve">4.4393515586853</t>
   </si>
   <si>
     <t xml:space="preserve">4.48800277709961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51232767105103</t>
+    <t xml:space="preserve">4.51232814788818</t>
   </si>
   <si>
     <t xml:space="preserve">4.44847345352173</t>
@@ -1136,76 +1136,76 @@
     <t xml:space="preserve">4.38766050338745</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30860376358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29340076446533</t>
+    <t xml:space="preserve">4.30860328674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29339981079102</t>
   </si>
   <si>
     <t xml:space="preserve">4.37245750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46063709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45759534835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718935012817</t>
+    <t xml:space="preserve">4.46063661575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45759582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718887329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.55489635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57922172546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62179088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70084762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72517395019531</t>
+    <t xml:space="preserve">4.57922124862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62179136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70084810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72517347335815</t>
   </si>
   <si>
     <t xml:space="preserve">4.7403769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73429489135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77078247070312</t>
+    <t xml:space="preserve">4.73429536819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77078342437744</t>
   </si>
   <si>
     <t xml:space="preserve">4.81639242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76470136642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80423021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83463716506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71301078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61570930480957</t>
+    <t xml:space="preserve">4.81943416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76470184326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80422973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83463621139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71301126480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61571073532104</t>
   </si>
   <si>
     <t xml:space="preserve">4.691725730896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62787294387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5366530418396</t>
+    <t xml:space="preserve">4.6278715133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53665208816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.25691223144531</t>
@@ -1214,40 +1214,40 @@
     <t xml:space="preserve">4.2994818687439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4059042930603</t>
+    <t xml:space="preserve">4.40590476989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.39374208450317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43327045440674</t>
+    <t xml:space="preserve">4.43326997756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.42414855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42110824584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43023014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52449035644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50320625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31468439102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27819776535034</t>
+    <t xml:space="preserve">4.42110776901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43022918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52448987960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5032057762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31468534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27819728851318</t>
   </si>
   <si>
     <t xml:space="preserve">4.32076549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38461971282959</t>
+    <t xml:space="preserve">4.38462066650391</t>
   </si>
   <si>
     <t xml:space="preserve">4.41502666473389</t>
@@ -1256,37 +1256,37 @@
     <t xml:space="preserve">4.40894556045532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35725450515747</t>
+    <t xml:space="preserve">4.35725498199463</t>
   </si>
   <si>
     <t xml:space="preserve">4.33292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26907539367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29644060134888</t>
+    <t xml:space="preserve">4.2690749168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29644107818604</t>
   </si>
   <si>
     <t xml:space="preserve">4.30556297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23562812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29035997390747</t>
+    <t xml:space="preserve">4.23562860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29036045074463</t>
   </si>
   <si>
     <t xml:space="preserve">4.2660346031189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26299381256104</t>
+    <t xml:space="preserve">4.26299428939819</t>
   </si>
   <si>
     <t xml:space="preserve">4.22650623321533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21738386154175</t>
+    <t xml:space="preserve">4.21738433837891</t>
   </si>
   <si>
     <t xml:space="preserve">4.28731966018677</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">4.38646936416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32702350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20500373840332</t>
+    <t xml:space="preserve">4.32702398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.205002784729</t>
   </si>
   <si>
     <t xml:space="preserve">4.11427021026611</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">4.14555835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16745901107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24567651748657</t>
+    <t xml:space="preserve">4.16745853424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24567699432373</t>
   </si>
   <si>
     <t xml:space="preserve">4.23003339767456</t>
@@ -1322,112 +1322,112 @@
     <t xml:space="preserve">4.25506353378296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24254846572876</t>
+    <t xml:space="preserve">4.24254751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.16120195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21439027786255</t>
+    <t xml:space="preserve">4.21438980102539</t>
   </si>
   <si>
     <t xml:space="preserve">4.17997407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17058801651001</t>
+    <t xml:space="preserve">4.17058706283569</t>
   </si>
   <si>
     <t xml:space="preserve">4.08924102783203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458636283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83581399917603</t>
+    <t xml:space="preserve">4.02040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458707809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8358142375946</t>
   </si>
   <si>
     <t xml:space="preserve">3.82329964637756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77636861801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80765604972839</t>
+    <t xml:space="preserve">3.77636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80765557289124</t>
   </si>
   <si>
     <t xml:space="preserve">3.81704163551331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79826927185059</t>
+    <t xml:space="preserve">3.79826974868774</t>
   </si>
   <si>
     <t xml:space="preserve">3.73882389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63557577133179</t>
+    <t xml:space="preserve">3.63557624816895</t>
   </si>
   <si>
     <t xml:space="preserve">3.74195289611816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262639045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8264274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66060590744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72630834579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74508118629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6387050151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77011132240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71692228317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379446983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74821019172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69815039634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68250703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72318005561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76072573661804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60116004943848</t>
+    <t xml:space="preserve">3.78262543678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82642793655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66060543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72630953788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74508190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63870477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77011060714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71692276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379399299622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74820971488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6981508731842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6825065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72318053245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373419761658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76072525978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64183402061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60116052627563</t>
   </si>
   <si>
     <t xml:space="preserve">3.57925939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63244724273682</t>
+    <t xml:space="preserve">3.63244795799255</t>
   </si>
   <si>
     <t xml:space="preserve">3.68876433372498</t>
@@ -1436,91 +1436,91 @@
     <t xml:space="preserve">3.67624974250793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70440793037415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56361532211304</t>
+    <t xml:space="preserve">3.70440769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56361556053162</t>
   </si>
   <si>
     <t xml:space="preserve">3.62931871414185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66686296463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61993217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261899471283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84520101547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99537897109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88587379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91090297698975</t>
+    <t xml:space="preserve">3.66686367988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6199324131012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62618970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84520077705383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99537825584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88587355613708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91090440750122</t>
   </si>
   <si>
     <t xml:space="preserve">3.87022995948792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92341804504395</t>
+    <t xml:space="preserve">3.92341876029968</t>
   </si>
   <si>
     <t xml:space="preserve">3.87961649894714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84207201004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78575420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79514074325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77324080467224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7075366973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698279380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452704429626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81078481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80139803886414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75446748733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73256635665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563556671143</t>
+    <t xml:space="preserve">3.84207129478455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78575491905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79514169692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77323985099792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70753693580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698207855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452680587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80139827728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75446772575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7325656414032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563580513</t>
   </si>
   <si>
     <t xml:space="preserve">3.82017064094543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75759649276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81391263008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77949738502502</t>
+    <t xml:space="preserve">3.75759625434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81391310691833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7794976234436</t>
   </si>
   <si>
     <t xml:space="preserve">3.86397314071655</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">3.8733594417572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89213132858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9922502040863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97660779953003</t>
+    <t xml:space="preserve">3.89213109016418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99225044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97660684585571</t>
   </si>
   <si>
     <t xml:space="preserve">3.98912167549133</t>
@@ -1544,91 +1544,91 @@
     <t xml:space="preserve">4.00163650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44472408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47288250923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37276339530945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37589240074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39466428756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39779329299927</t>
+    <t xml:space="preserve">3.4447238445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47288298606873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37276291847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37589192390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39466452598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098161697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39779281616211</t>
   </si>
   <si>
     <t xml:space="preserve">3.31018829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29141664505005</t>
+    <t xml:space="preserve">3.29141712188721</t>
   </si>
   <si>
     <t xml:space="preserve">3.24448561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22258472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16313815116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18503999710083</t>
+    <t xml:space="preserve">3.22258400917053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313886642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18504023551941</t>
   </si>
   <si>
     <t xml:space="preserve">3.13498044013977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21006965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2069411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26325821876526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31644678115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30706000328064</t>
+    <t xml:space="preserve">3.21006941795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20694088935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26325798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31644654273987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30705976486206</t>
   </si>
   <si>
     <t xml:space="preserve">3.31331729888916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28515887260437</t>
+    <t xml:space="preserve">3.28515958786011</t>
   </si>
   <si>
     <t xml:space="preserve">3.25387167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25074362754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2784378528595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13193368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541566848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890469551086</t>
+    <t xml:space="preserve">3.25074338912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27843809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13193416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541590690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890445709229</t>
   </si>
   <si>
     <t xml:space="preserve">3.32727289199829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48354339599609</t>
+    <t xml:space="preserve">3.48354363441467</t>
   </si>
   <si>
     <t xml:space="preserve">3.45098781585693</t>
@@ -1637,40 +1637,40 @@
     <t xml:space="preserve">3.44773173332214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44122052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42494249343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41843104362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146027565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192711830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23351001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28820562362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680676460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4086639881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33378410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31099462509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3533182144165</t>
+    <t xml:space="preserve">3.4412202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494320869446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843175888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29146099090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192664146423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2335102558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28820586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40866422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3337836265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31099510192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331749916077</t>
   </si>
   <si>
     <t xml:space="preserve">3.30773854255676</t>
@@ -1679,37 +1679,37 @@
     <t xml:space="preserve">3.15537476539612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32076191902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31425046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28494930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41517496109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4021532535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36634111404419</t>
+    <t xml:space="preserve">3.32076168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31425070762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2849497795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41517543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40215349197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36634063720703</t>
   </si>
   <si>
     <t xml:space="preserve">3.44447588920593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46401023864746</t>
+    <t xml:space="preserve">3.46401000022888</t>
   </si>
   <si>
     <t xml:space="preserve">3.50633406639099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48679971694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075439453125</t>
+    <t xml:space="preserve">3.48680019378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075463294983</t>
   </si>
   <si>
     <t xml:space="preserve">3.49331068992615</t>
@@ -1718,46 +1718,46 @@
     <t xml:space="preserve">3.46726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45749926567078</t>
+    <t xml:space="preserve">3.45749831199646</t>
   </si>
   <si>
     <t xml:space="preserve">3.50958919525146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47052145004272</t>
+    <t xml:space="preserve">3.47052121162415</t>
   </si>
   <si>
     <t xml:space="preserve">3.58121347427368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71795129776001</t>
+    <t xml:space="preserve">3.71795058250427</t>
   </si>
   <si>
     <t xml:space="preserve">3.77655267715454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83189868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864332199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87096619606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92305731773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87422180175781</t>
+    <t xml:space="preserve">3.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83189845085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864236831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87096667289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92305636405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87422204017639</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073325157166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88724398612976</t>
+    <t xml:space="preserve">3.88724517822266</t>
   </si>
   <si>
     <t xml:space="preserve">3.99142503738403</t>
@@ -1766,40 +1766,40 @@
     <t xml:space="preserve">3.95886898040771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00770330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99793696403503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06304979324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97189116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01747035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06630516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956052780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12165117263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09235000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11513996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12816333770752</t>
+    <t xml:space="preserve">4.00770282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9718906879425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01746988296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0825834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1216516494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09235143661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11514043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12816286087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.09886169433594</t>
@@ -1811,49 +1811,49 @@
     <t xml:space="preserve">4.08583927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11188459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16071939468384</t>
+    <t xml:space="preserve">4.11188411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16071891784668</t>
   </si>
   <si>
     <t xml:space="preserve">4.13141822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26164484024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24862194061279</t>
+    <t xml:space="preserve">4.26164436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24862146377563</t>
   </si>
   <si>
     <t xml:space="preserve">4.24536609649658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24210977554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23559999465942</t>
+    <t xml:space="preserve">4.24211025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23559904098511</t>
   </si>
   <si>
     <t xml:space="preserve">4.2323431968689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3235011100769</t>
+    <t xml:space="preserve">4.32350015640259</t>
   </si>
   <si>
     <t xml:space="preserve">4.38210296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40489292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884759902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233591079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37569141387939</t>
+    <t xml:space="preserve">4.40489196777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37569189071655</t>
   </si>
   <si>
     <t xml:space="preserve">4.2884464263916</t>
@@ -1868,115 +1868,118 @@
     <t xml:space="preserve">4.4126033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39247035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36226987838745</t>
+    <t xml:space="preserve">4.39246988296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36226940155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233638763428</t>
   </si>
   <si>
     <t xml:space="preserve">4.22804546356201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23811292648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25153541564941</t>
+    <t xml:space="preserve">4.238112449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25153493881226</t>
   </si>
   <si>
     <t xml:space="preserve">4.14751195907593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10388851165771</t>
+    <t xml:space="preserve">4.10388898849487</t>
   </si>
   <si>
     <t xml:space="preserve">4.16093397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10724449157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1642894744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12737798690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12402200698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06697702407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07704448699951</t>
+    <t xml:space="preserve">4.10724496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16428995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12402296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06697654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07704401016235</t>
   </si>
   <si>
     <t xml:space="preserve">4.08039999008179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04684495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02671098709106</t>
+    <t xml:space="preserve">4.04684400558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02671051025391</t>
   </si>
   <si>
     <t xml:space="preserve">4.00657749176025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03342151641846</t>
+    <t xml:space="preserve">4.03342199325562</t>
   </si>
   <si>
     <t xml:space="preserve">4.09046649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14415550231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13408899307251</t>
+    <t xml:space="preserve">4.14415645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13408946990967</t>
   </si>
   <si>
     <t xml:space="preserve">4.17435598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15757846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11060047149658</t>
+    <t xml:space="preserve">4.1575779914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11059999465942</t>
   </si>
   <si>
     <t xml:space="preserve">4.13744497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07368803024292</t>
+    <t xml:space="preserve">4.07368850708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.19784545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21797895431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24482488632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34213542938232</t>
+    <t xml:space="preserve">4.2179799079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24482345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34213590621948</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28509092330933</t>
+    <t xml:space="preserve">4.28508996963501</t>
   </si>
   <si>
     <t xml:space="preserve">4.33878040313721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34549188613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34884786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47300434112549</t>
+    <t xml:space="preserve">4.34549140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34884691238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47300338745117</t>
   </si>
   <si>
     <t xml:space="preserve">4.50991535186768</t>
@@ -1985,25 +1988,25 @@
     <t xml:space="preserve">4.46293783187866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41931390762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978185653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48307085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51662683486938</t>
+    <t xml:space="preserve">4.45622491836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41931486129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48307132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51662635803223</t>
   </si>
   <si>
     <t xml:space="preserve">4.5367603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4931378364563</t>
+    <t xml:space="preserve">4.49313735961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.44280385971069</t>
@@ -2012,43 +2015,43 @@
     <t xml:space="preserve">4.426025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42267036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4495153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42938089370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5065598487854</t>
+    <t xml:space="preserve">4.42266941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44951486587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42938137054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50656080245972</t>
   </si>
   <si>
     <t xml:space="preserve">4.46964836120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40924739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39582490921021</t>
+    <t xml:space="preserve">4.40924787521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39582538604736</t>
   </si>
   <si>
     <t xml:space="preserve">4.20120143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20455646514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21126747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14080047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33542490005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273735046387</t>
+    <t xml:space="preserve">4.20455598831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21126794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14079999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33542537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273687362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.38575887680054</t>
@@ -2057,61 +2060,61 @@
     <t xml:space="preserve">4.46629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41595840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50320529937744</t>
+    <t xml:space="preserve">4.41595935821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50320434570312</t>
   </si>
   <si>
     <t xml:space="preserve">4.52333784103394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6172947883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70454025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65756177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67769527435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72467279434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73138475418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69782829284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61393928527832</t>
+    <t xml:space="preserve">4.60722827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61729526519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59716033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70453977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65756130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67769575119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72467374801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73138523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69782876968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61393880844116</t>
   </si>
   <si>
     <t xml:space="preserve">4.64078330993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60387277603149</t>
+    <t xml:space="preserve">4.60387229919434</t>
   </si>
   <si>
     <t xml:space="preserve">4.62736129760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62400579452515</t>
+    <t xml:space="preserve">4.62400531768799</t>
   </si>
   <si>
     <t xml:space="preserve">4.62065076828003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56024885177612</t>
+    <t xml:space="preserve">4.56024980545044</t>
   </si>
   <si>
     <t xml:space="preserve">4.66762828826904</t>
@@ -2126,43 +2129,43 @@
     <t xml:space="preserve">4.68105030059814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82534074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86560773849487</t>
+    <t xml:space="preserve">4.82534122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86560821533203</t>
   </si>
   <si>
     <t xml:space="preserve">4.90252017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.942786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98305320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04345512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07365465164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08707714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09714365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11727809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15083360671997</t>
+    <t xml:space="preserve">4.94278717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98305511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04345417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07365560531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08707761764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09714460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11727714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15083408355713</t>
   </si>
   <si>
     <t xml:space="preserve">5.16090059280396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15754461288452</t>
+    <t xml:space="preserve">5.15754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">5.16425561904907</t>
@@ -2171,115 +2174,115 @@
     <t xml:space="preserve">5.17432260513306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16761112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2347240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6340389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175186157227</t>
+    <t xml:space="preserve">5.16761159896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23472309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54343795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63403940200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175090789795</t>
   </si>
   <si>
     <t xml:space="preserve">5.89241981506348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77161836624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78504133224487</t>
+    <t xml:space="preserve">5.77161884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78504037857056</t>
   </si>
   <si>
     <t xml:space="preserve">5.87102508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02923679351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17025136947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18400812149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26999378204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32846307754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40069007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878183364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28031206130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26311445236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33534240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38349342346191</t>
+    <t xml:space="preserve">6.02923727035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17025184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18400764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26999235153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840238571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32846164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40069055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26311540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33534288406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38349294662476</t>
   </si>
   <si>
     <t xml:space="preserve">6.33190202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21496295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23216104507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25967597961426</t>
+    <t xml:space="preserve">6.21496391296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23216009140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25967454910278</t>
   </si>
   <si>
     <t xml:space="preserve">6.23559951782227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30438804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28375148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27687215805054</t>
+    <t xml:space="preserve">6.30438661575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28375101089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2768726348877</t>
   </si>
   <si>
     <t xml:space="preserve">6.24935722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1668119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13585758209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1461763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09114503860474</t>
+    <t xml:space="preserve">6.16681241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13585710525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14617586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">6.11866092681885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03611516952515</t>
+    <t xml:space="preserve">6.0361156463623</t>
   </si>
   <si>
     <t xml:space="preserve">5.91229820251465</t>
@@ -2291,49 +2294,46 @@
     <t xml:space="preserve">6.0533127784729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19088745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00860071182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00516080856323</t>
+    <t xml:space="preserve">6.19088840484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00859975814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00516033172607</t>
   </si>
   <si>
     <t xml:space="preserve">6.10490274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03267669677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92949533462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95700883865356</t>
+    <t xml:space="preserve">6.03267574310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92949485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95700979232788</t>
   </si>
   <si>
     <t xml:space="preserve">5.90885877609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73001050949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8572678565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78504037857056</t>
+    <t xml:space="preserve">5.73001146316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85726833343506</t>
   </si>
   <si>
     <t xml:space="preserve">5.60619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61651086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66810131072998</t>
+    <t xml:space="preserve">5.61651134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66810178756714</t>
   </si>
   <si>
     <t xml:space="preserve">5.71625328063965</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">5.81255531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80567741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80911540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87790393829346</t>
+    <t xml:space="preserve">5.80567646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80911636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8779034614563</t>
   </si>
   <si>
     <t xml:space="preserve">5.98108530044556</t>
@@ -2363,67 +2363,67 @@
     <t xml:space="preserve">5.8675856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70593452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40326929092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35511779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.372314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505805969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06277132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00430107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98366403579712</t>
+    <t xml:space="preserve">5.70593547821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40326881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3551173210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37231492996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505710601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0627703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00430059432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98366451263428</t>
   </si>
   <si>
     <t xml:space="preserve">4.9492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69819641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58813571929932</t>
+    <t xml:space="preserve">4.69819593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58813524246216</t>
   </si>
   <si>
     <t xml:space="preserve">4.26483345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75580477714539</t>
+    <t xml:space="preserve">3.75580501556396</t>
   </si>
   <si>
     <t xml:space="preserve">3.71453285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3650918006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36784338951111</t>
+    <t xml:space="preserve">3.36509156227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36784315109253</t>
   </si>
   <si>
     <t xml:space="preserve">3.08306217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84092974662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80516004562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91109299659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90283870697021</t>
+    <t xml:space="preserve">2.84092998504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8051598072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91109323501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90283823013306</t>
   </si>
   <si>
     <t xml:space="preserve">3.25365567207336</t>
@@ -2432,16 +2432,16 @@
     <t xml:space="preserve">3.35133409500122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53568482398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41599416732788</t>
+    <t xml:space="preserve">3.53568458557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41599440574646</t>
   </si>
   <si>
     <t xml:space="preserve">3.24815249443054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1986255645752</t>
+    <t xml:space="preserve">3.19862508773804</t>
   </si>
   <si>
     <t xml:space="preserve">3.18899512290955</t>
@@ -2453,25 +2453,25 @@
     <t xml:space="preserve">3.14359569549561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25778245925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43938231468201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59415435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76268410682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44970011711121</t>
+    <t xml:space="preserve">3.25778293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43938207626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.594153881073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7626838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44969987869263</t>
   </si>
   <si>
     <t xml:space="preserve">3.49097299575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59759402275085</t>
+    <t xml:space="preserve">3.59759306907654</t>
   </si>
   <si>
     <t xml:space="preserve">3.52880573272705</t>
@@ -2480,67 +2480,67 @@
     <t xml:space="preserve">3.36096405982971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4840943813324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56319975852966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54600310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68013834953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8555474281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01031923294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83147144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65950274467468</t>
+    <t xml:space="preserve">3.48409366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320023536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5460033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68013858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85554718971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01031970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83147120475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6595025062561</t>
   </si>
   <si>
     <t xml:space="preserve">3.60447239875793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64574480056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68701767921448</t>
+    <t xml:space="preserve">3.64574503898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68701791763306</t>
   </si>
   <si>
     <t xml:space="preserve">3.69045662879944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84866881370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745638847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421481132507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80739641189575</t>
+    <t xml:space="preserve">3.84866857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745591163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019951820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421433448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80739545822144</t>
   </si>
   <si>
     <t xml:space="preserve">3.81427526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92089629173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95528960227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03439569473267</t>
+    <t xml:space="preserve">3.92089462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95528936386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03439521789551</t>
   </si>
   <si>
     <t xml:space="preserve">4.07222843170166</t>
@@ -2552,52 +2552,52 @@
     <t xml:space="preserve">4.12037944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08598566055298</t>
+    <t xml:space="preserve">4.08598613739014</t>
   </si>
   <si>
     <t xml:space="preserve">4.23731851577759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28547048568726</t>
+    <t xml:space="preserve">4.2854700088501</t>
   </si>
   <si>
     <t xml:space="preserve">4.44712114334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65348386764526</t>
+    <t xml:space="preserve">4.65348339080811</t>
   </si>
   <si>
     <t xml:space="preserve">4.76010465621948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57781791687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33018207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34737873077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4918327331543</t>
+    <t xml:space="preserve">4.5778169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33018255233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34737968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49183320999146</t>
   </si>
   <si>
     <t xml:space="preserve">4.44368171691895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42304468154907</t>
+    <t xml:space="preserve">4.42304515838623</t>
   </si>
   <si>
     <t xml:space="preserve">4.46775722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4539999961853</t>
+    <t xml:space="preserve">4.45400047302246</t>
   </si>
   <si>
     <t xml:space="preserve">4.49527215957642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30266666412354</t>
+    <t xml:space="preserve">4.30266714096069</t>
   </si>
   <si>
     <t xml:space="preserve">4.29234886169434</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">4.39553022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32330322265625</t>
+    <t xml:space="preserve">4.32330274581909</t>
   </si>
   <si>
     <t xml:space="preserve">4.52622652053833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41616630554199</t>
+    <t xml:space="preserve">4.41616678237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.52278757095337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50215148925781</t>
+    <t xml:space="preserve">4.50215101242065</t>
   </si>
   <si>
     <t xml:space="preserve">4.31298494338989</t>
@@ -2639,73 +2639,73 @@
     <t xml:space="preserve">4.53310537338257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53654479980469</t>
+    <t xml:space="preserve">4.53654432296753</t>
   </si>
   <si>
     <t xml:space="preserve">4.5571813583374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66380167007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61221075057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57093858718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52966547012329</t>
+    <t xml:space="preserve">4.66380262374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61221122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57093954086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52966642379761</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40928745269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39209079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42648410797119</t>
+    <t xml:space="preserve">4.40928792953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39209127426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42648458480835</t>
   </si>
   <si>
     <t xml:space="preserve">4.26139450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42992353439331</t>
+    <t xml:space="preserve">4.42992448806763</t>
   </si>
   <si>
     <t xml:space="preserve">4.43680286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56062126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63628721237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68443775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60877227783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48839378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5640606880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45056009292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59501457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51590824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54686260223389</t>
+    <t xml:space="preserve">4.56062030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63628673553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68443822860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60877180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48839330673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56405973434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45055961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59501504898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51590871810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5468635559082</t>
   </si>
   <si>
     <t xml:space="preserve">4.40240859985352</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">4.2751522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081911087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35425806045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55030250549316</t>
+    <t xml:space="preserve">4.35081720352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35425758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55030202865601</t>
   </si>
   <si>
     <t xml:space="preserve">4.33362150192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23043966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32674264907837</t>
+    <t xml:space="preserve">4.23044013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32674217224121</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636415481567</t>
@@ -2738,40 +2738,40 @@
     <t xml:space="preserve">4.27859115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50558996200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43336296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29922771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31986331939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30610656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16165208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03783416748047</t>
+    <t xml:space="preserve">4.50559091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43336391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29922723770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31986427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30610609054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16165256500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03783464431763</t>
   </si>
   <si>
     <t xml:space="preserve">3.98968315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03095579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25107669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73258972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81169605255127</t>
+    <t xml:space="preserve">4.03095531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25107622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73259019851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81169462203979</t>
   </si>
   <si>
     <t xml:space="preserve">4.93207406997681</t>
@@ -2786,46 +2786,46 @@
     <t xml:space="preserve">5.20034551620483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19346618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12467956542969</t>
+    <t xml:space="preserve">5.1934666633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12468004226685</t>
   </si>
   <si>
     <t xml:space="preserve">5.22442102432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24161911010742</t>
+    <t xml:space="preserve">5.24161815643311</t>
   </si>
   <si>
     <t xml:space="preserve">5.3791937828064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34136056900024</t>
+    <t xml:space="preserve">5.26569414138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34136009216309</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2966480255127</t>
+    <t xml:space="preserve">5.29664850234985</t>
   </si>
   <si>
     <t xml:space="preserve">5.15563344955444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11092185974121</t>
+    <t xml:space="preserve">5.11092233657837</t>
   </si>
   <si>
     <t xml:space="preserve">5.10404300689697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04557371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00774002075195</t>
+    <t xml:space="preserve">5.04557323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00774049758911</t>
   </si>
   <si>
     <t xml:space="preserve">5.00086164474487</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">4.91831684112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88736200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89423990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89768075942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88392210006714</t>
+    <t xml:space="preserve">4.88736248016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89424085617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89767980575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8839225769043</t>
   </si>
   <si>
     <t xml:space="preserve">4.8667254447937</t>
@@ -2861,79 +2861,79 @@
     <t xml:space="preserve">4.89080142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91487741470337</t>
+    <t xml:space="preserve">4.91487693786621</t>
   </si>
   <si>
     <t xml:space="preserve">4.85984706878662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87016439437866</t>
+    <t xml:space="preserve">4.87016487121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.05933046340942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03869485855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03181600570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71539354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59845447540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53998374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61565160751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67068099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02837657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12811899185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31728410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25537586212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27257299423218</t>
+    <t xml:space="preserve">5.03869390487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03181648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71539258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59845399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53998422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61565113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6706805229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02837705612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12811851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31728458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25537633895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">5.2588152885437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15219449996948</t>
+    <t xml:space="preserve">5.15219354629517</t>
   </si>
   <si>
     <t xml:space="preserve">5.07652854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09028577804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14875555038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493762969971</t>
+    <t xml:space="preserve">5.0902853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14875507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493715286255</t>
   </si>
   <si>
     <t xml:space="preserve">5.05245208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96990728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1349983215332</t>
+    <t xml:space="preserve">4.9699068069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13499736785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.16251277923584</t>
@@ -2942,43 +2942,43 @@
     <t xml:space="preserve">5.14187669754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23817873001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29320859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32760238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34480094909668</t>
+    <t xml:space="preserve">5.23817920684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29320907592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32760286331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34479951858521</t>
   </si>
   <si>
     <t xml:space="preserve">5.33104181289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33792066574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45142078399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58899641036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50645160675049</t>
+    <t xml:space="preserve">5.33792114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45141983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58899593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50645112991333</t>
   </si>
   <si>
     <t xml:space="preserve">5.52708673477173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44454097747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48237466812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48925447463989</t>
+    <t xml:space="preserve">5.4445424079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4823751449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48925399780273</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492042541504</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">5.53740453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51952028274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5511622428894</t>
+    <t xml:space="preserve">5.51952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55116271972656</t>
   </si>
   <si>
     <t xml:space="preserve">5.47824811935425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40258169174194</t>
+    <t xml:space="preserve">5.40258073806763</t>
   </si>
   <si>
     <t xml:space="preserve">5.45898723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41221189498901</t>
+    <t xml:space="preserve">5.41221141815186</t>
   </si>
   <si>
     <t xml:space="preserve">5.41496324539185</t>
@@ -3011,49 +3011,49 @@
     <t xml:space="preserve">5.36543655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3833212852478</t>
+    <t xml:space="preserve">5.38332080841064</t>
   </si>
   <si>
     <t xml:space="preserve">5.43972635269165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39019966125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32554006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37644147872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39983034133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37506675720215</t>
+    <t xml:space="preserve">5.39020013809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32553911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37644290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39982938766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37506628036499</t>
   </si>
   <si>
     <t xml:space="preserve">5.34617567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46036243438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37368965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43697452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51401710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57730197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55529022216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046642303467</t>
+    <t xml:space="preserve">5.46036291122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37369060516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43697500228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5140175819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57730102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55528974533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046689987183</t>
   </si>
   <si>
     <t xml:space="preserve">5.4232177734375</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">5.44247770309448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39845418930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47484111785889</t>
+    <t xml:space="preserve">5.3984546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47484064102173</t>
   </si>
   <si>
     <t xml:space="preserve">5.43066644668579</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">5.42928647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44308996200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59493923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58113574981689</t>
+    <t xml:space="preserve">5.44309091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59493970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58113527297974</t>
   </si>
   <si>
     <t xml:space="preserve">5.5673303604126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57837438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55766725540161</t>
+    <t xml:space="preserve">5.57837343215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55766773223877</t>
   </si>
   <si>
     <t xml:space="preserve">5.60046148300171</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">5.70813655853271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74264717102051</t>
+    <t xml:space="preserve">5.74264669418335</t>
   </si>
   <si>
     <t xml:space="preserve">5.6377329826355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67224454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69571208953857</t>
+    <t xml:space="preserve">5.67224407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69571161270142</t>
   </si>
   <si>
     <t xml:space="preserve">5.66948318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76473474502563</t>
+    <t xml:space="preserve">5.76473522186279</t>
   </si>
   <si>
     <t xml:space="preserve">5.7771577835083</t>
@@ -3122,94 +3122,94 @@
     <t xml:space="preserve">5.6750054359436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65291786193848</t>
+    <t xml:space="preserve">5.65291738510132</t>
   </si>
   <si>
     <t xml:space="preserve">5.61288547515869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67914628982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83927774429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66120100021362</t>
+    <t xml:space="preserve">5.67914724349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83927822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66120004653931</t>
   </si>
   <si>
     <t xml:space="preserve">5.79234313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66258144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6653413772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68466901779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328762054443</t>
+    <t xml:space="preserve">5.66258096694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66534185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68466854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328809738159</t>
   </si>
   <si>
     <t xml:space="preserve">5.68604850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65015649795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55352640151978</t>
+    <t xml:space="preserve">5.65015745162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55352592468262</t>
   </si>
   <si>
     <t xml:space="preserve">5.63635301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72746229171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66810321807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68742942810059</t>
+    <t xml:space="preserve">5.72746276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66810274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68742895126343</t>
   </si>
   <si>
     <t xml:space="preserve">5.60460233688354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59355974197388</t>
+    <t xml:space="preserve">5.59355926513672</t>
   </si>
   <si>
     <t xml:space="preserve">5.36164426803589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40443897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57975387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62392902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362546920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81443023681641</t>
+    <t xml:space="preserve">5.40443801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57975435256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62392807006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81442975997925</t>
   </si>
   <si>
     <t xml:space="preserve">5.81995153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79924583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79510450363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73160362243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74540758132935</t>
+    <t xml:space="preserve">5.79924535751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79510259628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73160314559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74540853500366</t>
   </si>
   <si>
     <t xml:space="preserve">5.71503829956055</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">5.8075270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88069200515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95523548126221</t>
+    <t xml:space="preserve">5.88069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95523595809937</t>
   </si>
   <si>
     <t xml:space="preserve">5.96351861953735</t>
@@ -3233,55 +3233,55 @@
     <t xml:space="preserve">6.04910564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0311598777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981229782104</t>
+    <t xml:space="preserve">6.03115940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06981182098389</t>
   </si>
   <si>
     <t xml:space="preserve">6.0325403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07809448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9469518661499</t>
+    <t xml:space="preserve">6.07809495925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94695281982422</t>
   </si>
   <si>
     <t xml:space="preserve">5.92348480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98284482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97318124771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99802827835083</t>
+    <t xml:space="preserve">5.98284435272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97318172454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99802875518799</t>
   </si>
   <si>
     <t xml:space="preserve">5.98560523986816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03668212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05048561096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06705188751221</t>
+    <t xml:space="preserve">6.03668117523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05048513412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06705045700073</t>
   </si>
   <si>
     <t xml:space="preserve">6.06567096710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08775663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09051895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06014919281006</t>
+    <t xml:space="preserve">6.08775806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09051990509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0601487159729</t>
   </si>
   <si>
     <t xml:space="preserve">6.04220247268677</t>
@@ -3290,16 +3290,16 @@
     <t xml:space="preserve">6.03944253921509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01045322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15678071975708</t>
+    <t xml:space="preserve">6.01045370101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15677976608276</t>
   </si>
   <si>
     <t xml:space="preserve">6.19681310653687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15125799179077</t>
+    <t xml:space="preserve">6.15125846862793</t>
   </si>
   <si>
     <t xml:space="preserve">6.20233488082886</t>
@@ -3311,58 +3311,58 @@
     <t xml:space="preserve">5.9593768119812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14849710464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34590101242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30034589767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32519340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32243394851685</t>
+    <t xml:space="preserve">6.14849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34590196609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30034637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32519435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32243347167969</t>
   </si>
   <si>
     <t xml:space="preserve">6.39835834503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4535756111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5571084022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57229328155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542440414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690439224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71585941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420970916748</t>
+    <t xml:space="preserve">6.45357656478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55711030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57229375839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343637466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60542392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690343856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616344451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585893630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420827865601</t>
   </si>
   <si>
     <t xml:space="preserve">6.72000122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77245950698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80696964263916</t>
+    <t xml:space="preserve">6.77245903015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80697011947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.827392578125</t>
@@ -3374,46 +3374,46 @@
     <t xml:space="preserve">6.70931911468506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62562131881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61366319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56284666061401</t>
+    <t xml:space="preserve">6.62561988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61366367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56284618377686</t>
   </si>
   <si>
     <t xml:space="preserve">6.66149139404297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60918045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56583642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50605297088623</t>
+    <t xml:space="preserve">6.60917997360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56583690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50605154037476</t>
   </si>
   <si>
     <t xml:space="preserve">6.58227634429932</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49708414077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55387926101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68241596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65850210189819</t>
+    <t xml:space="preserve">6.49708366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55387878417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6824164390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65850162506104</t>
   </si>
   <si>
     <t xml:space="preserve">6.66448068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73771667480469</t>
+    <t xml:space="preserve">6.73771619796753</t>
   </si>
   <si>
     <t xml:space="preserve">6.77657604217529</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">6.78404951095581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84532928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83187675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74369478225708</t>
+    <t xml:space="preserve">6.84532880783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83187770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74369430541992</t>
   </si>
   <si>
     <t xml:space="preserve">6.66298627853394</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">6.56434154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70861196517944</t>
+    <t xml:space="preserve">6.7086124420166</t>
   </si>
   <si>
     <t xml:space="preserve">6.58429384231567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7761435508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68866014480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38783931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43848752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32951736450195</t>
+    <t xml:space="preserve">6.77614402770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38783979415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43848848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32951641082764</t>
   </si>
   <si>
     <t xml:space="preserve">6.49374103546143</t>
@@ -3464,67 +3464,67 @@
     <t xml:space="preserve">6.44309186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47685766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5489935874939</t>
+    <t xml:space="preserve">6.47685670852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54899406433105</t>
   </si>
   <si>
     <t xml:space="preserve">6.68405485153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62112855911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56127166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51522731781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50601816177368</t>
+    <t xml:space="preserve">6.62112951278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56127262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51522779464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50601863861084</t>
   </si>
   <si>
     <t xml:space="preserve">6.51062345504761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52443647384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44462633132935</t>
+    <t xml:space="preserve">6.52443599700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4446268081665</t>
   </si>
   <si>
     <t xml:space="preserve">6.2451024055481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42927980422974</t>
+    <t xml:space="preserve">6.42927932739258</t>
   </si>
   <si>
     <t xml:space="preserve">6.48299646377563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58889865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65335988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64568519592285</t>
+    <t xml:space="preserve">6.5888991355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65335941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64568614959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.66103458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74391317367554</t>
+    <t xml:space="preserve">6.74391269683838</t>
   </si>
   <si>
     <t xml:space="preserve">6.7945613861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85288381576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66410350799561</t>
+    <t xml:space="preserve">6.85288333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66410303115845</t>
   </si>
   <si>
     <t xml:space="preserve">6.78688812255859</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">6.97566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.106125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13221740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99255132675171</t>
+    <t xml:space="preserve">7.10612630844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13221645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99255037307739</t>
   </si>
   <si>
     <t xml:space="preserve">6.96185445785522</t>
@@ -3551,22 +3551,22 @@
     <t xml:space="preserve">6.79763031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79149198532104</t>
+    <t xml:space="preserve">6.7914924621582</t>
   </si>
   <si>
     <t xml:space="preserve">6.70554256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40779161453247</t>
+    <t xml:space="preserve">6.40779256820679</t>
   </si>
   <si>
     <t xml:space="preserve">6.41700077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55052852630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51829719543457</t>
+    <t xml:space="preserve">6.55052804946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51829767227173</t>
   </si>
   <si>
     <t xml:space="preserve">6.46611404418945</t>
@@ -3578,49 +3578,49 @@
     <t xml:space="preserve">6.67177724838257</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76386499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69786882400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45844030380249</t>
+    <t xml:space="preserve">6.76386547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69786834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45843982696533</t>
   </si>
   <si>
     <t xml:space="preserve">6.54438877105713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69940423965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79916524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56894588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34486436843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52290153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47225332260132</t>
+    <t xml:space="preserve">6.69940376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79916477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56894683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52290058135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47225284576416</t>
   </si>
   <si>
     <t xml:space="preserve">6.38476991653442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36328268051147</t>
+    <t xml:space="preserve">6.36328220367432</t>
   </si>
   <si>
     <t xml:space="preserve">6.29575157165527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23435926437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28500699996948</t>
+    <t xml:space="preserve">6.23435878753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28500747680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.75089693069458</t>
@@ -3629,16 +3629,16 @@
     <t xml:space="preserve">5.88749408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64959955215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43933248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46388912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33650064468384</t>
+    <t xml:space="preserve">5.64960050582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43933296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46388959884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.336501121521</t>
   </si>
   <si>
     <t xml:space="preserve">4.98810148239136</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">4.92977905273438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07098054885864</t>
+    <t xml:space="preserve">5.07098007202148</t>
   </si>
   <si>
     <t xml:space="preserve">5.62657833099365</t>
@@ -3659,28 +3659,28 @@
     <t xml:space="preserve">5.41938018798828</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50993394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62811374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92125988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88135576248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86447238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82149791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97190809249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90898084640503</t>
+    <t xml:space="preserve">5.50993347167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62811279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92125940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88135480880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86447286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82149744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97190856933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90898180007935</t>
   </si>
   <si>
     <t xml:space="preserve">5.87214612960815</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">5.96116495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12538814544678</t>
+    <t xml:space="preserve">6.12538862228394</t>
   </si>
   <si>
     <t xml:space="preserve">6.06860065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9519567489624</t>
+    <t xml:space="preserve">5.95195531845093</t>
   </si>
   <si>
     <t xml:space="preserve">6.05325317382812</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">5.98879146575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93353796005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72787523269653</t>
+    <t xml:space="preserve">5.93353843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72787570953369</t>
   </si>
   <si>
     <t xml:space="preserve">5.7155966758728</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">5.85679864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82303333282471</t>
+    <t xml:space="preserve">5.82303237915039</t>
   </si>
   <si>
     <t xml:space="preserve">5.77084922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81842851638794</t>
+    <t xml:space="preserve">5.81842803955078</t>
   </si>
   <si>
     <t xml:space="preserve">5.86293745040894</t>
@@ -3737,37 +3737,37 @@
     <t xml:space="preserve">5.89671611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87098073959351</t>
+    <t xml:space="preserve">5.87098026275635</t>
   </si>
   <si>
     <t xml:space="preserve">5.78090476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65865993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56536769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60397148132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55089139938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61040449142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56375932693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59271144866943</t>
+    <t xml:space="preserve">5.6586594581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56536722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60397100448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55089092254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61040496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56375980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59271192550659</t>
   </si>
   <si>
     <t xml:space="preserve">5.55732488632202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62166404724121</t>
+    <t xml:space="preserve">5.62166500091553</t>
   </si>
   <si>
     <t xml:space="preserve">5.58788633346558</t>
@@ -3776,31 +3776,31 @@
     <t xml:space="preserve">5.50263643264771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56054210662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81146621704102</t>
+    <t xml:space="preserve">5.56054258346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81146574020386</t>
   </si>
   <si>
     <t xml:space="preserve">5.66348505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70852327346802</t>
+    <t xml:space="preserve">5.7085223197937</t>
   </si>
   <si>
     <t xml:space="preserve">5.74069261550903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76321172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6892204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817302703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510774612427</t>
+    <t xml:space="preserve">5.76321125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68922090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817445755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510726928711</t>
   </si>
   <si>
     <t xml:space="preserve">5.75516939163208</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">5.91280078887939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84685325622559</t>
+    <t xml:space="preserve">5.84685277938843</t>
   </si>
   <si>
     <t xml:space="preserve">5.75034379959106</t>
@@ -3833,25 +3833,25 @@
     <t xml:space="preserve">5.72299957275391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55249977111816</t>
+    <t xml:space="preserve">5.55249929428101</t>
   </si>
   <si>
     <t xml:space="preserve">5.17450475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13107585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20828342437744</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13107633590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20828294754028</t>
   </si>
   <si>
     <t xml:space="preserve">5.01043939590454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05226039886475</t>
+    <t xml:space="preserve">5.05225944519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.11820793151855</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">5.11981678009033</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15198659896851</t>
+    <t xml:space="preserve">5.15198612213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.30157566070557</t>
@@ -3869,91 +3869,91 @@
     <t xml:space="preserve">5.16807126998901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17932987213135</t>
+    <t xml:space="preserve">5.17933034896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.14876890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04904317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07156133651733</t>
+    <t xml:space="preserve">5.04904270172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07156181335449</t>
   </si>
   <si>
     <t xml:space="preserve">5.05386829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80294418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88819456100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03456735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17611360549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295803070068</t>
+    <t xml:space="preserve">4.80294466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88819360733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0345664024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17611312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03295850753784</t>
   </si>
   <si>
     <t xml:space="preserve">5.10855722427368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03778314590454</t>
+    <t xml:space="preserve">5.0377836227417</t>
   </si>
   <si>
     <t xml:space="preserve">4.85924100875854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9123215675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98631143569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12142467498779</t>
+    <t xml:space="preserve">4.91232109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98631191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12142515182495</t>
   </si>
   <si>
     <t xml:space="preserve">4.9348406791687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01848173141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0152645111084</t>
+    <t xml:space="preserve">5.01848077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01526498794556</t>
   </si>
   <si>
     <t xml:space="preserve">4.96379327774048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99274635314941</t>
+    <t xml:space="preserve">4.9927453994751</t>
   </si>
   <si>
     <t xml:space="preserve">5.18737268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21150064468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15842056274414</t>
+    <t xml:space="preserve">5.21149969100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15842008590698</t>
   </si>
   <si>
     <t xml:space="preserve">5.45599031448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59431982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50746250152588</t>
+    <t xml:space="preserve">5.59432029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50746202468872</t>
   </si>
   <si>
     <t xml:space="preserve">5.48976898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46242380142212</t>
+    <t xml:space="preserve">5.46242427825928</t>
   </si>
   <si>
     <t xml:space="preserve">5.50424480438232</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">5.5364146232605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56858396530151</t>
+    <t xml:space="preserve">5.56858444213867</t>
   </si>
   <si>
     <t xml:space="preserve">5.51067924499512</t>
@@ -3971,34 +3971,34 @@
     <t xml:space="preserve">5.40291023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44312286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33374500274658</t>
+    <t xml:space="preserve">5.44312191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33374547958374</t>
   </si>
   <si>
     <t xml:space="preserve">5.19219827651978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28388261795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22919368743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16324520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0410008430481</t>
+    <t xml:space="preserve">5.28388166427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22919321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.163245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04100036621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.14394378662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12946653366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00883054733276</t>
+    <t xml:space="preserve">5.12946701049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00883102416992</t>
   </si>
   <si>
     <t xml:space="preserve">5.24688673019409</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">5.18254709243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19863224029541</t>
+    <t xml:space="preserve">5.19863271713257</t>
   </si>
   <si>
     <t xml:space="preserve">5.31765985488892</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">5.53963184356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41577816009521</t>
+    <t xml:space="preserve">5.41577768325806</t>
   </si>
   <si>
     <t xml:space="preserve">5.49459362030029</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">5.25653791427612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33052778244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08925580978394</t>
+    <t xml:space="preserve">5.3305287361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08925533294678</t>
   </si>
   <si>
     <t xml:space="preserve">5.15037679672241</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">5.18898153305054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99596309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16002893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08603811264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.135901927948</t>
+    <t xml:space="preserve">4.99596261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1600284576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08603763580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13590145111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.9879207611084</t>
@@ -4067,37 +4067,37 @@
     <t xml:space="preserve">5.45920753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39808416366577</t>
+    <t xml:space="preserve">5.39808464050293</t>
   </si>
   <si>
     <t xml:space="preserve">5.37878322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32409381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33696269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28709888458252</t>
+    <t xml:space="preserve">5.32409429550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33696222305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28709840774536</t>
   </si>
   <si>
     <t xml:space="preserve">5.14555168151855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30961799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35626459121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47368335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54284858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61362171173096</t>
+    <t xml:space="preserve">5.30961751937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35626411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47368383407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54284906387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61362218856812</t>
   </si>
   <si>
     <t xml:space="preserve">5.64579153060913</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">5.90315008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9240608215332</t>
+    <t xml:space="preserve">5.92406034469604</t>
   </si>
   <si>
     <t xml:space="preserve">6.04308843612671</t>
@@ -4121,61 +4121,61 @@
     <t xml:space="preserve">6.11707925796509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09616851806641</t>
+    <t xml:space="preserve">6.09616804122925</t>
   </si>
   <si>
     <t xml:space="preserve">6.02539491653442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06560707092285</t>
+    <t xml:space="preserve">6.06560659408569</t>
   </si>
   <si>
     <t xml:space="preserve">6.08651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21519660949707</t>
+    <t xml:space="preserve">6.21519708633423</t>
   </si>
   <si>
     <t xml:space="preserve">6.27149343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24897432327271</t>
+    <t xml:space="preserve">6.24897527694702</t>
   </si>
   <si>
     <t xml:space="preserve">6.26023387908936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716764450073</t>
+    <t xml:space="preserve">6.43716716766357</t>
   </si>
   <si>
     <t xml:space="preserve">6.35996007919312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45968627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49668169021606</t>
+    <t xml:space="preserve">6.45968675613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49668216705322</t>
   </si>
   <si>
     <t xml:space="preserve">6.46451234817505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45646905899048</t>
+    <t xml:space="preserve">6.45646953582764</t>
   </si>
   <si>
     <t xml:space="preserve">6.50472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50969696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290462493896</t>
+    <t xml:space="preserve">6.50969743728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290414810181</t>
   </si>
   <si>
     <t xml:space="preserve">6.56108474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47820138931274</t>
+    <t xml:space="preserve">6.47820091247559</t>
   </si>
   <si>
     <t xml:space="preserve">6.49312019348145</t>
@@ -4187,19 +4187,19 @@
     <t xml:space="preserve">6.52461671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53124713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61413145065308</t>
+    <t xml:space="preserve">6.67878007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53124761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61413097381592</t>
   </si>
   <si>
     <t xml:space="preserve">6.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51301288604736</t>
+    <t xml:space="preserve">6.51301240921021</t>
   </si>
   <si>
     <t xml:space="preserve">6.47488594055176</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">6.46825551986694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54616594314575</t>
+    <t xml:space="preserve">6.54616546630859</t>
   </si>
   <si>
     <t xml:space="preserve">6.54948139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44007444381714</t>
+    <t xml:space="preserve">6.4400749206543</t>
   </si>
   <si>
     <t xml:space="preserve">6.39200210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55776977539062</t>
+    <t xml:space="preserve">6.55777025222778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51466989517212</t>
@@ -4235,22 +4235,22 @@
     <t xml:space="preserve">6.46328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54450798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56274271011353</t>
+    <t xml:space="preserve">6.54450845718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56274318695068</t>
   </si>
   <si>
     <t xml:space="preserve">6.68209552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64728498458862</t>
+    <t xml:space="preserve">6.64728450775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.73514175415039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86609792709351</t>
+    <t xml:space="preserve">6.86609840393066</t>
   </si>
   <si>
     <t xml:space="preserve">6.87935924530029</t>
@@ -4265,58 +4265,58 @@
     <t xml:space="preserve">7.11640739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11806440353394</t>
+    <t xml:space="preserve">7.11806488037109</t>
   </si>
   <si>
     <t xml:space="preserve">7.10646152496338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9721884727478</t>
+    <t xml:space="preserve">6.97218894958496</t>
   </si>
   <si>
     <t xml:space="preserve">6.98545074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0749659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13464164733887</t>
+    <t xml:space="preserve">7.07496500015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13464117050171</t>
   </si>
   <si>
     <t xml:space="preserve">7.19100189208984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20757913589478</t>
+    <t xml:space="preserve">7.20757961273193</t>
   </si>
   <si>
     <t xml:space="preserve">7.2672553062439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26559734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34019327163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40152788162231</t>
+    <t xml:space="preserve">7.26559782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34019374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40152740478516</t>
   </si>
   <si>
     <t xml:space="preserve">7.40484237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45788764953613</t>
+    <t xml:space="preserve">7.45788812637329</t>
   </si>
   <si>
     <t xml:space="preserve">7.49767255783081</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54077196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54242992401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47446441650391</t>
+    <t xml:space="preserve">7.540771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54243040084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47446489334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.58884477615356</t>
@@ -4328,91 +4328,91 @@
     <t xml:space="preserve">7.64023303985596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67504453659058</t>
+    <t xml:space="preserve">7.67504405975342</t>
   </si>
   <si>
     <t xml:space="preserve">7.69327831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5258526802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46286058425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49435758590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55900573730469</t>
+    <t xml:space="preserve">7.52585220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46286010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49435615539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.559006690979</t>
   </si>
   <si>
     <t xml:space="preserve">7.60542154312134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59713411331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60210561752319</t>
+    <t xml:space="preserve">7.59713363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60210657119751</t>
   </si>
   <si>
     <t xml:space="preserve">7.66675567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71814346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72643232345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77781963348389</t>
+    <t xml:space="preserve">7.71814441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72643136978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77781915664673</t>
   </si>
   <si>
     <t xml:space="preserve">7.45457315444946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87604331970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03518009185791</t>
+    <t xml:space="preserve">6.87604284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03518056869507</t>
   </si>
   <si>
     <t xml:space="preserve">6.66883373260498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73348379135132</t>
+    <t xml:space="preserve">6.73348331451416</t>
   </si>
   <si>
     <t xml:space="preserve">6.51135492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76166391372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00036954879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86941337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76663684844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76000642776489</t>
+    <t xml:space="preserve">6.76166439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00037050247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86941289901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76663637161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76000595092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.67214965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83460235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93406200408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92743158340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01363086700439</t>
+    <t xml:space="preserve">6.83460187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93406248092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92743110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01363134384155</t>
   </si>
   <si>
     <t xml:space="preserve">6.96887397766113</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">7.05341529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06999206542969</t>
+    <t xml:space="preserve">7.06999158859253</t>
   </si>
   <si>
     <t xml:space="preserve">7.07993793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15950584411621</t>
+    <t xml:space="preserve">7.15950632095337</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
@@ -4439,25 +4439,25 @@
     <t xml:space="preserve">7.18271398544312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08656883239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14293003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1634407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05917739868164</t>
+    <t xml:space="preserve">7.0865683555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1429295539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16344022750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05917692184448</t>
   </si>
   <si>
     <t xml:space="preserve">7.01473665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05746841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00277185440063</t>
+    <t xml:space="preserve">7.05746793746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00277233123779</t>
   </si>
   <si>
     <t xml:space="preserve">6.7805700302124</t>
@@ -4478,25 +4478,25 @@
     <t xml:space="preserve">6.92072772979736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77031469345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65921354293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76005840301514</t>
+    <t xml:space="preserve">6.77031517028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65921401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76005887985229</t>
   </si>
   <si>
     <t xml:space="preserve">6.71049118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71220016479492</t>
+    <t xml:space="preserve">6.71220064163208</t>
   </si>
   <si>
     <t xml:space="preserve">6.79937171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78569746017456</t>
+    <t xml:space="preserve">6.78569793701172</t>
   </si>
   <si>
     <t xml:space="preserve">6.9549126625061</t>
@@ -4508,25 +4508,25 @@
     <t xml:space="preserve">6.93782091140747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74638557434082</t>
+    <t xml:space="preserve">6.74638605117798</t>
   </si>
   <si>
     <t xml:space="preserve">6.86774158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86261367797852</t>
+    <t xml:space="preserve">6.86261415481567</t>
   </si>
   <si>
     <t xml:space="preserve">6.79082584381104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73100185394287</t>
+    <t xml:space="preserve">6.73100137710571</t>
   </si>
   <si>
     <t xml:space="preserve">6.84893989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0301194190979</t>
+    <t xml:space="preserve">7.03011989593506</t>
   </si>
   <si>
     <t xml:space="preserve">6.96858739852905</t>
@@ -4535,19 +4535,19 @@
     <t xml:space="preserve">6.98397016525269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00619029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99422550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99593448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0232834815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06259489059448</t>
+    <t xml:space="preserve">7.00619077682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99422597885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99593496322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02328300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06259536743164</t>
   </si>
   <si>
     <t xml:space="preserve">7.09678030014038</t>
@@ -4556,10 +4556,10 @@
     <t xml:space="preserve">7.12583780288696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14634847640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15660381317139</t>
+    <t xml:space="preserve">7.14634895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15660333633423</t>
   </si>
   <si>
     <t xml:space="preserve">7.11045408248901</t>
@@ -4571,22 +4571,22 @@
     <t xml:space="preserve">7.04208469390869</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98226070404053</t>
+    <t xml:space="preserve">6.98226118087769</t>
   </si>
   <si>
     <t xml:space="preserve">6.87116003036499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94636678695679</t>
+    <t xml:space="preserve">6.94636726379395</t>
   </si>
   <si>
     <t xml:space="preserve">6.97029638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07797813415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09165334701538</t>
+    <t xml:space="preserve">7.07797861099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09165287017822</t>
   </si>
   <si>
     <t xml:space="preserve">6.96345901489258</t>
@@ -4595,16 +4595,16 @@
     <t xml:space="preserve">6.90534496307373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72587394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84039354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8882532119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123935699463</t>
+    <t xml:space="preserve">6.72587442398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88825273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
     <t xml:space="preserve">7.06088638305664</t>
@@ -4613,37 +4613,37 @@
     <t xml:space="preserve">7.13096475601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12925577163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14976644515991</t>
+    <t xml:space="preserve">7.12925624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14976739883423</t>
   </si>
   <si>
     <t xml:space="preserve">7.30530834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34291172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34974813461304</t>
+    <t xml:space="preserve">7.34291124343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3497486114502</t>
   </si>
   <si>
     <t xml:space="preserve">7.38393354415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38564252853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41982746124268</t>
+    <t xml:space="preserve">7.38564300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41982793807983</t>
   </si>
   <si>
     <t xml:space="preserve">7.44033908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46768569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57536840438843</t>
+    <t xml:space="preserve">7.46768617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57536888122559</t>
   </si>
   <si>
     <t xml:space="preserve">7.55485773086548</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">7.27112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21813678741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20446348190308</t>
+    <t xml:space="preserve">7.21813726425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20446300506592</t>
   </si>
   <si>
     <t xml:space="preserve">7.20788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19249820709229</t>
+    <t xml:space="preserve">7.19249773025513</t>
   </si>
   <si>
     <t xml:space="preserve">6.76347780227661</t>
@@ -4670,25 +4670,25 @@
     <t xml:space="preserve">6.94465827941895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03182888031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13609266281128</t>
+    <t xml:space="preserve">7.0318284034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13609313964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.97200536727905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91047286987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92756509780884</t>
+    <t xml:space="preserve">6.91047334671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92756462097168</t>
   </si>
   <si>
     <t xml:space="preserve">6.97371482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95662307739258</t>
+    <t xml:space="preserve">6.95662260055542</t>
   </si>
   <si>
     <t xml:space="preserve">6.9497857093811</t>
@@ -4709,19 +4709,19 @@
     <t xml:space="preserve">7.19078874588013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03695678710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17882347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18737030029297</t>
+    <t xml:space="preserve">7.03695726394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17882394790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18736982345581</t>
   </si>
   <si>
     <t xml:space="preserve">7.16856813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22497415542603</t>
+    <t xml:space="preserve">7.22497367858887</t>
   </si>
   <si>
     <t xml:space="preserve">7.08139705657959</t>
@@ -4733,19 +4733,19 @@
     <t xml:space="preserve">7.1993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04037570953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02840995788574</t>
+    <t xml:space="preserve">7.04037523269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0284104347229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97884273529053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87799692153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83697557449341</t>
+    <t xml:space="preserve">6.87799739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83697509765625</t>
   </si>
   <si>
     <t xml:space="preserve">6.80279064178467</t>
@@ -4763,13 +4763,13 @@
     <t xml:space="preserve">6.88312482833862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76518678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78740739822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77715110778809</t>
+    <t xml:space="preserve">6.76518726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78740692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77715158462524</t>
   </si>
   <si>
     <t xml:space="preserve">6.72416496276855</t>
@@ -4778,13 +4778,13 @@
     <t xml:space="preserve">6.66946935653687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57887935638428</t>
+    <t xml:space="preserve">6.57887983322144</t>
   </si>
   <si>
     <t xml:space="preserve">6.60109949111938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55153179168701</t>
+    <t xml:space="preserve">6.55153131484985</t>
   </si>
   <si>
     <t xml:space="preserve">6.48999834060669</t>
@@ -4796,10 +4796,10 @@
     <t xml:space="preserve">6.49341726303101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53443908691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58571672439575</t>
+    <t xml:space="preserve">6.53443956375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58571624755859</t>
   </si>
   <si>
     <t xml:space="preserve">6.61819171905518</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">6.74980354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88483381271362</t>
+    <t xml:space="preserve">6.88483333587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.80449962615967</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">7.00789928436279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99080753326416</t>
+    <t xml:space="preserve">6.990807056427</t>
   </si>
   <si>
     <t xml:space="preserve">7.16685914993286</t>
@@ -4832,10 +4832,10 @@
     <t xml:space="preserve">7.29847145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28137874603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17198753356934</t>
+    <t xml:space="preserve">7.28137922286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17198705673218</t>
   </si>
   <si>
     <t xml:space="preserve">7.1942081451416</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">7.29675436019897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26316070556641</t>
+    <t xml:space="preserve">7.26316118240356</t>
   </si>
   <si>
     <t xml:space="preserve">7.23487281799316</t>
@@ -4874,10 +4874,10 @@
     <t xml:space="preserve">7.25785732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24901628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30029106140137</t>
+    <t xml:space="preserve">7.24901676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30029058456421</t>
   </si>
   <si>
     <t xml:space="preserve">7.2773060798645</t>
@@ -4889,7 +4889,7 @@
     <t xml:space="preserve">7.40637397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47532749176025</t>
+    <t xml:space="preserve">7.47532796859741</t>
   </si>
   <si>
     <t xml:space="preserve">7.44527053833008</t>
@@ -4904,10 +4904,10 @@
     <t xml:space="preserve">7.54074573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51952791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54781818389893</t>
+    <t xml:space="preserve">7.51952838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54781770706177</t>
   </si>
   <si>
     <t xml:space="preserve">7.48239994049072</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">7.49654388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54428243637085</t>
+    <t xml:space="preserve">7.54428291320801</t>
   </si>
   <si>
     <t xml:space="preserve">7.58671474456787</t>
@@ -4940,34 +4940,34 @@
     <t xml:space="preserve">7.79711246490479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80241775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81832981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72815895080566</t>
+    <t xml:space="preserve">7.80241727828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81833028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72815847396851</t>
   </si>
   <si>
     <t xml:space="preserve">7.8625316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04640865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11182594299316</t>
+    <t xml:space="preserve">8.04640960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11182689666748</t>
   </si>
   <si>
     <t xml:space="preserve">8.11005878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21967792510986</t>
+    <t xml:space="preserve">8.21967887878418</t>
   </si>
   <si>
     <t xml:space="preserve">8.28509521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2762565612793</t>
+    <t xml:space="preserve">8.27625560760498</t>
   </si>
   <si>
     <t xml:space="preserve">8.37880229949951</t>
@@ -4985,10 +4985,10 @@
     <t xml:space="preserve">8.36642646789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39294719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33106422424316</t>
+    <t xml:space="preserve">8.39294815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33106517791748</t>
   </si>
   <si>
     <t xml:space="preserve">8.33813762664795</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">8.5732889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67583560943604</t>
+    <t xml:space="preserve">8.67583656311035</t>
   </si>
   <si>
     <t xml:space="preserve">8.75009346008301</t>
@@ -5018,19 +5018,19 @@
     <t xml:space="preserve">8.61572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62456226348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57152080535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54500007629395</t>
+    <t xml:space="preserve">8.62456130981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5715217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54499912261963</t>
   </si>
   <si>
     <t xml:space="preserve">8.59273719787598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62809753417969</t>
+    <t xml:space="preserve">8.628098487854</t>
   </si>
   <si>
     <t xml:space="preserve">8.737717628479</t>
@@ -5051,34 +5051,34 @@
     <t xml:space="preserve">8.78191947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84026432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88888645172119</t>
+    <t xml:space="preserve">8.84026527404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">8.86236476898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76070213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73064613342285</t>
+    <t xml:space="preserve">8.76070117950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73064517974854</t>
   </si>
   <si>
     <t xml:space="preserve">8.6298656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77661418914795</t>
+    <t xml:space="preserve">8.77661514282227</t>
   </si>
   <si>
     <t xml:space="preserve">8.82258319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97286796569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87120628356934</t>
+    <t xml:space="preserve">8.97286891937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87120532989502</t>
   </si>
   <si>
     <t xml:space="preserve">9.07011127471924</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">9.14967441558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13199329376221</t>
+    <t xml:space="preserve">9.13199234008789</t>
   </si>
   <si>
     <t xml:space="preserve">9.06127166748047</t>
@@ -5108,10 +5108,10 @@
     <t xml:space="preserve">9.07895183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03474998474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95518779754639</t>
+    <t xml:space="preserve">9.03475093841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9551887512207</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910488128662</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">8.83142471313477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9905481338501</t>
+    <t xml:space="preserve">8.99054908752441</t>
   </si>
   <si>
     <t xml:space="preserve">9.00899124145508</t>
@@ -28381,7 +28381,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28407,7 +28407,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G849" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28433,7 +28433,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G850" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28459,7 +28459,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28485,7 +28485,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28511,7 +28511,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G853" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28537,7 +28537,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G854" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28563,7 +28563,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28589,7 +28589,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G856" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28615,7 +28615,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G857" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28641,7 +28641,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G858" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28667,7 +28667,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G859" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28693,7 +28693,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G860" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28719,7 +28719,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28745,7 +28745,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G862" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28771,7 +28771,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28797,7 +28797,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28823,7 +28823,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G865" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28849,7 +28849,7 @@
         <v>6</v>
       </c>
       <c r="G866" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28875,7 +28875,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G867" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28901,7 +28901,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G868" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28927,7 +28927,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G869" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28953,7 +28953,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G870" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28979,7 +28979,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G871" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29005,7 +29005,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G872" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29031,7 +29031,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29057,7 +29057,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G874" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29083,7 +29083,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29109,7 +29109,7 @@
         <v>6.125</v>
       </c>
       <c r="G876" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29135,7 +29135,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G877" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -29161,7 +29161,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G878" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -29187,7 +29187,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29213,7 +29213,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -29239,7 +29239,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G881" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -29265,7 +29265,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G882" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -29291,7 +29291,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G883" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -29317,7 +29317,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G884" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -29343,7 +29343,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G885" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -29369,7 +29369,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G886" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29395,7 +29395,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G887" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29421,7 +29421,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G888" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -29447,7 +29447,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G889" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -29473,7 +29473,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G890" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -29499,7 +29499,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G891" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29525,7 +29525,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29551,7 +29551,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29577,7 +29577,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G894" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29603,7 +29603,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29629,7 +29629,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G896" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29655,7 +29655,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G897" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29681,7 +29681,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G898" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29707,7 +29707,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29733,7 +29733,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G900" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29759,7 +29759,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G901" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29785,7 +29785,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G902" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29811,7 +29811,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29837,7 +29837,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29863,7 +29863,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G905" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29889,7 +29889,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29915,7 +29915,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G907" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29941,7 +29941,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G908" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29967,7 +29967,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G909" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30019,7 +30019,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G911" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -30045,7 +30045,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G912" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -30071,7 +30071,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -30097,7 +30097,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G914" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -30123,7 +30123,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G915" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -30149,7 +30149,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G916" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G917" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -30201,7 +30201,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G918" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30227,7 +30227,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G919" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30253,7 +30253,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G920" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30279,7 +30279,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30305,7 +30305,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30357,7 +30357,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G924" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30383,7 +30383,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30409,7 +30409,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G926" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30435,7 +30435,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G927" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30461,7 +30461,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G928" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30487,7 +30487,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G929" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30513,7 +30513,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G930" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30539,7 +30539,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G931" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30565,7 +30565,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30591,7 +30591,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G933" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30617,7 +30617,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G934" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30643,7 +30643,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30669,7 +30669,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G936" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30695,7 +30695,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G937" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30721,7 +30721,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G938" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30747,7 +30747,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30773,7 +30773,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G940" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30799,7 +30799,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G941" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30825,7 +30825,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G942" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30851,7 +30851,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G943" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30877,7 +30877,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G944" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30903,7 +30903,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30929,7 +30929,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G946" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30955,7 +30955,7 @@
         <v>7</v>
       </c>
       <c r="G947" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30981,7 +30981,7 @@
         <v>6.875</v>
       </c>
       <c r="G948" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31007,7 +31007,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31033,7 +31033,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G950" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31059,7 +31059,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G951" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31085,7 +31085,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31111,7 +31111,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G953" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31137,7 +31137,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G954" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31163,7 +31163,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31189,7 +31189,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G956" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31215,7 +31215,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G957" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31241,7 +31241,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G958" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31267,7 +31267,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G959" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31293,7 +31293,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G960" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31319,7 +31319,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G961" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31345,7 +31345,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G962" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31371,7 +31371,7 @@
         <v>7.25</v>
       </c>
       <c r="G963" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31397,7 +31397,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G964" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31423,7 +31423,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G965" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31449,7 +31449,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31475,7 +31475,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G967" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31501,7 +31501,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G968" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31527,7 +31527,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G969" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31553,7 +31553,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G970" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31579,7 +31579,7 @@
         <v>7.625</v>
       </c>
       <c r="G971" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31605,7 +31605,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G972" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31631,7 +31631,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G973" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31657,7 +31657,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31683,7 +31683,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G975" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31709,7 +31709,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G976" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31735,7 +31735,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G977" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31761,7 +31761,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G978" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31787,7 +31787,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G979" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31813,7 +31813,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G980" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31839,7 +31839,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G981" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31865,7 +31865,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G982" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31891,7 +31891,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G983" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31917,7 +31917,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G984" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31943,7 +31943,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G985" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31969,7 +31969,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G986" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31995,7 +31995,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G987" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32021,7 +32021,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G988" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32047,7 +32047,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G989" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32073,7 +32073,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G990" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32099,7 +32099,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G991" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32125,7 +32125,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G992" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -32151,7 +32151,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G993" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -32177,7 +32177,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32203,7 +32203,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G995" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32229,7 +32229,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G996" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32255,7 +32255,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G997" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32281,7 +32281,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G998" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32307,7 +32307,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G999" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32333,7 +32333,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32359,7 +32359,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1001" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -32385,7 +32385,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32411,7 +32411,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G1003" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32437,7 +32437,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1004" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -32463,7 +32463,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1005" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32489,7 +32489,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1006" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32515,7 +32515,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1007" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32541,7 +32541,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32567,7 +32567,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G1009" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32593,7 +32593,7 @@
         <v>9.125</v>
       </c>
       <c r="G1010" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32619,7 +32619,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32645,7 +32645,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G1012" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32671,7 +32671,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1013" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32697,7 +32697,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1014" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32723,7 +32723,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1015" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32749,7 +32749,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G1016" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32775,7 +32775,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G1017" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32801,7 +32801,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1018" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32827,7 +32827,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1019" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32853,7 +32853,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1020" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32879,7 +32879,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G1021" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32905,7 +32905,7 @@
         <v>9</v>
       </c>
       <c r="G1022" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32931,7 +32931,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1023" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32957,7 +32957,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1024" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32983,7 +32983,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1025" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -33009,7 +33009,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1026" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -33035,7 +33035,7 @@
         <v>8.875</v>
       </c>
       <c r="G1027" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -33061,7 +33061,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1028" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -33087,7 +33087,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1029" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -33113,7 +33113,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1030" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -33139,7 +33139,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1031" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -33165,7 +33165,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1032" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -33191,7 +33191,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33217,7 +33217,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1034" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33243,7 +33243,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1035" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33269,7 +33269,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1036" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33373,7 +33373,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33529,7 +33529,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1046" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -71055,7 +71055,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6510648148</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>871195</v>
@@ -71064,7 +71064,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="D2490" t="n">
-        <v>17.0599994659424</v>
+        <v>17.0100002288818</v>
       </c>
       <c r="E2490" t="n">
         <v>17.2000007629395</v>
@@ -71076,6 +71076,32 @@
         <v>1993</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6497800926</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>822568</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>17.1299991607666</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>16.7700004577637</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>17.0900001525879</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>16.8600006103516</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="1998">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446698188782</t>
+    <t xml:space="preserve">3.7844672203064</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277378082275</t>
+    <t xml:space="preserve">3.73277401924133</t>
   </si>
   <si>
     <t xml:space="preserve">3.49607491493225</t>
@@ -53,64 +53,64 @@
     <t xml:space="preserve">3.4144549369812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40901255607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4334990978241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144335746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688454627991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658270835876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937485694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920241355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157656669617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040415763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41989612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187864303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2267279624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13966608047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18863821029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30562710762024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03083872795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89208436012268</t>
+    <t xml:space="preserve">3.40901327133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349885940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688502311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937604904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29202437400818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157608985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41989588737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.428058385849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077850341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187840461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276173591614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22672748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13966631889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18863844871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30562734603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03083896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89208388328552</t>
   </si>
   <si>
     <t xml:space="preserve">3.1559898853302</t>
@@ -119,304 +119,304 @@
     <t xml:space="preserve">3.25393390655518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31378960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40357136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36548233032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36820340156555</t>
+    <t xml:space="preserve">3.3137891292572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40357112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36548280715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36820244789124</t>
   </si>
   <si>
     <t xml:space="preserve">3.46614742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43621969223022</t>
+    <t xml:space="preserve">3.43622016906738</t>
   </si>
   <si>
     <t xml:space="preserve">3.36004137992859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49063420295715</t>
+    <t xml:space="preserve">3.49063372612</t>
   </si>
   <si>
     <t xml:space="preserve">3.56681275367737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56409215927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69196486473083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71100902557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61850619316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380236625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623173713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7926287651062</t>
+    <t xml:space="preserve">3.56409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6919641494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71100926399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61850595474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652200698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380188941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093580245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623292922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79262828826904</t>
   </si>
   <si>
     <t xml:space="preserve">3.76542210578918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70284605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181913375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72189235687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6946849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387511253357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439447402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432196617126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86608743667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71372961997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6348295211792</t>
+    <t xml:space="preserve">3.70284652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181937217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72189092636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69468545913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81439518928528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84432220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8660876750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71373057365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63482999801636</t>
   </si>
   <si>
     <t xml:space="preserve">3.54232692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637770652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77630496025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821568489075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8796911239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91778016090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85248374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407773017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88579130172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94962882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97460913658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96628284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88023996353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92464876174927</t>
+    <t xml:space="preserve">3.74637746810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77630472183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73821544647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87969136238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91778063774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85248422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407796859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88579034805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94962954521179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97460865974426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9662823677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88023948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92464828491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.8885669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00236463546753</t>
+    <t xml:space="preserve">4.00236415863037</t>
   </si>
   <si>
     <t xml:space="preserve">3.98848700523376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04122304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93019962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07730436325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99681329727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96905755996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06065130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742419242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93575119972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95240449905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91909766197205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08008146286011</t>
+    <t xml:space="preserve">4.04122257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93020009994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07730484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99681305885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96905827522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0606517791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742466926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93575048446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92187285423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95240497589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9190981388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130253791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08008003234863</t>
   </si>
   <si>
     <t xml:space="preserve">4.29102325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23551321029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16334772109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1883282661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21608304977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18277597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15502023696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03289556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05232524871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09673357009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06342697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69427728652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53051853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55272269248962</t>
+    <t xml:space="preserve">4.23551177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16334819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21608352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18277740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559198379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15502119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03289604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0523247718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09673452377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06342744827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69427704811096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5305187702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55272316932678</t>
   </si>
   <si>
     <t xml:space="preserve">3.48888540267944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6026828289032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78587079048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8247287273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80529952049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685292243958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288262367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13916444778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26961588859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23630905151367</t>
+    <t xml:space="preserve">3.60268330574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78587126731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82472848892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8052990436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685339927673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13916325569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.269615650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23630833625793</t>
   </si>
   <si>
     <t xml:space="preserve">3.40561842918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41394543647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904438018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19189953804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410465240479</t>
+    <t xml:space="preserve">3.4139449596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1919002532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410393714905</t>
   </si>
   <si>
     <t xml:space="preserve">3.39174056053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47778224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59713220596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49721264839172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941657066345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5388457775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.558274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54162073135376</t>
+    <t xml:space="preserve">3.47778367996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59713244438171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721217155457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941561698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53884530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55827450752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5416214466095</t>
   </si>
   <si>
     <t xml:space="preserve">3.51386547088623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63599038124084</t>
+    <t xml:space="preserve">3.635990858078</t>
   </si>
   <si>
     <t xml:space="preserve">3.58047842979431</t>
@@ -425,76 +425,76 @@
     <t xml:space="preserve">3.64154100418091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39451503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34455633163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949582099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54717302322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56937646865845</t>
+    <t xml:space="preserve">3.39451551437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34455609321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5471715927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56937623023987</t>
   </si>
   <si>
     <t xml:space="preserve">3.46945643424988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41116976737976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4528021812439</t>
+    <t xml:space="preserve">3.41116952896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280313491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.37231135368347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4805588722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51664090156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45002794265747</t>
+    <t xml:space="preserve">3.48055863380432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51664066314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.450026512146</t>
   </si>
   <si>
     <t xml:space="preserve">3.47500777244568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51108980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56660103797913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58325409889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59990811347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49166011810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52219128608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50831413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31402492523193</t>
+    <t xml:space="preserve">3.51109004020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56660079956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58325386047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994702339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215285301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59990859031677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49166035652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52219176292419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50831460952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31402444839478</t>
   </si>
   <si>
     <t xml:space="preserve">3.37786293029785</t>
@@ -506,151 +506,151 @@
     <t xml:space="preserve">3.36120915412903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38896441459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29737138748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19745111465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23075795173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29182052612305</t>
+    <t xml:space="preserve">3.38896465301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29737162590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19745087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23075747489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29181981086731</t>
   </si>
   <si>
     <t xml:space="preserve">3.26684021949768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27516746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337392807007</t>
+    <t xml:space="preserve">3.27516627311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337416648865</t>
   </si>
   <si>
     <t xml:space="preserve">3.39729189872742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4639048576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4083936214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46112871170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32235097885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38618898391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43059825897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43614983558655</t>
+    <t xml:space="preserve">3.46390533447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839409828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4611291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32235169410706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38618922233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43059778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43614959716797</t>
   </si>
   <si>
     <t xml:space="preserve">3.50276279449463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5638256072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33900499343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835423469543</t>
+    <t xml:space="preserve">3.56382608413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33900427818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835375785828</t>
   </si>
   <si>
     <t xml:space="preserve">3.54439663887024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42227149009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38341379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30014681816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28303289413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37145519256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3914213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37715911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41423988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45702457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4855477809906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73370099067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930400848389</t>
+    <t xml:space="preserve">3.42227172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38341403007507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30014705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2830331325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37145495414734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39142155647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37715983390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41424036026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45702481269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48554825782776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118562698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73370122909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79930448532104</t>
   </si>
   <si>
     <t xml:space="preserve">4.09309482574463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95047903060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89343214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95333027839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93906879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93051218986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635089874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92480707168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90484023094177</t>
+    <t xml:space="preserve">3.95047855377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8934314250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95333051681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93906927108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93051195144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635113716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92480683326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90484070777893</t>
   </si>
   <si>
     <t xml:space="preserve">3.93621611595154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94192123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.921954870224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89628410339355</t>
+    <t xml:space="preserve">3.9419207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92195463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8962836265564</t>
   </si>
   <si>
     <t xml:space="preserve">3.94477343559265</t>
@@ -659,25 +659,25 @@
     <t xml:space="preserve">3.96473979949951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10735654830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12447023391724</t>
+    <t xml:space="preserve">4.10735559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12447071075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.04175186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426746368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15014171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30131530761719</t>
+    <t xml:space="preserve">4.07883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2442684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15014123916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30131435394287</t>
   </si>
   <si>
     <t xml:space="preserve">4.21574449539185</t>
@@ -686,145 +686,145 @@
     <t xml:space="preserve">4.20433568954468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26708650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21289253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20718812942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09879875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23571109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18151712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1701078414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17581176757812</t>
+    <t xml:space="preserve">4.26708698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21289300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20718765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09879922866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23571157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18151664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17010736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1758131980896</t>
   </si>
   <si>
     <t xml:space="preserve">4.03319549560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03889942169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08453845977783</t>
+    <t xml:space="preserve">4.03889989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08453702926636</t>
   </si>
   <si>
     <t xml:space="preserve">4.07027578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97044515609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99326324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.981853723526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05886602401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11306095123291</t>
+    <t xml:space="preserve">3.97044444084167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99326300621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98185324668884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05886697769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11306047439575</t>
   </si>
   <si>
     <t xml:space="preserve">4.06171894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04745721817017</t>
+    <t xml:space="preserve">4.04745674133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.02749109268188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75651955604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105108261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5197765827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53689002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692414283752</t>
+    <t xml:space="preserve">3.75651979446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6110508441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51977586746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688979148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692390441895</t>
   </si>
   <si>
     <t xml:space="preserve">3.63386988639832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6823582649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64242672920227</t>
+    <t xml:space="preserve">3.68235850334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64242649078369</t>
   </si>
   <si>
     <t xml:space="preserve">3.65098357200623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69091582298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7194390296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73084878921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81641936302185</t>
+    <t xml:space="preserve">3.69091606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71943926811218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73084902763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81641888618469</t>
   </si>
   <si>
     <t xml:space="preserve">3.78789496421814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81071400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76792907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78218984603882</t>
+    <t xml:space="preserve">3.81071448326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7679295539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7821900844574</t>
   </si>
   <si>
     <t xml:space="preserve">3.80215668678284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83353281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064649581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90769195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91625022888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94762563705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9761483669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92765974998474</t>
+    <t xml:space="preserve">3.83353209495544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064625740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91624999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94762587547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97614860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92765951156616</t>
   </si>
   <si>
     <t xml:space="preserve">3.89057993888855</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">3.85349869728088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82212328910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8734655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10278224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10869359970093</t>
+    <t xml:space="preserve">3.8221230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87346529960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10278272628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10869407653809</t>
   </si>
   <si>
     <t xml:space="preserve">4.17076778411865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1146068572998</t>
+    <t xml:space="preserve">4.11460590362549</t>
   </si>
   <si>
     <t xml:space="preserve">4.15303230285645</t>
@@ -857,25 +857,25 @@
     <t xml:space="preserve">4.12938499450684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10573816299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16485691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23579883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875284194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919418334961</t>
+    <t xml:space="preserve">4.10573720932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16485643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23579740524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875331878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919466018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.34516525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35107755661011</t>
+    <t xml:space="preserve">4.35107803344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.36290073394775</t>
@@ -884,46 +884,46 @@
     <t xml:space="preserve">4.35994529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39837217330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28900384902954</t>
+    <t xml:space="preserve">4.39837169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2890043258667</t>
   </si>
   <si>
     <t xml:space="preserve">4.30082750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37176895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340227127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51956367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.469313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4752254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45453405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.368812084198</t>
+    <t xml:space="preserve">4.37176847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51956272125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46931314468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47522497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45453357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36881303787231</t>
   </si>
   <si>
     <t xml:space="preserve">4.33334255218506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41315174102783</t>
+    <t xml:space="preserve">4.41315078735352</t>
   </si>
   <si>
     <t xml:space="preserve">4.30673885345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41906261444092</t>
+    <t xml:space="preserve">4.41906213760376</t>
   </si>
   <si>
     <t xml:space="preserve">4.43384265899658</t>
@@ -935,40 +935,40 @@
     <t xml:space="preserve">4.30969476699829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28604745864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31856298446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39245939254761</t>
+    <t xml:space="preserve">4.286048412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31856250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39245986938477</t>
   </si>
   <si>
     <t xml:space="preserve">4.29491567611694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33629751205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25353336334229</t>
+    <t xml:space="preserve">4.33629846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25353288650513</t>
   </si>
   <si>
     <t xml:space="preserve">4.3244743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37472486495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32742977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3392539024353</t>
+    <t xml:space="preserve">4.37472438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3274302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33925437927246</t>
   </si>
   <si>
     <t xml:space="preserve">4.38063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49295997619629</t>
+    <t xml:space="preserve">4.49296092987061</t>
   </si>
   <si>
     <t xml:space="preserve">4.37768077850342</t>
@@ -980,58 +980,58 @@
     <t xml:space="preserve">4.38950395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31560707092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27126789093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21510601043701</t>
+    <t xml:space="preserve">4.31560659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27126741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21510648727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.342209815979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3215184211731</t>
+    <t xml:space="preserve">4.32151889801025</t>
   </si>
   <si>
     <t xml:space="preserve">4.25648880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28309202194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23284196853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22101831436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16190052032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19737100601196</t>
+    <t xml:space="preserve">4.28309106826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057744979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22101783752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16190004348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19737148284912</t>
   </si>
   <si>
     <t xml:space="preserve">4.24170923233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17963552474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22397422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26831197738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2919602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35403347015381</t>
+    <t xml:space="preserve">4.1796350479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22397375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26831245422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29195976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35403299331665</t>
   </si>
   <si>
     <t xml:space="preserve">4.43679857254028</t>
@@ -1043,37 +1043,37 @@
     <t xml:space="preserve">4.26535654067993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1885027885437</t>
+    <t xml:space="preserve">4.18850326538086</t>
   </si>
   <si>
     <t xml:space="preserve">4.17372369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16781187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24762058258057</t>
+    <t xml:space="preserve">4.16781234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24762105941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.21806192398071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2801365852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23866844177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13528633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13832759857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16873455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16569232940674</t>
+    <t xml:space="preserve">4.28013563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23866891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13528680801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13832664489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16873359680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1656928062439</t>
   </si>
   <si>
     <t xml:space="preserve">4.25083112716675</t>
@@ -1082,37 +1082,37 @@
     <t xml:space="preserve">4.25995349884033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27211570739746</t>
+    <t xml:space="preserve">4.27211618423462</t>
   </si>
   <si>
     <t xml:space="preserve">4.36637592315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3694167137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117292404175</t>
+    <t xml:space="preserve">4.36941766738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509229660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117244720459</t>
   </si>
   <si>
     <t xml:space="preserve">4.32988882064819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38157987594604</t>
+    <t xml:space="preserve">4.38157892227173</t>
   </si>
   <si>
     <t xml:space="preserve">4.3359694480896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39678287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44543313980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50016498565674</t>
+    <t xml:space="preserve">4.39678192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44543266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5001654624939</t>
   </si>
   <si>
     <t xml:space="preserve">4.54577445983887</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">4.4393515586853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48800277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51232814788818</t>
+    <t xml:space="preserve">4.48800182342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51232767105103</t>
   </si>
   <si>
     <t xml:space="preserve">4.44847345352173</t>
@@ -1133,103 +1133,103 @@
     <t xml:space="preserve">4.46367692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38766050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30860328674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29339981079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37245750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46063661575317</t>
+    <t xml:space="preserve">4.38766098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30860424041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29340028762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3724570274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">4.45759582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718887329102</t>
+    <t xml:space="preserve">4.42718935012817</t>
   </si>
   <si>
     <t xml:space="preserve">4.55489635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57922124862671</t>
+    <t xml:space="preserve">4.57922220230103</t>
   </si>
   <si>
     <t xml:space="preserve">4.62179136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70084810256958</t>
+    <t xml:space="preserve">4.70084714889526</t>
   </si>
   <si>
     <t xml:space="preserve">4.72517347335815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7403769493103</t>
+    <t xml:space="preserve">4.74037599563599</t>
   </si>
   <si>
     <t xml:space="preserve">4.73429536819458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77078342437744</t>
+    <t xml:space="preserve">4.77078247070312</t>
   </si>
   <si>
     <t xml:space="preserve">4.81639242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81943416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76470184326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80422973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83463621139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71301126480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61571073532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.691725730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6278715133667</t>
+    <t xml:space="preserve">4.81943321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76470136642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80423021316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83463668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71301031112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61570978164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69172668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62787199020386</t>
   </si>
   <si>
     <t xml:space="preserve">4.53665208816528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25691223144531</t>
+    <t xml:space="preserve">4.25691366195679</t>
   </si>
   <si>
     <t xml:space="preserve">4.2994818687439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40590476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39374208450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43326997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42414855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42110776901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43022918701172</t>
+    <t xml:space="preserve">4.4059042930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39374256134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43327045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42414808273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42110824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43022966384888</t>
   </si>
   <si>
     <t xml:space="preserve">4.52448987960815</t>
@@ -1238,40 +1238,40 @@
     <t xml:space="preserve">4.5032057762146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31468534469604</t>
+    <t xml:space="preserve">4.31468486785889</t>
   </si>
   <si>
     <t xml:space="preserve">4.27819728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32076549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38462066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41502666473389</t>
+    <t xml:space="preserve">4.32076644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38462018966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41502714157104</t>
   </si>
   <si>
     <t xml:space="preserve">4.40894556045532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35725498199463</t>
+    <t xml:space="preserve">4.35725355148315</t>
   </si>
   <si>
     <t xml:space="preserve">4.33292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2690749168396</t>
+    <t xml:space="preserve">4.26907587051392</t>
   </si>
   <si>
     <t xml:space="preserve">4.29644107818604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30556297302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23562860488892</t>
+    <t xml:space="preserve">4.30556344985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2356276512146</t>
   </si>
   <si>
     <t xml:space="preserve">4.29036045074463</t>
@@ -1280,91 +1280,91 @@
     <t xml:space="preserve">4.2660346031189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26299428939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22650623321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21738433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28731966018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32380676269531</t>
+    <t xml:space="preserve">4.26299381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22650575637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21738386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731870651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32380723953247</t>
   </si>
   <si>
     <t xml:space="preserve">4.38646936416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32702398300171</t>
+    <t xml:space="preserve">4.32702350616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.205002784729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11427021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14555835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16745853424072</t>
+    <t xml:space="preserve">4.11427068710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14555740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16745948791504</t>
   </si>
   <si>
     <t xml:space="preserve">4.24567699432373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23003339767456</t>
+    <t xml:space="preserve">4.23003435134888</t>
   </si>
   <si>
     <t xml:space="preserve">4.25506353378296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24254751205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16120195388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21438980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17997407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17058706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08924102783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458707809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8358142375946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82329964637756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77636814117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80765557289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81704163551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79826974868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73882389068604</t>
+    <t xml:space="preserve">4.2425479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16120100021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21438932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17997360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17058753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08924007415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02040958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83581399917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82329940795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77636885643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80765628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81704211235046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7982702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73882365226746</t>
   </si>
   <si>
     <t xml:space="preserve">3.63557624816895</t>
@@ -1373,124 +1373,124 @@
     <t xml:space="preserve">3.74195289611816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262543678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82642793655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66060543060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72630953788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74508190155029</t>
+    <t xml:space="preserve">3.78262591362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82642817497253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66060590744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72630906105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74508142471313</t>
   </si>
   <si>
     <t xml:space="preserve">3.63870477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77011060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71692276000977</t>
+    <t xml:space="preserve">3.7701108455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7169234752655</t>
   </si>
   <si>
     <t xml:space="preserve">3.71379399299622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74820971488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6981508731842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6825065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72318053245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373419761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76072525978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183402061462</t>
+    <t xml:space="preserve">3.74820947647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69815063476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68250608444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72318005561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373443603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7607250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64183330535889</t>
   </si>
   <si>
     <t xml:space="preserve">3.60116052627563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57925939559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63244795799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68876433372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67624974250793</t>
+    <t xml:space="preserve">3.57925891876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6324474811554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68876385688782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67624926567078</t>
   </si>
   <si>
     <t xml:space="preserve">3.70440769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56361556053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62931871414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686367988586</t>
+    <t xml:space="preserve">3.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62931799888611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686272621155</t>
   </si>
   <si>
     <t xml:space="preserve">3.6199324131012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62618970870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84520077705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99537825584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88587355613708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91090440750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87022995948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341876029968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961649894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84207129478455</t>
+    <t xml:space="preserve">3.62619018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8452000617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99537897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88587427139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91090369224548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87023067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341804504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84207153320312</t>
   </si>
   <si>
     <t xml:space="preserve">3.78575491905212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79514169692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77323985099792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70753693580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698207855225</t>
+    <t xml:space="preserve">3.79514122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77323937416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70753622055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698279380798</t>
   </si>
   <si>
     <t xml:space="preserve">3.80452680587769</t>
@@ -1499,97 +1499,97 @@
     <t xml:space="preserve">3.81078457832336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80139827728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75446772575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7325656414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563580513</t>
+    <t xml:space="preserve">3.80139803886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75446748733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73256683349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563556671143</t>
   </si>
   <si>
     <t xml:space="preserve">3.82017064094543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75759625434875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81391310691833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7794976234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397314071655</t>
+    <t xml:space="preserve">3.75759649276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81391334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77949738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397290229797</t>
   </si>
   <si>
     <t xml:space="preserve">3.8733594417572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89213109016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99225044250488</t>
+    <t xml:space="preserve">3.89213156700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9922513961792</t>
   </si>
   <si>
     <t xml:space="preserve">3.97660684585571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98912167549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00163650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4447238445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47288298606873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37276291847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37589192390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39466452598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098161697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39779281616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31018829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29141712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24448561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22258400917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16313886642456</t>
+    <t xml:space="preserve">3.98912119865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00163698196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47288250923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37276363372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37589263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39466428756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4509813785553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39779257774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31018853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24448537826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22258448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313862800598</t>
   </si>
   <si>
     <t xml:space="preserve">3.18504023551941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13498044013977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21006941795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20694088935852</t>
+    <t xml:space="preserve">3.13498091697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21007013320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20694065093994</t>
   </si>
   <si>
     <t xml:space="preserve">3.26325798034668</t>
@@ -1598,229 +1598,229 @@
     <t xml:space="preserve">3.31644654273987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30705976486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31331729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28515958786011</t>
+    <t xml:space="preserve">3.30706000328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3133180141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28515934944153</t>
   </si>
   <si>
     <t xml:space="preserve">3.25387167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25074338912964</t>
+    <t xml:space="preserve">3.25074315071106</t>
   </si>
   <si>
     <t xml:space="preserve">3.27843809127808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13193416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541590690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890445709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727289199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48354363441467</t>
+    <t xml:space="preserve">3.13193392753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541566848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890469551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727265357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48354434967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.45098781585693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44773173332214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4412202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42494320869446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41843175888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192664146423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2335102558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28820586204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40866422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3337836265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31099510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331749916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30773854255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15537476539612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076168060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31425070762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2849497795105</t>
+    <t xml:space="preserve">3.44773244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44122076034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494225502014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2914605140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23351001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28820514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680652618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4086639881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33378386497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31099438667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1553750038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076144218445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31425046920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28494930267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40215349197388</t>
+    <t xml:space="preserve">3.4021532535553</t>
   </si>
   <si>
     <t xml:space="preserve">3.36634063720703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44447588920593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46401000022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633406639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48680019378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075463294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331068992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726560592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45749831199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50958919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47052121162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58121347427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71795058250427</t>
+    <t xml:space="preserve">3.44447612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4640097618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633311271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48679971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45749878883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5095899105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47052145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58121275901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71795129776001</t>
   </si>
   <si>
     <t xml:space="preserve">3.77655267715454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70818424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83189845085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864236831665</t>
+    <t xml:space="preserve">3.7081835269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8318989276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864332199097</t>
   </si>
   <si>
     <t xml:space="preserve">3.87096667289734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92305636405945</t>
+    <t xml:space="preserve">3.92305612564087</t>
   </si>
   <si>
     <t xml:space="preserve">3.87422204017639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88073325157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88724517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99142503738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95886898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00770282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9979362487793</t>
+    <t xml:space="preserve">3.88073301315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99142527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95886874198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00770378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99793601036072</t>
   </si>
   <si>
     <t xml:space="preserve">4.06304931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9718906879425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01746988296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06630420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0825834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1216516494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09235143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11514043807983</t>
+    <t xml:space="preserve">3.97189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01747035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12165117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09235000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11513996124268</t>
   </si>
   <si>
     <t xml:space="preserve">4.12816286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09886169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14118528366089</t>
+    <t xml:space="preserve">4.0988621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14118480682373</t>
   </si>
   <si>
     <t xml:space="preserve">4.08583927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11188411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16071891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13141822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26164436340332</t>
+    <t xml:space="preserve">4.11188459396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16071939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13141870498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26164484024048</t>
   </si>
   <si>
     <t xml:space="preserve">4.24862146377563</t>
@@ -1832,25 +1832,25 @@
     <t xml:space="preserve">4.24211025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23559904098511</t>
+    <t xml:space="preserve">4.23559951782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.2323431968689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32350015640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38210296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40489196777344</t>
+    <t xml:space="preserve">4.3235011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38210391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40489292144775</t>
   </si>
   <si>
     <t xml:space="preserve">4.37884712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37233686447144</t>
+    <t xml:space="preserve">4.37233591079712</t>
   </si>
   <si>
     <t xml:space="preserve">4.37569189071655</t>
@@ -1862,40 +1862,37 @@
     <t xml:space="preserve">4.32871341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3320689201355</t>
+    <t xml:space="preserve">4.33206939697266</t>
   </si>
   <si>
     <t xml:space="preserve">4.4126033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39246988296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36226940155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233638763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22804546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.238112449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25153493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751195907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10388898849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10724496841431</t>
+    <t xml:space="preserve">4.39247035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22804594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23811197280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25153541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10388851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16093254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10724449157715</t>
   </si>
   <si>
     <t xml:space="preserve">4.16428995132446</t>
@@ -1904,13 +1901,13 @@
     <t xml:space="preserve">4.12737846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12402296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06697654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07704401016235</t>
+    <t xml:space="preserve">4.12402248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06697797775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0770435333252</t>
   </si>
   <si>
     <t xml:space="preserve">4.08039999008179</t>
@@ -1922,10 +1919,10 @@
     <t xml:space="preserve">4.02671051025391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00657749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03342199325562</t>
+    <t xml:space="preserve">4.0065770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03342151641846</t>
   </si>
   <si>
     <t xml:space="preserve">4.09046649932861</t>
@@ -1934,40 +1931,40 @@
     <t xml:space="preserve">4.14415645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13408946990967</t>
+    <t xml:space="preserve">4.13408899307251</t>
   </si>
   <si>
     <t xml:space="preserve">4.17435598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1575779914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11059999465942</t>
+    <t xml:space="preserve">4.15757846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11060047149658</t>
   </si>
   <si>
     <t xml:space="preserve">4.13744497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07368850708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19784545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2179799079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24482345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34213590621948</t>
+    <t xml:space="preserve">4.07368898391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19784593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21797847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24482393264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34213542938232</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28508996963501</t>
+    <t xml:space="preserve">4.28509044647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.33878040313721</t>
@@ -1979,28 +1976,28 @@
     <t xml:space="preserve">4.34884691238403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47300338745117</t>
+    <t xml:space="preserve">4.47300386428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.50991535186768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46293783187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45622491836548</t>
+    <t xml:space="preserve">4.4629373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45622634887695</t>
   </si>
   <si>
     <t xml:space="preserve">4.41931486129761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48978233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48307132720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51662635803223</t>
+    <t xml:space="preserve">4.48978185653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48307037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51662731170654</t>
   </si>
   <si>
     <t xml:space="preserve">4.5367603302002</t>
@@ -2009,22 +2006,22 @@
     <t xml:space="preserve">4.49313735961914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44280385971069</t>
+    <t xml:space="preserve">4.44280338287354</t>
   </si>
   <si>
     <t xml:space="preserve">4.426025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42266941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44951486587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42938137054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50656080245972</t>
+    <t xml:space="preserve">4.42267036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4495153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42938089370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50656032562256</t>
   </si>
   <si>
     <t xml:space="preserve">4.46964836120605</t>
@@ -2036,16 +2033,16 @@
     <t xml:space="preserve">4.39582538604736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20120143890381</t>
+    <t xml:space="preserve">4.20120096206665</t>
   </si>
   <si>
     <t xml:space="preserve">4.20455598831177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21126794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14079999923706</t>
+    <t xml:space="preserve">4.21126842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
     <t xml:space="preserve">4.33542537689209</t>
@@ -2054,13 +2051,13 @@
     <t xml:space="preserve">4.43273687362671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38575887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46629333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595935821533</t>
+    <t xml:space="preserve">4.38575839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46629238128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595888137817</t>
   </si>
   <si>
     <t xml:space="preserve">4.50320434570312</t>
@@ -2069,34 +2066,34 @@
     <t xml:space="preserve">4.52333784103394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722827911377</t>
+    <t xml:space="preserve">4.60722684860229</t>
   </si>
   <si>
     <t xml:space="preserve">4.61729526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59716033935547</t>
+    <t xml:space="preserve">4.59716081619263</t>
   </si>
   <si>
     <t xml:space="preserve">4.70453977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65756130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67769575119019</t>
+    <t xml:space="preserve">4.65756177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67769527435303</t>
   </si>
   <si>
     <t xml:space="preserve">4.72467374801636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73138523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69782876968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61393880844116</t>
+    <t xml:space="preserve">4.73138475418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.697829246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61393928527832</t>
   </si>
   <si>
     <t xml:space="preserve">4.64078330993652</t>
@@ -2105,16 +2102,16 @@
     <t xml:space="preserve">4.60387229919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62736129760742</t>
+    <t xml:space="preserve">4.62736177444458</t>
   </si>
   <si>
     <t xml:space="preserve">4.62400531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62065076828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56024980545044</t>
+    <t xml:space="preserve">4.62065029144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56024932861328</t>
   </si>
   <si>
     <t xml:space="preserve">4.66762828826904</t>
@@ -2123,46 +2120,46 @@
     <t xml:space="preserve">4.66427230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66091728210449</t>
+    <t xml:space="preserve">4.66091775894165</t>
   </si>
   <si>
     <t xml:space="preserve">4.68105030059814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82534122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86560821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90252017974854</t>
+    <t xml:space="preserve">4.82534074783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86560869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90251970291138</t>
   </si>
   <si>
     <t xml:space="preserve">4.94278717041016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98305511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04345417022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07365560531616</t>
+    <t xml:space="preserve">4.98305416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04345464706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.073655128479</t>
   </si>
   <si>
     <t xml:space="preserve">5.08707761764526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09714460372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11727714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15083408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16090059280396</t>
+    <t xml:space="preserve">5.09714365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1172776222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15083312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16090106964111</t>
   </si>
   <si>
     <t xml:space="preserve">5.15754508972168</t>
@@ -2171,166 +2168,169 @@
     <t xml:space="preserve">5.16425561904907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17432260513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16761159896851</t>
+    <t xml:space="preserve">5.17432308197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16761112213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.23472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54343795776367</t>
+    <t xml:space="preserve">5.54343748092651</t>
   </si>
   <si>
     <t xml:space="preserve">5.63403940200806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79175090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89241981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77161884307861</t>
+    <t xml:space="preserve">5.79175233840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89241886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77161836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7850399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87102508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02923679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17025232315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18400859832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2699933052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32846164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40069055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878135681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26311492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33534145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3834924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33190298080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2321605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25967597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23559999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28375101089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27687215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24935722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16681289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13585758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14617586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09114456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0361156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91229867935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573667526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05331230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00860023498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00516080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10490322113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03267621994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92949390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95701026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90885829925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73001098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85726737976074</t>
   </si>
   <si>
     <t xml:space="preserve">5.78504037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87102508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02923727035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17025184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18400764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26999235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840238571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32846164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40069055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28031158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26311540603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33534288406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38349294662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33190202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23216009140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25967454910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23559951782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30438661575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28375101089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2768726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24935722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16681241989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13585710525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14617586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11866092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0361156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91229820251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0533127784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00859975814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00516033172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10490274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267574310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92949485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95700979232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90885877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73001146316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85726833343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60619258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61651134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249509811401</t>
+    <t xml:space="preserve">5.60619211196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61651086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249557495117</t>
   </si>
   <si>
     <t xml:space="preserve">5.66810178756714</t>
@@ -2339,28 +2339,28 @@
     <t xml:space="preserve">5.71625328063965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77816152572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81255531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80567646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80911636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8779034614563</t>
+    <t xml:space="preserve">5.77816200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81255578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80567598342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80911588668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87790393829346</t>
   </si>
   <si>
     <t xml:space="preserve">5.98108530044556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01547956466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8675856590271</t>
+    <t xml:space="preserve">6.01547908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86758518218994</t>
   </si>
   <si>
     <t xml:space="preserve">5.70593547821045</t>
@@ -2369,160 +2369,160 @@
     <t xml:space="preserve">5.40326881408691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3551173210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37231492996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505710601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0627703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00430059432983</t>
+    <t xml:space="preserve">5.35511827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.372314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06276988983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00430011749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.98366451263428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9492712020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69819593429565</t>
+    <t xml:space="preserve">4.94927167892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69819688796997</t>
   </si>
   <si>
     <t xml:space="preserve">4.58813524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26483345031738</t>
+    <t xml:space="preserve">4.26483297348022</t>
   </si>
   <si>
     <t xml:space="preserve">3.75580501556396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71453285217285</t>
+    <t xml:space="preserve">3.71453309059143</t>
   </si>
   <si>
     <t xml:space="preserve">3.36509156227112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36784315109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08306217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8051598072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91109323501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90283823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25365567207336</t>
+    <t xml:space="preserve">3.36784243583679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092950820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516004562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91109299659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90283799171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25365495681763</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133409500122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53568458557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41599440574646</t>
+    <t xml:space="preserve">3.53568506240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4159939289093</t>
   </si>
   <si>
     <t xml:space="preserve">3.24815249443054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19862508773804</t>
+    <t xml:space="preserve">3.19862532615662</t>
   </si>
   <si>
     <t xml:space="preserve">3.18899512290955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20000076293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14359569549561</t>
+    <t xml:space="preserve">3.20000100135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14359521865845</t>
   </si>
   <si>
     <t xml:space="preserve">3.25778293609619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43938207626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.594153881073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7626838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44969987869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49097299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59759306907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52880573272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48409366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320023536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5460033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68013858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85554718971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01031970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83147120475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6595025062561</t>
+    <t xml:space="preserve">3.43938183784485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59415435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76268339157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44970011711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49097228050232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59759402275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52880620956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096429824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48409390449524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56319952011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54600310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68013906478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85554766654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01031923294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83147168159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65950298309326</t>
   </si>
   <si>
     <t xml:space="preserve">3.60447239875793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64574503898621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68701791763306</t>
+    <t xml:space="preserve">3.64574551582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68701767921448</t>
   </si>
   <si>
     <t xml:space="preserve">3.69045662879944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84866857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745591163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019951820374</t>
+    <t xml:space="preserve">3.84866905212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745686531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.790198802948</t>
   </si>
   <si>
     <t xml:space="preserve">3.70421433448792</t>
@@ -2531,31 +2531,31 @@
     <t xml:space="preserve">3.80739545822144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81427526473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92089462280273</t>
+    <t xml:space="preserve">3.81427454948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92089557647705</t>
   </si>
   <si>
     <t xml:space="preserve">3.95528936386108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03439521789551</t>
+    <t xml:space="preserve">4.03439474105835</t>
   </si>
   <si>
     <t xml:space="preserve">4.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16853094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12037944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08598613739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23731851577759</t>
+    <t xml:space="preserve">4.16853141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12038040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08598566055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2373194694519</t>
   </si>
   <si>
     <t xml:space="preserve">4.2854700088501</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">4.44712114334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65348339080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76010465621948</t>
+    <t xml:space="preserve">4.65348434448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76010417938232</t>
   </si>
   <si>
     <t xml:space="preserve">4.5778169631958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33018255233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34737968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49183320999146</t>
+    <t xml:space="preserve">4.33018207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34737873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4918327331543</t>
   </si>
   <si>
     <t xml:space="preserve">4.44368171691895</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">4.42304515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46775722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45400047302246</t>
+    <t xml:space="preserve">4.46775770187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4539999961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.49527215957642</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">4.30266714096069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29234886169434</t>
+    <t xml:space="preserve">4.29234838485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.33706045150757</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">4.37489366531372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39553022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32330274581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52622652053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41616678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52278757095337</t>
+    <t xml:space="preserve">4.39552974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32330322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52622699737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41616725921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52278709411621</t>
   </si>
   <si>
     <t xml:space="preserve">4.50215101242065</t>
@@ -2630,16 +2630,16 @@
     <t xml:space="preserve">4.31298494338989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41960573196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4711971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53310537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53654432296753</t>
+    <t xml:space="preserve">4.41960620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47119665145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53310632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53654479980469</t>
   </si>
   <si>
     <t xml:space="preserve">4.5571813583374</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">4.61221122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093954086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52966642379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743942260742</t>
+    <t xml:space="preserve">4.57093858718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52966547012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743894577026</t>
   </si>
   <si>
     <t xml:space="preserve">4.40928792953491</t>
@@ -2666,22 +2666,22 @@
     <t xml:space="preserve">4.39209127426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42648458480835</t>
+    <t xml:space="preserve">4.42648506164551</t>
   </si>
   <si>
     <t xml:space="preserve">4.26139450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42992448806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43680286407471</t>
+    <t xml:space="preserve">4.42992401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43680334091187</t>
   </si>
   <si>
     <t xml:space="preserve">4.56062030792236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63628673553467</t>
+    <t xml:space="preserve">4.63628721237183</t>
   </si>
   <si>
     <t xml:space="preserve">4.68443822860718</t>
@@ -2690,31 +2690,31 @@
     <t xml:space="preserve">4.60877180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48839330673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56405973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45055961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59501504898071</t>
+    <t xml:space="preserve">4.48839378356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56406021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45056056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5950140953064</t>
   </si>
   <si>
     <t xml:space="preserve">4.51590871810913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5468635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40240859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2751522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081720352173</t>
+    <t xml:space="preserve">4.54686307907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40240955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27515172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35081768035889</t>
   </si>
   <si>
     <t xml:space="preserve">4.35425758361816</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">4.20636415481567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27859115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50559091567993</t>
+    <t xml:space="preserve">4.2785906791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50559043884277</t>
   </si>
   <si>
     <t xml:space="preserve">4.43336391448975</t>
@@ -2747,61 +2747,61 @@
     <t xml:space="preserve">4.29922723770142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30610609054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16165256500244</t>
+    <t xml:space="preserve">4.31986379623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30610656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16165208816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.03783464431763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98968315124512</t>
+    <t xml:space="preserve">3.98968362808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.03095531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25107622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73259019851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81169462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93207406997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81513452529907</t>
+    <t xml:space="preserve">4.25107574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73258972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81169509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93207359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">4.96646738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20034551620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1934666633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12468004226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22442102432251</t>
+    <t xml:space="preserve">5.20034599304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19346714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12467956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22442150115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.24161815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3791937828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569414138794</t>
+    <t xml:space="preserve">5.37919330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2656946182251</t>
   </si>
   <si>
     <t xml:space="preserve">5.34136009216309</t>
@@ -2810,46 +2810,46 @@
     <t xml:space="preserve">5.23130035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29664850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11092233657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10404300689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04557323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00774049758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00086164474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91831684112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88736248016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89424085617065</t>
+    <t xml:space="preserve">5.2966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15563297271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11092138290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10404253005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04557371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00774097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00086212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91831636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88736152648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89423990249634</t>
   </si>
   <si>
     <t xml:space="preserve">4.89767980575562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8839225769043</t>
+    <t xml:space="preserve">4.88392210006714</t>
   </si>
   <si>
     <t xml:space="preserve">4.8667254447937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76698303222656</t>
+    <t xml:space="preserve">4.7669825553894</t>
   </si>
   <si>
     <t xml:space="preserve">4.83577108383179</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">4.89080142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91487693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85984706878662</t>
+    <t xml:space="preserve">4.91487789154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85984659194946</t>
   </si>
   <si>
     <t xml:space="preserve">4.87016487121582</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">5.05933046340942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03869390487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03181648254395</t>
+    <t xml:space="preserve">5.03869438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03181600570679</t>
   </si>
   <si>
     <t xml:space="preserve">4.71539258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59845399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53998422622681</t>
+    <t xml:space="preserve">4.59845352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53998374938965</t>
   </si>
   <si>
     <t xml:space="preserve">4.61565113067627</t>
@@ -2894,58 +2894,58 @@
     <t xml:space="preserve">4.6706805229187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02837705612183</t>
+    <t xml:space="preserve">5.02837610244751</t>
   </si>
   <si>
     <t xml:space="preserve">5.12811851501465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31728458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25537633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27257204055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2588152885437</t>
+    <t xml:space="preserve">5.31728410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25537538528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27257251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25881576538086</t>
   </si>
   <si>
     <t xml:space="preserve">5.15219354629517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07652854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0902853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14875507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493715286255</t>
+    <t xml:space="preserve">5.07652759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14875459671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493667602539</t>
   </si>
   <si>
     <t xml:space="preserve">5.05245208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9699068069458</t>
+    <t xml:space="preserve">4.96990728378296</t>
   </si>
   <si>
     <t xml:space="preserve">5.13499736785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16251277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14187669754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23817920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29320907592773</t>
+    <t xml:space="preserve">5.16251230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14187622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23817873001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29320859909058</t>
   </si>
   <si>
     <t xml:space="preserve">5.32760286331177</t>
@@ -2960,22 +2960,22 @@
     <t xml:space="preserve">5.33792114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45141983032227</t>
+    <t xml:space="preserve">5.45142078399658</t>
   </si>
   <si>
     <t xml:space="preserve">5.58899593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708673477173</t>
+    <t xml:space="preserve">5.50645017623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708721160889</t>
   </si>
   <si>
     <t xml:space="preserve">5.4445424079895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4823751449585</t>
+    <t xml:space="preserve">5.48237562179565</t>
   </si>
   <si>
     <t xml:space="preserve">5.48925399780273</t>
@@ -2987,46 +2987,46 @@
     <t xml:space="preserve">5.53740453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51952075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55116271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47824811935425</t>
+    <t xml:space="preserve">5.51952028274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5511622428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">5.40258073806763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45898723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41221141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41496324539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36543655395508</t>
+    <t xml:space="preserve">5.45898675918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41221046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.414963722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36543560028076</t>
   </si>
   <si>
     <t xml:space="preserve">5.38332080841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43972635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39020013809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32553911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37644290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39982938766479</t>
+    <t xml:space="preserve">5.43972730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39019918441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32553958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37644147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39982986450195</t>
   </si>
   <si>
     <t xml:space="preserve">5.37506628036499</t>
@@ -3035,43 +3035,43 @@
     <t xml:space="preserve">5.34617567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46036291122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37369060516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43697500228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5140175819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57730102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55528974533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4232177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44247770309448</t>
+    <t xml:space="preserve">5.46036338806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37368965148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43697547912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51401710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57730150222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55529022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42321729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44247817993164</t>
   </si>
   <si>
     <t xml:space="preserve">5.3984546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47484064102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43066644668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42928647994995</t>
+    <t xml:space="preserve">5.47484111785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43066596984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42928600311279</t>
   </si>
   <si>
     <t xml:space="preserve">5.44309091567993</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">5.59493970870972</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58113527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5673303604126</t>
+    <t xml:space="preserve">5.58113574981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56732988357544</t>
   </si>
   <si>
     <t xml:space="preserve">5.57837343215942</t>
@@ -3095,91 +3095,91 @@
     <t xml:space="preserve">5.60046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70813655853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74264669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6377329826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69571161270142</t>
+    <t xml:space="preserve">5.70813608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74264717102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63773345947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69571113586426</t>
   </si>
   <si>
     <t xml:space="preserve">5.66948318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76473522186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7771577835083</t>
+    <t xml:space="preserve">5.76473474502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77715730667114</t>
   </si>
   <si>
     <t xml:space="preserve">5.6750054359436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65291738510132</t>
+    <t xml:space="preserve">5.65291786193848</t>
   </si>
   <si>
     <t xml:space="preserve">5.61288547515869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67914724349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83927822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66120004653931</t>
+    <t xml:space="preserve">5.67914628982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83927774429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66120052337646</t>
   </si>
   <si>
     <t xml:space="preserve">5.79234313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66258096694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66534185409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328809738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68604850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65015745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55352592468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63635301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72746276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66810274124146</t>
+    <t xml:space="preserve">5.66258192062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66534233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68466806411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68604898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65015697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55352544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63635349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72746181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6681022644043</t>
   </si>
   <si>
     <t xml:space="preserve">5.68742895126343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60460233688354</t>
+    <t xml:space="preserve">5.6046028137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.59355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36164426803589</t>
+    <t xml:space="preserve">5.36164474487305</t>
   </si>
   <si>
     <t xml:space="preserve">5.40443801879883</t>
@@ -3188,55 +3188,55 @@
     <t xml:space="preserve">5.57975435256958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62392807006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362451553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81442975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81995153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79924535751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79510259628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73160314559937</t>
+    <t xml:space="preserve">5.62392854690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81995248794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79924583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79510354995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73160266876221</t>
   </si>
   <si>
     <t xml:space="preserve">5.74540853500366</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71503829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75507164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8075270652771</t>
+    <t xml:space="preserve">5.71503734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75507116317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80752754211426</t>
   </si>
   <si>
     <t xml:space="preserve">5.88069105148315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95523595809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96351861953735</t>
+    <t xml:space="preserve">5.95523548126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">6.04910564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03115940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981182098389</t>
+    <t xml:space="preserve">6.0311598777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06981229782104</t>
   </si>
   <si>
     <t xml:space="preserve">6.0325403213501</t>
@@ -3245,10 +3245,10 @@
     <t xml:space="preserve">6.07809495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94695281982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92348480224609</t>
+    <t xml:space="preserve">5.9469518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92348527908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.98284435272217</t>
@@ -3260,16 +3260,16 @@
     <t xml:space="preserve">5.99802875518799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98560523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03668117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05048513412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06705045700073</t>
+    <t xml:space="preserve">5.98560571670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03668165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05048561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06705141067505</t>
   </si>
   <si>
     <t xml:space="preserve">6.06567096710205</t>
@@ -3278,88 +3278,88 @@
     <t xml:space="preserve">6.08775806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09051990509033</t>
+    <t xml:space="preserve">6.09051847457886</t>
   </si>
   <si>
     <t xml:space="preserve">6.0601487159729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04220247268677</t>
+    <t xml:space="preserve">6.04220342636108</t>
   </si>
   <si>
     <t xml:space="preserve">6.03944253921509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01045370101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15677976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19681310653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15125846862793</t>
+    <t xml:space="preserve">6.01045322418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15678071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19681167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15125799179077</t>
   </si>
   <si>
     <t xml:space="preserve">6.20233488082886</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14573669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9593768119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14849805831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34590196609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30034637451172</t>
+    <t xml:space="preserve">6.1457371711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95937633514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14849710464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34590101242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30034685134888</t>
   </si>
   <si>
     <t xml:space="preserve">6.32519435882568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32243347167969</t>
+    <t xml:space="preserve">6.32243299484253</t>
   </si>
   <si>
     <t xml:space="preserve">6.39835834503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45357656478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55711030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57229375839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343637466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690343856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616344451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71585893630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420827865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72000122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245903015137</t>
+    <t xml:space="preserve">6.4535756111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55710935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57229423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343732833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60542345046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585988998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72000217437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245855331421</t>
   </si>
   <si>
     <t xml:space="preserve">6.80697011947632</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">6.827392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70334053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70931911468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561988830566</t>
+    <t xml:space="preserve">6.70334100723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70931768417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62562084197998</t>
   </si>
   <si>
     <t xml:space="preserve">6.61366367340088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56284618377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66149139404297</t>
+    <t xml:space="preserve">6.56284666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66149044036865</t>
   </si>
   <si>
     <t xml:space="preserve">6.60917997360229</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">6.50605154037476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58227634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49708366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55387878417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6824164390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65850162506104</t>
+    <t xml:space="preserve">6.58227682113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49708461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55387926101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68241596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65850114822388</t>
   </si>
   <si>
     <t xml:space="preserve">6.66448068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73771619796753</t>
+    <t xml:space="preserve">6.73771667480469</t>
   </si>
   <si>
     <t xml:space="preserve">6.77657604217529</t>
@@ -3425,25 +3425,25 @@
     <t xml:space="preserve">6.84532880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83187770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74369430541992</t>
+    <t xml:space="preserve">6.8318772315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74369525909424</t>
   </si>
   <si>
     <t xml:space="preserve">6.66298627853394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56434154510498</t>
+    <t xml:space="preserve">6.5643424987793</t>
   </si>
   <si>
     <t xml:space="preserve">6.7086124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58429384231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77614402770996</t>
+    <t xml:space="preserve">6.58429431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7761435508728</t>
   </si>
   <si>
     <t xml:space="preserve">6.68865966796875</t>
@@ -3455,43 +3455,43 @@
     <t xml:space="preserve">6.43848848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32951641082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49374103546143</t>
+    <t xml:space="preserve">6.32951688766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49374055862427</t>
   </si>
   <si>
     <t xml:space="preserve">6.44309186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47685670852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54899406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68405485153198</t>
+    <t xml:space="preserve">6.47685718536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54899311065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68405532836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.62112951278687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56127262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51522779464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50601863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51062345504761</t>
+    <t xml:space="preserve">6.56127214431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51522731781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50601768493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51062297821045</t>
   </si>
   <si>
     <t xml:space="preserve">6.52443599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4446268081665</t>
+    <t xml:space="preserve">6.44462585449219</t>
   </si>
   <si>
     <t xml:space="preserve">6.2451024055481</t>
@@ -3503,31 +3503,31 @@
     <t xml:space="preserve">6.48299646377563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5888991355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65335941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64568614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103458404541</t>
+    <t xml:space="preserve">6.58889818191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65335893630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64568567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103315353394</t>
   </si>
   <si>
     <t xml:space="preserve">6.74391269683838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7945613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85288333892822</t>
+    <t xml:space="preserve">6.79456186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85288429260254</t>
   </si>
   <si>
     <t xml:space="preserve">6.66410303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78688812255859</t>
+    <t xml:space="preserve">6.78688716888428</t>
   </si>
   <si>
     <t xml:space="preserve">6.84981393814087</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">6.97566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10612630844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13221645355225</t>
+    <t xml:space="preserve">7.10612678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13221740722656</t>
   </si>
   <si>
     <t xml:space="preserve">6.99255037307739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96185445785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79763031005859</t>
+    <t xml:space="preserve">6.96185350418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79763078689575</t>
   </si>
   <si>
     <t xml:space="preserve">6.7914924621582</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">6.70554256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40779256820679</t>
+    <t xml:space="preserve">6.40779161453247</t>
   </si>
   <si>
     <t xml:space="preserve">6.41700077056885</t>
@@ -3569,49 +3569,49 @@
     <t xml:space="preserve">6.51829767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46611404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57201480865479</t>
+    <t xml:space="preserve">6.46611356735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57201528549194</t>
   </si>
   <si>
     <t xml:space="preserve">6.67177724838257</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76386547088623</t>
+    <t xml:space="preserve">6.76386499404907</t>
   </si>
   <si>
     <t xml:space="preserve">6.69786834716797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45843982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54438877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69940376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79916477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56894683837891</t>
+    <t xml:space="preserve">6.45844030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54438924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69940328598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79916572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56894588470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.34486484527588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52290058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47225284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38476991653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36328220367432</t>
+    <t xml:space="preserve">6.5229024887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47225332260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38476943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36328268051147</t>
   </si>
   <si>
     <t xml:space="preserve">6.29575157165527</t>
@@ -3623,16 +3623,16 @@
     <t xml:space="preserve">6.28500747680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75089693069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88749408721924</t>
+    <t xml:space="preserve">5.75089740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8874945640564</t>
   </si>
   <si>
     <t xml:space="preserve">5.64960050582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43933296203613</t>
+    <t xml:space="preserve">5.43933200836182</t>
   </si>
   <si>
     <t xml:space="preserve">5.46388959884644</t>
@@ -3644,46 +3644,46 @@
     <t xml:space="preserve">4.98810148239136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92977905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07098007202148</t>
+    <t xml:space="preserve">4.92977809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07098054885864</t>
   </si>
   <si>
     <t xml:space="preserve">5.62657833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29966592788696</t>
+    <t xml:space="preserve">5.29966640472412</t>
   </si>
   <si>
     <t xml:space="preserve">5.41938018798828</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50993347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62811279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92125940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88135480880737</t>
+    <t xml:space="preserve">5.50993299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62811326980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92125988006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88135576248169</t>
   </si>
   <si>
     <t xml:space="preserve">5.86447286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82149744033813</t>
+    <t xml:space="preserve">5.82149839401245</t>
   </si>
   <si>
     <t xml:space="preserve">5.97190856933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90898180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87214612960815</t>
+    <t xml:space="preserve">5.90898132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87214660644531</t>
   </si>
   <si>
     <t xml:space="preserve">5.92586421966553</t>
@@ -3695,16 +3695,16 @@
     <t xml:space="preserve">6.12538862228394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06860065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95195531845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05325317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98879146575928</t>
+    <t xml:space="preserve">6.06860160827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95195579528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05325222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98879098892212</t>
   </si>
   <si>
     <t xml:space="preserve">5.93353843688965</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">5.72787570953369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7155966758728</t>
+    <t xml:space="preserve">5.71559715270996</t>
   </si>
   <si>
     <t xml:space="preserve">5.85679864883423</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">5.77084922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81842803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86293745040894</t>
+    <t xml:space="preserve">5.81842851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86293792724609</t>
   </si>
   <si>
     <t xml:space="preserve">5.7985987663269</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">5.89671611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87098026275635</t>
+    <t xml:space="preserve">5.87098073959351</t>
   </si>
   <si>
     <t xml:space="preserve">5.78090476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6586594581604</t>
+    <t xml:space="preserve">5.65865993499756</t>
   </si>
   <si>
     <t xml:space="preserve">5.56536722183228</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">5.61040496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56375980377197</t>
+    <t xml:space="preserve">5.56375932693481</t>
   </si>
   <si>
     <t xml:space="preserve">5.59271192550659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55732488632202</t>
+    <t xml:space="preserve">5.55732536315918</t>
   </si>
   <si>
     <t xml:space="preserve">5.62166500091553</t>
@@ -3773,19 +3773,19 @@
     <t xml:space="preserve">5.58788633346558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50263643264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56054258346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81146574020386</t>
+    <t xml:space="preserve">5.50263595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56054210662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81146621704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.66348505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7085223197937</t>
+    <t xml:space="preserve">5.70852279663086</t>
   </si>
   <si>
     <t xml:space="preserve">5.74069261550903</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">5.76321125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68922090530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817445755005</t>
+    <t xml:space="preserve">5.68922138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817350387573</t>
   </si>
   <si>
     <t xml:space="preserve">5.89510726928711</t>
@@ -3806,25 +3806,25 @@
     <t xml:space="preserve">5.75516939163208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76803636550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9514045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94175338745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91280078887939</t>
+    <t xml:space="preserve">5.76803684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95140504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94175386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91280126571655</t>
   </si>
   <si>
     <t xml:space="preserve">5.84685277938843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75034379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706541061401</t>
+    <t xml:space="preserve">5.75034427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706588745117</t>
   </si>
   <si>
     <t xml:space="preserve">5.80503177642822</t>
@@ -3842,25 +3842,25 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13107633590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20828294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01043939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225944519043</t>
+    <t xml:space="preserve">5.13107585906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20828247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01043891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225992202759</t>
   </si>
   <si>
     <t xml:space="preserve">5.11820793151855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11981678009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15198612213135</t>
+    <t xml:space="preserve">5.11981582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15198659896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.30157566070557</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">5.14876890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04904270172119</t>
+    <t xml:space="preserve">5.04904317855835</t>
   </si>
   <si>
     <t xml:space="preserve">5.07156181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05386829376221</t>
+    <t xml:space="preserve">5.05386877059937</t>
   </si>
   <si>
     <t xml:space="preserve">4.80294466018677</t>
@@ -3893,37 +3893,37 @@
     <t xml:space="preserve">5.0345664024353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17611312866211</t>
+    <t xml:space="preserve">5.17611360549927</t>
   </si>
   <si>
     <t xml:space="preserve">5.03295850753784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10855722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0377836227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85924100875854</t>
+    <t xml:space="preserve">5.10855674743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03778314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8592414855957</t>
   </si>
   <si>
     <t xml:space="preserve">4.91232109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98631191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12142515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9348406791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01848077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01526498794556</t>
+    <t xml:space="preserve">4.98631143569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12142562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93483972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01848125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0152645111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.96379327774048</t>
@@ -3935,52 +3935,52 @@
     <t xml:space="preserve">5.18737268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21149969100952</t>
+    <t xml:space="preserve">5.21150016784668</t>
   </si>
   <si>
     <t xml:space="preserve">5.15842008590698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45599031448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59432029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50746202468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48976898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46242427825928</t>
+    <t xml:space="preserve">5.45598983764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59432077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50746154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48976850509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">5.50424480438232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5364146232605</t>
+    <t xml:space="preserve">5.53641510009766</t>
   </si>
   <si>
     <t xml:space="preserve">5.56858444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51067924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40291023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44312191009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33374547958374</t>
+    <t xml:space="preserve">5.51067876815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4029107093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44312238693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33374452590942</t>
   </si>
   <si>
     <t xml:space="preserve">5.19219827651978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28388166427612</t>
+    <t xml:space="preserve">5.28388214111328</t>
   </si>
   <si>
     <t xml:space="preserve">5.22919321060181</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">5.04100036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14394378662109</t>
+    <t xml:space="preserve">5.14394283294678</t>
   </si>
   <si>
     <t xml:space="preserve">5.12946701049805</t>
@@ -4001,55 +4001,55 @@
     <t xml:space="preserve">5.00883102416992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24688673019409</t>
+    <t xml:space="preserve">5.24688720703125</t>
   </si>
   <si>
     <t xml:space="preserve">5.08121252059937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18254709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19863271713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31765985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53963184356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41577768325806</t>
+    <t xml:space="preserve">5.11659908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1825475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19863319396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31766033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53963136672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41577816009521</t>
   </si>
   <si>
     <t xml:space="preserve">5.49459362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28870725631714</t>
+    <t xml:space="preserve">5.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">5.25653791427612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3305287361145</t>
+    <t xml:space="preserve">5.33052778244019</t>
   </si>
   <si>
     <t xml:space="preserve">5.08925533294678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15037679672241</t>
+    <t xml:space="preserve">5.15037727355957</t>
   </si>
   <si>
     <t xml:space="preserve">5.18898153305054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99596261978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1600284576416</t>
+    <t xml:space="preserve">4.99596309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16002798080444</t>
   </si>
   <si>
     <t xml:space="preserve">5.08603763580322</t>
@@ -4061,28 +4061,28 @@
     <t xml:space="preserve">4.9879207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20345735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45920753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39808464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37878322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32409429550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33696222305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28709840774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14555168151855</t>
+    <t xml:space="preserve">5.20345783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45920705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39808416366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37878274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32409381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33696174621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28709983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14555215835571</t>
   </si>
   <si>
     <t xml:space="preserve">5.30961751937866</t>
@@ -4091,16 +4091,16 @@
     <t xml:space="preserve">5.35626411437988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47368383407593</t>
+    <t xml:space="preserve">5.47368335723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.54284906387329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61362218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64579153060913</t>
+    <t xml:space="preserve">5.61362171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64579248428345</t>
   </si>
   <si>
     <t xml:space="preserve">5.67152738571167</t>
@@ -4118,28 +4118,28 @@
     <t xml:space="preserve">6.04308843612671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11707925796509</t>
+    <t xml:space="preserve">6.11707878112793</t>
   </si>
   <si>
     <t xml:space="preserve">6.09616804122925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02539491653442</t>
+    <t xml:space="preserve">6.02539443969727</t>
   </si>
   <si>
     <t xml:space="preserve">6.06560659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08651733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21519708633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27149343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24897527694702</t>
+    <t xml:space="preserve">6.08651685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21519660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27149391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24897432327271</t>
   </si>
   <si>
     <t xml:space="preserve">6.26023387908936</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">6.43716716766357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35996007919312</t>
+    <t xml:space="preserve">6.35996103286743</t>
   </si>
   <si>
     <t xml:space="preserve">6.45968675613403</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">6.56108474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47820091247559</t>
+    <t xml:space="preserve">6.47820138931274</t>
   </si>
   <si>
     <t xml:space="preserve">6.49312019348145</t>
@@ -4184,13 +4184,13 @@
     <t xml:space="preserve">6.52958917617798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52461671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67878007888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53124761581421</t>
+    <t xml:space="preserve">6.52461624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67877960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53124713897705</t>
   </si>
   <si>
     <t xml:space="preserve">6.61413097381592</t>
@@ -4199,16 +4199,16 @@
     <t xml:space="preserve">6.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51301240921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47488594055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46825551986694</t>
+    <t xml:space="preserve">6.51301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47488641738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52627420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46825504302979</t>
   </si>
   <si>
     <t xml:space="preserve">6.54616546630859</t>
@@ -4217,10 +4217,10 @@
     <t xml:space="preserve">6.54948139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4400749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39200210571289</t>
+    <t xml:space="preserve">6.44007444381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39200162887573</t>
   </si>
   <si>
     <t xml:space="preserve">6.55777025222778</t>
@@ -4247,13 +4247,13 @@
     <t xml:space="preserve">6.64728450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73514175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86609840393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87935924530029</t>
+    <t xml:space="preserve">6.73514127731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86609792709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87935876846313</t>
   </si>
   <si>
     <t xml:space="preserve">7.00202703475952</t>
@@ -4268,19 +4268,19 @@
     <t xml:space="preserve">7.11806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10646152496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97218894958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98545074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07496500015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13464117050171</t>
+    <t xml:space="preserve">7.10646200180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9721884727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98545026779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07496547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13464164733887</t>
   </si>
   <si>
     <t xml:space="preserve">7.19100189208984</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">7.40484237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45788812637329</t>
+    <t xml:space="preserve">7.45788764953613</t>
   </si>
   <si>
     <t xml:space="preserve">7.49767255783081</t>
@@ -4313,13 +4313,13 @@
     <t xml:space="preserve">7.540771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243040084839</t>
+    <t xml:space="preserve">7.54243087768555</t>
   </si>
   <si>
     <t xml:space="preserve">7.47446489334106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58884477615356</t>
+    <t xml:space="preserve">7.58884525299072</t>
   </si>
   <si>
     <t xml:space="preserve">7.6203408241272</t>
@@ -4337,10 +4337,10 @@
     <t xml:space="preserve">7.52585220336914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46286010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49435615539551</t>
+    <t xml:space="preserve">7.46286058425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49435710906982</t>
   </si>
   <si>
     <t xml:space="preserve">7.559006690979</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">7.59713363647461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60210657119751</t>
+    <t xml:space="preserve">7.60210609436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.66675567626953</t>
@@ -4361,10 +4361,10 @@
     <t xml:space="preserve">7.71814441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72643136978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77781915664673</t>
+    <t xml:space="preserve">7.72643041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77782011032104</t>
   </si>
   <si>
     <t xml:space="preserve">7.45457315444946</t>
@@ -4382,10 +4382,10 @@
     <t xml:space="preserve">6.73348331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51135492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76166439056396</t>
+    <t xml:space="preserve">6.51135444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76166391372681</t>
   </si>
   <si>
     <t xml:space="preserve">7.00037050247192</t>
@@ -4406,10 +4406,10 @@
     <t xml:space="preserve">6.83460187911987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93406248092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92743110656738</t>
+    <t xml:space="preserve">6.93406295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92743158340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.01363134384155</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">6.89262056350708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05341529846191</t>
+    <t xml:space="preserve">7.05341577529907</t>
   </si>
   <si>
     <t xml:space="preserve">7.06999158859253</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">7.07993793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15950632095337</t>
+    <t xml:space="preserve">7.15950584411621</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">7.1429295539856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16344022750854</t>
+    <t xml:space="preserve">7.1634407043457</t>
   </si>
   <si>
     <t xml:space="preserve">7.05917692184448</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">7.01473665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05746793746948</t>
+    <t xml:space="preserve">7.05746841430664</t>
   </si>
   <si>
     <t xml:space="preserve">7.00277233123779</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">6.72245645523071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92414712905884</t>
+    <t xml:space="preserve">6.92414665222168</t>
   </si>
   <si>
     <t xml:space="preserve">6.92585611343384</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">6.92072772979736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77031517028809</t>
+    <t xml:space="preserve">6.77031469345093</t>
   </si>
   <si>
     <t xml:space="preserve">6.65921401977539</t>
@@ -4508,19 +4508,19 @@
     <t xml:space="preserve">6.93782091140747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74638605117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86774158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86261415481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79082584381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73100137710571</t>
+    <t xml:space="preserve">6.74638557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86774206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86261367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79082536697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73100185394287</t>
   </si>
   <si>
     <t xml:space="preserve">6.84893989562988</t>
@@ -4529,19 +4529,19 @@
     <t xml:space="preserve">7.03011989593506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96858739852905</t>
+    <t xml:space="preserve">6.96858692169189</t>
   </si>
   <si>
     <t xml:space="preserve">6.98397016525269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00619077682495</t>
+    <t xml:space="preserve">7.00619029998779</t>
   </si>
   <si>
     <t xml:space="preserve">6.99422597885132</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99593496322632</t>
+    <t xml:space="preserve">6.99593448638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.02328300476074</t>
@@ -4550,10 +4550,10 @@
     <t xml:space="preserve">7.06259536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09678030014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12583780288696</t>
+    <t xml:space="preserve">7.09677982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1258373260498</t>
   </si>
   <si>
     <t xml:space="preserve">7.14634895324707</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">7.04208469390869</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98226118087769</t>
+    <t xml:space="preserve">6.98226070404053</t>
   </si>
   <si>
     <t xml:space="preserve">6.87116003036499</t>
@@ -4583,22 +4583,22 @@
     <t xml:space="preserve">6.97029638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07797861099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09165287017822</t>
+    <t xml:space="preserve">7.07797813415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09165334701538</t>
   </si>
   <si>
     <t xml:space="preserve">6.96345901489258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90534496307373</t>
+    <t xml:space="preserve">6.90534448623657</t>
   </si>
   <si>
     <t xml:space="preserve">6.72587442398071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84039306640625</t>
+    <t xml:space="preserve">6.84039354324341</t>
   </si>
   <si>
     <t xml:space="preserve">6.88825273513794</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">7.12925624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14976739883423</t>
+    <t xml:space="preserve">7.14976692199707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30530834197998</t>
@@ -4631,22 +4631,22 @@
     <t xml:space="preserve">7.38393354415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38564300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41982793807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44033908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46768617630005</t>
+    <t xml:space="preserve">7.38564252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41982746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44033861160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46768522262573</t>
   </si>
   <si>
     <t xml:space="preserve">7.57536888122559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55485773086548</t>
+    <t xml:space="preserve">7.55485820770264</t>
   </si>
   <si>
     <t xml:space="preserve">7.27112340927124</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">7.20788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19249773025513</t>
+    <t xml:space="preserve">7.19249820709229</t>
   </si>
   <si>
     <t xml:space="preserve">6.76347780227661</t>
@@ -4679,16 +4679,16 @@
     <t xml:space="preserve">6.97200536727905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91047334671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92756462097168</t>
+    <t xml:space="preserve">6.91047286987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92756509780884</t>
   </si>
   <si>
     <t xml:space="preserve">6.97371482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95662260055542</t>
+    <t xml:space="preserve">6.95662307739258</t>
   </si>
   <si>
     <t xml:space="preserve">6.9497857093811</t>
@@ -4700,10 +4700,10 @@
     <t xml:space="preserve">7.15318536758423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17027854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21300888061523</t>
+    <t xml:space="preserve">7.17027807235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21300840377808</t>
   </si>
   <si>
     <t xml:space="preserve">7.19078874588013</t>
@@ -4712,13 +4712,13 @@
     <t xml:space="preserve">7.03695726394653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17882394790649</t>
+    <t xml:space="preserve">7.17882347106934</t>
   </si>
   <si>
     <t xml:space="preserve">7.18736982345581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16856813430786</t>
+    <t xml:space="preserve">7.1685676574707</t>
   </si>
   <si>
     <t xml:space="preserve">7.22497367858887</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">7.08139705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11558198928833</t>
+    <t xml:space="preserve">7.11558246612549</t>
   </si>
   <si>
     <t xml:space="preserve">7.1993350982666</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">7.04037523269653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0284104347229</t>
+    <t xml:space="preserve">7.02841091156006</t>
   </si>
   <si>
     <t xml:space="preserve">6.97884273529053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87799739837646</t>
+    <t xml:space="preserve">6.87799692153931</t>
   </si>
   <si>
     <t xml:space="preserve">6.83697509765625</t>
@@ -4754,13 +4754,13 @@
     <t xml:space="preserve">6.8916711807251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76860523223877</t>
+    <t xml:space="preserve">6.76860570907593</t>
   </si>
   <si>
     <t xml:space="preserve">6.86090421676636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88312482833862</t>
+    <t xml:space="preserve">6.88312530517578</t>
   </si>
   <si>
     <t xml:space="preserve">6.76518726348877</t>
@@ -4790,25 +4790,25 @@
     <t xml:space="preserve">6.48999834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49854516983032</t>
+    <t xml:space="preserve">6.49854469299316</t>
   </si>
   <si>
     <t xml:space="preserve">6.49341726303101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53443956375122</t>
+    <t xml:space="preserve">6.53443908691406</t>
   </si>
   <si>
     <t xml:space="preserve">6.58571624755859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61819171905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74980354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88483333587646</t>
+    <t xml:space="preserve">6.61819124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74980401992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88483381271362</t>
   </si>
   <si>
     <t xml:space="preserve">6.80449962615967</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">7.00789928436279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.990807056427</t>
+    <t xml:space="preserve">6.99080753326416</t>
   </si>
   <si>
     <t xml:space="preserve">7.16685914993286</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">7.17198705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1942081451416</t>
+    <t xml:space="preserve">7.19420766830444</t>
   </si>
   <si>
     <t xml:space="preserve">7.29675436019897</t>
@@ -6003,6 +6003,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.1299991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -28381,7 +28384,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28407,7 +28410,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G849" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28433,7 +28436,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G850" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28459,7 +28462,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28485,7 +28488,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28511,7 +28514,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G853" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28537,7 +28540,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G854" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28563,7 +28566,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28589,7 +28592,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G856" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28615,7 +28618,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G857" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28641,7 +28644,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G858" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28667,7 +28670,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G859" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28693,7 +28696,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G860" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28719,7 +28722,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28745,7 +28748,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G862" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28771,7 +28774,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28797,7 +28800,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28823,7 +28826,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G865" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28849,7 +28852,7 @@
         <v>6</v>
       </c>
       <c r="G866" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28875,7 +28878,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G867" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28901,7 +28904,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G868" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28927,7 +28930,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G869" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28953,7 +28956,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G870" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28979,7 +28982,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G871" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29005,7 +29008,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G872" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29031,7 +29034,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29057,7 +29060,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G874" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29083,7 +29086,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29109,7 +29112,7 @@
         <v>6.125</v>
       </c>
       <c r="G876" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29135,7 +29138,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G877" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -29161,7 +29164,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G878" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -29187,7 +29190,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29213,7 +29216,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -29239,7 +29242,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G881" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -29265,7 +29268,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G882" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -29291,7 +29294,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G883" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -29317,7 +29320,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G884" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -29343,7 +29346,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G885" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -29369,7 +29372,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G886" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29395,7 +29398,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G887" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29421,7 +29424,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G888" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -29447,7 +29450,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G889" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -29473,7 +29476,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G890" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -29499,7 +29502,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G891" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29525,7 +29528,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29551,7 +29554,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29577,7 +29580,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G894" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29603,7 +29606,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29629,7 +29632,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G896" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29655,7 +29658,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G897" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29681,7 +29684,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G898" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29707,7 +29710,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29733,7 +29736,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G900" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29759,7 +29762,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G901" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29785,7 +29788,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G902" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29811,7 +29814,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29837,7 +29840,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29863,7 +29866,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G905" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29889,7 +29892,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29915,7 +29918,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G907" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29941,7 +29944,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G908" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29967,7 +29970,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G909" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30019,7 +30022,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G911" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -30045,7 +30048,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G912" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -30071,7 +30074,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -30097,7 +30100,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G914" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -30123,7 +30126,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G915" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -30149,7 +30152,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G916" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -30175,7 +30178,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G917" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -30201,7 +30204,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G918" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30227,7 +30230,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G919" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30253,7 +30256,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G920" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30279,7 +30282,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30305,7 +30308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30357,7 +30360,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G924" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30383,7 +30386,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30409,7 +30412,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G926" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30435,7 +30438,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G927" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30461,7 +30464,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G928" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30487,7 +30490,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G929" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30513,7 +30516,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G930" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30539,7 +30542,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G931" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30565,7 +30568,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30591,7 +30594,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G933" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30617,7 +30620,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G934" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30643,7 +30646,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30669,7 +30672,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G936" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30695,7 +30698,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G937" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30721,7 +30724,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G938" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30747,7 +30750,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30773,7 +30776,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G940" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30799,7 +30802,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G941" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30825,7 +30828,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G942" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30851,7 +30854,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G943" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30877,7 +30880,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G944" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30903,7 +30906,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30929,7 +30932,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G946" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30955,7 +30958,7 @@
         <v>7</v>
       </c>
       <c r="G947" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30981,7 +30984,7 @@
         <v>6.875</v>
       </c>
       <c r="G948" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31007,7 +31010,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31033,7 +31036,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G950" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31059,7 +31062,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G951" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31085,7 +31088,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31111,7 +31114,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G953" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31137,7 +31140,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G954" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31163,7 +31166,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31189,7 +31192,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G956" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31215,7 +31218,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G957" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31241,7 +31244,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G958" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31267,7 +31270,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G959" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31293,7 +31296,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G960" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31319,7 +31322,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G961" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31345,7 +31348,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G962" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31371,7 +31374,7 @@
         <v>7.25</v>
       </c>
       <c r="G963" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31397,7 +31400,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G964" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31423,7 +31426,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G965" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31449,7 +31452,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31475,7 +31478,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G967" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31501,7 +31504,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G968" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31527,7 +31530,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G969" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31553,7 +31556,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G970" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31579,7 +31582,7 @@
         <v>7.625</v>
       </c>
       <c r="G971" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31605,7 +31608,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G972" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31631,7 +31634,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G973" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31657,7 +31660,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31683,7 +31686,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G975" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31709,7 +31712,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G976" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31735,7 +31738,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G977" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31761,7 +31764,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G978" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31787,7 +31790,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G979" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31813,7 +31816,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G980" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31839,7 +31842,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G981" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31865,7 +31868,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G982" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31891,7 +31894,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G983" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31917,7 +31920,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G984" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31943,7 +31946,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G985" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31969,7 +31972,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G986" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31995,7 +31998,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G987" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32021,7 +32024,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G988" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32047,7 +32050,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G989" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32073,7 +32076,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G990" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32099,7 +32102,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G991" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32125,7 +32128,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G992" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -32151,7 +32154,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G993" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -32177,7 +32180,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32203,7 +32206,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G995" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32229,7 +32232,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G996" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32255,7 +32258,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G997" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32281,7 +32284,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G998" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32307,7 +32310,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G999" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32333,7 +32336,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32359,7 +32362,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1001" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -32385,7 +32388,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32411,7 +32414,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G1003" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32437,7 +32440,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1004" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -32463,7 +32466,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1005" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32489,7 +32492,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1006" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32515,7 +32518,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1007" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32541,7 +32544,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32567,7 +32570,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G1009" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32593,7 +32596,7 @@
         <v>9.125</v>
       </c>
       <c r="G1010" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32619,7 +32622,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32645,7 +32648,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G1012" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32671,7 +32674,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1013" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32697,7 +32700,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1014" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32723,7 +32726,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1015" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32749,7 +32752,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G1016" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32775,7 +32778,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G1017" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32801,7 +32804,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1018" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32827,7 +32830,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1019" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32853,7 +32856,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1020" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32879,7 +32882,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G1021" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32905,7 +32908,7 @@
         <v>9</v>
       </c>
       <c r="G1022" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32931,7 +32934,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1023" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32957,7 +32960,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1024" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32983,7 +32986,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1025" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -33009,7 +33012,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1026" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -33035,7 +33038,7 @@
         <v>8.875</v>
       </c>
       <c r="G1027" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -33061,7 +33064,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1028" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -33087,7 +33090,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1029" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -33113,7 +33116,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1030" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -33139,7 +33142,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1031" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -33165,7 +33168,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1032" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -33191,7 +33194,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33217,7 +33220,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1034" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33243,7 +33246,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1035" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33269,7 +33272,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1036" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33373,7 +33376,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33529,7 +33532,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1046" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -71081,7 +71084,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6497800926</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>822568</v>
@@ -71102,6 +71105,32 @@
         <v>1986</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494675926</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>2068568</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>16.5900001525879</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>16.0599994659424</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="1998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1999">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,103 +38,103 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7844672203064</t>
+    <t xml:space="preserve">3.78446674346924</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277401924133</t>
+    <t xml:space="preserve">3.73277425765991</t>
   </si>
   <si>
     <t xml:space="preserve">3.49607491493225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4144549369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901327133179</t>
+    <t xml:space="preserve">3.41445446014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901398658752</t>
   </si>
   <si>
     <t xml:space="preserve">3.43349885940552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53144383430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658223152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937604904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29202437400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157608985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040344238281</t>
+    <t xml:space="preserve">3.53144288063049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688478469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658246994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2920241355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040320396423</t>
   </si>
   <si>
     <t xml:space="preserve">3.41989588737488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.428058385849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276173591614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22672748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13966631889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18863844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30562734603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89208388328552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1559898853302</t>
+    <t xml:space="preserve">3.42805862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077874183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276125907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2267279624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13966584205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18863773345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30562663078308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03083848953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89208340644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15599012374878</t>
   </si>
   <si>
     <t xml:space="preserve">3.25393390655518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3137891292572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40357112884521</t>
+    <t xml:space="preserve">3.31378936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40357160568237</t>
   </si>
   <si>
     <t xml:space="preserve">3.36548280715942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36820244789124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46614742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43622016906738</t>
+    <t xml:space="preserve">3.36820316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46614718437195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43621945381165</t>
   </si>
   <si>
     <t xml:space="preserve">3.36004137992859</t>
@@ -143,73 +143,73 @@
     <t xml:space="preserve">3.49063372612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56681275367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6919641494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71100926399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61850595474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652200698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380188941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79262828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76542210578918</t>
+    <t xml:space="preserve">3.56681251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409192085266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69196367263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71100878715515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61850500106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652272224426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380165100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623269081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79262900352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76542329788208</t>
   </si>
   <si>
     <t xml:space="preserve">3.70284652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75181937217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72189092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69468545913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439518928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8660876750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71373057365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63482999801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54232692718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74637746810913</t>
+    <t xml:space="preserve">3.75181865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72189116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69468474388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387463569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81439423561096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84432172775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86608743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71372818946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54232621192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74637842178345</t>
   </si>
   <si>
     <t xml:space="preserve">3.77630472183228</t>
@@ -218,115 +218,115 @@
     <t xml:space="preserve">3.73821544647217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87969136238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91778063774109</t>
+    <t xml:space="preserve">3.87969064712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91778016090393</t>
   </si>
   <si>
     <t xml:space="preserve">3.85248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94407796859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88579034805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94962954521179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97460865974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9662823677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88023948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92464828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8885669708252</t>
+    <t xml:space="preserve">3.94407725334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88579082489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9496283531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97460913658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96628260612488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88023972511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92464923858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88856625556946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00236415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98848700523376</t>
+    <t xml:space="preserve">3.9884877204895</t>
   </si>
   <si>
     <t xml:space="preserve">4.04122257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93020009994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07730484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99681305885315</t>
+    <t xml:space="preserve">3.93019986152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07730531692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99681282043457</t>
   </si>
   <si>
     <t xml:space="preserve">3.96905827522278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0606517791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742466926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93575048446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95240497589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9190981388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130253791809</t>
+    <t xml:space="preserve">4.06065082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742371559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93575072288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92187333106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95240473747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91909766197205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130182266235</t>
   </si>
   <si>
     <t xml:space="preserve">4.08008003234863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29102325439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23551177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16334819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18832778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21608352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18277740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559198379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15502119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03289604187012</t>
+    <t xml:space="preserve">4.29102373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23551225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1633472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18832731246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21608304977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18277645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15502071380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03289556503296</t>
   </si>
   <si>
     <t xml:space="preserve">4.0523247718811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09673452377319</t>
+    <t xml:space="preserve">4.09673404693604</t>
   </si>
   <si>
     <t xml:space="preserve">4.06342744827271</t>
@@ -335,130 +335,130 @@
     <t xml:space="preserve">3.69427704811096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5305187702179</t>
+    <t xml:space="preserve">3.53051853179932</t>
   </si>
   <si>
     <t xml:space="preserve">3.55272316932678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48888540267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60268330574036</t>
+    <t xml:space="preserve">3.48888516426086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60268259048462</t>
   </si>
   <si>
     <t xml:space="preserve">3.78587126731873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82472848892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8052990436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685339927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13916325569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.269615650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23630833625793</t>
+    <t xml:space="preserve">3.8247287273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80529975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288262367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13916420936584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26961588859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23630857467651</t>
   </si>
   <si>
     <t xml:space="preserve">3.40561842918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4139449596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463510513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1919002532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410393714905</t>
+    <t xml:space="preserve">3.41394519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904509544373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463534355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19189977645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410441398621</t>
   </si>
   <si>
     <t xml:space="preserve">3.39174056053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47778367996216</t>
+    <t xml:space="preserve">3.47778344154358</t>
   </si>
   <si>
     <t xml:space="preserve">3.59713244438171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49721217155457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941561698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53884530067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55827450752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5416214466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.635990858078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58047842979431</t>
+    <t xml:space="preserve">3.4972128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941633224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5388457775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55827403068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5416202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386475563049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63598990440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58047866821289</t>
   </si>
   <si>
     <t xml:space="preserve">3.64154100418091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39451551437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34455609321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949605941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5471715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56937623023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46945643424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116952896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280313491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231135368347</t>
+    <t xml:space="preserve">3.3945152759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34455561637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4194962978363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54717183113098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56937599182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46945595741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41116905212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280265808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231063842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.48055863380432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51664066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.450026512146</t>
+    <t xml:space="preserve">3.51664090156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45002698898315</t>
   </si>
   <si>
     <t xml:space="preserve">3.47500777244568</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">3.51109004020691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56660079956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58325386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994702339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215285301208</t>
+    <t xml:space="preserve">3.56660127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58325409889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994750022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215213775635</t>
   </si>
   <si>
     <t xml:space="preserve">3.65264320373535</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">3.59990859031677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49166035652161</t>
+    <t xml:space="preserve">3.49166107177734</t>
   </si>
   <si>
     <t xml:space="preserve">3.52219176292419</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.50831460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31402444839478</t>
+    <t xml:space="preserve">3.31402468681335</t>
   </si>
   <si>
     <t xml:space="preserve">3.37786293029785</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">3.30847334861755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36120915412903</t>
+    <t xml:space="preserve">3.36120963096619</t>
   </si>
   <si>
     <t xml:space="preserve">3.38896465301514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29737162590027</t>
+    <t xml:space="preserve">3.29737091064453</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745087623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23075747489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29181981086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26684021949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27516627311707</t>
+    <t xml:space="preserve">3.23075795173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29182076454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26684045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27516651153564</t>
   </si>
   <si>
     <t xml:space="preserve">3.43337416648865</t>
@@ -542,76 +542,76 @@
     <t xml:space="preserve">3.4611291885376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32235169410706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38618922233582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43059778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43614959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50276279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56382608413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398458480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33900427818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835375785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54439663887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42227172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38341403007507</t>
+    <t xml:space="preserve">3.32235145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38618946075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43059754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43614935874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50276303291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382536888123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398530006409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33900475502014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5443959236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42227244377136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38341331481934</t>
   </si>
   <si>
     <t xml:space="preserve">3.30014705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2830331325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37145495414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39142155647278</t>
+    <t xml:space="preserve">3.28303289413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37145471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3914213180542</t>
   </si>
   <si>
     <t xml:space="preserve">3.37715983390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41424036026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45702481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48554825782776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118562698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73370122909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930448532104</t>
+    <t xml:space="preserve">3.41424012184143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45702576637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48554801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118586540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256031990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73370146751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79930472373962</t>
   </si>
   <si>
     <t xml:space="preserve">4.09309482574463</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">3.95047855377197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934314250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95333051681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93906927108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93051195144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635113716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92480683326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90484070777893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93621611595154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9419207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92195463180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8962836265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477343559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96473979949951</t>
+    <t xml:space="preserve">3.89343047142029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95333027839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93906855583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93051171302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635209083557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92480731010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90484046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93621683120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94192123413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92195510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89628338813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96474027633667</t>
   </si>
   <si>
     <t xml:space="preserve">4.10735559463501</t>
@@ -665,40 +665,40 @@
     <t xml:space="preserve">4.12447071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04175186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2442684173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15014123916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30131435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574449539185</t>
+    <t xml:space="preserve">4.04175329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07883358001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15014171600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30131530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.215744972229</t>
   </si>
   <si>
     <t xml:space="preserve">4.20433568954468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26708698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21289300918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20718765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09879922866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23571157455444</t>
+    <t xml:space="preserve">4.26708650588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21289253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20718717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09880018234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2357120513916</t>
   </si>
   <si>
     <t xml:space="preserve">4.18151664733887</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">4.17010736465454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1758131980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03319549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03889989852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08453702926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07027578353882</t>
+    <t xml:space="preserve">4.17581224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03319597244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03890037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08453798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07027626037598</t>
   </si>
   <si>
     <t xml:space="preserve">3.97044444084167</t>
@@ -728,109 +728,109 @@
     <t xml:space="preserve">3.99326300621033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98185324668884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05886697769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11306047439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06171894073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04745674133301</t>
+    <t xml:space="preserve">3.98185348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05886650085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11306095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06171941757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04745721817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.02749109268188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75651979446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672161102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6110508441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51977586746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688979148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386988639832</t>
+    <t xml:space="preserve">3.75651955604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672232627869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105012893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51977610588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53689026832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692461967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386940956116</t>
   </si>
   <si>
     <t xml:space="preserve">3.68235850334167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64242649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65098357200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71943926811218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73084902763367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81641888618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78789496421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81071448326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7679295539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7821900844574</t>
+    <t xml:space="preserve">3.64242625236511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6509838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71943950653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73084878921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81641864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7878942489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81071400642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779334068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76792788505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78219056129456</t>
   </si>
   <si>
     <t xml:space="preserve">3.80215668678284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83353209495544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064625740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90769338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91624999046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94762587547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97614860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92765951156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89057993888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349869728088</t>
+    <t xml:space="preserve">3.83353161811829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064744949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9076931476593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9162495136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94762682914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9761483669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92766046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89057970046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349941253662</t>
   </si>
   <si>
     <t xml:space="preserve">3.8221230506897</t>
@@ -839,121 +839,121 @@
     <t xml:space="preserve">3.87346529960632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10278272628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10869407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17076778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11460590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15303230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12938499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10573720932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16485643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23579740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875331878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919466018677</t>
+    <t xml:space="preserve">4.10278177261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10869359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17076826095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11460638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15303325653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12938547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10573816299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23579692840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875427246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919513702393</t>
   </si>
   <si>
     <t xml:space="preserve">4.34516525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35107803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36290073394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35994529724121</t>
+    <t xml:space="preserve">4.35107755661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36290121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35994434356689</t>
   </si>
   <si>
     <t xml:space="preserve">4.39837169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2890043258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30082750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37176847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51956272125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46931314468384</t>
+    <t xml:space="preserve">4.28900337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30082702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3717679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340227127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51956367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46931266784668</t>
   </si>
   <si>
     <t xml:space="preserve">4.47522497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45453357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36881303787231</t>
+    <t xml:space="preserve">4.45453405380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36881351470947</t>
   </si>
   <si>
     <t xml:space="preserve">4.33334255218506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41315078735352</t>
+    <t xml:space="preserve">4.41315031051636</t>
   </si>
   <si>
     <t xml:space="preserve">4.30673885345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41906213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43384265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38654756546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30969476699829</t>
+    <t xml:space="preserve">4.41906261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43384218215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38654851913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30969429016113</t>
   </si>
   <si>
     <t xml:space="preserve">4.286048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31856250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39245986938477</t>
+    <t xml:space="preserve">4.31856203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39246034622192</t>
   </si>
   <si>
     <t xml:space="preserve">4.29491567611694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33629846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25353288650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3244743347168</t>
+    <t xml:space="preserve">4.3362979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25353336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32447385787964</t>
   </si>
   <si>
     <t xml:space="preserve">4.37472438812256</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">4.3274302482605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33925437927246</t>
+    <t xml:space="preserve">4.3392539024353</t>
   </si>
   <si>
     <t xml:space="preserve">4.38063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49296092987061</t>
+    <t xml:space="preserve">4.49296045303345</t>
   </si>
   <si>
     <t xml:space="preserve">4.37768077850342</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">4.40723943710327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38950395584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31560659408569</t>
+    <t xml:space="preserve">4.38950443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31560754776001</t>
   </si>
   <si>
     <t xml:space="preserve">4.27126741409302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21510648727417</t>
+    <t xml:space="preserve">4.21510601043701</t>
   </si>
   <si>
     <t xml:space="preserve">4.342209815979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32151889801025</t>
+    <t xml:space="preserve">4.3215184211731</t>
   </si>
   <si>
     <t xml:space="preserve">4.25648880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28309106826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057744979858</t>
+    <t xml:space="preserve">4.28309154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057697296143</t>
   </si>
   <si>
     <t xml:space="preserve">4.23284149169922</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">4.16190004348755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19737148284912</t>
+    <t xml:space="preserve">4.19737005233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.24170923233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1796350479126</t>
+    <t xml:space="preserve">4.17963552474976</t>
   </si>
   <si>
     <t xml:space="preserve">4.22397375106812</t>
@@ -1028,25 +1028,25 @@
     <t xml:space="preserve">4.26831245422363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29195976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35403299331665</t>
+    <t xml:space="preserve">4.29195928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35403347015381</t>
   </si>
   <si>
     <t xml:space="preserve">4.43679857254028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42201900482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26535654067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18850326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17372369766235</t>
+    <t xml:space="preserve">4.42201852798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26535606384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1885027885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17372417449951</t>
   </si>
   <si>
     <t xml:space="preserve">4.16781234741211</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">4.24762105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21806192398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28013563156128</t>
+    <t xml:space="preserve">4.21806240081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28013610839844</t>
   </si>
   <si>
     <t xml:space="preserve">4.23866891860962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13528680801392</t>
+    <t xml:space="preserve">4.13528633117676</t>
   </si>
   <si>
     <t xml:space="preserve">4.13832664489746</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">4.1656928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25083112716675</t>
+    <t xml:space="preserve">4.25083065032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.25995349884033</t>
@@ -1088,40 +1088,40 @@
     <t xml:space="preserve">4.36637592315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36941766738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509229660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32988882064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38157892227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3359694480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39678192138672</t>
+    <t xml:space="preserve">4.36941623687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32988834381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38157987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33596849441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39678287506104</t>
   </si>
   <si>
     <t xml:space="preserve">4.44543266296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5001654624939</t>
+    <t xml:space="preserve">4.50016450881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.54577445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4393515586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48800182342529</t>
+    <t xml:space="preserve">4.43935203552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48800230026245</t>
   </si>
   <si>
     <t xml:space="preserve">4.51232767105103</t>
@@ -1133,25 +1133,25 @@
     <t xml:space="preserve">4.46367692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38766098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30860424041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29340028762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3724570274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46063709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45759582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718935012817</t>
+    <t xml:space="preserve">4.38766050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30860376358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29340076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37245798110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46063661575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45759630203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718982696533</t>
   </si>
   <si>
     <t xml:space="preserve">4.55489635467529</t>
@@ -1163,64 +1163,64 @@
     <t xml:space="preserve">4.62179136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70084714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72517347335815</t>
+    <t xml:space="preserve">4.70084810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.725172996521</t>
   </si>
   <si>
     <t xml:space="preserve">4.74037599563599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73429536819458</t>
+    <t xml:space="preserve">4.73429489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.77078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81639242172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76470136642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80423021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83463668823242</t>
+    <t xml:space="preserve">4.81639337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76470184326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80423069000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83463621139526</t>
   </si>
   <si>
     <t xml:space="preserve">4.71301031112671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61570978164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69172668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62787199020386</t>
+    <t xml:space="preserve">4.61571025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.691725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62787246704102</t>
   </si>
   <si>
     <t xml:space="preserve">4.53665208816528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25691366195679</t>
+    <t xml:space="preserve">4.25691270828247</t>
   </si>
   <si>
     <t xml:space="preserve">4.2994818687439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4059042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39374256134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43327045440674</t>
+    <t xml:space="preserve">4.40590476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39374208450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43326950073242</t>
   </si>
   <si>
     <t xml:space="preserve">4.42414808273315</t>
@@ -1241,136 +1241,136 @@
     <t xml:space="preserve">4.31468486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27819728851318</t>
+    <t xml:space="preserve">4.2781982421875</t>
   </si>
   <si>
     <t xml:space="preserve">4.32076644897461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38462018966675</t>
+    <t xml:space="preserve">4.38461971282959</t>
   </si>
   <si>
     <t xml:space="preserve">4.41502714157104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40894556045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35725355148315</t>
+    <t xml:space="preserve">4.40894508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35725402832031</t>
   </si>
   <si>
     <t xml:space="preserve">4.33292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26907587051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29644107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30556344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2356276512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29036045074463</t>
+    <t xml:space="preserve">4.2690749168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29644060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30556297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23562812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29035949707031</t>
   </si>
   <si>
     <t xml:space="preserve">4.2660346031189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26299381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22650575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21738386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28731870651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32380723953247</t>
+    <t xml:space="preserve">4.26299428939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22650623321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21738338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731918334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32380819320679</t>
   </si>
   <si>
     <t xml:space="preserve">4.38646936416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32702350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.205002784729</t>
+    <t xml:space="preserve">4.32702398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20500326156616</t>
   </si>
   <si>
     <t xml:space="preserve">4.11427068710327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14555740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16745948791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23003435134888</t>
+    <t xml:space="preserve">4.14555835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16745901107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24567794799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23003387451172</t>
   </si>
   <si>
     <t xml:space="preserve">4.25506353378296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2425479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16120100021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21438932418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17997360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17058753967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08924007415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02040958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458660125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83581399917603</t>
+    <t xml:space="preserve">4.24254846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16120195388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21438980102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17997407913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17058801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08924055099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458612442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83581447601318</t>
   </si>
   <si>
     <t xml:space="preserve">3.82329940795898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77636885643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80765628814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81704211235046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7982702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73882365226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63557624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195289611816</t>
+    <t xml:space="preserve">3.7763683795929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80765557289124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81704258918762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79826951026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73882341384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63557696342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195265769958</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262591362</t>
@@ -1379,49 +1379,49 @@
     <t xml:space="preserve">3.82642817497253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66060590744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72630906105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74508142471313</t>
+    <t xml:space="preserve">3.66060543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72630882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74508094787598</t>
   </si>
   <si>
     <t xml:space="preserve">3.63870477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7701108455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7169234752655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379399299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74820947647095</t>
+    <t xml:space="preserve">3.77011132240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71692323684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379351615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74820995330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.69815063476562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68250608444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72318005561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373443603516</t>
+    <t xml:space="preserve">3.68250751495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72317981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373467445374</t>
   </si>
   <si>
     <t xml:space="preserve">3.7607250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64183330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60116052627563</t>
+    <t xml:space="preserve">3.64183306694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60116028785706</t>
   </si>
   <si>
     <t xml:space="preserve">3.57925891876221</t>
@@ -1430,73 +1430,73 @@
     <t xml:space="preserve">3.6324474811554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68876385688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67624926567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70440769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62931799888611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686272621155</t>
+    <t xml:space="preserve">3.68876504898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67624950408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70440816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56361556053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62931895256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686296463013</t>
   </si>
   <si>
     <t xml:space="preserve">3.6199324131012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62619018554688</t>
+    <t xml:space="preserve">3.62619042396545</t>
   </si>
   <si>
     <t xml:space="preserve">3.8452000617981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99537897109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88587427139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91090369224548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87023067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84207153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78575491905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79514122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77323937416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70753622055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698279380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452680587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81078457832336</t>
+    <t xml:space="preserve">3.99537944793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88587379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91090440750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87023043632507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341828346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961626052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84207248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78575444221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79514050483704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77323985099792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7075366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7669825553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452704429626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078481674194</t>
   </si>
   <si>
     <t xml:space="preserve">3.80139803886414</t>
@@ -1505,40 +1505,40 @@
     <t xml:space="preserve">3.75446748733521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73256683349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82017064094543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75759649276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81391334533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77949738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397290229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8733594417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89213156700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9922513961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97660684585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912119865417</t>
+    <t xml:space="preserve">3.73256635665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563580513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82017111778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75759673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81391286849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77949786186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397361755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335896492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89213061332703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99225068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97660708427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912215232849</t>
   </si>
   <si>
     <t xml:space="preserve">4.00163698196411</t>
@@ -1547,31 +1547,31 @@
     <t xml:space="preserve">3.44472408294678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47288250923157</t>
+    <t xml:space="preserve">3.47288274765015</t>
   </si>
   <si>
     <t xml:space="preserve">3.37276363372803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37589263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39466428756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4509813785553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39779257774353</t>
+    <t xml:space="preserve">3.375892162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39466452598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098090171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39779353141785</t>
   </si>
   <si>
     <t xml:space="preserve">3.31018853187561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29141664505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24448537826538</t>
+    <t xml:space="preserve">3.29141616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24448561668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.22258448600769</t>
@@ -1583,28 +1583,28 @@
     <t xml:space="preserve">3.18504023551941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13498091697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21007013320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20694065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26325798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31644654273987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30706000328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3133180141449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28515934944153</t>
+    <t xml:space="preserve">3.13498115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20694088935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26325845718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31644630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30706024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331849098206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28515887260437</t>
   </si>
   <si>
     <t xml:space="preserve">3.25387167930603</t>
@@ -1613,130 +1613,130 @@
     <t xml:space="preserve">3.25074315071106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27843809127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13193392753601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541566848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890469551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727265357971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48354434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44773244857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44122076034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42494225502014</t>
+    <t xml:space="preserve">3.27843832969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13193416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890421867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48354411125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44773268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44122052192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494249343872</t>
   </si>
   <si>
     <t xml:space="preserve">3.41843128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2914605140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23351001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28820514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4086639881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33378386497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31099438667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1553750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076144218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31425046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28494930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41517543792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4021532535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36634063720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44447612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4640097618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633311271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48679971694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331045150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45749878883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5095899105072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47052145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58121275901794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71795129776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77655267715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7081835269928</t>
+    <t xml:space="preserve">3.29146122932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192759513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23351073265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28820490837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40866446495056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33378481864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31099486351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3533182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30773854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15537476539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31425023078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28494954109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4151759147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40215277671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36634159088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44447636604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46401023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633406639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48680019378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075463294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331140518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726536750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45749855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50958943367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47052097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5812132358551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71795105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77655243873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70818400382996</t>
   </si>
   <si>
     <t xml:space="preserve">3.8318989276886</t>
@@ -1748,34 +1748,34 @@
     <t xml:space="preserve">3.87096667289734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92305612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87422204017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073301315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88724422454834</t>
+    <t xml:space="preserve">3.92305684089661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87422180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073396682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8872447013855</t>
   </si>
   <si>
     <t xml:space="preserve">3.99142527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95886874198914</t>
+    <t xml:space="preserve">3.95886921882629</t>
   </si>
   <si>
     <t xml:space="preserve">4.00770378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99793601036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97189140319824</t>
+    <t xml:space="preserve">3.99793696403503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06305027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9718918800354</t>
   </si>
   <si>
     <t xml:space="preserve">4.01747035980225</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">4.06630516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06956100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258295059204</t>
+    <t xml:space="preserve">4.06956148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0825834274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.12165117263794</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">4.09235000610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11513996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12816286087036</t>
+    <t xml:space="preserve">4.11513948440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12816190719604</t>
   </si>
   <si>
     <t xml:space="preserve">4.0988621711731</t>
@@ -1808,31 +1808,31 @@
     <t xml:space="preserve">4.14118480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08583927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11188459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16071939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13141870498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26164484024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24862146377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24536609649658</t>
+    <t xml:space="preserve">4.08583974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11188411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16071891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1314172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26164436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24862194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24536657333374</t>
   </si>
   <si>
     <t xml:space="preserve">4.24211025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23559951782227</t>
+    <t xml:space="preserve">4.23559904098511</t>
   </si>
   <si>
     <t xml:space="preserve">4.2323431968689</t>
@@ -1841,91 +1841,91 @@
     <t xml:space="preserve">4.3235011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38210391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40489292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233591079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37569189071655</t>
+    <t xml:space="preserve">4.38210296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4048924446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37569236755371</t>
   </si>
   <si>
     <t xml:space="preserve">4.2884464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32871341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33206939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4126033782959</t>
+    <t xml:space="preserve">4.32871294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33206844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41260242462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.39247035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36226987838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22804594039917</t>
+    <t xml:space="preserve">4.36226940155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22804641723633</t>
   </si>
   <si>
     <t xml:space="preserve">4.23811197280884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25153541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751148223877</t>
+    <t xml:space="preserve">4.25153493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751195907593</t>
   </si>
   <si>
     <t xml:space="preserve">4.10388851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16093254089355</t>
+    <t xml:space="preserve">4.16093349456787</t>
   </si>
   <si>
     <t xml:space="preserve">4.10724449157715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16428995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12737846374512</t>
+    <t xml:space="preserve">4.16428899765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12737894058228</t>
   </si>
   <si>
     <t xml:space="preserve">4.12402248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06697797775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0770435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08039999008179</t>
+    <t xml:space="preserve">4.06697750091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07704305648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">4.04684400558472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02671051025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0065770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03342151641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09046649932861</t>
+    <t xml:space="preserve">4.02671003341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00657749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0334210395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09046602249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.14415645599365</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">4.17435598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15757846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13744497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368898391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19784593582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21797847747803</t>
+    <t xml:space="preserve">4.15757894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11059999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1374454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19784498214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21797943115234</t>
   </si>
   <si>
     <t xml:space="preserve">4.24482393264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34213542938232</t>
+    <t xml:space="preserve">4.34213590621948</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28509044647217</t>
+    <t xml:space="preserve">4.28509092330933</t>
   </si>
   <si>
     <t xml:space="preserve">4.33878040313721</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">4.34549140930176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34884691238403</t>
+    <t xml:space="preserve">4.34884643554688</t>
   </si>
   <si>
     <t xml:space="preserve">4.47300386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50991535186768</t>
+    <t xml:space="preserve">4.50991487503052</t>
   </si>
   <si>
     <t xml:space="preserve">4.4629373550415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45622634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41931486129761</t>
+    <t xml:space="preserve">4.45622587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41931390762329</t>
   </si>
   <si>
     <t xml:space="preserve">4.48978185653687</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">4.48307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51662731170654</t>
+    <t xml:space="preserve">4.51662683486938</t>
   </si>
   <si>
     <t xml:space="preserve">4.5367603302002</t>
@@ -2015,73 +2015,73 @@
     <t xml:space="preserve">4.42267036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4495153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42938089370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50656032562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46964836120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40924787521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39582538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20120096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455598831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21126842498779</t>
+    <t xml:space="preserve">4.44951486587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42938137054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5065598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46964883804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40924692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39582586288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20120143890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21126890182495</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33542537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273687362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38575839996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46629238128662</t>
+    <t xml:space="preserve">4.33542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38575887680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46629333496094</t>
   </si>
   <si>
     <t xml:space="preserve">4.41595888137817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50320434570312</t>
+    <t xml:space="preserve">4.50320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">4.52333784103394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722684860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61729526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70453977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65756177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67769527435303</t>
+    <t xml:space="preserve">4.60722732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61729431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59716033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70454072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6575608253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67769479751587</t>
   </si>
   <si>
     <t xml:space="preserve">4.72467374801636</t>
@@ -2090,40 +2090,40 @@
     <t xml:space="preserve">4.73138475418091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.697829246521</t>
+    <t xml:space="preserve">4.69782876968384</t>
   </si>
   <si>
     <t xml:space="preserve">4.61393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64078330993652</t>
+    <t xml:space="preserve">4.64078378677368</t>
   </si>
   <si>
     <t xml:space="preserve">4.60387229919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62736177444458</t>
+    <t xml:space="preserve">4.62736129760742</t>
   </si>
   <si>
     <t xml:space="preserve">4.62400531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62065029144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56024932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66762828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66427230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66091775894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68105030059814</t>
+    <t xml:space="preserve">4.62065076828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56024980545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66762733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66427278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66091680526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68105125427246</t>
   </si>
   <si>
     <t xml:space="preserve">4.82534074783325</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">4.98305416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04345464706421</t>
+    <t xml:space="preserve">5.04345512390137</t>
   </si>
   <si>
     <t xml:space="preserve">5.073655128479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08707761764526</t>
+    <t xml:space="preserve">5.08707714080811</t>
   </si>
   <si>
     <t xml:space="preserve">5.09714365005493</t>
@@ -2156,52 +2156,52 @@
     <t xml:space="preserve">5.1172776222229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15083312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16090106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15754508972168</t>
+    <t xml:space="preserve">5.15083408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1609001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15754461288452</t>
   </si>
   <si>
     <t xml:space="preserve">5.16425561904907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17432308197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16761112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23472309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54343748092651</t>
+    <t xml:space="preserve">5.1743221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16761159896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23472356796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54343891143799</t>
   </si>
   <si>
     <t xml:space="preserve">5.63403940200806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79175233840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89241886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77161836624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7850399017334</t>
+    <t xml:space="preserve">5.79175138473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89241981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77161884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78504085540771</t>
   </si>
   <si>
     <t xml:space="preserve">5.87102508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02923679351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17025232315063</t>
+    <t xml:space="preserve">6.02923727035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17025136947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.18400859832764</t>
@@ -2210,37 +2210,37 @@
     <t xml:space="preserve">6.2699933052063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21840286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32846164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40069055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878135681152</t>
+    <t xml:space="preserve">6.21840238571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32846307754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40068960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878231048584</t>
   </si>
   <si>
     <t xml:space="preserve">6.28031158447266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26311492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33534145355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3834924697876</t>
+    <t xml:space="preserve">6.2631139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3353419303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38349342346191</t>
   </si>
   <si>
     <t xml:space="preserve">6.33190298080444</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21496295928955</t>
+    <t xml:space="preserve">6.21496343612671</t>
   </si>
   <si>
     <t xml:space="preserve">6.2321605682373</t>
@@ -2255,49 +2255,49 @@
     <t xml:space="preserve">6.30438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28375101089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27687215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24935722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16681289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13585758209229</t>
+    <t xml:space="preserve">6.28375196456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27687168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2493577003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1668119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13585805892944</t>
   </si>
   <si>
     <t xml:space="preserve">6.14617586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09114456176758</t>
+    <t xml:space="preserve">6.09114503860474</t>
   </si>
   <si>
     <t xml:space="preserve">6.11866092681885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0361156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91229867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573667526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00860023498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00516080856323</t>
+    <t xml:space="preserve">6.03611516952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91229820251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05331325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088840484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00860071182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00516128540039</t>
   </si>
   <si>
     <t xml:space="preserve">6.10490322113037</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">6.03267621994019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92949390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95701026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90885829925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73001098632812</t>
+    <t xml:space="preserve">5.92949533462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95700931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90885925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73001050949097</t>
   </si>
   <si>
     <t xml:space="preserve">5.85726737976074</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">5.78504037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60619211196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61651086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249557495117</t>
+    <t xml:space="preserve">5.60619258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61651134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249509811401</t>
   </si>
   <si>
     <t xml:space="preserve">5.66810178756714</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">5.77816200256348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81255578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80567598342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80911588668823</t>
+    <t xml:space="preserve">5.81255531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80567646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80911636352539</t>
   </si>
   <si>
     <t xml:space="preserve">5.87790393829346</t>
@@ -2360,61 +2360,61 @@
     <t xml:space="preserve">6.01547908782959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86758518218994</t>
+    <t xml:space="preserve">5.8675856590271</t>
   </si>
   <si>
     <t xml:space="preserve">5.70593547821045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40326881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35511827468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.372314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505805969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06276988983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00430011749268</t>
+    <t xml:space="preserve">5.40326929092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35511779785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37231492996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505758285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0627703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00430107116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.98366451263428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94927167892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69819688796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58813524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26483297348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75580501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71453309059143</t>
+    <t xml:space="preserve">4.94927072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69819498062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58813571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26483392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75580549240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71453261375427</t>
   </si>
   <si>
     <t xml:space="preserve">3.36509156227112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36784243583679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08306193351746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092950820923</t>
+    <t xml:space="preserve">3.36784291267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08306169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092998504639</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516004562378</t>
@@ -2423,61 +2423,61 @@
     <t xml:space="preserve">2.91109299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90283799171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25365495681763</t>
+    <t xml:space="preserve">2.90283823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25365543365479</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133409500122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53568506240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4159939289093</t>
+    <t xml:space="preserve">3.53568482398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41599440574646</t>
   </si>
   <si>
     <t xml:space="preserve">3.24815249443054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19862532615662</t>
+    <t xml:space="preserve">3.19862580299377</t>
   </si>
   <si>
     <t xml:space="preserve">3.18899512290955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20000100135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14359521865845</t>
+    <t xml:space="preserve">3.20000147819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14359498023987</t>
   </si>
   <si>
     <t xml:space="preserve">3.25778293609619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43938183784485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59415435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76268339157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44970011711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49097228050232</t>
+    <t xml:space="preserve">3.43938207626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.594153881073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7626838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44969987869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4909725189209</t>
   </si>
   <si>
     <t xml:space="preserve">3.59759402275085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52880620956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096429824829</t>
+    <t xml:space="preserve">3.52880644798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.48409390449524</t>
@@ -2489,73 +2489,73 @@
     <t xml:space="preserve">3.54600310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68013906478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85554766654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01031923294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83147168159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65950298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60447239875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64574551582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68701767921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69045662879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84866905212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745686531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.790198802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421433448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80739545822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81427454948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92089557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95528936386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03439474105835</t>
+    <t xml:space="preserve">3.68013834953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85554718971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01031970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83147144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65950274467468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60447263717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64574503898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6870174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69045686721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84866809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745638847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421528816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80739617347717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81427526473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92089533805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95528888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03439569473267</t>
   </si>
   <si>
     <t xml:space="preserve">4.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16853141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12038040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08598566055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2373194694519</t>
+    <t xml:space="preserve">4.16853094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12037944793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08598613739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23731851577759</t>
   </si>
   <si>
     <t xml:space="preserve">4.2854700088501</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">4.44712114334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65348434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76010417938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5778169631958</t>
+    <t xml:space="preserve">4.65348386764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7601056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57781791687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018207550049</t>
@@ -2579,25 +2579,25 @@
     <t xml:space="preserve">4.34737873077393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4918327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44368171691895</t>
+    <t xml:space="preserve">4.49183368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4436821937561</t>
   </si>
   <si>
     <t xml:space="preserve">4.42304515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46775770187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4539999961853</t>
+    <t xml:space="preserve">4.46775722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45399951934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.49527215957642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30266714096069</t>
+    <t xml:space="preserve">4.30266618728638</t>
   </si>
   <si>
     <t xml:space="preserve">4.29234838485718</t>
@@ -2615,46 +2615,46 @@
     <t xml:space="preserve">4.32330322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52622699737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41616725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52278709411621</t>
+    <t xml:space="preserve">4.52622652053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52278661727905</t>
   </si>
   <si>
     <t xml:space="preserve">4.50215101242065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31298494338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41960620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47119665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53310632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53654479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5571813583374</t>
+    <t xml:space="preserve">4.31298542022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41960573196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47119617462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53310537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53654432296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55718088150024</t>
   </si>
   <si>
     <t xml:space="preserve">4.66380262374878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61221122741699</t>
+    <t xml:space="preserve">4.61221170425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093858718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52966547012329</t>
+    <t xml:space="preserve">4.52966594696045</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743894577026</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">4.39209127426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42648506164551</t>
+    <t xml:space="preserve">4.42648458480835</t>
   </si>
   <si>
     <t xml:space="preserve">4.26139450073242</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">4.42992401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43680334091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56062030792236</t>
+    <t xml:space="preserve">4.43680286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56062126159668</t>
   </si>
   <si>
     <t xml:space="preserve">4.63628721237183</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">4.60877180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48839378356934</t>
+    <t xml:space="preserve">4.48839330673218</t>
   </si>
   <si>
     <t xml:space="preserve">4.56406021118164</t>
@@ -2708,46 +2708,46 @@
     <t xml:space="preserve">4.54686307907104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40240955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27515172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081768035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35425758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55030202865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33362150192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23044013977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32674217224121</t>
+    <t xml:space="preserve">4.40240907669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3508186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35425710678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55030250549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33362197875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23044061660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32674264907837</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636415481567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2785906791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50559043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43336391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29922723770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31986379623413</t>
+    <t xml:space="preserve">4.27859115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50559091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43336296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29922819137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31986427307129</t>
   </si>
   <si>
     <t xml:space="preserve">4.30610656738281</t>
@@ -2759,28 +2759,28 @@
     <t xml:space="preserve">4.03783464431763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98968362808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03095531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25107574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73258972167969</t>
+    <t xml:space="preserve">3.98968315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03095579147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25107622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73258924484253</t>
   </si>
   <si>
     <t xml:space="preserve">4.81169509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93207359313965</t>
+    <t xml:space="preserve">4.93207406997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.81513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96646738052368</t>
+    <t xml:space="preserve">4.96646785736084</t>
   </si>
   <si>
     <t xml:space="preserve">5.20034599304199</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">5.19346714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12467956542969</t>
+    <t xml:space="preserve">5.12467908859253</t>
   </si>
   <si>
     <t xml:space="preserve">5.22442150115967</t>
@@ -2801,25 +2801,25 @@
     <t xml:space="preserve">5.37919330596924</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2656946182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34136009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23130035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2966480255127</t>
+    <t xml:space="preserve">5.26569414138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34135961532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23129987716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29664850234985</t>
   </si>
   <si>
     <t xml:space="preserve">5.15563297271729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11092138290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10404253005981</t>
+    <t xml:space="preserve">5.11092233657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10404300689697</t>
   </si>
   <si>
     <t xml:space="preserve">5.04557371139526</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">5.00774097442627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00086212158203</t>
+    <t xml:space="preserve">5.00086164474487</t>
   </si>
   <si>
     <t xml:space="preserve">4.91831636428833</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">4.88736152648926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89423990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89767980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88392210006714</t>
+    <t xml:space="preserve">4.8942403793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89768075942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8839225769043</t>
   </si>
   <si>
     <t xml:space="preserve">4.8667254447937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7669825553894</t>
+    <t xml:space="preserve">4.76698398590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.83577108383179</t>
@@ -2858,46 +2858,46 @@
     <t xml:space="preserve">4.85296773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89080142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91487789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85984659194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87016487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05933046340942</t>
+    <t xml:space="preserve">4.89080190658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91487741470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8598461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87016439437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05933141708374</t>
   </si>
   <si>
     <t xml:space="preserve">5.03869438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03181600570679</t>
+    <t xml:space="preserve">5.03181552886963</t>
   </si>
   <si>
     <t xml:space="preserve">4.71539258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59845352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53998374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61565113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6706805229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02837610244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12811851501465</t>
+    <t xml:space="preserve">4.59845399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53998470306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61565017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67068099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02837657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12811899185181</t>
   </si>
   <si>
     <t xml:space="preserve">5.31728410720825</t>
@@ -2906,37 +2906,37 @@
     <t xml:space="preserve">5.25537538528442</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27257251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25881576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15219354629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07652759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09028625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14875459671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05245208740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96990728378296</t>
+    <t xml:space="preserve">5.27257299423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2588152885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15219402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07652854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0902853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14875507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493715286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05245161056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9699068069458</t>
   </si>
   <si>
     <t xml:space="preserve">5.13499736785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16251230239868</t>
+    <t xml:space="preserve">5.16251277923584</t>
   </si>
   <si>
     <t xml:space="preserve">5.14187622070312</t>
@@ -2945,37 +2945,37 @@
     <t xml:space="preserve">5.23817873001099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29320859909058</t>
+    <t xml:space="preserve">5.29320907592773</t>
   </si>
   <si>
     <t xml:space="preserve">5.32760286331177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34479951858521</t>
+    <t xml:space="preserve">5.34479999542236</t>
   </si>
   <si>
     <t xml:space="preserve">5.33104181289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33792114257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45142078399658</t>
+    <t xml:space="preserve">5.33792161941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45142126083374</t>
   </si>
   <si>
     <t xml:space="preserve">5.58899593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50645017623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4445424079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48237562179565</t>
+    <t xml:space="preserve">5.50645112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44454193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48237466812134</t>
   </si>
   <si>
     <t xml:space="preserve">5.48925399780273</t>
@@ -2984,28 +2984,28 @@
     <t xml:space="preserve">5.56492042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53740453720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51952028274536</t>
+    <t xml:space="preserve">5.53740549087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">5.5511622428894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47824859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40258073806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45898675918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41221046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.414963722229</t>
+    <t xml:space="preserve">5.47824811935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40258169174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45898723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41221141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41496324539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.36543560028076</t>
@@ -3014,64 +3014,64 @@
     <t xml:space="preserve">5.38332080841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43972730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39019918441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32553958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37644147872925</t>
+    <t xml:space="preserve">5.43972682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39020013809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32554006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37644243240356</t>
   </si>
   <si>
     <t xml:space="preserve">5.39982986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37506628036499</t>
+    <t xml:space="preserve">5.37506675720215</t>
   </si>
   <si>
     <t xml:space="preserve">5.34617567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46036338806152</t>
+    <t xml:space="preserve">5.46036291122437</t>
   </si>
   <si>
     <t xml:space="preserve">5.37368965148926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43697547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51401710510254</t>
+    <t xml:space="preserve">5.43697452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51401662826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.57730150222778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55529022216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046594619751</t>
+    <t xml:space="preserve">5.55529069900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046642303467</t>
   </si>
   <si>
     <t xml:space="preserve">5.42321729660034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44247817993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3984546661377</t>
+    <t xml:space="preserve">5.44247770309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39845418930054</t>
   </si>
   <si>
     <t xml:space="preserve">5.47484111785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43066596984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42928600311279</t>
+    <t xml:space="preserve">5.43066692352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42928552627563</t>
   </si>
   <si>
     <t xml:space="preserve">5.44309091567993</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">5.59493970870972</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58113574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56732988357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57837343215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55766773223877</t>
+    <t xml:space="preserve">5.58113527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5673303604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57837390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55766725540161</t>
   </si>
   <si>
     <t xml:space="preserve">5.60046148300171</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">5.70813608169556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74264717102051</t>
+    <t xml:space="preserve">5.74264621734619</t>
   </si>
   <si>
     <t xml:space="preserve">5.63773345947266</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">5.67224454879761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69571113586426</t>
+    <t xml:space="preserve">5.69571208953857</t>
   </si>
   <si>
     <t xml:space="preserve">5.66948318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76473474502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77715730667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6750054359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291786193848</t>
+    <t xml:space="preserve">5.76473426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77715873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67500591278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291833877563</t>
   </si>
   <si>
     <t xml:space="preserve">5.61288547515869</t>
@@ -3140,19 +3140,19 @@
     <t xml:space="preserve">5.79234313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66258192062378</t>
+    <t xml:space="preserve">5.66258144378662</t>
   </si>
   <si>
     <t xml:space="preserve">5.66534233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68466806411743</t>
+    <t xml:space="preserve">5.68466854095459</t>
   </si>
   <si>
     <t xml:space="preserve">5.68328762054443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68604898452759</t>
+    <t xml:space="preserve">5.68604850769043</t>
   </si>
   <si>
     <t xml:space="preserve">5.65015697479248</t>
@@ -3164,16 +3164,16 @@
     <t xml:space="preserve">5.63635349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72746181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6681022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68742895126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6046028137207</t>
+    <t xml:space="preserve">5.72746276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66810321807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68742942810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60460186004639</t>
   </si>
   <si>
     <t xml:space="preserve">5.59355926513672</t>
@@ -3182,37 +3182,37 @@
     <t xml:space="preserve">5.36164474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40443801879883</t>
+    <t xml:space="preserve">5.40443754196167</t>
   </si>
   <si>
     <t xml:space="preserve">5.57975435256958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62392854690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362499237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81995248794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79924583435059</t>
+    <t xml:space="preserve">5.62392902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81442975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8199520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79924535751343</t>
   </si>
   <si>
     <t xml:space="preserve">5.79510354995728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73160266876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74540853500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71503734588623</t>
+    <t xml:space="preserve">5.73160409927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71503829956055</t>
   </si>
   <si>
     <t xml:space="preserve">5.75507116317749</t>
@@ -3221,73 +3221,73 @@
     <t xml:space="preserve">5.80752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88069105148315</t>
+    <t xml:space="preserve">5.88069152832031</t>
   </si>
   <si>
     <t xml:space="preserve">5.95523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9635181427002</t>
+    <t xml:space="preserve">5.96351861953735</t>
   </si>
   <si>
     <t xml:space="preserve">6.04910564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0311598777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981229782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0325403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9469518661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92348527908325</t>
+    <t xml:space="preserve">6.03116035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06981182098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03253984451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07809448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94695329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92348480224609</t>
   </si>
   <si>
     <t xml:space="preserve">5.98284435272217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97318172454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99802875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98560571670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03668165206909</t>
+    <t xml:space="preserve">5.97318124771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99802923202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98560523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03668117523193</t>
   </si>
   <si>
     <t xml:space="preserve">6.05048561096191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06705141067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06567096710205</t>
+    <t xml:space="preserve">6.06705188751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06567049026489</t>
   </si>
   <si>
     <t xml:space="preserve">6.08775806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09051847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0601487159729</t>
+    <t xml:space="preserve">6.09051895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06014919281006</t>
   </si>
   <si>
     <t xml:space="preserve">6.04220342636108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03944253921509</t>
+    <t xml:space="preserve">6.03944206237793</t>
   </si>
   <si>
     <t xml:space="preserve">6.01045322418213</t>
@@ -3296,25 +3296,25 @@
     <t xml:space="preserve">6.15678071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19681167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15125799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20233488082886</t>
+    <t xml:space="preserve">6.19681310653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15125846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2023344039917</t>
   </si>
   <si>
     <t xml:space="preserve">6.1457371711731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95937633514404</t>
+    <t xml:space="preserve">5.9593768119812</t>
   </si>
   <si>
     <t xml:space="preserve">6.14849710464478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34590101242065</t>
+    <t xml:space="preserve">6.3459005355835</t>
   </si>
   <si>
     <t xml:space="preserve">6.30034685134888</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">6.39835834503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4535756111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55710935592651</t>
+    <t xml:space="preserve">6.45357656478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55710887908936</t>
   </si>
   <si>
     <t xml:space="preserve">6.57229423522949</t>
@@ -3341,40 +3341,40 @@
     <t xml:space="preserve">6.70343732833862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60542345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690439224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6661639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71585988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72000217437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245855331421</t>
+    <t xml:space="preserve">6.60542440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690343856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585893630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72000074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245759963989</t>
   </si>
   <si>
     <t xml:space="preserve">6.80697011947632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.827392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70334100723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70931768417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62562084197998</t>
+    <t xml:space="preserve">6.82739353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70931911468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62562131881714</t>
   </si>
   <si>
     <t xml:space="preserve">6.61366367340088</t>
@@ -3383,31 +3383,31 @@
     <t xml:space="preserve">6.56284666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66149044036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60917997360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56583690643311</t>
+    <t xml:space="preserve">6.66149091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60917901992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56583642959595</t>
   </si>
   <si>
     <t xml:space="preserve">6.50605154037476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58227682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49708461761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55387926101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68241596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65850114822388</t>
+    <t xml:space="preserve">6.58227586746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49708414077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.553879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68241691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65850162506104</t>
   </si>
   <si>
     <t xml:space="preserve">6.66448068618774</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">6.78404951095581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84532880783081</t>
+    <t xml:space="preserve">6.84532833099365</t>
   </si>
   <si>
     <t xml:space="preserve">6.8318772315979</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">6.66298627853394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5643424987793</t>
+    <t xml:space="preserve">6.56434202194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.7086124420166</t>
@@ -3443,55 +3443,55 @@
     <t xml:space="preserve">6.58429431915283</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7761435508728</t>
+    <t xml:space="preserve">6.77614402770996</t>
   </si>
   <si>
     <t xml:space="preserve">6.68865966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38783979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43848848342896</t>
+    <t xml:space="preserve">6.38783931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4384880065918</t>
   </si>
   <si>
     <t xml:space="preserve">6.32951688766479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49374055862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44309186935425</t>
+    <t xml:space="preserve">6.49374103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44309234619141</t>
   </si>
   <si>
     <t xml:space="preserve">6.47685718536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54899311065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68405532836914</t>
+    <t xml:space="preserve">6.5489935874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6840558052063</t>
   </si>
   <si>
     <t xml:space="preserve">6.62112951278687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56127214431763</t>
+    <t xml:space="preserve">6.56127262115479</t>
   </si>
   <si>
     <t xml:space="preserve">6.51522731781006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50601768493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51062297821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52443599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44462585449219</t>
+    <t xml:space="preserve">6.506019115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51062393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52443647384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4446268081665</t>
   </si>
   <si>
     <t xml:space="preserve">6.2451024055481</t>
@@ -3500,94 +3500,94 @@
     <t xml:space="preserve">6.42927932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48299646377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58889818191528</t>
+    <t xml:space="preserve">6.48299694061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5888991355896</t>
   </si>
   <si>
     <t xml:space="preserve">6.65335893630981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64568567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103315353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74391269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79456186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85288429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66410303115845</t>
+    <t xml:space="preserve">6.64568519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74391317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79456090927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85288381576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66410350799561</t>
   </si>
   <si>
     <t xml:space="preserve">6.78688716888428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84981393814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97566795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10612678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13221740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99255037307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96185350418091</t>
+    <t xml:space="preserve">6.84981346130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97566843032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10612630844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13221788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99255132675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96185493469238</t>
   </si>
   <si>
     <t xml:space="preserve">6.79763078689575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7914924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70554256439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40779161453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41700077056885</t>
+    <t xml:space="preserve">6.79149198532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70554351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40779256820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41700124740601</t>
   </si>
   <si>
     <t xml:space="preserve">6.55052804946899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51829767227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46611356735229</t>
+    <t xml:space="preserve">6.51829814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46611452102661</t>
   </si>
   <si>
     <t xml:space="preserve">6.57201528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67177724838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76386499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69786834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45844030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54438924789429</t>
+    <t xml:space="preserve">6.67177772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76386594772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69786882400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45844078063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54438877105713</t>
   </si>
   <si>
     <t xml:space="preserve">6.69940328598022</t>
@@ -3596,55 +3596,55 @@
     <t xml:space="preserve">6.79916572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56894588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5229024887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47225332260132</t>
+    <t xml:space="preserve">6.56894683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34486436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52290201187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47225284576416</t>
   </si>
   <si>
     <t xml:space="preserve">6.38476943969727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36328268051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29575157165527</t>
+    <t xml:space="preserve">6.36328172683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29575109481812</t>
   </si>
   <si>
     <t xml:space="preserve">6.23435878753662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28500747680664</t>
+    <t xml:space="preserve">6.2850079536438</t>
   </si>
   <si>
     <t xml:space="preserve">5.75089740753174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8874945640564</t>
+    <t xml:space="preserve">5.88749408721924</t>
   </si>
   <si>
     <t xml:space="preserve">5.64960050582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43933200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46388959884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.336501121521</t>
+    <t xml:space="preserve">5.43933296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46388912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33650064468384</t>
   </si>
   <si>
     <t xml:space="preserve">4.98810148239136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92977809906006</t>
+    <t xml:space="preserve">4.92977857589722</t>
   </si>
   <si>
     <t xml:space="preserve">5.07098054885864</t>
@@ -3653,55 +3653,55 @@
     <t xml:space="preserve">5.62657833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29966640472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41938018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50993299484253</t>
+    <t xml:space="preserve">5.2996654510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41937971115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50993347167969</t>
   </si>
   <si>
     <t xml:space="preserve">5.62811326980591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92125988006592</t>
+    <t xml:space="preserve">5.92126035690308</t>
   </si>
   <si>
     <t xml:space="preserve">5.88135576248169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86447286605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82149839401245</t>
+    <t xml:space="preserve">5.86447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82149791717529</t>
   </si>
   <si>
     <t xml:space="preserve">5.97190856933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90898132324219</t>
+    <t xml:space="preserve">5.90898084640503</t>
   </si>
   <si>
     <t xml:space="preserve">5.87214660644531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92586421966553</t>
+    <t xml:space="preserve">5.92586517333984</t>
   </si>
   <si>
     <t xml:space="preserve">5.96116495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12538862228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06860160827637</t>
+    <t xml:space="preserve">6.12538814544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06860065460205</t>
   </si>
   <si>
     <t xml:space="preserve">5.95195579528809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05325222015381</t>
+    <t xml:space="preserve">6.05325317382812</t>
   </si>
   <si>
     <t xml:space="preserve">5.98879098892212</t>
@@ -3710,43 +3710,43 @@
     <t xml:space="preserve">5.93353843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72787570953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71559715270996</t>
+    <t xml:space="preserve">5.72787523269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7155966758728</t>
   </si>
   <si>
     <t xml:space="preserve">5.85679864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82303237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77084922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81842851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86293792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7985987663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89671611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87098073959351</t>
+    <t xml:space="preserve">5.82303285598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77084970474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81842803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89671564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87098026275635</t>
   </si>
   <si>
     <t xml:space="preserve">5.78090476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65865993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56536722183228</t>
+    <t xml:space="preserve">5.6586594581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56536769866943</t>
   </si>
   <si>
     <t xml:space="preserve">5.60397100448608</t>
@@ -3761,19 +3761,19 @@
     <t xml:space="preserve">5.56375932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59271192550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55732536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62166500091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58788633346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50263595581055</t>
+    <t xml:space="preserve">5.59271144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55732488632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62166452407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58788585662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50263643264771</t>
   </si>
   <si>
     <t xml:space="preserve">5.56054210662842</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">5.66348505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70852279663086</t>
+    <t xml:space="preserve">5.7085223197937</t>
   </si>
   <si>
     <t xml:space="preserve">5.74069261550903</t>
@@ -3794,43 +3794,43 @@
     <t xml:space="preserve">5.76321125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68922138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75516939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76803684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95140504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91280126571655</t>
+    <t xml:space="preserve">5.68922090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75516891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76803636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9514045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94175338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91280031204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.84685277938843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75034427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706588745117</t>
+    <t xml:space="preserve">5.75034379959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8870644569397</t>
   </si>
   <si>
     <t xml:space="preserve">5.80503177642822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72299957275391</t>
+    <t xml:space="preserve">5.72299909591675</t>
   </si>
   <si>
     <t xml:space="preserve">5.55249929428101</t>
@@ -3839,22 +3839,22 @@
     <t xml:space="preserve">5.17450475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323230743408</t>
   </si>
   <si>
     <t xml:space="preserve">5.13107585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20828247070312</t>
+    <t xml:space="preserve">5.2082839012146</t>
   </si>
   <si>
     <t xml:space="preserve">5.01043891906738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05225992202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11820793151855</t>
+    <t xml:space="preserve">5.05226039886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1182074546814</t>
   </si>
   <si>
     <t xml:space="preserve">5.11981582641602</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">5.15198659896851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30157566070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16807126998901</t>
+    <t xml:space="preserve">5.30157518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16807079315186</t>
   </si>
   <si>
     <t xml:space="preserve">5.17933034896851</t>
@@ -3875,28 +3875,28 @@
     <t xml:space="preserve">5.14876890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04904317855835</t>
+    <t xml:space="preserve">5.04904270172119</t>
   </si>
   <si>
     <t xml:space="preserve">5.07156181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05386877059937</t>
+    <t xml:space="preserve">5.05386829376221</t>
   </si>
   <si>
     <t xml:space="preserve">4.80294466018677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88819360733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0345664024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17611360549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295850753784</t>
+    <t xml:space="preserve">4.88819456100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03456687927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17611312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03295755386353</t>
   </si>
   <si>
     <t xml:space="preserve">5.10855674743652</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">5.03778314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8592414855957</t>
+    <t xml:space="preserve">4.85924100875854</t>
   </si>
   <si>
     <t xml:space="preserve">4.91232109069824</t>
@@ -3914,43 +3914,43 @@
     <t xml:space="preserve">4.98631143569946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12142562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93483972549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01848125457764</t>
+    <t xml:space="preserve">5.12142467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93484020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01848173141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.0152645111084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96379327774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9927453994751</t>
+    <t xml:space="preserve">4.96379280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99274635314941</t>
   </si>
   <si>
     <t xml:space="preserve">5.18737268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21150016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15842008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45598983764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59432077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50746154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48976850509644</t>
+    <t xml:space="preserve">5.21149969100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15841960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45599031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59432029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50746202468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48976898193359</t>
   </si>
   <si>
     <t xml:space="preserve">5.46242380142212</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">5.50424480438232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53641510009766</t>
+    <t xml:space="preserve">5.53641414642334</t>
   </si>
   <si>
     <t xml:space="preserve">5.56858444213867</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">5.51067876815796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4029107093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44312238693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33374452590942</t>
+    <t xml:space="preserve">5.40291023254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44312286376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33374500274658</t>
   </si>
   <si>
     <t xml:space="preserve">5.19219827651978</t>
@@ -3989,16 +3989,16 @@
     <t xml:space="preserve">5.163245677948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04100036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14394283294678</t>
+    <t xml:space="preserve">5.0410008430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14394330978394</t>
   </si>
   <si>
     <t xml:space="preserve">5.12946701049805</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00883102416992</t>
+    <t xml:space="preserve">5.00883054733276</t>
   </si>
   <si>
     <t xml:space="preserve">5.24688720703125</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">5.08121252059937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1825475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19863319396973</t>
+    <t xml:space="preserve">5.11659955978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18254709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19863224029541</t>
   </si>
   <si>
     <t xml:space="preserve">5.31766033172607</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">5.53963136672974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41577816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49459362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25653791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33052778244019</t>
+    <t xml:space="preserve">5.41577863693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49459409713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28870820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25653743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33052825927734</t>
   </si>
   <si>
     <t xml:space="preserve">5.08925533294678</t>
@@ -4043,28 +4043,28 @@
     <t xml:space="preserve">5.15037727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18898153305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99596309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16002798080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08603763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13590145111084</t>
+    <t xml:space="preserve">5.18898105621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99596261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1600284576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08603811264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.135901927948</t>
   </si>
   <si>
     <t xml:space="preserve">4.9879207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20345783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45920705795288</t>
+    <t xml:space="preserve">5.20345735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45920753479004</t>
   </si>
   <si>
     <t xml:space="preserve">5.39808416366577</t>
@@ -4073,115 +4073,115 @@
     <t xml:space="preserve">5.37878274917603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32409381866455</t>
+    <t xml:space="preserve">5.32409429550171</t>
   </si>
   <si>
     <t xml:space="preserve">5.33696174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28709983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14555215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30961751937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35626411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47368335723877</t>
+    <t xml:space="preserve">5.28709888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14555168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30961799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35626459121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47368431091309</t>
   </si>
   <si>
     <t xml:space="preserve">5.54284906387329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61362171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64579248428345</t>
+    <t xml:space="preserve">5.61362218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64579200744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.67152738571167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73908424377441</t>
+    <t xml:space="preserve">5.73908376693726</t>
   </si>
   <si>
     <t xml:space="preserve">5.90315008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92406034469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04308843612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11707878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09616804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02539443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06560659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08651685714722</t>
+    <t xml:space="preserve">5.92405986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04308795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11707925796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09616756439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02539539337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06560611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08651781082153</t>
   </si>
   <si>
     <t xml:space="preserve">6.21519660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24897432327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26023387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43716716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35996103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45968675613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49668216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46451234817505</t>
+    <t xml:space="preserve">6.27149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24897527694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26023435592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43716812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35996007919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45968627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49668169021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46451187133789</t>
   </si>
   <si>
     <t xml:space="preserve">6.45646953582764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50472450256348</t>
+    <t xml:space="preserve">6.50472402572632</t>
   </si>
   <si>
     <t xml:space="preserve">6.50969743728638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53290414810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56108474731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47820138931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49312019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52958917617798</t>
+    <t xml:space="preserve">6.53290510177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56108522415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47820091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4931206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52958869934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.52461624145508</t>
@@ -4193,46 +4193,46 @@
     <t xml:space="preserve">6.53124713897705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61413097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57434606552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51301288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47488641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52627420425415</t>
+    <t xml:space="preserve">6.61413049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5743465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51301240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4748854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52627468109131</t>
   </si>
   <si>
     <t xml:space="preserve">6.46825504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54616546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54948139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44007444381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39200162887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55777025222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51466989517212</t>
+    <t xml:space="preserve">6.54616594314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5494818687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4400749206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39200258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55776977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51467037200928</t>
   </si>
   <si>
     <t xml:space="preserve">6.49146270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46328258514404</t>
+    <t xml:space="preserve">6.46328210830688</t>
   </si>
   <si>
     <t xml:space="preserve">6.54450845718384</t>
@@ -4241,22 +4241,22 @@
     <t xml:space="preserve">6.56274318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68209552764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64728450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73514127731323</t>
+    <t xml:space="preserve">6.68209600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64728498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73514175415039</t>
   </si>
   <si>
     <t xml:space="preserve">6.86609792709351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87935876846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00202703475952</t>
+    <t xml:space="preserve">6.87935924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00202751159668</t>
   </si>
   <si>
     <t xml:space="preserve">7.04015398025513</t>
@@ -4268,28 +4268,28 @@
     <t xml:space="preserve">7.11806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10646200180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9721884727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98545026779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07496547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13464164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19100189208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20757961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2672553062439</t>
+    <t xml:space="preserve">7.10646057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97218894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98545122146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07496500015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13464069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.191002368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20757913589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26725578308105</t>
   </si>
   <si>
     <t xml:space="preserve">7.26559782028198</t>
@@ -4298,82 +4298,82 @@
     <t xml:space="preserve">7.34019374847412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40152740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40484237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45788764953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49767255783081</t>
+    <t xml:space="preserve">7.40152788162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40484285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45788860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49767208099365</t>
   </si>
   <si>
     <t xml:space="preserve">7.540771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47446489334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58884525299072</t>
+    <t xml:space="preserve">7.54243040084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47446537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58884477615356</t>
   </si>
   <si>
     <t xml:space="preserve">7.6203408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64023303985596</t>
+    <t xml:space="preserve">7.64023399353027</t>
   </si>
   <si>
     <t xml:space="preserve">7.67504405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69327831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52585220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46286058425903</t>
+    <t xml:space="preserve">7.69327783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52585315704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46286153793335</t>
   </si>
   <si>
     <t xml:space="preserve">7.49435710906982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.559006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60542154312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59713363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60210609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66675567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71814441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72643041610718</t>
+    <t xml:space="preserve">7.55900716781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6054220199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59713411331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60210561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66675615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71814346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72643136978149</t>
   </si>
   <si>
     <t xml:space="preserve">7.77782011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45457315444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87604284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03518056869507</t>
+    <t xml:space="preserve">7.45457410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87604331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03518104553223</t>
   </si>
   <si>
     <t xml:space="preserve">6.66883373260498</t>
@@ -4382,28 +4382,28 @@
     <t xml:space="preserve">6.73348331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51135444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76166391372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00037050247192</t>
+    <t xml:space="preserve">6.51135492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76166439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00036907196045</t>
   </si>
   <si>
     <t xml:space="preserve">6.86941289901733</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76663637161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76000595092773</t>
+    <t xml:space="preserve">6.76663684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76000642776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.67214965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83460187911987</t>
+    <t xml:space="preserve">6.83460235595703</t>
   </si>
   <si>
     <t xml:space="preserve">6.93406295776367</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">6.92743158340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01363134384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96887397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89262056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05341577529907</t>
+    <t xml:space="preserve">7.01363182067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96887350082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89262104034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05341529846191</t>
   </si>
   <si>
     <t xml:space="preserve">7.06999158859253</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">7.07993793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15950584411621</t>
+    <t xml:space="preserve">7.15950632095337</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18271398544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0865683555603</t>
+    <t xml:space="preserve">7.18271446228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08656883239746</t>
   </si>
   <si>
     <t xml:space="preserve">7.1429295539856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1634407043457</t>
+    <t xml:space="preserve">7.16344118118286</t>
   </si>
   <si>
     <t xml:space="preserve">7.05917692184448</t>
@@ -4454,40 +4454,40 @@
     <t xml:space="preserve">7.01473665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05746841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00277233123779</t>
+    <t xml:space="preserve">7.05746793746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00277185440063</t>
   </si>
   <si>
     <t xml:space="preserve">6.7805700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85406827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72245645523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92414665222168</t>
+    <t xml:space="preserve">6.85406875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7224555015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92414712905884</t>
   </si>
   <si>
     <t xml:space="preserve">6.92585611343384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92072772979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77031469345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65921401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76005887985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71049118041992</t>
+    <t xml:space="preserve">6.92072725296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77031421661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65921354293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76005935668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71049165725708</t>
   </si>
   <si>
     <t xml:space="preserve">6.71220064163208</t>
@@ -4499,22 +4499,22 @@
     <t xml:space="preserve">6.78569793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9549126625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98738861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93782091140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74638557434082</t>
+    <t xml:space="preserve">6.95491218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98738813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93782043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74638509750366</t>
   </si>
   <si>
     <t xml:space="preserve">6.86774206161499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86261367797852</t>
+    <t xml:space="preserve">6.86261415481567</t>
   </si>
   <si>
     <t xml:space="preserve">6.79082536697388</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">6.84893989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03011989593506</t>
+    <t xml:space="preserve">7.0301194190979</t>
   </si>
   <si>
     <t xml:space="preserve">6.96858692169189</t>
@@ -4538,19 +4538,19 @@
     <t xml:space="preserve">7.00619029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99422597885132</t>
+    <t xml:space="preserve">6.99422550201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.99593448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02328300476074</t>
+    <t xml:space="preserve">7.02328252792358</t>
   </si>
   <si>
     <t xml:space="preserve">7.06259536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09677982330322</t>
+    <t xml:space="preserve">7.09678030014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.1258373260498</t>
@@ -4562,61 +4562,61 @@
     <t xml:space="preserve">7.15660333633423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11045408248901</t>
+    <t xml:space="preserve">7.11045360565186</t>
   </si>
   <si>
     <t xml:space="preserve">7.12754678726196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04208469390869</t>
+    <t xml:space="preserve">7.04208374023438</t>
   </si>
   <si>
     <t xml:space="preserve">6.98226070404053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87116003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94636726379395</t>
+    <t xml:space="preserve">6.87116050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94636678695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.97029638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07797813415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09165334701538</t>
+    <t xml:space="preserve">7.07797861099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09165287017822</t>
   </si>
   <si>
     <t xml:space="preserve">6.96345901489258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90534448623657</t>
+    <t xml:space="preserve">6.90534496307373</t>
   </si>
   <si>
     <t xml:space="preserve">6.72587442398071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84039354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88825273513794</t>
+    <t xml:space="preserve">6.84039402008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8882532119751</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13096475601196</t>
+    <t xml:space="preserve">7.0608868598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13096523284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.12925624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14976692199707</t>
+    <t xml:space="preserve">7.14976739883423</t>
   </si>
   <si>
     <t xml:space="preserve">7.30530834197998</t>
@@ -4625,13 +4625,13 @@
     <t xml:space="preserve">7.34291124343872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3497486114502</t>
+    <t xml:space="preserve">7.34974908828735</t>
   </si>
   <si>
     <t xml:space="preserve">7.38393354415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38564252853394</t>
+    <t xml:space="preserve">7.38564300537109</t>
   </si>
   <si>
     <t xml:space="preserve">7.41982746124268</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">7.44033861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46768522262573</t>
+    <t xml:space="preserve">7.46768665313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.57536888122559</t>
@@ -4649,37 +4649,37 @@
     <t xml:space="preserve">7.55485820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21813726425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20446300506592</t>
+    <t xml:space="preserve">7.2711238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21813631057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20446252822876</t>
   </si>
   <si>
     <t xml:space="preserve">7.20788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19249820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76347780227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94465827941895</t>
+    <t xml:space="preserve">7.19249868392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76347732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94465780258179</t>
   </si>
   <si>
     <t xml:space="preserve">7.0318284034729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13609313964844</t>
+    <t xml:space="preserve">7.1360936164856</t>
   </si>
   <si>
     <t xml:space="preserve">6.97200536727905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91047286987305</t>
+    <t xml:space="preserve">6.91047334671021</t>
   </si>
   <si>
     <t xml:space="preserve">6.92756509780884</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">6.97371482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95662307739258</t>
+    <t xml:space="preserve">6.95662260055542</t>
   </si>
   <si>
     <t xml:space="preserve">6.9497857093811</t>
@@ -4700,55 +4700,55 @@
     <t xml:space="preserve">7.15318536758423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17027807235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21300840377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19078874588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03695726394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17882347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18736982345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1685676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22497367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08139705657959</t>
+    <t xml:space="preserve">7.17027759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21300792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19078826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03695678710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17882299423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18736934661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16856813430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22497415542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08139753341675</t>
   </si>
   <si>
     <t xml:space="preserve">7.11558246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04037523269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841091156006</t>
+    <t xml:space="preserve">7.19933462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04037475585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0284104347229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97884273529053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87799692153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83697509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80279064178467</t>
+    <t xml:space="preserve">6.87799739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83697557449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80279016494751</t>
   </si>
   <si>
     <t xml:space="preserve">6.8916711807251</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">6.76860570907593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86090421676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88312530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76518726348877</t>
+    <t xml:space="preserve">6.86090469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88312482833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76518678665161</t>
   </si>
   <si>
     <t xml:space="preserve">6.78740692138672</t>
@@ -4772,16 +4772,16 @@
     <t xml:space="preserve">6.77715158462524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72416496276855</t>
+    <t xml:space="preserve">6.72416543960571</t>
   </si>
   <si>
     <t xml:space="preserve">6.66946935653687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57887983322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60109949111938</t>
+    <t xml:space="preserve">6.57887935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60109996795654</t>
   </si>
   <si>
     <t xml:space="preserve">6.55153131484985</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">6.48999834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49854469299316</t>
+    <t xml:space="preserve">6.49854516983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.49341726303101</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">6.58571624755859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61819124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74980401992798</t>
+    <t xml:space="preserve">6.61819219589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74980354309082</t>
   </si>
   <si>
     <t xml:space="preserve">6.88483381271362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80449962615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82842874526978</t>
+    <t xml:space="preserve">6.80449914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82842922210693</t>
   </si>
   <si>
     <t xml:space="preserve">6.84552192687988</t>
@@ -4832,13 +4832,13 @@
     <t xml:space="preserve">7.29847145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28137922286987</t>
+    <t xml:space="preserve">7.28137874603271</t>
   </si>
   <si>
     <t xml:space="preserve">7.17198705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19420766830444</t>
+    <t xml:space="preserve">7.19420719146729</t>
   </si>
   <si>
     <t xml:space="preserve">7.29675436019897</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">7.26316118240356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23487281799316</t>
+    <t xml:space="preserve">7.23487234115601</t>
   </si>
   <si>
     <t xml:space="preserve">7.19597578048706</t>
@@ -4862,13 +4862,13 @@
     <t xml:space="preserve">7.17475891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19243907928467</t>
+    <t xml:space="preserve">7.19243860244751</t>
   </si>
   <si>
     <t xml:space="preserve">7.21896028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26669788360596</t>
+    <t xml:space="preserve">7.2666974067688</t>
   </si>
   <si>
     <t xml:space="preserve">7.25785732269287</t>
@@ -4877,7 +4877,7 @@
     <t xml:space="preserve">7.24901676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30029058456421</t>
+    <t xml:space="preserve">7.30029106140137</t>
   </si>
   <si>
     <t xml:space="preserve">7.2773060798645</t>
@@ -4889,25 +4889,25 @@
     <t xml:space="preserve">7.40637397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47532796859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44527053833008</t>
+    <t xml:space="preserve">7.47532749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44527101516724</t>
   </si>
   <si>
     <t xml:space="preserve">7.551353931427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61854028701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54074573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51952838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54781770706177</t>
+    <t xml:space="preserve">7.61853981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5407452583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51952886581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54781723022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.48239994049072</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">7.49654388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54428291320801</t>
+    <t xml:space="preserve">7.54428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">7.58671474456787</t>
@@ -4937,22 +4937,22 @@
     <t xml:space="preserve">7.65390110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79711246490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80241727828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81833028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72815847396851</t>
+    <t xml:space="preserve">7.79711294174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80241775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72815895080566</t>
   </si>
   <si>
     <t xml:space="preserve">7.8625316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04640960693359</t>
+    <t xml:space="preserve">8.04640865325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.11182689666748</t>
@@ -4961,25 +4961,25 @@
     <t xml:space="preserve">8.11005878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21967887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28509521484375</t>
+    <t xml:space="preserve">8.21967792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28509616851807</t>
   </si>
   <si>
     <t xml:space="preserve">8.27625560760498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37880229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43361186981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41946792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26741504669189</t>
+    <t xml:space="preserve">8.37880325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43361282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41946887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26741600036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.36642646789551</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">8.33106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33813762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46366882324219</t>
+    <t xml:space="preserve">8.33813858032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4636697769165</t>
   </si>
   <si>
     <t xml:space="preserve">8.44952487945557</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">8.5732889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67583656311035</t>
+    <t xml:space="preserve">8.67583560943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.75009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50079822540283</t>
+    <t xml:space="preserve">8.50079917907715</t>
   </si>
   <si>
     <t xml:space="preserve">8.68644428253174</t>
@@ -5021,10 +5021,10 @@
     <t xml:space="preserve">8.62456130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5715217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54499912261963</t>
+    <t xml:space="preserve">8.57152080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54500102996826</t>
   </si>
   <si>
     <t xml:space="preserve">8.59273719787598</t>
@@ -5036,37 +5036,37 @@
     <t xml:space="preserve">8.737717628479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783058166504</t>
+    <t xml:space="preserve">8.79783153533936</t>
   </si>
   <si>
     <t xml:space="preserve">8.78722286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7695426940918</t>
+    <t xml:space="preserve">8.76954174041748</t>
   </si>
   <si>
     <t xml:space="preserve">8.79959964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78191947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84026527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88888549804688</t>
+    <t xml:space="preserve">8.7819185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84026432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88888645172119</t>
   </si>
   <si>
     <t xml:space="preserve">8.86236476898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76070117950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73064517974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6298656463623</t>
+    <t xml:space="preserve">8.76070213317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73064613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62986660003662</t>
   </si>
   <si>
     <t xml:space="preserve">8.77661514282227</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">8.82258319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97286891937256</t>
+    <t xml:space="preserve">8.97286701202393</t>
   </si>
   <si>
     <t xml:space="preserve">8.87120532989502</t>
@@ -5084,34 +5084,34 @@
     <t xml:space="preserve">9.07011127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10547256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11431407928467</t>
+    <t xml:space="preserve">9.10547351837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11431312561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.14967441558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13199234008789</t>
+    <t xml:space="preserve">9.13199329376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.06127166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9993896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87562561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07895183563232</t>
+    <t xml:space="preserve">8.99938869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87562656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07895278930664</t>
   </si>
   <si>
     <t xml:space="preserve">9.03475093841553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9551887512207</t>
+    <t xml:space="preserve">8.95518779754639</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910488128662</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">8.91982746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74744129180908</t>
+    <t xml:space="preserve">8.7474422454834</t>
   </si>
   <si>
     <t xml:space="preserve">8.83142471313477</t>
@@ -5138,28 +5138,28 @@
     <t xml:space="preserve">9.12886428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24873924255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14269638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3040657043457</t>
+    <t xml:space="preserve">9.24873828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14269733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30406475067139</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705539703369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41471767425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4792652130127</t>
+    <t xml:space="preserve">9.41471862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47926616668701</t>
   </si>
   <si>
     <t xml:space="preserve">9.62680244445801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66368675231934</t>
+    <t xml:space="preserve">9.66368770599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.70057201385498</t>
@@ -5168,13 +5168,13 @@
     <t xml:space="preserve">9.94954013824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0601930618286</t>
+    <t xml:space="preserve">10.0601940155029</t>
   </si>
   <si>
     <t xml:space="preserve">10.0509719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99564552307129</t>
+    <t xml:space="preserve">9.99564647674561</t>
   </si>
   <si>
     <t xml:space="preserve">9.95876216888428</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">9.7651195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97720432281494</t>
+    <t xml:space="preserve">9.97720336914062</t>
   </si>
   <si>
     <t xml:space="preserve">10.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98642539978027</t>
+    <t xml:space="preserve">9.98642444610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901416778564</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">9.49770832061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55303478240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7927827835083</t>
+    <t xml:space="preserve">9.55303382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79278182983398</t>
   </si>
   <si>
     <t xml:space="preserve">9.68212985992432</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">9.57147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50693035125732</t>
+    <t xml:space="preserve">9.50692939758301</t>
   </si>
   <si>
     <t xml:space="preserve">9.69135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667739868164</t>
+    <t xml:space="preserve">9.74667644500732</t>
   </si>
   <si>
     <t xml:space="preserve">9.82044506072998</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">9.86655044555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91265678405762</t>
+    <t xml:space="preserve">9.9126558303833</t>
   </si>
   <si>
     <t xml:space="preserve">9.96798324584961</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">10.0233097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90343475341797</t>
+    <t xml:space="preserve">9.90343570709229</t>
   </si>
   <si>
     <t xml:space="preserve">10.1062994003296</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">10.2077302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48848724365234</t>
+    <t xml:space="preserve">9.48848628997803</t>
   </si>
   <si>
     <t xml:space="preserve">9.25796031951904</t>
@@ -5282,10 +5282,10 @@
     <t xml:space="preserve">8.99515914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96749687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31328773498535</t>
+    <t xml:space="preserve">8.96749591827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31328678131104</t>
   </si>
   <si>
     <t xml:space="preserve">9.43315982818604</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">9.58991813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82966709136963</t>
+    <t xml:space="preserve">9.82966613769531</t>
   </si>
   <si>
     <t xml:space="preserve">9.84810924530029</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">10.0878562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1892890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2446146011353</t>
+    <t xml:space="preserve">10.1892881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2446155548096</t>
   </si>
   <si>
     <t xml:space="preserve">10.014087677002</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">10.0970773696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0694150924683</t>
+    <t xml:space="preserve">10.0694141387939</t>
   </si>
   <si>
     <t xml:space="preserve">10.1247415542603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1800670623779</t>
+    <t xml:space="preserve">10.1800680160522</t>
   </si>
   <si>
     <t xml:space="preserve">10.3737096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198150634766</t>
+    <t xml:space="preserve">10.4198160171509</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907199859619</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">10.3552675247192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183841705322</t>
+    <t xml:space="preserve">10.3183832168579</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765743255615</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">10.2999420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3091630935669</t>
+    <t xml:space="preserve">10.3091621398926</t>
   </si>
   <si>
     <t xml:space="preserve">10.2169523239136</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">10.2722787857056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276042938232</t>
+    <t xml:space="preserve">10.3276052474976</t>
   </si>
   <si>
     <t xml:space="preserve">10.4567003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4935846328735</t>
+    <t xml:space="preserve">10.4935836791992</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042375564575</t>
@@ -5396,22 +5396,22 @@
     <t xml:space="preserve">10.4474792480469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5581321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134576797485</t>
+    <t xml:space="preserve">10.5581312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134586334229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4843626022339</t>
+    <t xml:space="preserve">10.4843635559082</t>
   </si>
   <si>
     <t xml:space="preserve">10.6226797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7517747879028</t>
+    <t xml:space="preserve">10.7517738342285</t>
   </si>
   <si>
     <t xml:space="preserve">10.9177541732788</t>
@@ -6006,6 +6006,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.4500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6599998474121</t>
   </si>
 </sst>
 </file>
@@ -71110,7 +71113,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494675926</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>2068568</v>
@@ -71131,6 +71134,32 @@
         <v>1997</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6496064815</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>801909</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>16.8199996948242</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>16.5300006866455</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>16.5599994659424</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>16.6599998474121</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="2000">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446674346924</t>
+    <t xml:space="preserve">3.78446698188782</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">3.73277425765991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49607491493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41445446014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901398658752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43349885940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144288063049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658246994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920241355896</t>
+    <t xml:space="preserve">3.49607539176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41445469856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349957466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688502311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658270835876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937628746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29202389717102</t>
   </si>
   <si>
     <t xml:space="preserve">3.10157585144043</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">3.21040320396423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41989588737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077874183655</t>
+    <t xml:space="preserve">3.41989541053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.428058385849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077802658081</t>
   </si>
   <si>
     <t xml:space="preserve">3.35187864303589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36276125907898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2267279624939</t>
+    <t xml:space="preserve">3.36276173591614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22672772407532</t>
   </si>
   <si>
     <t xml:space="preserve">3.13966584205627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18863773345947</t>
+    <t xml:space="preserve">3.18863797187805</t>
   </si>
   <si>
     <t xml:space="preserve">3.30562663078308</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">3.03083848953247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89208340644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15599012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393390655518</t>
+    <t xml:space="preserve">2.89208388328552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15599036216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393438339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.31378936767578</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">3.40357160568237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36548280715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36820316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46614718437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43621945381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36004137992859</t>
+    <t xml:space="preserve">3.36548233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36820363998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46614742279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4362199306488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36004042625427</t>
   </si>
   <si>
     <t xml:space="preserve">3.49063372612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56681251525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409192085266</t>
+    <t xml:space="preserve">3.56681299209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409239768982</t>
   </si>
   <si>
     <t xml:space="preserve">3.69196367263794</t>
@@ -155,73 +155,73 @@
     <t xml:space="preserve">3.71100878715515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61850500106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652272224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623269081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79262900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76542329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70284652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72189116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69468474388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387463569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439423561096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432172775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86608743667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71372818946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63482975959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54232621192932</t>
+    <t xml:space="preserve">3.61850547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652319908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380188941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7409360408783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623245239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79262971878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76542234420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70284605026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181889533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72189164161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6946849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387487411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81439471244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.844322681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86608791351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71372961997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63483023643494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54232597351074</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637842178345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77630472183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821544647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87969064712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91778016090393</t>
+    <t xml:space="preserve">3.77630519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73821568489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87969160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91778063774109</t>
   </si>
   <si>
     <t xml:space="preserve">3.85248422622681</t>
@@ -230,58 +230,58 @@
     <t xml:space="preserve">3.94407725334167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88579082489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9496283531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97460913658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96628260612488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88023972511292</t>
+    <t xml:space="preserve">3.88579177856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94962930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97460889816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9662823677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88023924827576</t>
   </si>
   <si>
     <t xml:space="preserve">3.92464923858643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88856625556946</t>
+    <t xml:space="preserve">3.88856720924377</t>
   </si>
   <si>
     <t xml:space="preserve">4.00236415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9884877204895</t>
+    <t xml:space="preserve">3.98848676681519</t>
   </si>
   <si>
     <t xml:space="preserve">4.04122257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93019986152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07730531692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99681282043457</t>
+    <t xml:space="preserve">3.93020057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07730484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99681377410889</t>
   </si>
   <si>
     <t xml:space="preserve">3.96905827522278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06065082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742371559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93575072288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187333106995</t>
+    <t xml:space="preserve">4.06065130233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742466926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93575167655945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9218738079071</t>
   </si>
   <si>
     <t xml:space="preserve">3.95240473747253</t>
@@ -290,43 +290,43 @@
     <t xml:space="preserve">3.91909766197205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94130182266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08008003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29102373123169</t>
+    <t xml:space="preserve">3.94130229949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08008050918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29102325439453</t>
   </si>
   <si>
     <t xml:space="preserve">4.23551225662231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1633472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18832731246948</t>
+    <t xml:space="preserve">4.16334819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18832778930664</t>
   </si>
   <si>
     <t xml:space="preserve">4.21608304977417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18277645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559150695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15502071380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03289556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0523247718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09673404693604</t>
+    <t xml:space="preserve">4.18277597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15502023696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03289604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05232524871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09673309326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.06342744827271</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">3.69427704811096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53051853179932</t>
+    <t xml:space="preserve">3.53051829338074</t>
   </si>
   <si>
     <t xml:space="preserve">3.55272316932678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48888516426086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60268259048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78587126731873</t>
+    <t xml:space="preserve">3.48888492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60268306732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78587079048157</t>
   </si>
   <si>
     <t xml:space="preserve">3.8247287273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80529975891113</t>
+    <t xml:space="preserve">3.80530023574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.94685363769531</t>
@@ -362,223 +362,223 @@
     <t xml:space="preserve">3.35288262367249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13916420936584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26961588859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23630857467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40561842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41394519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904509544373</t>
+    <t xml:space="preserve">3.13916373252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.269615650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23630881309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4056191444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41394448280334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904438018799</t>
   </si>
   <si>
     <t xml:space="preserve">3.24463534355164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19189977645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410441398621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39174056053162</t>
+    <t xml:space="preserve">3.1919002532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410417556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3917407989502</t>
   </si>
   <si>
     <t xml:space="preserve">3.47778344154358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59713244438171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4972128868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941633224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5388457775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55827403068542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5416202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386475563049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63598990440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58047866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64154100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3945152759552</t>
+    <t xml:space="preserve">3.59713196754456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941680908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53884530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55827379226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54162096977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386499404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63599038124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58047890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6415421962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39451575279236</t>
   </si>
   <si>
     <t xml:space="preserve">3.34455561637878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4194962978363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54717183113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56937599182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46945595741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116905212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280265808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231063842773</t>
+    <t xml:space="preserve">3.41949605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54717230796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56937718391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46945571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41116952896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280194282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231135368347</t>
   </si>
   <si>
     <t xml:space="preserve">3.48055863380432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51664090156555</t>
+    <t xml:space="preserve">3.51664113998413</t>
   </si>
   <si>
     <t xml:space="preserve">3.45002698898315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47500777244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51109004020691</t>
+    <t xml:space="preserve">3.4750075340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51108884811401</t>
   </si>
   <si>
     <t xml:space="preserve">3.56660127639771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58325409889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994750022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59990859031677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49166107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52219176292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50831460952759</t>
+    <t xml:space="preserve">3.58325433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994821548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215166091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264344215393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59990739822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49166011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52219223976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50831437110901</t>
   </si>
   <si>
     <t xml:space="preserve">3.31402468681335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37786293029785</t>
+    <t xml:space="preserve">3.37786197662354</t>
   </si>
   <si>
     <t xml:space="preserve">3.30847334861755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36120963096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38896465301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29737091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19745087623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23075795173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29182076454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26684045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27516651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337416648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39729189872742</t>
+    <t xml:space="preserve">3.36120891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38896441459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29737138748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19745111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23075819015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29182004928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2668399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27516746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337392807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39729142189026</t>
   </si>
   <si>
     <t xml:space="preserve">3.46390533447266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40839409828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4611291885376</t>
+    <t xml:space="preserve">3.4083936214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46112966537476</t>
   </si>
   <si>
     <t xml:space="preserve">3.32235145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38618946075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43059754371643</t>
+    <t xml:space="preserve">3.38618874549866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43059825897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.43614935874939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50276303291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56382536888123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398530006409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33900475502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5443959236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42227244377136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38341331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30014705657959</t>
+    <t xml:space="preserve">3.50276327133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382584571838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3390040397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835447311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54439616203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42227149009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38341355323792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30014681816101</t>
   </si>
   <si>
     <t xml:space="preserve">3.28303289413452</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">3.37715983390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41424012184143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45702576637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48554801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118586540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256031990051</t>
+    <t xml:space="preserve">3.41423964500427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45702433586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48554849624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256079673767</t>
   </si>
   <si>
     <t xml:space="preserve">3.73370146751404</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">3.79930472373962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09309482574463</t>
+    <t xml:space="preserve">4.09309434890747</t>
   </si>
   <si>
     <t xml:space="preserve">3.95047855377197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89343047142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95333027839661</t>
+    <t xml:space="preserve">3.89343190193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95333075523376</t>
   </si>
   <si>
     <t xml:space="preserve">3.93906855583191</t>
@@ -632,82 +632,82 @@
     <t xml:space="preserve">3.93051171302795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85635209083557</t>
+    <t xml:space="preserve">3.8563506603241</t>
   </si>
   <si>
     <t xml:space="preserve">3.92480731010437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90484046936035</t>
+    <t xml:space="preserve">3.90484094619751</t>
   </si>
   <si>
     <t xml:space="preserve">3.93621683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94192123413086</t>
+    <t xml:space="preserve">3.94192028045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.92195510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89628338813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96474027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10735559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12447071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04175329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07883358001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15014171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30131530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.215744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20433568954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26708650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21289253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20718717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09880018234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2357120513916</t>
+    <t xml:space="preserve">3.89628458023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96473979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10735654830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12447023391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04175281524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2442684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1501407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30131483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574592590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20433521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26708698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21289300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20718812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09879970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23571109771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.18151664733887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17010736465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17581224441528</t>
+    <t xml:space="preserve">4.1701078414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1758131980896</t>
   </si>
   <si>
     <t xml:space="preserve">4.03319597244263</t>
@@ -716,130 +716,130 @@
     <t xml:space="preserve">4.03890037536621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07027626037598</t>
+    <t xml:space="preserve">4.08453750610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07027578353882</t>
   </si>
   <si>
     <t xml:space="preserve">3.97044444084167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99326300621033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98185348510742</t>
+    <t xml:space="preserve">3.99326348304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98185396194458</t>
   </si>
   <si>
     <t xml:space="preserve">4.05886650085449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11306095123291</t>
+    <t xml:space="preserve">4.11306047439575</t>
   </si>
   <si>
     <t xml:space="preserve">4.06171941757202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04745721817017</t>
+    <t xml:space="preserve">4.04745626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.02749109268188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75651955604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672232627869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105012893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51977610588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53689026832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692461967468</t>
+    <t xml:space="preserve">3.75651931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672184944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105060577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51977634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53689098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692414283752</t>
   </si>
   <si>
     <t xml:space="preserve">3.63386940956116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68235850334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64242625236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6509838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091534614563</t>
+    <t xml:space="preserve">3.6823582649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64242649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65098333358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091582298279</t>
   </si>
   <si>
     <t xml:space="preserve">3.71943950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73084878921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81641864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7878942489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81071400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779334068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76792788505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78219056129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80215668678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83353161811829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064744949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9076931476593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9162495136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94762682914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9761483669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92766046524048</t>
+    <t xml:space="preserve">3.73084783554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81641912460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7878954410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81071352958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779381752014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76792883872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80215692520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8335325717926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064673423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769267082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91624999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94762587547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97614932060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92765951156616</t>
   </si>
   <si>
     <t xml:space="preserve">3.89057970046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85349941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221230506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87346529960632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10278177261353</t>
+    <t xml:space="preserve">3.85349798202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87346482276917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10278224945068</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869359970093</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">4.11460638046265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15303325653076</t>
+    <t xml:space="preserve">4.1530327796936</t>
   </si>
   <si>
     <t xml:space="preserve">4.12938547134399</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">4.23579692840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23875427246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35107755661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36290121078491</t>
+    <t xml:space="preserve">4.23875379562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34516572952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35107803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36290073394775</t>
   </si>
   <si>
     <t xml:space="preserve">4.35994434356689</t>
@@ -887,64 +887,64 @@
     <t xml:space="preserve">4.39837169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28900337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30082702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3717679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340227127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51956367492676</t>
+    <t xml:space="preserve">4.2890043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30082750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37176847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5195631980896</t>
   </si>
   <si>
     <t xml:space="preserve">4.46931266784668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47522497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45453405380249</t>
+    <t xml:space="preserve">4.47522449493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45453357696533</t>
   </si>
   <si>
     <t xml:space="preserve">4.36881351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33334255218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41315031051636</t>
+    <t xml:space="preserve">4.3333420753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41315126419067</t>
   </si>
   <si>
     <t xml:space="preserve">4.30673885345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41906261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43384218215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38654851913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30969429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.286048412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31856203079224</t>
+    <t xml:space="preserve">4.41906213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43384265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38654804229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30969476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28604745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31856250762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.39246034622192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29491567611694</t>
+    <t xml:space="preserve">4.2949161529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.3362979888916</t>
@@ -953,52 +953,52 @@
     <t xml:space="preserve">4.25353336334229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32447385787964</t>
+    <t xml:space="preserve">4.32447481155396</t>
   </si>
   <si>
     <t xml:space="preserve">4.37472438812256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3274302482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3392539024353</t>
+    <t xml:space="preserve">4.32743120193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33925342559814</t>
   </si>
   <si>
     <t xml:space="preserve">4.38063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49296045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37768077850342</t>
+    <t xml:space="preserve">4.49295949935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3776798248291</t>
   </si>
   <si>
     <t xml:space="preserve">4.40723943710327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38950443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31560754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27126741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21510601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.342209815979</t>
+    <t xml:space="preserve">4.38950395584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31560659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27126932144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21510696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34220933914185</t>
   </si>
   <si>
     <t xml:space="preserve">4.3215184211731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25648880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28309154510498</t>
+    <t xml:space="preserve">4.25648832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2830924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.25057697296143</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">4.23284149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22101783752441</t>
+    <t xml:space="preserve">4.22101736068726</t>
   </si>
   <si>
     <t xml:space="preserve">4.16190004348755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19737005233765</t>
+    <t xml:space="preserve">4.1973705291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.24170923233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17963552474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22397375106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26831245422363</t>
+    <t xml:space="preserve">4.1796350479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22397470474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26831197738647</t>
   </si>
   <si>
     <t xml:space="preserve">4.29195928573608</t>
@@ -1034,40 +1034,40 @@
     <t xml:space="preserve">4.35403347015381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43679857254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42201852798462</t>
+    <t xml:space="preserve">4.43679809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42201995849609</t>
   </si>
   <si>
     <t xml:space="preserve">4.26535606384277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1885027885437</t>
+    <t xml:space="preserve">4.18850326538086</t>
   </si>
   <si>
     <t xml:space="preserve">4.17372417449951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16781234741211</t>
+    <t xml:space="preserve">4.16781187057495</t>
   </si>
   <si>
     <t xml:space="preserve">4.24762105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21806240081787</t>
+    <t xml:space="preserve">4.21806192398071</t>
   </si>
   <si>
     <t xml:space="preserve">4.28013610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23866891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13528633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13832664489746</t>
+    <t xml:space="preserve">4.23866844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13528680801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13832712173462</t>
   </si>
   <si>
     <t xml:space="preserve">4.16873359680176</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">4.25083065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25995349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27211618423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36637592315674</t>
+    <t xml:space="preserve">4.25995445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27211570739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3663763999939</t>
   </si>
   <si>
     <t xml:space="preserve">4.36941623687744</t>
@@ -1094,43 +1094,43 @@
     <t xml:space="preserve">4.34509181976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35117340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32988834381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38157987594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33596849441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39678287506104</t>
+    <t xml:space="preserve">4.35117292404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32988786697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38157939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33596897125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39678239822388</t>
   </si>
   <si>
     <t xml:space="preserve">4.44543266296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50016450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54577445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43935203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48800230026245</t>
+    <t xml:space="preserve">4.5001654624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54577493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43935251235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48800277709961</t>
   </si>
   <si>
     <t xml:space="preserve">4.51232767105103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44847345352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46367692947388</t>
+    <t xml:space="preserve">4.44847393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46367645263672</t>
   </si>
   <si>
     <t xml:space="preserve">4.38766050338745</t>
@@ -1142,34 +1142,34 @@
     <t xml:space="preserve">4.29340076446533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37245798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46063661575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45759630203247</t>
+    <t xml:space="preserve">4.37245750427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46063613891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45759582519531</t>
   </si>
   <si>
     <t xml:space="preserve">4.42718982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55489635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57922220230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62179136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70084810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.725172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74037599563599</t>
+    <t xml:space="preserve">4.55489683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57922172546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62179088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70084857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72517347335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7403769493103</t>
   </si>
   <si>
     <t xml:space="preserve">4.73429489135742</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">4.77078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81639337539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76470184326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80423069000244</t>
+    <t xml:space="preserve">4.81639242172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76470136642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80423021316528</t>
   </si>
   <si>
     <t xml:space="preserve">4.83463621139526</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">4.71301031112671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61571025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.691725730896</t>
+    <t xml:space="preserve">4.61570978164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69172620773315</t>
   </si>
   <si>
     <t xml:space="preserve">4.62787246704102</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">4.25691270828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2994818687439</t>
+    <t xml:space="preserve">4.29948139190674</t>
   </si>
   <si>
     <t xml:space="preserve">4.40590476989746</t>
@@ -1220,46 +1220,46 @@
     <t xml:space="preserve">4.39374208450317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43326950073242</t>
+    <t xml:space="preserve">4.43326997756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.42414808273315</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42110824584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43022966384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52448987960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5032057762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31468486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2781982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32076644897461</t>
+    <t xml:space="preserve">4.42110776901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43022918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.524489402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50320529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31468534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27819728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32076692581177</t>
   </si>
   <si>
     <t xml:space="preserve">4.38461971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41502714157104</t>
+    <t xml:space="preserve">4.41502666473389</t>
   </si>
   <si>
     <t xml:space="preserve">4.40894508361816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35725402832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33292865753174</t>
+    <t xml:space="preserve">4.35725355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3329291343689</t>
   </si>
   <si>
     <t xml:space="preserve">4.2690749168396</t>
@@ -1271,79 +1271,79 @@
     <t xml:space="preserve">4.30556297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23562812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29035949707031</t>
+    <t xml:space="preserve">4.2356276512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29035997390747</t>
   </si>
   <si>
     <t xml:space="preserve">4.2660346031189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26299428939819</t>
+    <t xml:space="preserve">4.26299381256104</t>
   </si>
   <si>
     <t xml:space="preserve">4.22650623321533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21738338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28731918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32380819320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38646936416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32702398300171</t>
+    <t xml:space="preserve">4.21738433837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32380723953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38647031784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32702302932739</t>
   </si>
   <si>
     <t xml:space="preserve">4.20500326156616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11427068710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14555835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16745901107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24567794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23003387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25506353378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254846572876</t>
+    <t xml:space="preserve">4.11427021026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14555788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16745853424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24567747116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23003339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25506401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2425479888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.16120195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21438980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17997407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17058801651001</t>
+    <t xml:space="preserve">4.21438932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17997360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17058753967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.08924055099487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458612442017</t>
+    <t xml:space="preserve">4.02040958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458707809448</t>
   </si>
   <si>
     <t xml:space="preserve">3.83581447601318</t>
@@ -1352,106 +1352,106 @@
     <t xml:space="preserve">3.82329940795898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7763683795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80765557289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81704258918762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79826951026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73882341384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63557696342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195265769958</t>
+    <t xml:space="preserve">3.77636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80765628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81704115867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79826974868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73882412910461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63557600975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195194244385</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262591362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82642817497253</t>
+    <t xml:space="preserve">3.82642793655396</t>
   </si>
   <si>
     <t xml:space="preserve">3.66060543060303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72630882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74508094787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63870477676392</t>
+    <t xml:space="preserve">3.72630953788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74508142471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63870453834534</t>
   </si>
   <si>
     <t xml:space="preserve">3.77011132240295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71692323684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379351615906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74820995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69815063476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68250751495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72317981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7607250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183306694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60116028785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57925891876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6324474811554</t>
+    <t xml:space="preserve">3.71692299842834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379423141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74821019172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69815015792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68250608444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72318077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76072525978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64183354377747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60116004943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57925868034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63244724273682</t>
   </si>
   <si>
     <t xml:space="preserve">3.68876504898071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67624950408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70440816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56361556053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62931895256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686296463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6199324131012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62619042396545</t>
+    <t xml:space="preserve">3.67624855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70440793037415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5636157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.629319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686367988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61993265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6261899471283</t>
   </si>
   <si>
     <t xml:space="preserve">3.8452000617981</t>
@@ -1460,34 +1460,34 @@
     <t xml:space="preserve">3.99537944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88587379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91090440750122</t>
+    <t xml:space="preserve">3.88587331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9109034538269</t>
   </si>
   <si>
     <t xml:space="preserve">3.87023043632507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92341828346252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961626052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84207248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78575444221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79514050483704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77323985099792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7075366973877</t>
+    <t xml:space="preserve">3.92341876029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8420717716217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78575468063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79514074325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7732400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70753693580627</t>
   </si>
   <si>
     <t xml:space="preserve">3.7669825553894</t>
@@ -1496,22 +1496,22 @@
     <t xml:space="preserve">3.80452704429626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81078481674194</t>
+    <t xml:space="preserve">3.81078386306763</t>
   </si>
   <si>
     <t xml:space="preserve">3.80139803886414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75446748733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73256635665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563580513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82017111778259</t>
+    <t xml:space="preserve">3.75446796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73256683349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82017064094543</t>
   </si>
   <si>
     <t xml:space="preserve">3.75759673118591</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">3.81391286849976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77949786186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397361755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335896492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89213061332703</t>
+    <t xml:space="preserve">3.77949690818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397266387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8733594417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89213156700134</t>
   </si>
   <si>
     <t xml:space="preserve">3.99225068092346</t>
@@ -1547,154 +1547,154 @@
     <t xml:space="preserve">3.44472408294678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47288274765015</t>
+    <t xml:space="preserve">3.47288298606873</t>
   </si>
   <si>
     <t xml:space="preserve">3.37276363372803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.375892162323</t>
+    <t xml:space="preserve">3.37589168548584</t>
   </si>
   <si>
     <t xml:space="preserve">3.39466452598572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45098090171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39779353141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31018853187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29141616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24448561668396</t>
+    <t xml:space="preserve">3.4509813785553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39779257774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31018924713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29141688346863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24448537826538</t>
   </si>
   <si>
     <t xml:space="preserve">3.22258448600769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16313862800598</t>
+    <t xml:space="preserve">3.16313886642456</t>
   </si>
   <si>
     <t xml:space="preserve">3.18504023551941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13498115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21006965637207</t>
+    <t xml:space="preserve">3.13498067855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21007013320923</t>
   </si>
   <si>
     <t xml:space="preserve">3.20694088935852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26325845718384</t>
+    <t xml:space="preserve">3.2632577419281</t>
   </si>
   <si>
     <t xml:space="preserve">3.31644630432129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30706024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31331849098206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28515887260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25387167930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27843832969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13193416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541543006897</t>
+    <t xml:space="preserve">3.30706000328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331777572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28515863418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25387120246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2507426738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2784378528595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13193440437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541614532471</t>
   </si>
   <si>
     <t xml:space="preserve">3.25890421867371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32727336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48354411125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44773268699646</t>
+    <t xml:space="preserve">3.32727313041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48354434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44773197174072</t>
   </si>
   <si>
     <t xml:space="preserve">3.44122052192688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42494249343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41843128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146122932434</t>
+    <t xml:space="preserve">3.4249427318573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29146075248718</t>
   </si>
   <si>
     <t xml:space="preserve">3.27192759513855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23351073265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28820490837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40866446495056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33378481864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31099486351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3533182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30773854255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15537476539612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076168060303</t>
+    <t xml:space="preserve">3.2335102558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28820562362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680676460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33378386497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31099534034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15537452697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076191902161</t>
   </si>
   <si>
     <t xml:space="preserve">3.31425023078918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28494954109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4151759147644</t>
+    <t xml:space="preserve">3.2849497795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41517567634583</t>
   </si>
   <si>
     <t xml:space="preserve">3.40215277671814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634159088135</t>
+    <t xml:space="preserve">3.36634111404419</t>
   </si>
   <si>
     <t xml:space="preserve">3.44447636604309</t>
@@ -1703,46 +1703,46 @@
     <t xml:space="preserve">3.46401023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50633406639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48680019378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075463294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331140518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726536750793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45749855041504</t>
+    <t xml:space="preserve">3.50633382797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4867992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075487136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726560592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4574990272522</t>
   </si>
   <si>
     <t xml:space="preserve">3.50958943367004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47052097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5812132358551</t>
+    <t xml:space="preserve">3.47052121162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58121395111084</t>
   </si>
   <si>
     <t xml:space="preserve">3.71795105934143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77655243873596</t>
+    <t xml:space="preserve">3.77655291557312</t>
   </si>
   <si>
     <t xml:space="preserve">3.70818400382996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8318989276886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864332199097</t>
+    <t xml:space="preserve">3.83189797401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864284515381</t>
   </si>
   <si>
     <t xml:space="preserve">3.87096667289734</t>
@@ -1751,43 +1751,43 @@
     <t xml:space="preserve">3.92305684089661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87422180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073396682739</t>
+    <t xml:space="preserve">3.87422227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073301315308</t>
   </si>
   <si>
     <t xml:space="preserve">3.8872447013855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95886921882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00770378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99793696403503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06305027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9718918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01747035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06630516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0825834274292</t>
+    <t xml:space="preserve">3.99142575263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95886874198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00770425796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99793601036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0174708366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956052780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258390426636</t>
   </si>
   <si>
     <t xml:space="preserve">4.12165117263794</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">4.09235000610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11513948440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12816190719604</t>
+    <t xml:space="preserve">4.11514043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12816333770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.0988621711731</t>
@@ -1808,40 +1808,40 @@
     <t xml:space="preserve">4.14118480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08583974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11188411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16071891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1314172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26164436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24862194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24536657333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24211025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23559904098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2323431968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3235011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38210296630859</t>
+    <t xml:space="preserve">4.08583879470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11188459396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16071939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13141775131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26164388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24862146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24210977554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23559951782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23234367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32350158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38210248947144</t>
   </si>
   <si>
     <t xml:space="preserve">4.4048924446106</t>
@@ -1850,67 +1850,70 @@
     <t xml:space="preserve">4.37884759902954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37233686447144</t>
+    <t xml:space="preserve">4.37233591079712</t>
   </si>
   <si>
     <t xml:space="preserve">4.37569236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2884464263916</t>
+    <t xml:space="preserve">4.28844690322876</t>
   </si>
   <si>
     <t xml:space="preserve">4.32871294021606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33206844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41260242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39247035980225</t>
+    <t xml:space="preserve">4.3320689201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39246988296509</t>
   </si>
   <si>
     <t xml:space="preserve">4.36226940155029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23811197280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25153493881226</t>
+    <t xml:space="preserve">4.37233543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22804594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23811292648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25153541564941</t>
   </si>
   <si>
     <t xml:space="preserve">4.14751195907593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10388851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16093349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10724449157715</t>
+    <t xml:space="preserve">4.10388898849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10724401473999</t>
   </si>
   <si>
     <t xml:space="preserve">4.16428899765015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12737894058228</t>
+    <t xml:space="preserve">4.12737798690796</t>
   </si>
   <si>
     <t xml:space="preserve">4.12402248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06697750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07704305648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08039951324463</t>
+    <t xml:space="preserve">4.06697702407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07704401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08039903640747</t>
   </si>
   <si>
     <t xml:space="preserve">4.04684400558472</t>
@@ -1919,28 +1922,28 @@
     <t xml:space="preserve">4.02671003341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00657749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0334210395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09046602249146</t>
+    <t xml:space="preserve">4.00657653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03342151641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09046649932861</t>
   </si>
   <si>
     <t xml:space="preserve">4.14415645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13408899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435598373413</t>
+    <t xml:space="preserve">4.13408994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435646057129</t>
   </si>
   <si>
     <t xml:space="preserve">4.15757894515991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11059999465942</t>
+    <t xml:space="preserve">4.11060047149658</t>
   </si>
   <si>
     <t xml:space="preserve">4.1374454498291</t>
@@ -1952,25 +1955,25 @@
     <t xml:space="preserve">4.19784498214722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21797943115234</t>
+    <t xml:space="preserve">4.21797847747803</t>
   </si>
   <si>
     <t xml:space="preserve">4.24482393264771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34213590621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28173542022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28509092330933</t>
+    <t xml:space="preserve">4.34213542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28173494338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28509187698364</t>
   </si>
   <si>
     <t xml:space="preserve">4.33878040313721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34549140930176</t>
+    <t xml:space="preserve">4.34549188613892</t>
   </si>
   <si>
     <t xml:space="preserve">4.34884643554688</t>
@@ -1982,40 +1985,40 @@
     <t xml:space="preserve">4.50991487503052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4629373550415</t>
+    <t xml:space="preserve">4.46293687820435</t>
   </si>
   <si>
     <t xml:space="preserve">4.45622587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41931390762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978185653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48307037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51662683486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5367603302002</t>
+    <t xml:space="preserve">4.41931486129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48307085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51662731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53675985336304</t>
   </si>
   <si>
     <t xml:space="preserve">4.49313735961914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44280338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.426025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42267036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44951486587524</t>
+    <t xml:space="preserve">4.44280385971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42602634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42267084121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4495153427124</t>
   </si>
   <si>
     <t xml:space="preserve">4.42938137054443</t>
@@ -2024,61 +2027,61 @@
     <t xml:space="preserve">4.5065598487854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46964883804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40924692153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39582586288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20120143890381</t>
+    <t xml:space="preserve">4.4696478843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40924835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39582538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20120048522949</t>
   </si>
   <si>
     <t xml:space="preserve">4.20455646514893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21126890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14080047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33542490005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38575887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46629333496094</t>
+    <t xml:space="preserve">4.21126747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14080142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33542442321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273687362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38575792312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46629285812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.41595888137817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50320339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52333784103394</t>
+    <t xml:space="preserve">4.50320482254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52333831787109</t>
   </si>
   <si>
     <t xml:space="preserve">4.60722732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61729431152344</t>
+    <t xml:space="preserve">4.6172947883606</t>
   </si>
   <si>
     <t xml:space="preserve">4.59716033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70454072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6575608253479</t>
+    <t xml:space="preserve">4.70454025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65756177902222</t>
   </si>
   <si>
     <t xml:space="preserve">4.67769479751587</t>
@@ -2093,10 +2096,10 @@
     <t xml:space="preserve">4.69782876968384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61393928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64078378677368</t>
+    <t xml:space="preserve">4.61393880844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64078283309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.60387229919434</t>
@@ -2105,7 +2108,7 @@
     <t xml:space="preserve">4.62736129760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62400531768799</t>
+    <t xml:space="preserve">4.62400579452515</t>
   </si>
   <si>
     <t xml:space="preserve">4.62065076828003</t>
@@ -2114,16 +2117,16 @@
     <t xml:space="preserve">4.56024980545044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66762733459473</t>
+    <t xml:space="preserve">4.6676287651062</t>
   </si>
   <si>
     <t xml:space="preserve">4.66427278518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66091680526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68105125427246</t>
+    <t xml:space="preserve">4.66091728210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6810507774353</t>
   </si>
   <si>
     <t xml:space="preserve">4.82534074783325</t>
@@ -2132,25 +2135,25 @@
     <t xml:space="preserve">4.86560869216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90251970291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94278717041016</t>
+    <t xml:space="preserve">4.90251922607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94278621673584</t>
   </si>
   <si>
     <t xml:space="preserve">4.98305416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04345512390137</t>
+    <t xml:space="preserve">5.04345417022705</t>
   </si>
   <si>
     <t xml:space="preserve">5.073655128479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08707714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09714365005493</t>
+    <t xml:space="preserve">5.08707761764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09714412689209</t>
   </si>
   <si>
     <t xml:space="preserve">5.1172776222229</t>
@@ -2165,37 +2168,37 @@
     <t xml:space="preserve">5.15754461288452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16425561904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1743221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16761159896851</t>
+    <t xml:space="preserve">5.16425609588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17432260513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16761112213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.23472356796265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54343891143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63403940200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175138473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89241981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77161884307861</t>
+    <t xml:space="preserve">5.54343795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175281524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89241933822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77161836624146</t>
   </si>
   <si>
     <t xml:space="preserve">5.78504085540771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87102508544922</t>
+    <t xml:space="preserve">5.87102460861206</t>
   </si>
   <si>
     <t xml:space="preserve">6.02923727035522</t>
@@ -2213,67 +2216,67 @@
     <t xml:space="preserve">6.21840238571167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32846307754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40068960189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28031158447266</t>
+    <t xml:space="preserve">6.32846260070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909963607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40068912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878087997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28031301498413</t>
   </si>
   <si>
     <t xml:space="preserve">6.2631139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3353419303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38349342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33190298080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496343612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2321605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25967597961426</t>
+    <t xml:space="preserve">6.33534145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38349294662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33190202713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23216009140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2596755027771</t>
   </si>
   <si>
     <t xml:space="preserve">6.23559999465942</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30438804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28375196456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27687168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2493577003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1668119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13585805892944</t>
+    <t xml:space="preserve">6.30438709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28375148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27687215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24935722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16681241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13585758209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.14617586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09114503860474</t>
+    <t xml:space="preserve">6.09114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">6.11866092681885</t>
@@ -2288,13 +2291,13 @@
     <t xml:space="preserve">5.91573762893677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05331325531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00860071182251</t>
+    <t xml:space="preserve">6.0533127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00859975814819</t>
   </si>
   <si>
     <t xml:space="preserve">6.00516128540039</t>
@@ -2303,25 +2306,22 @@
     <t xml:space="preserve">6.10490322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03267621994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92949533462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95700931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90885925292969</t>
+    <t xml:space="preserve">6.03267669677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92949485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95700979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90885829925537</t>
   </si>
   <si>
     <t xml:space="preserve">5.73001050949097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85726737976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78504037857056</t>
+    <t xml:space="preserve">5.8572678565979</t>
   </si>
   <si>
     <t xml:space="preserve">5.60619258880615</t>
@@ -2333,46 +2333,46 @@
     <t xml:space="preserve">5.70249509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66810178756714</t>
+    <t xml:space="preserve">5.66810131072998</t>
   </si>
   <si>
     <t xml:space="preserve">5.71625328063965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77816200256348</t>
+    <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.81255531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80567646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80911636352539</t>
+    <t xml:space="preserve">5.80567693710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80911588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.87790393829346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98108530044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01547908782959</t>
+    <t xml:space="preserve">5.9810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01547861099243</t>
   </si>
   <si>
     <t xml:space="preserve">5.8675856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70593547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40326929092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35511779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37231492996216</t>
+    <t xml:space="preserve">5.70593452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40326881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35511827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.372314453125</t>
   </si>
   <si>
     <t xml:space="preserve">5.24505758285522</t>
@@ -2384,61 +2384,61 @@
     <t xml:space="preserve">5.00430107116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98366451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94927072525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69819498062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58813571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26483392715454</t>
+    <t xml:space="preserve">4.98366498947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9492712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6981954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58813524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26483345031738</t>
   </si>
   <si>
     <t xml:space="preserve">3.75580549240112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71453261375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36509156227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36784291267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08306169509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092998504639</t>
+    <t xml:space="preserve">3.71453285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3650918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36784267425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092974662781</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516004562378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91109299659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90283823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25365543365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35133409500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53568482398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41599440574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24815249443054</t>
+    <t xml:space="preserve">2.91109251976013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90283846855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25365519523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35133385658264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53568434715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4159939289093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24815273284912</t>
   </si>
   <si>
     <t xml:space="preserve">3.19862580299377</t>
@@ -2450,100 +2450,100 @@
     <t xml:space="preserve">3.20000147819519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14359498023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25778293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43938207626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.594153881073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7626838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44969987869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4909725189209</t>
+    <t xml:space="preserve">3.14359545707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25778269767761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43938231468201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59415411949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76268458366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44970035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49097299575806</t>
   </si>
   <si>
     <t xml:space="preserve">3.59759402275085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52880644798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096405982971</t>
+    <t xml:space="preserve">3.52880597114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096429824829</t>
   </si>
   <si>
     <t xml:space="preserve">3.48409390449524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56319952011108</t>
+    <t xml:space="preserve">3.56319975852966</t>
   </si>
   <si>
     <t xml:space="preserve">3.54600310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68013834953308</t>
+    <t xml:space="preserve">3.6801393032074</t>
   </si>
   <si>
     <t xml:space="preserve">3.85554718971252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01031970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83147144317627</t>
+    <t xml:space="preserve">4.01031923294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83147192001343</t>
   </si>
   <si>
     <t xml:space="preserve">3.65950274467468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60447263717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64574503898621</t>
+    <t xml:space="preserve">3.60447216033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64574527740479</t>
   </si>
   <si>
     <t xml:space="preserve">3.6870174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69045686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84866809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745638847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421528816223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80739617347717</t>
+    <t xml:space="preserve">3.69045662879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84866905212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745686531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019951820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421457290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80739521980286</t>
   </si>
   <si>
     <t xml:space="preserve">3.81427526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92089533805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95528888702393</t>
+    <t xml:space="preserve">3.92089581489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95528936386108</t>
   </si>
   <si>
     <t xml:space="preserve">4.03439569473267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07222843170166</t>
+    <t xml:space="preserve">4.07222890853882</t>
   </si>
   <si>
     <t xml:space="preserve">4.16853094100952</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">4.12037944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08598613739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23731851577759</t>
+    <t xml:space="preserve">4.08598661422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23731899261475</t>
   </si>
   <si>
     <t xml:space="preserve">4.2854700088501</t>
@@ -2564,43 +2564,43 @@
     <t xml:space="preserve">4.44712114334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65348386764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7601056098938</t>
+    <t xml:space="preserve">4.65348434448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76010513305664</t>
   </si>
   <si>
     <t xml:space="preserve">4.57781791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33018207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34737873077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49183368682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4436821937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42304515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46775722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45399951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49527215957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30266618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29234838485718</t>
+    <t xml:space="preserve">4.33018255233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34737920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49183320999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44368171691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42304468154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46775770187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4539999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49527168273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30266666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29234886169434</t>
   </si>
   <si>
     <t xml:space="preserve">4.33706045150757</t>
@@ -2609,25 +2609,25 @@
     <t xml:space="preserve">4.37489366531372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39552974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32330322265625</t>
+    <t xml:space="preserve">4.39553070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32330274581909</t>
   </si>
   <si>
     <t xml:space="preserve">4.52622652053833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41616678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52278661727905</t>
+    <t xml:space="preserve">4.41616630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52278757095337</t>
   </si>
   <si>
     <t xml:space="preserve">4.50215101242065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31298542022705</t>
+    <t xml:space="preserve">4.31298494338989</t>
   </si>
   <si>
     <t xml:space="preserve">4.41960573196411</t>
@@ -2636,46 +2636,46 @@
     <t xml:space="preserve">4.47119617462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53310537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53654432296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55718088150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66380262374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61221170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57093858718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52966594696045</t>
+    <t xml:space="preserve">4.53310585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53654527664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55718183517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66380214691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61221122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57093906402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52966642379761</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743894577026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40928792953491</t>
+    <t xml:space="preserve">4.40928840637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.39209127426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42648458480835</t>
+    <t xml:space="preserve">4.42648506164551</t>
   </si>
   <si>
     <t xml:space="preserve">4.26139450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42992401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43680286407471</t>
+    <t xml:space="preserve">4.42992448806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43680238723755</t>
   </si>
   <si>
     <t xml:space="preserve">4.56062126159668</t>
@@ -2696,10 +2696,10 @@
     <t xml:space="preserve">4.56406021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45056056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5950140953064</t>
+    <t xml:space="preserve">4.45056009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59501457214355</t>
   </si>
   <si>
     <t xml:space="preserve">4.51590871810913</t>
@@ -2708,67 +2708,67 @@
     <t xml:space="preserve">4.54686307907104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40240907669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2751522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3508186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35425710678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55030250549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33362197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23044061660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32674264907837</t>
+    <t xml:space="preserve">4.40240955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27515172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35081815719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35425806045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55030202865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33362150192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23044013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32674217224121</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636415481567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27859115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50559091567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43336296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29922819137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30610656738281</t>
+    <t xml:space="preserve">4.27859163284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50559043884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43336343765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29922771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31986331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3061056137085</t>
   </si>
   <si>
     <t xml:space="preserve">4.16165208816528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03783464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98968315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03095579147339</t>
+    <t xml:space="preserve">4.03783512115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98968362808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03095531463623</t>
   </si>
   <si>
     <t xml:space="preserve">4.25107622146606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73258924484253</t>
+    <t xml:space="preserve">4.73258972167969</t>
   </si>
   <si>
     <t xml:space="preserve">4.81169509887695</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">4.96646785736084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20034599304199</t>
+    <t xml:space="preserve">5.20034551620483</t>
   </si>
   <si>
     <t xml:space="preserve">5.19346714019775</t>
@@ -2798,37 +2798,37 @@
     <t xml:space="preserve">5.24161815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37919330596924</t>
+    <t xml:space="preserve">5.3791937828064</t>
   </si>
   <si>
     <t xml:space="preserve">5.26569414138794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34135961532593</t>
+    <t xml:space="preserve">5.3413610458374</t>
   </si>
   <si>
     <t xml:space="preserve">5.23129987716675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29664850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15563297271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11092233657837</t>
+    <t xml:space="preserve">5.2966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1556339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11092185974121</t>
   </si>
   <si>
     <t xml:space="preserve">5.10404300689697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04557371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00774097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00086164474487</t>
+    <t xml:space="preserve">5.04557418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00774049758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00086116790771</t>
   </si>
   <si>
     <t xml:space="preserve">4.91831636428833</t>
@@ -2840,157 +2840,157 @@
     <t xml:space="preserve">4.8942403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89768075942993</t>
+    <t xml:space="preserve">4.89767980575562</t>
   </si>
   <si>
     <t xml:space="preserve">4.8839225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8667254447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76698398590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83577108383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85296773910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89080190658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91487741470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8598461151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87016439437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05933141708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03869438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03181552886963</t>
+    <t xml:space="preserve">4.86672592163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76698350906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83577251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85296869277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89080142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91487693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85984706878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87016534805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05933094024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03869485855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03181600570679</t>
   </si>
   <si>
     <t xml:space="preserve">4.71539258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59845399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53998470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61565017700195</t>
+    <t xml:space="preserve">4.59845352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53998422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61565113067627</t>
   </si>
   <si>
     <t xml:space="preserve">4.67068099975586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02837657928467</t>
+    <t xml:space="preserve">5.02837610244751</t>
   </si>
   <si>
     <t xml:space="preserve">5.12811899185181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31728410720825</t>
+    <t xml:space="preserve">5.31728506088257</t>
   </si>
   <si>
     <t xml:space="preserve">5.25537538528442</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27257299423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2588152885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15219402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07652854919434</t>
+    <t xml:space="preserve">5.27257251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25881576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15219449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07652807235718</t>
   </si>
   <si>
     <t xml:space="preserve">5.0902853012085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14875507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493715286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05245161056519</t>
+    <t xml:space="preserve">5.14875555038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05245208740234</t>
   </si>
   <si>
     <t xml:space="preserve">4.9699068069458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13499736785889</t>
+    <t xml:space="preserve">5.13499784469604</t>
   </si>
   <si>
     <t xml:space="preserve">5.16251277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14187622070312</t>
+    <t xml:space="preserve">5.14187669754028</t>
   </si>
   <si>
     <t xml:space="preserve">5.23817873001099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29320907592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32760286331177</t>
+    <t xml:space="preserve">5.29320955276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32760238647461</t>
   </si>
   <si>
     <t xml:space="preserve">5.34479999542236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33104181289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33792161941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45142126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58899593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44454193115234</t>
+    <t xml:space="preserve">5.33104228973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33792114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45142078399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58899545669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50645065307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708673477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44454145431519</t>
   </si>
   <si>
     <t xml:space="preserve">5.48237466812134</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48925399780273</t>
+    <t xml:space="preserve">5.48925352096558</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53740549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51952075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5511622428894</t>
+    <t xml:space="preserve">5.53740501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51952028274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55116271972656</t>
   </si>
   <si>
     <t xml:space="preserve">5.47824811935425</t>
@@ -2999,37 +2999,37 @@
     <t xml:space="preserve">5.40258169174194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45898723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41221141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41496324539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36543560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38332080841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43972682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39020013809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32554006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37644243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39982986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37506675720215</t>
+    <t xml:space="preserve">5.45898675918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41221189498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41496276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36543607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38332033157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43972635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39019918441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32553911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37644195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39982938766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37506628036499</t>
   </si>
   <si>
     <t xml:space="preserve">5.34617567062378</t>
@@ -3038,25 +3038,25 @@
     <t xml:space="preserve">5.46036291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37368965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43697452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51401662826538</t>
+    <t xml:space="preserve">5.37369012832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43697500228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51401710510254</t>
   </si>
   <si>
     <t xml:space="preserve">5.57730150222778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55529069900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046642303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42321729660034</t>
+    <t xml:space="preserve">5.55529022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4232177734375</t>
   </si>
   <si>
     <t xml:space="preserve">5.44247770309448</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">5.47484111785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43066692352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42928552627563</t>
+    <t xml:space="preserve">5.43066740036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42928647994995</t>
   </si>
   <si>
     <t xml:space="preserve">5.44309091567993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59493970870972</t>
+    <t xml:space="preserve">5.5949387550354</t>
   </si>
   <si>
     <t xml:space="preserve">5.58113527297974</t>
@@ -3086,40 +3086,40 @@
     <t xml:space="preserve">5.5673303604126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57837390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55766725540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70813608169556</t>
+    <t xml:space="preserve">5.57837343215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55766773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60046195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70813655853271</t>
   </si>
   <si>
     <t xml:space="preserve">5.74264621734619</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63773345947266</t>
+    <t xml:space="preserve">5.63773393630981</t>
   </si>
   <si>
     <t xml:space="preserve">5.67224454879761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69571208953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66948318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76473426818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77715873718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500591278076</t>
+    <t xml:space="preserve">5.69571161270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66948366165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76473379135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77715826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6750054359436</t>
   </si>
   <si>
     <t xml:space="preserve">5.65291833877563</t>
@@ -3137,31 +3137,31 @@
     <t xml:space="preserve">5.66120052337646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79234313964844</t>
+    <t xml:space="preserve">5.79234266281128</t>
   </si>
   <si>
     <t xml:space="preserve">5.66258144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328762054443</t>
+    <t xml:space="preserve">5.66534185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68466901779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328809738159</t>
   </si>
   <si>
     <t xml:space="preserve">5.68604850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65015697479248</t>
+    <t xml:space="preserve">5.65015745162964</t>
   </si>
   <si>
     <t xml:space="preserve">5.55352544784546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63635349273682</t>
+    <t xml:space="preserve">5.63635301589966</t>
   </si>
   <si>
     <t xml:space="preserve">5.72746276855469</t>
@@ -3170,49 +3170,49 @@
     <t xml:space="preserve">5.66810321807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68742942810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60460186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59355926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36164474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40443754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57975435256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62392902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362451553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81442975997925</t>
+    <t xml:space="preserve">5.68742847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6046028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59355974197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36164426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40443706512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57975482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62392854690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81443023681641</t>
   </si>
   <si>
     <t xml:space="preserve">5.8199520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79924535751343</t>
+    <t xml:space="preserve">5.79924488067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.79510354995728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73160409927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74540758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71503829956055</t>
+    <t xml:space="preserve">5.73160266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7454080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71503782272339</t>
   </si>
   <si>
     <t xml:space="preserve">5.75507116317749</t>
@@ -3227,31 +3227,31 @@
     <t xml:space="preserve">5.95523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96351861953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04910564422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03116035461426</t>
+    <t xml:space="preserve">5.9635181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04910516738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0311598777771</t>
   </si>
   <si>
     <t xml:space="preserve">6.06981182098389</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03253984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07809448242188</t>
+    <t xml:space="preserve">6.0325403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07809495925903</t>
   </si>
   <si>
     <t xml:space="preserve">5.94695329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92348480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98284435272217</t>
+    <t xml:space="preserve">5.92348527908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98284387588501</t>
   </si>
   <si>
     <t xml:space="preserve">5.97318124771118</t>
@@ -3260,25 +3260,25 @@
     <t xml:space="preserve">5.99802923202515</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98560523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03668117523193</t>
+    <t xml:space="preserve">5.98560428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03668165206909</t>
   </si>
   <si>
     <t xml:space="preserve">6.05048561096191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06705188751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06567049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08775806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09051895141602</t>
+    <t xml:space="preserve">6.06705141067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06567096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08775758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0905179977417</t>
   </si>
   <si>
     <t xml:space="preserve">6.06014919281006</t>
@@ -3290,37 +3290,37 @@
     <t xml:space="preserve">6.03944206237793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01045322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15678071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19681310653687</t>
+    <t xml:space="preserve">6.01045417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15678024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19681262969971</t>
   </si>
   <si>
     <t xml:space="preserve">6.15125846862793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2023344039917</t>
+    <t xml:space="preserve">6.20233488082886</t>
   </si>
   <si>
     <t xml:space="preserve">6.1457371711731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9593768119812</t>
+    <t xml:space="preserve">5.95937633514404</t>
   </si>
   <si>
     <t xml:space="preserve">6.14849710464478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3459005355835</t>
+    <t xml:space="preserve">6.34590101242065</t>
   </si>
   <si>
     <t xml:space="preserve">6.30034685134888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32519435882568</t>
+    <t xml:space="preserve">6.32519340515137</t>
   </si>
   <si>
     <t xml:space="preserve">6.32243299484253</t>
@@ -3329,55 +3329,55 @@
     <t xml:space="preserve">6.39835834503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45357656478882</t>
+    <t xml:space="preserve">6.45357608795166</t>
   </si>
   <si>
     <t xml:space="preserve">6.55710887908936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57229423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343732833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542440414429</t>
+    <t xml:space="preserve">6.57229375839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343637466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60542583465576</t>
   </si>
   <si>
     <t xml:space="preserve">6.72690343856812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66616439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71585893630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72000074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245759963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80697011947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70334053039551</t>
+    <t xml:space="preserve">6.6661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585988998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420827865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72000026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.806969165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82739305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70334100723267</t>
   </si>
   <si>
     <t xml:space="preserve">6.70931911468506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62562131881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61366367340088</t>
+    <t xml:space="preserve">6.62562084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6136646270752</t>
   </si>
   <si>
     <t xml:space="preserve">6.56284666061401</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">6.66149091720581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60917901992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56583642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50605154037476</t>
+    <t xml:space="preserve">6.60917949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56583547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50605201721191</t>
   </si>
   <si>
     <t xml:space="preserve">6.58227586746216</t>
@@ -3401,34 +3401,34 @@
     <t xml:space="preserve">6.49708414077759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.553879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68241691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65850162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66448068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73771667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77657604217529</t>
+    <t xml:space="preserve">6.55388021469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68241548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65850210189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6644811630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73771619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77657508850098</t>
   </si>
   <si>
     <t xml:space="preserve">6.78404951095581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84532833099365</t>
+    <t xml:space="preserve">6.84532928466797</t>
   </si>
   <si>
     <t xml:space="preserve">6.8318772315979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74369525909424</t>
+    <t xml:space="preserve">6.74369478225708</t>
   </si>
   <si>
     <t xml:space="preserve">6.66298627853394</t>
@@ -3440,28 +3440,28 @@
     <t xml:space="preserve">6.7086124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58429431915283</t>
+    <t xml:space="preserve">6.58429384231567</t>
   </si>
   <si>
     <t xml:space="preserve">6.77614402770996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68865966796875</t>
+    <t xml:space="preserve">6.68866014480591</t>
   </si>
   <si>
     <t xml:space="preserve">6.38783931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4384880065918</t>
+    <t xml:space="preserve">6.43848848342896</t>
   </si>
   <si>
     <t xml:space="preserve">6.32951688766479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49374103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44309234619141</t>
+    <t xml:space="preserve">6.49374055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44309186935425</t>
   </si>
   <si>
     <t xml:space="preserve">6.47685718536377</t>
@@ -3470,25 +3470,25 @@
     <t xml:space="preserve">6.5489935874939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6840558052063</t>
+    <t xml:space="preserve">6.68405628204346</t>
   </si>
   <si>
     <t xml:space="preserve">6.62112951278687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56127262115479</t>
+    <t xml:space="preserve">6.56127214431763</t>
   </si>
   <si>
     <t xml:space="preserve">6.51522731781006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.506019115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51062393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52443647384644</t>
+    <t xml:space="preserve">6.50601863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51062297821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52443599700928</t>
   </si>
   <si>
     <t xml:space="preserve">6.4446268081665</t>
@@ -3497,148 +3497,148 @@
     <t xml:space="preserve">6.2451024055481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42927932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48299694061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5888991355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65335893630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74391317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79456090927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85288381576538</t>
+    <t xml:space="preserve">6.42927885055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48299741744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65335941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64568471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7439136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7945613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85288429260254</t>
   </si>
   <si>
     <t xml:space="preserve">6.66410350799561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78688716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84981346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97566843032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10612630844116</t>
+    <t xml:space="preserve">6.78688764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84981489181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97566747665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.106125831604</t>
   </si>
   <si>
     <t xml:space="preserve">7.13221788406372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99255132675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96185493469238</t>
+    <t xml:space="preserve">6.99255084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96185445785522</t>
   </si>
   <si>
     <t xml:space="preserve">6.79763078689575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79149198532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70554351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40779256820679</t>
+    <t xml:space="preserve">6.7914924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70554304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40779161453247</t>
   </si>
   <si>
     <t xml:space="preserve">6.41700124740601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55052804946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51829814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46611452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57201528549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67177772521973</t>
+    <t xml:space="preserve">6.55052757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46611404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57201480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67177724838257</t>
   </si>
   <si>
     <t xml:space="preserve">6.76386594772339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69786882400513</t>
+    <t xml:space="preserve">6.69786787033081</t>
   </si>
   <si>
     <t xml:space="preserve">6.45844078063965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54438877105713</t>
+    <t xml:space="preserve">6.54438924789429</t>
   </si>
   <si>
     <t xml:space="preserve">6.69940328598022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79916572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56894683837891</t>
+    <t xml:space="preserve">6.79916524887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56894588470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.34486436843872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52290201187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47225284576416</t>
+    <t xml:space="preserve">6.52290105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47225379943848</t>
   </si>
   <si>
     <t xml:space="preserve">6.38476943969727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36328172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29575109481812</t>
+    <t xml:space="preserve">6.36328220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29575157165527</t>
   </si>
   <si>
     <t xml:space="preserve">6.23435878753662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2850079536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75089740753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88749408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64960050582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43933296203613</t>
+    <t xml:space="preserve">6.28500747680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75089693069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8874945640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6496000289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43933248519897</t>
   </si>
   <si>
     <t xml:space="preserve">5.46388912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33650064468384</t>
+    <t xml:space="preserve">5.336501121521</t>
   </si>
   <si>
     <t xml:space="preserve">4.98810148239136</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">4.92977857589722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07098054885864</t>
+    <t xml:space="preserve">5.07098007202148</t>
   </si>
   <si>
     <t xml:space="preserve">5.62657833099365</t>
@@ -3659,40 +3659,40 @@
     <t xml:space="preserve">5.41937971115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50993347167969</t>
+    <t xml:space="preserve">5.50993394851685</t>
   </si>
   <si>
     <t xml:space="preserve">5.62811326980591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92126035690308</t>
+    <t xml:space="preserve">5.92126083374023</t>
   </si>
   <si>
     <t xml:space="preserve">5.88135576248169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86447238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82149791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97190856933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90898084640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87214660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92586517333984</t>
+    <t xml:space="preserve">5.86447334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82149839401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97190809249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87214612960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92586469650269</t>
   </si>
   <si>
     <t xml:space="preserve">5.96116495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12538814544678</t>
+    <t xml:space="preserve">6.12538862228394</t>
   </si>
   <si>
     <t xml:space="preserve">6.06860065460205</t>
@@ -3707,13 +3707,13 @@
     <t xml:space="preserve">5.98879098892212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93353843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72787523269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7155966758728</t>
+    <t xml:space="preserve">5.93353796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72787475585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71559619903564</t>
   </si>
   <si>
     <t xml:space="preserve">5.85679864883423</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">5.77084970474243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81842803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86293745040894</t>
+    <t xml:space="preserve">5.81842851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86293697357178</t>
   </si>
   <si>
     <t xml:space="preserve">5.79859828948975</t>
@@ -3737,22 +3737,22 @@
     <t xml:space="preserve">5.89671564102173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87098026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78090476989746</t>
+    <t xml:space="preserve">5.87098073959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78090524673462</t>
   </si>
   <si>
     <t xml:space="preserve">5.6586594581604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56536769866943</t>
+    <t xml:space="preserve">5.56536722183228</t>
   </si>
   <si>
     <t xml:space="preserve">5.60397100448608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55089092254639</t>
+    <t xml:space="preserve">5.55089139938354</t>
   </si>
   <si>
     <t xml:space="preserve">5.61040496826172</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">5.56054210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81146621704102</t>
+    <t xml:space="preserve">5.81146574020386</t>
   </si>
   <si>
     <t xml:space="preserve">5.66348505020142</t>
@@ -3788,22 +3788,22 @@
     <t xml:space="preserve">5.7085223197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74069261550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76321125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68922090530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75516891479492</t>
+    <t xml:space="preserve">5.74069213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76321172714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68922138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510774612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75516939163208</t>
   </si>
   <si>
     <t xml:space="preserve">5.76803636550903</t>
@@ -3821,22 +3821,22 @@
     <t xml:space="preserve">5.84685277938843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75034379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8870644569397</t>
+    <t xml:space="preserve">5.75034332275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706541061401</t>
   </si>
   <si>
     <t xml:space="preserve">5.80503177642822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72299909591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55249929428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17450475692749</t>
+    <t xml:space="preserve">5.72299957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55249977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17450523376465</t>
   </si>
   <si>
     <t xml:space="preserve">4.93323230743408</t>
@@ -3845,31 +3845,31 @@
     <t xml:space="preserve">5.13107585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2082839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01043891906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05226039886475</t>
+    <t xml:space="preserve">5.20828294754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01043939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225992202759</t>
   </si>
   <si>
     <t xml:space="preserve">5.1182074546814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11981582641602</t>
+    <t xml:space="preserve">5.11981678009033</t>
   </si>
   <si>
     <t xml:space="preserve">5.15198659896851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30157518386841</t>
+    <t xml:space="preserve">5.30157613754272</t>
   </si>
   <si>
     <t xml:space="preserve">5.16807079315186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17933034896851</t>
+    <t xml:space="preserve">5.17933082580566</t>
   </si>
   <si>
     <t xml:space="preserve">5.14876890182495</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">5.05386829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88819456100464</t>
+    <t xml:space="preserve">4.80294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88819408416748</t>
   </si>
   <si>
     <t xml:space="preserve">5.03456687927246</t>
@@ -3899,31 +3899,31 @@
     <t xml:space="preserve">5.03295755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10855674743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03778314590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85924100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98631143569946</t>
+    <t xml:space="preserve">5.10855770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0377836227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8592414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91232204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98631191253662</t>
   </si>
   <si>
     <t xml:space="preserve">5.12142467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93484020233154</t>
+    <t xml:space="preserve">4.9348406791687</t>
   </si>
   <si>
     <t xml:space="preserve">5.01848173141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0152645111084</t>
+    <t xml:space="preserve">5.01526403427124</t>
   </si>
   <si>
     <t xml:space="preserve">4.96379280090332</t>
@@ -3932,46 +3932,46 @@
     <t xml:space="preserve">4.99274635314941</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18737268447876</t>
+    <t xml:space="preserve">5.1873722076416</t>
   </si>
   <si>
     <t xml:space="preserve">5.21149969100952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15841960906982</t>
+    <t xml:space="preserve">5.15842008590698</t>
   </si>
   <si>
     <t xml:space="preserve">5.45599031448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59432029724121</t>
+    <t xml:space="preserve">5.59432077407837</t>
   </si>
   <si>
     <t xml:space="preserve">5.50746202468872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48976898193359</t>
+    <t xml:space="preserve">5.48976850509644</t>
   </si>
   <si>
     <t xml:space="preserve">5.46242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50424480438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53641414642334</t>
+    <t xml:space="preserve">5.50424528121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5364146232605</t>
   </si>
   <si>
     <t xml:space="preserve">5.56858444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51067876815796</t>
+    <t xml:space="preserve">5.51067924499512</t>
   </si>
   <si>
     <t xml:space="preserve">5.40291023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44312286376953</t>
+    <t xml:space="preserve">5.44312238693237</t>
   </si>
   <si>
     <t xml:space="preserve">5.33374500274658</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">5.163245677948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0410008430481</t>
+    <t xml:space="preserve">5.04100036621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.14394330978394</t>
@@ -4019,31 +4019,31 @@
     <t xml:space="preserve">5.31766033172607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53963136672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41577863693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49459409713745</t>
+    <t xml:space="preserve">5.53963184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41577816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49459362030029</t>
   </si>
   <si>
     <t xml:space="preserve">5.28870820999146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25653743743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33052825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08925533294678</t>
+    <t xml:space="preserve">5.25653791427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33052730560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08925485610962</t>
   </si>
   <si>
     <t xml:space="preserve">5.15037727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18898105621338</t>
+    <t xml:space="preserve">5.18898153305054</t>
   </si>
   <si>
     <t xml:space="preserve">4.99596261978149</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">5.1600284576416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08603811264038</t>
+    <t xml:space="preserve">5.08603763580322</t>
   </si>
   <si>
     <t xml:space="preserve">5.135901927948</t>
@@ -4061,19 +4061,19 @@
     <t xml:space="preserve">4.9879207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20345735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45920753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39808416366577</t>
+    <t xml:space="preserve">5.20345783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45920705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39808511734009</t>
   </si>
   <si>
     <t xml:space="preserve">5.37878274917603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32409429550171</t>
+    <t xml:space="preserve">5.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">5.33696174621582</t>
@@ -4085,22 +4085,22 @@
     <t xml:space="preserve">5.14555168151855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30961799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35626459121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47368431091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54284906387329</t>
+    <t xml:space="preserve">5.30961751937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35626411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47368383407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54284858703613</t>
   </si>
   <si>
     <t xml:space="preserve">5.61362218856812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64579200744629</t>
+    <t xml:space="preserve">5.64579153060913</t>
   </si>
   <si>
     <t xml:space="preserve">5.67152738571167</t>
@@ -4109,34 +4109,34 @@
     <t xml:space="preserve">5.73908376693726</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90315008163452</t>
+    <t xml:space="preserve">5.90315055847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.92405986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04308795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11707925796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09616756439209</t>
+    <t xml:space="preserve">6.04308843612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11707830429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09616804122925</t>
   </si>
   <si>
     <t xml:space="preserve">6.02539539337158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06560611724854</t>
+    <t xml:space="preserve">6.06560707092285</t>
   </si>
   <si>
     <t xml:space="preserve">6.08651781082153</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21519660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27149343490601</t>
+    <t xml:space="preserve">6.21519613265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27149391174316</t>
   </si>
   <si>
     <t xml:space="preserve">6.24897527694702</t>
@@ -4145,25 +4145,25 @@
     <t xml:space="preserve">6.26023435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716812133789</t>
+    <t xml:space="preserve">6.43716764450073</t>
   </si>
   <si>
     <t xml:space="preserve">6.35996007919312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45968627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49668169021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46451187133789</t>
+    <t xml:space="preserve">6.45968580245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49668216705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46451234817505</t>
   </si>
   <si>
     <t xml:space="preserve">6.45646953582764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50472402572632</t>
+    <t xml:space="preserve">6.50472450256348</t>
   </si>
   <si>
     <t xml:space="preserve">6.50969743728638</t>
@@ -4175,22 +4175,22 @@
     <t xml:space="preserve">6.56108522415161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47820091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4931206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52958869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52461624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53124713897705</t>
+    <t xml:space="preserve">6.47820138931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49312019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52958965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52461671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67878007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53124666213989</t>
   </si>
   <si>
     <t xml:space="preserve">6.61413049697876</t>
@@ -4202,19 +4202,19 @@
     <t xml:space="preserve">6.51301240921021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4748854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52627468109131</t>
+    <t xml:space="preserve">6.47488594055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52627420425415</t>
   </si>
   <si>
     <t xml:space="preserve">6.46825504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54616594314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494818687439</t>
+    <t xml:space="preserve">6.54616641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54948139190674</t>
   </si>
   <si>
     <t xml:space="preserve">6.4400749206543</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">6.39200258255005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55776977539062</t>
+    <t xml:space="preserve">6.55777025222778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51467037200928</t>
@@ -4247,28 +4247,28 @@
     <t xml:space="preserve">6.64728498458862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73514175415039</t>
+    <t xml:space="preserve">6.73514127731323</t>
   </si>
   <si>
     <t xml:space="preserve">6.86609792709351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87935924530029</t>
+    <t xml:space="preserve">6.87935972213745</t>
   </si>
   <si>
     <t xml:space="preserve">7.00202751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04015398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11640739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11806488037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10646057128906</t>
+    <t xml:space="preserve">7.04015445709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11640691757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11806440353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10646104812622</t>
   </si>
   <si>
     <t xml:space="preserve">6.97218894958496</t>
@@ -4277,13 +4277,13 @@
     <t xml:space="preserve">6.98545122146606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07496500015259</t>
+    <t xml:space="preserve">7.07496547698975</t>
   </si>
   <si>
     <t xml:space="preserve">7.13464069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.191002368927</t>
+    <t xml:space="preserve">7.19100093841553</t>
   </si>
   <si>
     <t xml:space="preserve">7.20757913589478</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">7.26559782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34019374847412</t>
+    <t xml:space="preserve">7.34019327163696</t>
   </si>
   <si>
     <t xml:space="preserve">7.40152788162231</t>
@@ -4313,28 +4313,28 @@
     <t xml:space="preserve">7.540771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243040084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47446537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58884477615356</t>
+    <t xml:space="preserve">7.54242944717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47446441650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58884525299072</t>
   </si>
   <si>
     <t xml:space="preserve">7.6203408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64023399353027</t>
+    <t xml:space="preserve">7.64023303985596</t>
   </si>
   <si>
     <t xml:space="preserve">7.67504405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69327783584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52585315704346</t>
+    <t xml:space="preserve">7.69327878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5258526802063</t>
   </si>
   <si>
     <t xml:space="preserve">7.46286153793335</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">7.49435710906982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55900716781616</t>
+    <t xml:space="preserve">7.55900526046753</t>
   </si>
   <si>
     <t xml:space="preserve">7.6054220199585</t>
@@ -4361,37 +4361,37 @@
     <t xml:space="preserve">7.71814346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72643136978149</t>
+    <t xml:space="preserve">7.72643232345581</t>
   </si>
   <si>
     <t xml:space="preserve">7.77782011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45457410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87604331970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03518104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66883373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73348331451416</t>
+    <t xml:space="preserve">7.45457363128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87604379653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03518152236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66883420944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73348379135132</t>
   </si>
   <si>
     <t xml:space="preserve">6.51135492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76166439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00036907196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86941289901733</t>
+    <t xml:space="preserve">6.76166391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00036954879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86941337585449</t>
   </si>
   <si>
     <t xml:space="preserve">6.76663684844971</t>
@@ -4403,40 +4403,40 @@
     <t xml:space="preserve">6.67214965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83460235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93406295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92743158340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01363182067871</t>
+    <t xml:space="preserve">6.83460187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93406248092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92743110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01363086700439</t>
   </si>
   <si>
     <t xml:space="preserve">6.96887350082397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89262104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05341529846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06999158859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07993793487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15950632095337</t>
+    <t xml:space="preserve">6.89262056350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05341577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06999206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07993745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15950536727905</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18271446228027</t>
+    <t xml:space="preserve">7.18271398544312</t>
   </si>
   <si>
     <t xml:space="preserve">7.08656883239746</t>
@@ -4457,13 +4457,13 @@
     <t xml:space="preserve">7.05746793746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00277185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7805700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85406875610352</t>
+    <t xml:space="preserve">7.00277233123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78057050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85406827926636</t>
   </si>
   <si>
     <t xml:space="preserve">6.7224555015564</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">6.92072725296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77031421661377</t>
+    <t xml:space="preserve">6.77031469345093</t>
   </si>
   <si>
     <t xml:space="preserve">6.65921354293823</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">6.76005935668945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71049165725708</t>
+    <t xml:space="preserve">6.71049118041992</t>
   </si>
   <si>
     <t xml:space="preserve">6.71220064163208</t>
@@ -4511,22 +4511,22 @@
     <t xml:space="preserve">6.74638509750366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86774206161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86261415481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79082536697388</t>
+    <t xml:space="preserve">6.86774158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86261367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79082584381104</t>
   </si>
   <si>
     <t xml:space="preserve">6.73100185394287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84893989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0301194190979</t>
+    <t xml:space="preserve">6.84893941879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011989593506</t>
   </si>
   <si>
     <t xml:space="preserve">6.96858692169189</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">6.99422550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99593448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02328252792358</t>
+    <t xml:space="preserve">6.99593496322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02328300476074</t>
   </si>
   <si>
     <t xml:space="preserve">7.06259536743164</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">7.11045360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12754678726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04208374023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98226070404053</t>
+    <t xml:space="preserve">7.1275463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04208421707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98226118087769</t>
   </si>
   <si>
     <t xml:space="preserve">6.87116050720215</t>
@@ -4598,16 +4598,16 @@
     <t xml:space="preserve">6.72587442398071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84039402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8882532119751</t>
+    <t xml:space="preserve">6.84039354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88825273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0608868598938</t>
+    <t xml:space="preserve">7.06088638305664</t>
   </si>
   <si>
     <t xml:space="preserve">7.13096523284912</t>
@@ -4619,7 +4619,7 @@
     <t xml:space="preserve">7.14976739883423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30530834197998</t>
+    <t xml:space="preserve">7.30530786514282</t>
   </si>
   <si>
     <t xml:space="preserve">7.34291124343872</t>
@@ -4628,10 +4628,10 @@
     <t xml:space="preserve">7.34974908828735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38393354415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38564300537109</t>
+    <t xml:space="preserve">7.38393306732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38564252853394</t>
   </si>
   <si>
     <t xml:space="preserve">7.41982746124268</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">7.20446252822876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788097381592</t>
+    <t xml:space="preserve">7.20788145065308</t>
   </si>
   <si>
     <t xml:space="preserve">7.19249868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76347732543945</t>
+    <t xml:space="preserve">6.76347780227661</t>
   </si>
   <si>
     <t xml:space="preserve">6.94465780258179</t>
@@ -4709,13 +4709,13 @@
     <t xml:space="preserve">7.19078826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03695678710938</t>
+    <t xml:space="preserve">7.03695726394653</t>
   </si>
   <si>
     <t xml:space="preserve">7.17882299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18736934661865</t>
+    <t xml:space="preserve">7.18736982345581</t>
   </si>
   <si>
     <t xml:space="preserve">7.16856813430786</t>
@@ -4736,7 +4736,7 @@
     <t xml:space="preserve">7.04037475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0284104347229</t>
+    <t xml:space="preserve">7.02841091156006</t>
   </si>
   <si>
     <t xml:space="preserve">6.97884273529053</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">6.76860570907593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86090469360352</t>
+    <t xml:space="preserve">6.86090421676636</t>
   </si>
   <si>
     <t xml:space="preserve">6.88312482833862</t>
@@ -4769,19 +4769,19 @@
     <t xml:space="preserve">6.78740692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77715158462524</t>
+    <t xml:space="preserve">6.7771520614624</t>
   </si>
   <si>
     <t xml:space="preserve">6.72416543960571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66946935653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57887935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60109996795654</t>
+    <t xml:space="preserve">6.66946887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57887983322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60109949111938</t>
   </si>
   <si>
     <t xml:space="preserve">6.55153131484985</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">6.48999834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49854516983032</t>
+    <t xml:space="preserve">6.49854469299316</t>
   </si>
   <si>
     <t xml:space="preserve">6.49341726303101</t>
@@ -4811,10 +4811,10 @@
     <t xml:space="preserve">6.88483381271362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80449914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82842922210693</t>
+    <t xml:space="preserve">6.80449962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82842874526978</t>
   </si>
   <si>
     <t xml:space="preserve">6.84552192687988</t>
@@ -4829,16 +4829,16 @@
     <t xml:space="preserve">7.16685914993286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29847145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28137874603271</t>
+    <t xml:space="preserve">7.29847097396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28137922286987</t>
   </si>
   <si>
     <t xml:space="preserve">7.17198705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19420719146729</t>
+    <t xml:space="preserve">7.19420766830444</t>
   </si>
   <si>
     <t xml:space="preserve">7.29675436019897</t>
@@ -6009,6 +6009,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.6599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6200008392334</t>
   </si>
 </sst>
 </file>
@@ -28387,7 +28390,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28413,7 +28416,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G849" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28439,7 +28442,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G850" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28465,7 +28468,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28491,7 +28494,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28517,7 +28520,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G853" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28543,7 +28546,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G854" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28569,7 +28572,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28595,7 +28598,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G856" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28621,7 +28624,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G857" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28647,7 +28650,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G858" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28673,7 +28676,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G859" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28699,7 +28702,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G860" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28725,7 +28728,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28751,7 +28754,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G862" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28777,7 +28780,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28803,7 +28806,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28829,7 +28832,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G865" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28855,7 +28858,7 @@
         <v>6</v>
       </c>
       <c r="G866" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28881,7 +28884,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G867" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28907,7 +28910,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G868" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28933,7 +28936,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G869" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28959,7 +28962,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G870" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28985,7 +28988,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G871" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29011,7 +29014,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G872" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29037,7 +29040,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29063,7 +29066,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G874" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29089,7 +29092,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29115,7 +29118,7 @@
         <v>6.125</v>
       </c>
       <c r="G876" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29141,7 +29144,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G877" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -29167,7 +29170,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G878" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -29193,7 +29196,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29219,7 +29222,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -29245,7 +29248,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G881" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -29271,7 +29274,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G882" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -29297,7 +29300,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G883" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -29323,7 +29326,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G884" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -29349,7 +29352,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G885" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -29375,7 +29378,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G886" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29401,7 +29404,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G887" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29427,7 +29430,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G888" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -29453,7 +29456,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G889" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -29479,7 +29482,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G890" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -29505,7 +29508,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G891" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29531,7 +29534,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29557,7 +29560,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29583,7 +29586,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G894" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29609,7 +29612,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29635,7 +29638,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G896" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29661,7 +29664,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G897" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29687,7 +29690,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G898" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29713,7 +29716,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29739,7 +29742,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G900" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29765,7 +29768,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G901" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29791,7 +29794,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G902" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29817,7 +29820,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29843,7 +29846,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29869,7 +29872,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G905" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29895,7 +29898,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29921,7 +29924,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G907" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29947,7 +29950,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G908" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29973,7 +29976,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G909" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30025,7 +30028,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G911" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -30051,7 +30054,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G912" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -30077,7 +30080,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -30103,7 +30106,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G914" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -30129,7 +30132,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G915" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -30155,7 +30158,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G916" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -30181,7 +30184,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G917" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -30207,7 +30210,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G918" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30233,7 +30236,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G919" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30259,7 +30262,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G920" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30285,7 +30288,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30311,7 +30314,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30363,7 +30366,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G924" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30389,7 +30392,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30415,7 +30418,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G926" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30441,7 +30444,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G927" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30467,7 +30470,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G928" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30493,7 +30496,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G929" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30519,7 +30522,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G930" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30545,7 +30548,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G931" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30571,7 +30574,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30597,7 +30600,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G933" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30623,7 +30626,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G934" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30649,7 +30652,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30675,7 +30678,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G936" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30701,7 +30704,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G937" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30727,7 +30730,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G938" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30753,7 +30756,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30779,7 +30782,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G940" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30805,7 +30808,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G941" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30831,7 +30834,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G942" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30857,7 +30860,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G943" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30883,7 +30886,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G944" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30909,7 +30912,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30935,7 +30938,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G946" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30961,7 +30964,7 @@
         <v>7</v>
       </c>
       <c r="G947" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30987,7 +30990,7 @@
         <v>6.875</v>
       </c>
       <c r="G948" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31013,7 +31016,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31039,7 +31042,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G950" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31065,7 +31068,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G951" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31091,7 +31094,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31117,7 +31120,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G953" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31143,7 +31146,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G954" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31169,7 +31172,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31195,7 +31198,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G956" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31221,7 +31224,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G957" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31247,7 +31250,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G958" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31273,7 +31276,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G959" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31299,7 +31302,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G960" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31325,7 +31328,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G961" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31351,7 +31354,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G962" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31377,7 +31380,7 @@
         <v>7.25</v>
       </c>
       <c r="G963" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31403,7 +31406,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G964" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31429,7 +31432,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G965" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31455,7 +31458,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31481,7 +31484,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G967" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31507,7 +31510,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G968" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31533,7 +31536,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G969" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31559,7 +31562,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G970" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31585,7 +31588,7 @@
         <v>7.625</v>
       </c>
       <c r="G971" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31611,7 +31614,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G972" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31637,7 +31640,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G973" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31663,7 +31666,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31689,7 +31692,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G975" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31715,7 +31718,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G976" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31741,7 +31744,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G977" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31767,7 +31770,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G978" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31793,7 +31796,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G979" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31819,7 +31822,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G980" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31845,7 +31848,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G981" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31871,7 +31874,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G982" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31897,7 +31900,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G983" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31923,7 +31926,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G984" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31949,7 +31952,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G985" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31975,7 +31978,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G986" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -32001,7 +32004,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G987" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32027,7 +32030,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G988" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32053,7 +32056,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G989" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32079,7 +32082,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G990" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32105,7 +32108,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G991" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32131,7 +32134,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G992" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -32157,7 +32160,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G993" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -32183,7 +32186,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32209,7 +32212,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G995" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32235,7 +32238,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G996" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32261,7 +32264,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G997" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32287,7 +32290,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G998" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32313,7 +32316,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G999" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32339,7 +32342,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32365,7 +32368,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1001" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -32391,7 +32394,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32417,7 +32420,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G1003" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32443,7 +32446,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1004" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -32469,7 +32472,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1005" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32495,7 +32498,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1006" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32521,7 +32524,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1007" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32547,7 +32550,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32573,7 +32576,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G1009" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32599,7 +32602,7 @@
         <v>9.125</v>
       </c>
       <c r="G1010" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32625,7 +32628,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32651,7 +32654,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G1012" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32677,7 +32680,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1013" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32703,7 +32706,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1014" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32729,7 +32732,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1015" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32755,7 +32758,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G1016" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32781,7 +32784,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G1017" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32807,7 +32810,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1018" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32833,7 +32836,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1019" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32859,7 +32862,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1020" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32885,7 +32888,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G1021" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32911,7 +32914,7 @@
         <v>9</v>
       </c>
       <c r="G1022" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32937,7 +32940,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1023" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32963,7 +32966,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1024" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32989,7 +32992,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1025" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -33015,7 +33018,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1026" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -33041,7 +33044,7 @@
         <v>8.875</v>
       </c>
       <c r="G1027" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -33067,7 +33070,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1028" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -33093,7 +33096,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1029" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -33119,7 +33122,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1030" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -33145,7 +33148,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1031" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -33171,7 +33174,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1032" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -33197,7 +33200,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33223,7 +33226,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1034" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33249,7 +33252,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1035" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33275,7 +33278,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1036" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33379,7 +33382,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33535,7 +33538,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1046" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -71139,7 +71142,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6496064815</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>801909</v>
@@ -71160,6 +71163,32 @@
         <v>1998</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6494675926</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>861261</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>16.8400001525879</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>16.5799999237061</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>16.7099990844727</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>16.6200008392334</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1999</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="2001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="2002">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446769714355</t>
+    <t xml:space="preserve">3.78446674346924</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49607563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41445446014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901303291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43350028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144407272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688454627991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658246994019</t>
+    <t xml:space="preserve">3.73277425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49607443809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4144549369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144311904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688502311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658294677734</t>
   </si>
   <si>
     <t xml:space="preserve">3.25937604904175</t>
@@ -74,37 +74,37 @@
     <t xml:space="preserve">3.29202437400818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10157608985901</t>
+    <t xml:space="preserve">3.10157585144043</t>
   </si>
   <si>
     <t xml:space="preserve">3.21040344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41989684104919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276197433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22672772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13966608047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18863844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30562710762024</t>
+    <t xml:space="preserve">3.41989612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.428058385849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077898025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187935829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276125907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22672820091248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13966655731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18863868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30562782287598</t>
   </si>
   <si>
     <t xml:space="preserve">3.03083872795105</t>
@@ -113,40 +113,40 @@
     <t xml:space="preserve">2.89208340644836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1559898853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393486022949</t>
+    <t xml:space="preserve">3.15598964691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393438339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.3137891292572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40357208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36548209190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36820316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46614766120911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43622016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36004090309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49063420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56681299209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409192085266</t>
+    <t xml:space="preserve">3.40357184410095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36548280715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36820340156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46614742279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4362199306488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36004114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49063348770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56681275367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409239768982</t>
   </si>
   <si>
     <t xml:space="preserve">3.69196391105652</t>
@@ -155,76 +155,76 @@
     <t xml:space="preserve">3.71100902557373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61850547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380188941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093699455261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623245239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79262948036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76542258262634</t>
+    <t xml:space="preserve">3.61850523948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652319908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380093574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093580245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79262852668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76542282104492</t>
   </si>
   <si>
     <t xml:space="preserve">3.70284605026245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75181984901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72189164161682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69468426704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439566612244</t>
+    <t xml:space="preserve">3.75181794166565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7218918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6946849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8143949508667</t>
   </si>
   <si>
     <t xml:space="preserve">3.84432220458984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86608719825745</t>
+    <t xml:space="preserve">3.86608672142029</t>
   </si>
   <si>
     <t xml:space="preserve">3.71372961997986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63482880592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54232668876648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74637722969055</t>
+    <t xml:space="preserve">3.63482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54232597351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74637794494629</t>
   </si>
   <si>
     <t xml:space="preserve">3.77630519866943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73821616172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8796911239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91778039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85248374938965</t>
+    <t xml:space="preserve">3.73821568489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87969160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91778063774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85248422622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.94407820701599</t>
@@ -236,73 +236,73 @@
     <t xml:space="preserve">3.94962930679321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96628165245056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88023948669434</t>
+    <t xml:space="preserve">3.97460985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9662823677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88023924827576</t>
   </si>
   <si>
     <t xml:space="preserve">3.92464900016785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88856601715088</t>
+    <t xml:space="preserve">3.88856649398804</t>
   </si>
   <si>
     <t xml:space="preserve">4.00236463546753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98848652839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04122257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93019914627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07730531692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99681377410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96905755996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06065130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742395401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93575096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95240473747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9190981388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08008003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29102325439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.235511302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16334772109985</t>
+    <t xml:space="preserve">3.98848628997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04122304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93019962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07730484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99681353569031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96905851364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0606517791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742538452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93575119972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92187285423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9524040222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91909718513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130206108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08008050918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29102277755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23551225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1633472442627</t>
   </si>
   <si>
     <t xml:space="preserve">4.18832731246948</t>
@@ -311,25 +311,25 @@
     <t xml:space="preserve">4.21608352661133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.182776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559150695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15502023696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03289556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05232524871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09673309326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06342649459839</t>
+    <t xml:space="preserve">4.18277645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559198379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15502166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03289604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0523247718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09673357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06342697143555</t>
   </si>
   <si>
     <t xml:space="preserve">3.69427680969238</t>
@@ -338,58 +338,58 @@
     <t xml:space="preserve">3.5305187702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5527229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4888858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60268354415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78587102890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82472896575928</t>
+    <t xml:space="preserve">3.5527241230011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48888540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6026828289032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78587055206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8247287273407</t>
   </si>
   <si>
     <t xml:space="preserve">3.80530023574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94685363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288214683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13916420936584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26961612701416</t>
+    <t xml:space="preserve">3.94685316085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288286209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13916444778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26961493492126</t>
   </si>
   <si>
     <t xml:space="preserve">3.23630881309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40561866760254</t>
+    <t xml:space="preserve">3.40561819076538</t>
   </si>
   <si>
     <t xml:space="preserve">3.41394472122192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28904485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463534355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19189977645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410465240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39174008369446</t>
+    <t xml:space="preserve">3.28904461860657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463486671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19190001487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39174103736877</t>
   </si>
   <si>
     <t xml:space="preserve">3.47778296470642</t>
@@ -398,91 +398,91 @@
     <t xml:space="preserve">3.59713220596313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49721169471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53884506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55827379226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5416214466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386594772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63599014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58047866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64154028892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3945152759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3445565700531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5471715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56937694549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4111692905426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280289649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231111526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48055791854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51664090156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45002698898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47500777244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51108956336975</t>
+    <t xml:space="preserve">3.49721240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941561698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53884530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55827403068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54162096977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386475563049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63599061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58047890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64154100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39451599121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34455561637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949582099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54717206954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56937623023987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4694561958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41116881370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280265808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231135368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4805588722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51664137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45002770423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47500729560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51108980178833</t>
   </si>
   <si>
     <t xml:space="preserve">3.56660175323486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58325386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994821548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264344215393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59990787506104</t>
+    <t xml:space="preserve">3.58325481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994750022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215166091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59990835189819</t>
   </si>
   <si>
     <t xml:space="preserve">3.49166083335876</t>
@@ -491,52 +491,52 @@
     <t xml:space="preserve">3.52219176292419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50831365585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31402397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37786316871643</t>
+    <t xml:space="preserve">3.50831460952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31402492523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37786293029785</t>
   </si>
   <si>
     <t xml:space="preserve">3.30847334861755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36120867729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38896465301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29737114906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19745063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23075747489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29182004928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26684021949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27516603469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337368965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39729118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46390557289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839338302612</t>
+    <t xml:space="preserve">3.36120915412903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38896489143372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29737162590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19745087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23075699806213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29182028770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2668399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27516722679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39729189872742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46390509605408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">3.46112966537476</t>
@@ -545,121 +545,121 @@
     <t xml:space="preserve">3.3223512172699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38618946075439</t>
+    <t xml:space="preserve">3.38618969917297</t>
   </si>
   <si>
     <t xml:space="preserve">3.43059849739075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43615007400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50276374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5638256072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398482322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33900451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835423469543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54439663887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42227220535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38341355323792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30014705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2830331325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37145495414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39142203330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37715983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41424012184143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45702481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48554825782776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118586540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73370099067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930448532104</t>
+    <t xml:space="preserve">3.43614912033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50276303291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382536888123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398410797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33900499343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835447311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54439687728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42227172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38341379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30014729499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28303289413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37145471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3914213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37715911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41423940658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45702505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48554873466492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118491172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256031990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73370146751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7993049621582</t>
   </si>
   <si>
     <t xml:space="preserve">4.09309434890747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95047783851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89343166351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95333003997803</t>
+    <t xml:space="preserve">3.95047855377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89343214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95333051681519</t>
   </si>
   <si>
     <t xml:space="preserve">3.93906903266907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93051171302795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635113716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92480707168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90484046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93621611595154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94192099571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92195534706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89628338813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96473979949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10735559463501</t>
+    <t xml:space="preserve">3.93051218986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635137557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92480659484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90483975410461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93621683120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9419207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92195439338684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89628386497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96474003791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10735654830933</t>
   </si>
   <si>
     <t xml:space="preserve">4.12447023391724</t>
@@ -671,58 +671,58 @@
     <t xml:space="preserve">4.07883262634277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24426794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15014123916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30131483078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.215744972229</t>
+    <t xml:space="preserve">4.2442684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1501407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30131435394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574449539185</t>
   </si>
   <si>
     <t xml:space="preserve">4.20433521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26708698272705</t>
+    <t xml:space="preserve">4.26708793640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.21289253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20718812942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09879875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2357120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18151712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17010736465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17581224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03319644927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03889942169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08453750610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07027578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97044444084167</t>
+    <t xml:space="preserve">4.20718717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09879922866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23571109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18151760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17010688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1758131980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03319549560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03890037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08453798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07027626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97044467926025</t>
   </si>
   <si>
     <t xml:space="preserve">3.99326324462891</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.05886650085449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11306095123291</t>
+    <t xml:space="preserve">4.11306142807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.06171894073486</t>
@@ -743,40 +743,40 @@
     <t xml:space="preserve">4.04745721817017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02749061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75651884078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672161102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105132102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51977705955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688955307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692461967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386940956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68235850334167</t>
+    <t xml:space="preserve">4.02749109268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75651955604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105036735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.519775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53689050674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.633868932724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6823582649231</t>
   </si>
   <si>
     <t xml:space="preserve">3.64242672920227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65098309516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091606140137</t>
+    <t xml:space="preserve">3.65098404884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091582298279</t>
   </si>
   <si>
     <t xml:space="preserve">3.7194390296936</t>
@@ -785,67 +785,67 @@
     <t xml:space="preserve">3.73084878921509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81641840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78789496421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81071329116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779381752014</t>
+    <t xml:space="preserve">3.81641888618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78789567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81071424484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779500961304</t>
   </si>
   <si>
     <t xml:space="preserve">3.76792931556702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78219079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8021559715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83353185653687</t>
+    <t xml:space="preserve">3.78219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80215764045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83353209495544</t>
   </si>
   <si>
     <t xml:space="preserve">3.85064601898193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90769362449646</t>
+    <t xml:space="preserve">3.90769290924072</t>
   </si>
   <si>
     <t xml:space="preserve">3.91625022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9476261138916</t>
+    <t xml:space="preserve">3.94762635231018</t>
   </si>
   <si>
     <t xml:space="preserve">3.97614908218384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92765998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89057898521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349893569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221230506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8734655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10278272628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10869455337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17076778411865</t>
+    <t xml:space="preserve">3.927659034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058017730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349869728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87346601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10278177261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10869359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17076730728149</t>
   </si>
   <si>
     <t xml:space="preserve">4.11460542678833</t>
@@ -854,58 +854,58 @@
     <t xml:space="preserve">4.1530327796936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12938499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10573816299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23579740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919466018677</t>
+    <t xml:space="preserve">4.12938547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10573863983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16485691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23579835891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875331878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919418334961</t>
   </si>
   <si>
     <t xml:space="preserve">4.34516525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35107755661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36290121078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35994529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39837121963501</t>
+    <t xml:space="preserve">4.35107803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36290073394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35994577407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39837169647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.28900384902954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30082702636719</t>
+    <t xml:space="preserve">4.30082750320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.3717679977417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46340131759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51956272125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46931266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47522497177124</t>
+    <t xml:space="preserve">4.46340227127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51956367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46931314468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4752254486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.45453405380249</t>
@@ -914,28 +914,28 @@
     <t xml:space="preserve">4.36881303787231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33334302902222</t>
+    <t xml:space="preserve">4.33334159851074</t>
   </si>
   <si>
     <t xml:space="preserve">4.41315174102783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30673837661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41906261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4338436126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38654899597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30969476699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.286048412323</t>
+    <t xml:space="preserve">4.30673933029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41906309127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43384218215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38654804229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30969572067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28604698181152</t>
   </si>
   <si>
     <t xml:space="preserve">4.31856298446655</t>
@@ -944,55 +944,55 @@
     <t xml:space="preserve">4.39245939254761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29491519927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33629846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25353288650513</t>
+    <t xml:space="preserve">4.29491472244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3362979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25353336334229</t>
   </si>
   <si>
     <t xml:space="preserve">4.3244743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37472438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32742977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33925437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38063621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49295997619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37768077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40723943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38950395584106</t>
+    <t xml:space="preserve">4.37472486495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3274302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3392539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38063526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49296092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37768030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40724039077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38950443267822</t>
   </si>
   <si>
     <t xml:space="preserve">4.31560659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27126789093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21510696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.342209815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32151889801025</t>
+    <t xml:space="preserve">4.27126884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21510648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34220886230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32151794433594</t>
   </si>
   <si>
     <t xml:space="preserve">4.25648880004883</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">4.28309154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25057697296143</t>
+    <t xml:space="preserve">4.25057649612427</t>
   </si>
   <si>
     <t xml:space="preserve">4.23284101486206</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22101879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16189956665039</t>
+    <t xml:space="preserve">4.22101831436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16190052032471</t>
   </si>
   <si>
     <t xml:space="preserve">4.19737100601196</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">4.17963600158691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22397422790527</t>
+    <t xml:space="preserve">4.22397470474243</t>
   </si>
   <si>
     <t xml:space="preserve">4.26831245422363</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">4.29195976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35403251647949</t>
+    <t xml:space="preserve">4.35403347015381</t>
   </si>
   <si>
     <t xml:space="preserve">4.43679857254028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42201852798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26535654067993</t>
+    <t xml:space="preserve">4.42201805114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26535606384277</t>
   </si>
   <si>
     <t xml:space="preserve">4.1885027885437</t>
@@ -1049,58 +1049,58 @@
     <t xml:space="preserve">4.17372417449951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16781187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24762153625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21806287765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28013515472412</t>
+    <t xml:space="preserve">4.16781234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24762105941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21806240081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28013610839844</t>
   </si>
   <si>
     <t xml:space="preserve">4.23866891860962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13528680801392</t>
+    <t xml:space="preserve">4.1352858543396</t>
   </si>
   <si>
     <t xml:space="preserve">4.13832712173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16873407363892</t>
+    <t xml:space="preserve">4.1687331199646</t>
   </si>
   <si>
     <t xml:space="preserve">4.16569328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25083208084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25995349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27211570739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36637496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3694167137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509134292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117197036743</t>
+    <t xml:space="preserve">4.25083112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25995397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27211666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36637592315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36941766738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117244720459</t>
   </si>
   <si>
     <t xml:space="preserve">4.32988834381104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38157892227173</t>
+    <t xml:space="preserve">4.38157939910889</t>
   </si>
   <si>
     <t xml:space="preserve">4.3359694480896</t>
@@ -1109,52 +1109,52 @@
     <t xml:space="preserve">4.39678287506104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44543313980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50016450881958</t>
+    <t xml:space="preserve">4.44543266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50016498565674</t>
   </si>
   <si>
     <t xml:space="preserve">4.54577493667603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43935108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48800182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51232719421387</t>
+    <t xml:space="preserve">4.4393515586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48800277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51232767105103</t>
   </si>
   <si>
     <t xml:space="preserve">4.44847440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46367740631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38766098022461</t>
+    <t xml:space="preserve">4.46367692947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38766050338745</t>
   </si>
   <si>
     <t xml:space="preserve">4.30860376358032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29340124130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37245750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46063613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45759582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55489683151245</t>
+    <t xml:space="preserve">4.29340076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3724570274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46063661575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45759534835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55489587783813</t>
   </si>
   <si>
     <t xml:space="preserve">4.57922172546387</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">4.62179088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70084810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.725172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74037647247314</t>
+    <t xml:space="preserve">4.70084762573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72517251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7403769493103</t>
   </si>
   <si>
     <t xml:space="preserve">4.73429489135742</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">4.77078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81639289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943273544312</t>
+    <t xml:space="preserve">4.81639242172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943368911743</t>
   </si>
   <si>
     <t xml:space="preserve">4.76470136642456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80423069000244</t>
+    <t xml:space="preserve">4.80422973632812</t>
   </si>
   <si>
     <t xml:space="preserve">4.83463621139526</t>
@@ -1196,64 +1196,64 @@
     <t xml:space="preserve">4.71301078796387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61571025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69172620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62787199020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5366530418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25691270828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29948139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40590476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39374160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43326997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42414808273315</t>
+    <t xml:space="preserve">4.61570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69172668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62787246704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53665256500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25691223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29948234558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4059042930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39374256134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43327045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42414903640747</t>
   </si>
   <si>
     <t xml:space="preserve">4.42110776901245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43022966384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52449035644531</t>
+    <t xml:space="preserve">4.43023014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52448987960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.50320529937744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31468534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27819681167603</t>
+    <t xml:space="preserve">4.31468486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27819728851318</t>
   </si>
   <si>
     <t xml:space="preserve">4.32076692581177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38462066650391</t>
+    <t xml:space="preserve">4.38461923599243</t>
   </si>
   <si>
     <t xml:space="preserve">4.41502666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40894460678101</t>
+    <t xml:space="preserve">4.40894508361816</t>
   </si>
   <si>
     <t xml:space="preserve">4.35725450515747</t>
@@ -1262,49 +1262,49 @@
     <t xml:space="preserve">4.3329291343689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26907539367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29644155502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30556297302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23562812805176</t>
+    <t xml:space="preserve">4.2690749168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29644060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30556344985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23562860488892</t>
   </si>
   <si>
     <t xml:space="preserve">4.29035949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26603507995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26299476623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22650575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21738386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28731918334961</t>
+    <t xml:space="preserve">4.26603555679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26299381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22650623321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21738481521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731966018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.32380723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38647031784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32702350616455</t>
+    <t xml:space="preserve">4.38646936416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32702398300171</t>
   </si>
   <si>
     <t xml:space="preserve">4.20500373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11427116394043</t>
+    <t xml:space="preserve">4.11427021026611</t>
   </si>
   <si>
     <t xml:space="preserve">4.14555788040161</t>
@@ -1313,109 +1313,109 @@
     <t xml:space="preserve">4.16745901107788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23003387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25506353378296</t>
+    <t xml:space="preserve">4.24567604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23003339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2550630569458</t>
   </si>
   <si>
     <t xml:space="preserve">4.2425479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16120147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21439027786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17997455596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17058753967285</t>
+    <t xml:space="preserve">4.16120195388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21438980102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17997407913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17058801651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.08924055099487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458636283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8358142375946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8233003616333</t>
+    <t xml:space="preserve">4.02040815353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83581447601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82329988479614</t>
   </si>
   <si>
     <t xml:space="preserve">3.77636861801147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80765557289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81704211235046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79826998710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73882389068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63557600975037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195241928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262543678284</t>
+    <t xml:space="preserve">3.80765533447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81704163551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79826974868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73882436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63557624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262591362</t>
   </si>
   <si>
     <t xml:space="preserve">3.82642769813538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66060614585876</t>
+    <t xml:space="preserve">3.66060519218445</t>
   </si>
   <si>
     <t xml:space="preserve">3.72630953788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74508166313171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63870477676392</t>
+    <t xml:space="preserve">3.74508094787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6387050151825</t>
   </si>
   <si>
     <t xml:space="preserve">3.77011108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71692252159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379423141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74820995330811</t>
+    <t xml:space="preserve">3.71692299842834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379399299622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74820971488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.69814991950989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6825065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72318077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76072549819946</t>
+    <t xml:space="preserve">3.68250679969788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72318053245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373419761658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76072525978088</t>
   </si>
   <si>
     <t xml:space="preserve">3.64183354377747</t>
@@ -1424,139 +1424,139 @@
     <t xml:space="preserve">3.60116028785706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57925868034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63244724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68876457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67624998092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70440816879272</t>
+    <t xml:space="preserve">3.57925915718079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6324474811554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68876481056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67624926567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70440793037415</t>
   </si>
   <si>
     <t xml:space="preserve">3.56361556053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62931871414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686344146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61993217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261899471283</t>
+    <t xml:space="preserve">3.62931895256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686415672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61993265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62619042396545</t>
   </si>
   <si>
     <t xml:space="preserve">3.84520030021667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99537968635559</t>
+    <t xml:space="preserve">3.99537897109985</t>
   </si>
   <si>
     <t xml:space="preserve">3.88587379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91090416908264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87023019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341756820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961626052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84207153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78575468063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79514026641846</t>
+    <t xml:space="preserve">3.91090297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87023067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341899871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961602210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84207129478455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78575539588928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79514050483704</t>
   </si>
   <si>
     <t xml:space="preserve">3.77324032783508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70753741264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81078457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80139851570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75446724891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7325656414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563485145569</t>
+    <t xml:space="preserve">3.70753645896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698207855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452680587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80139827728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75446748733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73256683349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563652038574</t>
   </si>
   <si>
     <t xml:space="preserve">3.82017064094543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75759696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81391334533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77949738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397290229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335896492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89213109016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99225068092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97660708427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912143707275</t>
+    <t xml:space="preserve">3.75759625434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81391286849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77949810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397337913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335920333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89213156700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99225091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97660732269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9891209602356</t>
   </si>
   <si>
     <t xml:space="preserve">4.00163602828979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44472432136536</t>
+    <t xml:space="preserve">3.4447238445282</t>
   </si>
   <si>
     <t xml:space="preserve">3.47288274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37276315689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37589168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39466500282288</t>
+    <t xml:space="preserve">3.37276268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.375892162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39466452598572</t>
   </si>
   <si>
     <t xml:space="preserve">3.4509813785553</t>
@@ -1565,151 +1565,151 @@
     <t xml:space="preserve">3.39779281616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31018877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29141712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24448537826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22258400917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16313886642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18503952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13497996330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21006989479065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2069411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26325750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31644678115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30705976486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31331825256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28515863418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25387191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25074362754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2784378528595</t>
+    <t xml:space="preserve">3.31018900871277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24448561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22258472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18504047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13498044013977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21006941795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20694136619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26325798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31644630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3070604801178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28515887260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25387167930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25074315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27843809127808</t>
   </si>
   <si>
     <t xml:space="preserve">3.13193368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26541519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727360725403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48354411125183</t>
+    <t xml:space="preserve">3.26541543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890469551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727265357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48354387283325</t>
   </si>
   <si>
     <t xml:space="preserve">3.45098757743835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4477322101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44122076034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4249427318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4184308052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146075248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192711830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23351001739502</t>
+    <t xml:space="preserve">3.44773173332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44122099876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494249343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29146122932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192735671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2335102558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.28820538520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40866374969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33378434181213</t>
+    <t xml:space="preserve">3.34680700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40866446495056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33378410339355</t>
   </si>
   <si>
     <t xml:space="preserve">3.31099486351013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35331845283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30773878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15537524223328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076168060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31425046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28494930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41517519950867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40215253829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36634063720703</t>
+    <t xml:space="preserve">3.3533182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30773854255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15537476539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076120376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28494954109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41517543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40215277671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36634135246277</t>
   </si>
   <si>
     <t xml:space="preserve">3.44447636604309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46401071548462</t>
+    <t xml:space="preserve">3.46401047706604</t>
   </si>
   <si>
     <t xml:space="preserve">3.50633358955383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4868004322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075463294983</t>
+    <t xml:space="preserve">3.48679971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075487136841</t>
   </si>
   <si>
     <t xml:space="preserve">3.49331068992615</t>
@@ -1718,76 +1718,76 @@
     <t xml:space="preserve">3.46726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45749878883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50958895683289</t>
+    <t xml:space="preserve">3.45749855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50958871841431</t>
   </si>
   <si>
     <t xml:space="preserve">3.47052121162415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58121371269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71795082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77655220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8318989276886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864284515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87096667289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92305684089661</t>
+    <t xml:space="preserve">3.5812132358551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71795105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77655291557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70818400382996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83189845085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864332199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87096691131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92305660247803</t>
   </si>
   <si>
     <t xml:space="preserve">3.87422227859497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8807327747345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8872447013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95886826515198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00770282745361</t>
+    <t xml:space="preserve">3.88073301315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88724446296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99142551422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95886850357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00770330429077</t>
   </si>
   <si>
     <t xml:space="preserve">3.9979362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97189164161682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01747035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06630516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0825834274292</t>
+    <t xml:space="preserve">4.06304979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97189116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01747131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0663046836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258390426636</t>
   </si>
   <si>
     <t xml:space="preserve">4.12165117263794</t>
@@ -1796,40 +1796,40 @@
     <t xml:space="preserve">4.09235095977783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11514091491699</t>
+    <t xml:space="preserve">4.11514043807983</t>
   </si>
   <si>
     <t xml:space="preserve">4.12816286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09886121749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14118528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08583879470825</t>
+    <t xml:space="preserve">4.09886169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14118576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08583974838257</t>
   </si>
   <si>
     <t xml:space="preserve">4.11188459396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16071939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13141775131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26164436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24862194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24536561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24210929870605</t>
+    <t xml:space="preserve">4.16071891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13141822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.261643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24862146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24536657333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24211072921753</t>
   </si>
   <si>
     <t xml:space="preserve">4.23559904098511</t>
@@ -1838,25 +1838,25 @@
     <t xml:space="preserve">4.2323431968689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32350158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38210344314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40489196777344</t>
+    <t xml:space="preserve">4.32350063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38210296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40489292144775</t>
   </si>
   <si>
     <t xml:space="preserve">4.37884712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37233638763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37569189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28844690322876</t>
+    <t xml:space="preserve">4.37233543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37569141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28844594955444</t>
   </si>
   <si>
     <t xml:space="preserve">4.32871341705322</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">4.22804594039917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23811292648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25153493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751148223877</t>
+    <t xml:space="preserve">4.238112449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2515344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751195907593</t>
   </si>
   <si>
     <t xml:space="preserve">4.10388803482056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10724449157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16428899765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12737798690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12402248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06697702407837</t>
+    <t xml:space="preserve">4.16093444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10724353790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1642894744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1273775100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12402200698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06697750091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.07704401016235</t>
@@ -1919,43 +1919,43 @@
     <t xml:space="preserve">4.02671051025391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0065770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03342151641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09046602249146</t>
+    <t xml:space="preserve">4.00657653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03342199325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09046697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.14415645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13408946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435598373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15757846832275</t>
+    <t xml:space="preserve">4.13408899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1575779914856</t>
   </si>
   <si>
     <t xml:space="preserve">4.11060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13744497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368803024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19784498214722</t>
+    <t xml:space="preserve">4.13744449615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368850708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19784593582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.21797895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24482393264771</t>
+    <t xml:space="preserve">4.24482345581055</t>
   </si>
   <si>
     <t xml:space="preserve">4.34213590621948</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">4.28173542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28509140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33878040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34549188613892</t>
+    <t xml:space="preserve">4.28509092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33877992630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34549140930176</t>
   </si>
   <si>
     <t xml:space="preserve">4.34884786605835</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">4.47300338745117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50991535186768</t>
+    <t xml:space="preserve">4.50991487503052</t>
   </si>
   <si>
     <t xml:space="preserve">4.4629373550415</t>
@@ -1988,88 +1988,88 @@
     <t xml:space="preserve">4.45622634887695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41931438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48307037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51662635803223</t>
+    <t xml:space="preserve">4.41931390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978185653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48307085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51662683486938</t>
   </si>
   <si>
     <t xml:space="preserve">4.5367603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4931378364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44280338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42602586746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42267036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44951486587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42938137054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50656032562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46964836120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40924787521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39582586288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20120096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455646514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21126747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14080047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33542537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273687362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38575887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46629285812378</t>
+    <t xml:space="preserve">4.49313831329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44280385971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.426025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42266988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44951438903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42938184738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5065598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4696478843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40924835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39582538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20120143890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455598831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21126794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14080095291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33542442321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38575839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46629333496094</t>
   </si>
   <si>
     <t xml:space="preserve">4.41595888137817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50320434570312</t>
+    <t xml:space="preserve">4.50320482254028</t>
   </si>
   <si>
     <t xml:space="preserve">4.52333784103394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61729526519775</t>
+    <t xml:space="preserve">4.60722684860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6172947883606</t>
   </si>
   <si>
     <t xml:space="preserve">4.59716081619263</t>
@@ -2081,37 +2081,37 @@
     <t xml:space="preserve">4.65756177902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67769575119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7246732711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73138427734375</t>
+    <t xml:space="preserve">4.67769527435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72467374801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73138475418091</t>
   </si>
   <si>
     <t xml:space="preserve">4.69782876968384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61393928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64078378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60387182235718</t>
+    <t xml:space="preserve">4.61393880844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64078330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60387229919434</t>
   </si>
   <si>
     <t xml:space="preserve">4.62736177444458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62400579452515</t>
+    <t xml:space="preserve">4.62400531768799</t>
   </si>
   <si>
     <t xml:space="preserve">4.62064981460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56024980545044</t>
+    <t xml:space="preserve">4.56024932861328</t>
   </si>
   <si>
     <t xml:space="preserve">4.66762781143188</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">4.66091728210449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6810507774353</t>
+    <t xml:space="preserve">4.68105030059814</t>
   </si>
   <si>
     <t xml:space="preserve">4.82534074783325</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">4.86560869216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90252017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94278717041016</t>
+    <t xml:space="preserve">4.90251970291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.942786693573</t>
   </si>
   <si>
     <t xml:space="preserve">4.98305416107178</t>
@@ -2147,40 +2147,40 @@
     <t xml:space="preserve">5.073655128479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08707714080811</t>
+    <t xml:space="preserve">5.08707761764526</t>
   </si>
   <si>
     <t xml:space="preserve">5.09714412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1172776222229</t>
+    <t xml:space="preserve">5.11727809906006</t>
   </si>
   <si>
     <t xml:space="preserve">5.15083360671997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1609001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15754461288452</t>
+    <t xml:space="preserve">5.16090059280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">5.16425657272339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17432308197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16761112213135</t>
+    <t xml:space="preserve">5.17432260513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16761159896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.23472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63403940200806</t>
+    <t xml:space="preserve">5.54343795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6340389251709</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175186157227</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">5.89241933822632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7716178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78503942489624</t>
+    <t xml:space="preserve">5.77161836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7850399017334</t>
   </si>
   <si>
     <t xml:space="preserve">5.87102508544922</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">6.18400907516479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26999378204346</t>
+    <t xml:space="preserve">6.2699933052063</t>
   </si>
   <si>
     <t xml:space="preserve">6.21840381622314</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">6.32846260070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40069055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878135681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28031253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2631139755249</t>
+    <t xml:space="preserve">6.34909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40069007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878183364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26311445236206</t>
   </si>
   <si>
     <t xml:space="preserve">6.33534145355225</t>
@@ -2237,58 +2237,58 @@
     <t xml:space="preserve">6.38349342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33190202713013</t>
+    <t xml:space="preserve">6.33190155029297</t>
   </si>
   <si>
     <t xml:space="preserve">6.21496343612671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23216104507446</t>
+    <t xml:space="preserve">6.23216009140015</t>
   </si>
   <si>
     <t xml:space="preserve">6.25967597961426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23559904098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30438613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28375053405762</t>
+    <t xml:space="preserve">6.23559951782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30438709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28375101089478</t>
   </si>
   <si>
     <t xml:space="preserve">6.27687215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2493577003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16681241989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13585805892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14617681503296</t>
+    <t xml:space="preserve">6.24935722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1668119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13585758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1461763381958</t>
   </si>
   <si>
     <t xml:space="preserve">6.09114503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11866044998169</t>
+    <t xml:space="preserve">6.11866092681885</t>
   </si>
   <si>
     <t xml:space="preserve">6.03611516952515</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91229772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573667526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05331373214722</t>
+    <t xml:space="preserve">5.91229820251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05331230163574</t>
   </si>
   <si>
     <t xml:space="preserve">6.19088840484619</t>
@@ -2297,25 +2297,25 @@
     <t xml:space="preserve">6.00860071182251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00515985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10490369796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0326771736145</t>
+    <t xml:space="preserve">6.00516128540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10490322113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03267621994019</t>
   </si>
   <si>
     <t xml:space="preserve">5.92949390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95700883865356</t>
+    <t xml:space="preserve">5.95700931549072</t>
   </si>
   <si>
     <t xml:space="preserve">5.90885782241821</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73001050949097</t>
+    <t xml:space="preserve">5.73001003265381</t>
   </si>
   <si>
     <t xml:space="preserve">5.85726833343506</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">5.78504085540771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60619258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61651086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66810131072998</t>
+    <t xml:space="preserve">5.60619211196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61651134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249605178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66810178756714</t>
   </si>
   <si>
     <t xml:space="preserve">5.71625328063965</t>
@@ -2342,79 +2342,79 @@
     <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81255626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80567598342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80911540985107</t>
+    <t xml:space="preserve">5.81255531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80567646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80911588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.8779034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98108530044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01547861099243</t>
+    <t xml:space="preserve">5.98108625411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01547956466675</t>
   </si>
   <si>
     <t xml:space="preserve">5.8675856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70593500137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40326929092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35511779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.372314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505805969238</t>
+    <t xml:space="preserve">5.70593452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40326881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35511827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37231492996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505710601807</t>
   </si>
   <si>
     <t xml:space="preserve">5.0627703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00430107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98366403579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94927072525024</t>
+    <t xml:space="preserve">5.00430059432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98366451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9492712020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.69819593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58813619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26483297348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75580477714539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71453237533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36509156227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36784267425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08306217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092950820923</t>
+    <t xml:space="preserve">4.58813571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26483345031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75580525398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71453261375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36509203910828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36784243583679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092974662781</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516004562378</t>
@@ -2423,70 +2423,70 @@
     <t xml:space="preserve">2.91109299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90283799171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25365567207336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35133409500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53568482398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41599440574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24815249443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19862532615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18899464607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20000100135803</t>
+    <t xml:space="preserve">2.90283823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25365543365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35133385658264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53568530082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41599416732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24815273284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1986255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18899488449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20000123977661</t>
   </si>
   <si>
     <t xml:space="preserve">3.14359545707703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25778245925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43938159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59415411949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76268362998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44969987869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49097228050232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59759378433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52880620956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48409390449524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56319952011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54600286483765</t>
+    <t xml:space="preserve">3.25778269767761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43938231468201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59415435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76268339157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44970011711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4909725189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5975935459137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52880597114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48409414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56319999694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5460033416748</t>
   </si>
   <si>
     <t xml:space="preserve">3.68013834953308</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">4.01031923294067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83147168159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6595025062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60447263717651</t>
+    <t xml:space="preserve">3.83147144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65950202941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60447239875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.64574503898621</t>
@@ -2513,82 +2513,82 @@
     <t xml:space="preserve">3.68701767921448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69045686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84866857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421433448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80739569664001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81427454948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92089533805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9552903175354</t>
+    <t xml:space="preserve">3.6904571056366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84866833686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745686531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019951820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421481132507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80739593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81427478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92089509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95529007911682</t>
   </si>
   <si>
     <t xml:space="preserve">4.03439474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0722279548645</t>
+    <t xml:space="preserve">4.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">4.16853094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12037944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08598613739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23731899261475</t>
+    <t xml:space="preserve">4.12037897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08598566055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23731803894043</t>
   </si>
   <si>
     <t xml:space="preserve">4.28547048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44712066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65348243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76010465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57781839370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33018112182617</t>
+    <t xml:space="preserve">4.44712114334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65348291397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76010417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57781744003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33018207550049</t>
   </si>
   <si>
     <t xml:space="preserve">4.34737920761108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49183320999146</t>
+    <t xml:space="preserve">4.49183368682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.44368124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42304563522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46775722503662</t>
+    <t xml:space="preserve">4.42304515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46775770187378</t>
   </si>
   <si>
     <t xml:space="preserve">4.4539999961853</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">4.49527215957642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30266666412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29234933853149</t>
+    <t xml:space="preserve">4.30266714096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29234886169434</t>
   </si>
   <si>
     <t xml:space="preserve">4.33706045150757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37489414215088</t>
+    <t xml:space="preserve">4.37489461898804</t>
   </si>
   <si>
     <t xml:space="preserve">4.39553022384644</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">4.32330274581909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52622699737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41616725921631</t>
+    <t xml:space="preserve">4.52622747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41616678237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.52278709411621</t>
@@ -2630,79 +2630,79 @@
     <t xml:space="preserve">4.31298542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41960668563843</t>
+    <t xml:space="preserve">4.41960620880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.4711971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53310632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53654479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55718088150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66380214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61221170425415</t>
+    <t xml:space="preserve">4.53310585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.536545753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5571813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66380167007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61221122741699</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093858718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52966642379761</t>
+    <t xml:space="preserve">4.52966594696045</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40928840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39209079742432</t>
+    <t xml:space="preserve">4.40928745269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39209127426147</t>
   </si>
   <si>
     <t xml:space="preserve">4.42648458480835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26139450073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42992401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43680191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56062078475952</t>
+    <t xml:space="preserve">4.26139402389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42992448806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43680286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56062030792236</t>
   </si>
   <si>
     <t xml:space="preserve">4.63628721237183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68443822860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60877180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48839378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56405973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45056009292603</t>
+    <t xml:space="preserve">4.68443775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60877132415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48839426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56406021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45056104660034</t>
   </si>
   <si>
     <t xml:space="preserve">4.5950140953064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51590919494629</t>
+    <t xml:space="preserve">4.51590967178345</t>
   </si>
   <si>
     <t xml:space="preserve">4.5468635559082</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">4.40240955352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27515172958374</t>
+    <t xml:space="preserve">4.2751522064209</t>
   </si>
   <si>
     <t xml:space="preserve">4.35081815719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35425758361816</t>
+    <t xml:space="preserve">4.35425806045532</t>
   </si>
   <si>
     <t xml:space="preserve">4.55030202865601</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">4.33362150192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23044013977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32674217224121</t>
+    <t xml:space="preserve">4.23043966293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32674264907837</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27859115600586</t>
+    <t xml:space="preserve">4.27859163284302</t>
   </si>
   <si>
     <t xml:space="preserve">4.50559043884277</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">4.29922771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31986379623413</t>
+    <t xml:space="preserve">4.31986427307129</t>
   </si>
   <si>
     <t xml:space="preserve">4.30610656738281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16165256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03783369064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98968267440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03095579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25107622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73259019851685</t>
+    <t xml:space="preserve">4.16165208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03783464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98968291282654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03095626831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25107669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73258924484253</t>
   </si>
   <si>
     <t xml:space="preserve">4.81169557571411</t>
@@ -2780,82 +2780,82 @@
     <t xml:space="preserve">4.81513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96646785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20034599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19346761703491</t>
+    <t xml:space="preserve">4.96646738052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20034551620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19346714019775</t>
   </si>
   <si>
     <t xml:space="preserve">5.12467908859253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22442102432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24161863327026</t>
+    <t xml:space="preserve">5.22442054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24161815643311</t>
   </si>
   <si>
     <t xml:space="preserve">5.3791937828064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34136056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23130035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29664754867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15563297271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11092138290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10404205322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04557323455811</t>
+    <t xml:space="preserve">5.2656946182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3413610458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23129987716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15563344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11092090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10404300689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04557371139526</t>
   </si>
   <si>
     <t xml:space="preserve">5.00774002075195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00086116790771</t>
+    <t xml:space="preserve">5.00086164474487</t>
   </si>
   <si>
     <t xml:space="preserve">4.91831684112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88736152648926</t>
+    <t xml:space="preserve">4.88736200332642</t>
   </si>
   <si>
     <t xml:space="preserve">4.8942403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89767980575562</t>
+    <t xml:space="preserve">4.89768028259277</t>
   </si>
   <si>
     <t xml:space="preserve">4.8839225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86672592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7669825553894</t>
+    <t xml:space="preserve">4.86672639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76698303222656</t>
   </si>
   <si>
     <t xml:space="preserve">4.83577108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85296869277954</t>
+    <t xml:space="preserve">4.85296773910522</t>
   </si>
   <si>
     <t xml:space="preserve">4.89080142974854</t>
@@ -2864,31 +2864,31 @@
     <t xml:space="preserve">4.91487789154053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85984754562378</t>
+    <t xml:space="preserve">4.85984706878662</t>
   </si>
   <si>
     <t xml:space="preserve">4.87016487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05933094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03869438171387</t>
+    <t xml:space="preserve">5.05933141708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03869533538818</t>
   </si>
   <si>
     <t xml:space="preserve">5.03181648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71539211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59845447540283</t>
+    <t xml:space="preserve">4.71539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59845352172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.53998470306396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61565065383911</t>
+    <t xml:space="preserve">4.61565113067627</t>
   </si>
   <si>
     <t xml:space="preserve">4.6706805229187</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">5.02837657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12811851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31728458404541</t>
+    <t xml:space="preserve">5.12811803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31728506088257</t>
   </si>
   <si>
     <t xml:space="preserve">5.25537586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27257251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2588152885437</t>
+    <t xml:space="preserve">5.27257299423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25881576538086</t>
   </si>
   <si>
     <t xml:space="preserve">5.15219402313232</t>
@@ -2918,16 +2918,16 @@
     <t xml:space="preserve">5.07652807235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0902853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14875507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493810653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05245161056519</t>
+    <t xml:space="preserve">5.09028482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14875459671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493715286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05245208740234</t>
   </si>
   <si>
     <t xml:space="preserve">4.9699068069458</t>
@@ -2939,49 +2939,49 @@
     <t xml:space="preserve">5.16251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14187622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23817873001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29320859909058</t>
+    <t xml:space="preserve">5.14187574386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23817920684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29320907592773</t>
   </si>
   <si>
     <t xml:space="preserve">5.32760238647461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34479904174805</t>
+    <t xml:space="preserve">5.34479999542236</t>
   </si>
   <si>
     <t xml:space="preserve">5.33104181289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33792018890381</t>
+    <t xml:space="preserve">5.33792114257812</t>
   </si>
   <si>
     <t xml:space="preserve">5.45142078399658</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58899641036987</t>
+    <t xml:space="preserve">5.58899593353271</t>
   </si>
   <si>
     <t xml:space="preserve">5.50645112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52708721160889</t>
+    <t xml:space="preserve">5.52708673477173</t>
   </si>
   <si>
     <t xml:space="preserve">5.44454193115234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4823751449585</t>
+    <t xml:space="preserve">5.48237466812134</t>
   </si>
   <si>
     <t xml:space="preserve">5.48925399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5649209022522</t>
+    <t xml:space="preserve">5.56491994857788</t>
   </si>
   <si>
     <t xml:space="preserve">5.53740549087524</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">5.55116271972656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47824764251709</t>
+    <t xml:space="preserve">5.47824811935425</t>
   </si>
   <si>
     <t xml:space="preserve">5.40258121490479</t>
@@ -3008,19 +3008,19 @@
     <t xml:space="preserve">5.41496324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36543607711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38332033157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43972635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39019918441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32553911209106</t>
+    <t xml:space="preserve">5.36543560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38332080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43972730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39020013809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32553958892822</t>
   </si>
   <si>
     <t xml:space="preserve">5.37644195556641</t>
@@ -3029,46 +3029,46 @@
     <t xml:space="preserve">5.39982986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37506675720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34617567062378</t>
+    <t xml:space="preserve">5.37506628036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34617519378662</t>
   </si>
   <si>
     <t xml:space="preserve">5.46036291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37369012832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43697547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51401710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57730197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55528974533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42321825027466</t>
+    <t xml:space="preserve">5.37369108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43697500228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5140175819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57730150222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55528926849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42321729660034</t>
   </si>
   <si>
     <t xml:space="preserve">5.44247817993164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39845418930054</t>
+    <t xml:space="preserve">5.39845371246338</t>
   </si>
   <si>
     <t xml:space="preserve">5.47484111785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43066692352295</t>
+    <t xml:space="preserve">5.43066740036011</t>
   </si>
   <si>
     <t xml:space="preserve">5.42928647994995</t>
@@ -3077,16 +3077,16 @@
     <t xml:space="preserve">5.44309091567993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59493923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58113527297974</t>
+    <t xml:space="preserve">5.5949387550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58113479614258</t>
   </si>
   <si>
     <t xml:space="preserve">5.56733083724976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57837390899658</t>
+    <t xml:space="preserve">5.57837438583374</t>
   </si>
   <si>
     <t xml:space="preserve">5.55766773223877</t>
@@ -3095,25 +3095,25 @@
     <t xml:space="preserve">5.60046100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70813655853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74264717102051</t>
+    <t xml:space="preserve">5.70813608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74264669418335</t>
   </si>
   <si>
     <t xml:space="preserve">5.63773345947266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67224454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69571208953857</t>
+    <t xml:space="preserve">5.67224407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69571161270142</t>
   </si>
   <si>
     <t xml:space="preserve">5.66948318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76473474502563</t>
+    <t xml:space="preserve">5.76473522186279</t>
   </si>
   <si>
     <t xml:space="preserve">5.77715826034546</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">5.61288499832153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67914628982544</t>
+    <t xml:space="preserve">5.6791467666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.83927774429321</t>
@@ -3137,28 +3137,28 @@
     <t xml:space="preserve">5.66120052337646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79234313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66258192062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328714370728</t>
+    <t xml:space="preserve">5.7923436164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66258144378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66534185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68466901779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328857421875</t>
   </si>
   <si>
     <t xml:space="preserve">5.68604850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65015649795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55352544784546</t>
+    <t xml:space="preserve">5.65015745162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55352640151978</t>
   </si>
   <si>
     <t xml:space="preserve">5.63635349273682</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">5.72746276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66810274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68742942810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6046028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59355878829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36164474487305</t>
+    <t xml:space="preserve">5.66810321807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68742990493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60460233688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59355926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36164426803589</t>
   </si>
   <si>
     <t xml:space="preserve">5.40443801879883</t>
@@ -3188,70 +3188,70 @@
     <t xml:space="preserve">5.57975435256958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62392807006836</t>
+    <t xml:space="preserve">5.62392854690552</t>
   </si>
   <si>
     <t xml:space="preserve">5.67362546920776</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81442975997925</t>
+    <t xml:space="preserve">5.81442928314209</t>
   </si>
   <si>
     <t xml:space="preserve">5.81995153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79924488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79510402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73160266876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7454080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71503782272339</t>
+    <t xml:space="preserve">5.79924535751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79510307312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73160314559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74540853500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71503829956055</t>
   </si>
   <si>
     <t xml:space="preserve">5.75507116317749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80752801895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88069248199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95523500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04910516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0311598777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981229782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0325403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94695234298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92348527908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98284530639648</t>
+    <t xml:space="preserve">5.80752849578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88069200515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95523548126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96351766586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04910564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03115940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06981134414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03254079818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07809448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94695281982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92348480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98284482955933</t>
   </si>
   <si>
     <t xml:space="preserve">5.97318124771118</t>
@@ -3275,91 +3275,91 @@
     <t xml:space="preserve">6.06567049026489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08775806427002</t>
+    <t xml:space="preserve">6.08775758743286</t>
   </si>
   <si>
     <t xml:space="preserve">6.09051895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06014919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04220342636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03944301605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01045274734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15678071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19681167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15125799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20233535766602</t>
+    <t xml:space="preserve">6.06014966964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04220247268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03944206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01045322418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15678024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19681262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15125846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2023344039917</t>
   </si>
   <si>
     <t xml:space="preserve">6.14573621749878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95937633514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14849758148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34590196609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30034637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32519388198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32243251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39835786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45357608795166</t>
+    <t xml:space="preserve">5.95937585830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14849710464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3459005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3003454208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32519340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32243347167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39835739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4535756111145</t>
   </si>
   <si>
     <t xml:space="preserve">6.55710935592651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57229375839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71585988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420875549316</t>
+    <t xml:space="preserve">6.57229423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343637466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60542440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420923233032</t>
   </si>
   <si>
     <t xml:space="preserve">6.72000122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77245807647705</t>
+    <t xml:space="preserve">6.77245855331421</t>
   </si>
   <si>
     <t xml:space="preserve">6.80697011947632</t>
@@ -3368,25 +3368,25 @@
     <t xml:space="preserve">6.82739305496216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70334100723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70931768417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62562036514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61366319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56284618377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66149091720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60917949676514</t>
+    <t xml:space="preserve">6.70334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7093186378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62562131881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6136646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56284666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66149139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60917901992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.56583642959595</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">6.58227682113647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49708414077759</t>
+    <t xml:space="preserve">6.49708461761475</t>
   </si>
   <si>
     <t xml:space="preserve">6.55387926101685</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">6.68241596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65850257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66448020935059</t>
+    <t xml:space="preserve">6.65850210189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66448068618774</t>
   </si>
   <si>
     <t xml:space="preserve">6.73771619796753</t>
@@ -3419,67 +3419,67 @@
     <t xml:space="preserve">6.77657651901245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78404903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84532785415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83187675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7436957359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66298627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56434106826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7086124420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58429384231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77614259719849</t>
+    <t xml:space="preserve">6.78404998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84532928466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8318772315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74369478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66298580169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56434202194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70861291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58429431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7761435508728</t>
   </si>
   <si>
     <t xml:space="preserve">6.68865966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38783979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32951736450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49374008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44309282302856</t>
+    <t xml:space="preserve">6.38783931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43848848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32951688766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49374055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44309186935425</t>
   </si>
   <si>
     <t xml:space="preserve">6.47685718536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5489935874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6840558052063</t>
+    <t xml:space="preserve">6.54899311065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68405628204346</t>
   </si>
   <si>
     <t xml:space="preserve">6.62112903594971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56127214431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51522779464722</t>
+    <t xml:space="preserve">6.56127166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51522731781006</t>
   </si>
   <si>
     <t xml:space="preserve">6.50601863861084</t>
@@ -3506,43 +3506,43 @@
     <t xml:space="preserve">6.58889865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65335988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64568471908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103410720825</t>
+    <t xml:space="preserve">6.65336036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64568567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103363037109</t>
   </si>
   <si>
     <t xml:space="preserve">6.74391269683838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7945613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85288381576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66410255432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78688716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84981393814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97566795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.106125831604</t>
+    <t xml:space="preserve">6.79456186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85288429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66410303115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78688669204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84981441497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97566699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10612630844116</t>
   </si>
   <si>
     <t xml:space="preserve">7.13221645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99255180358887</t>
+    <t xml:space="preserve">6.99255132675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.96185398101807</t>
@@ -3551,43 +3551,43 @@
     <t xml:space="preserve">6.79763126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79149198532104</t>
+    <t xml:space="preserve">6.7914924621582</t>
   </si>
   <si>
     <t xml:space="preserve">6.70554256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40779209136963</t>
+    <t xml:space="preserve">6.40779161453247</t>
   </si>
   <si>
     <t xml:space="preserve">6.41700077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55052757263184</t>
+    <t xml:space="preserve">6.55052804946899</t>
   </si>
   <si>
     <t xml:space="preserve">6.51829719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46611452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5720157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76386594772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69786930084229</t>
+    <t xml:space="preserve">6.46611404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57201623916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67177820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76386642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69786834716797</t>
   </si>
   <si>
     <t xml:space="preserve">6.45844030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54438924789429</t>
+    <t xml:space="preserve">6.54438877105713</t>
   </si>
   <si>
     <t xml:space="preserve">6.69940376281738</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">6.79916572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56894636154175</t>
+    <t xml:space="preserve">6.56894588470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.34486484527588</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">6.36328220367432</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29575204849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23435878753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2850079536438</t>
+    <t xml:space="preserve">6.29575157165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23435926437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28500747680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.75089693069458</t>
@@ -3632,37 +3632,37 @@
     <t xml:space="preserve">5.64960050582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43933248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46388959884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33650064468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98810148239136</t>
+    <t xml:space="preserve">5.43933200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46388912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33650159835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98810195922852</t>
   </si>
   <si>
     <t xml:space="preserve">4.92977905273438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07098054885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62657833099365</t>
+    <t xml:space="preserve">5.0709810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62657785415649</t>
   </si>
   <si>
     <t xml:space="preserve">5.29966640472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41937971115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50993347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62811279296875</t>
+    <t xml:space="preserve">5.41938066482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50993299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62811326980591</t>
   </si>
   <si>
     <t xml:space="preserve">5.92125988006592</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">5.88135528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86447238922119</t>
+    <t xml:space="preserve">5.86447191238403</t>
   </si>
   <si>
     <t xml:space="preserve">5.82149791717529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97190761566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90898132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.872145652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92586469650269</t>
+    <t xml:space="preserve">5.97190809249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87214612960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92586374282837</t>
   </si>
   <si>
     <t xml:space="preserve">5.96116495132446</t>
@@ -3695,16 +3695,16 @@
     <t xml:space="preserve">6.12538814544678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06860065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95195531845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05325317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98879098892212</t>
+    <t xml:space="preserve">6.06860113143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95195627212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05325269699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98879146575928</t>
   </si>
   <si>
     <t xml:space="preserve">5.93353843688965</t>
@@ -3716,70 +3716,70 @@
     <t xml:space="preserve">5.71559619903564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85679769515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82303237915039</t>
+    <t xml:space="preserve">5.85679817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82303285598755</t>
   </si>
   <si>
     <t xml:space="preserve">5.77084922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81842851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86293745040894</t>
+    <t xml:space="preserve">5.81842803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86293792724609</t>
   </si>
   <si>
     <t xml:space="preserve">5.79859828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89671611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87098026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78090476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6586594581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56536769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60397100448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55089044570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61040496826172</t>
+    <t xml:space="preserve">5.89671564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87097978591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78090524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65865993499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56536722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60397052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55089092254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61040449142456</t>
   </si>
   <si>
     <t xml:space="preserve">5.56375932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59271144866943</t>
+    <t xml:space="preserve">5.59271192550659</t>
   </si>
   <si>
     <t xml:space="preserve">5.55732488632202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62166404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58788585662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50263643264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56054162979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8114652633667</t>
+    <t xml:space="preserve">5.62166452407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58788633346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50263690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56054258346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81146574020386</t>
   </si>
   <si>
     <t xml:space="preserve">5.66348457336426</t>
@@ -3788,34 +3788,34 @@
     <t xml:space="preserve">5.7085223197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74069261550903</t>
+    <t xml:space="preserve">5.74069213867188</t>
   </si>
   <si>
     <t xml:space="preserve">5.76321172714233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68922090530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817445755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75516939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76803684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95140409469604</t>
+    <t xml:space="preserve">5.6892204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510822296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75516891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76803636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9514045715332</t>
   </si>
   <si>
     <t xml:space="preserve">5.94175386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91280078887939</t>
+    <t xml:space="preserve">5.91280126571655</t>
   </si>
   <si>
     <t xml:space="preserve">5.84685230255127</t>
@@ -3824,19 +3824,19 @@
     <t xml:space="preserve">5.75034332275391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88706541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80503225326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72299957275391</t>
+    <t xml:space="preserve">5.8870644569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80503177642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72299909591675</t>
   </si>
   <si>
     <t xml:space="preserve">5.55249977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17450523376465</t>
+    <t xml:space="preserve">5.17450475692749</t>
   </si>
   <si>
     <t xml:space="preserve">4.93323135375977</t>
@@ -3845,16 +3845,16 @@
     <t xml:space="preserve">5.13107585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20828342437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01043939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225992202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1182074546814</t>
+    <t xml:space="preserve">5.20828294754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01043891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11820793151855</t>
   </si>
   <si>
     <t xml:space="preserve">5.11981630325317</t>
@@ -3863,49 +3863,49 @@
     <t xml:space="preserve">5.15198612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30157566070557</t>
+    <t xml:space="preserve">5.30157518386841</t>
   </si>
   <si>
     <t xml:space="preserve">5.16807126998901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17933034896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14876937866211</t>
+    <t xml:space="preserve">5.17933082580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14876890182495</t>
   </si>
   <si>
     <t xml:space="preserve">5.04904270172119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07156181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05386781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88819456100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0345664024353</t>
+    <t xml:space="preserve">5.07156229019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05386829376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88819408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03456687927246</t>
   </si>
   <si>
     <t xml:space="preserve">5.17611312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03295803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10855770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0377836227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85924100875854</t>
+    <t xml:space="preserve">5.03295850753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10855722427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03778314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85924053192139</t>
   </si>
   <si>
     <t xml:space="preserve">4.91232109069824</t>
@@ -3914,19 +3914,19 @@
     <t xml:space="preserve">4.98631191253662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12142419815063</t>
+    <t xml:space="preserve">5.12142515182495</t>
   </si>
   <si>
     <t xml:space="preserve">4.93484020233154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01848077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01526498794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96379280090332</t>
+    <t xml:space="preserve">5.01848173141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0152645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96379232406616</t>
   </si>
   <si>
     <t xml:space="preserve">4.99274587631226</t>
@@ -3941,55 +3941,55 @@
     <t xml:space="preserve">5.15842056274414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45599031448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59432029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50746202468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48976802825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46242427825928</t>
+    <t xml:space="preserve">5.45598983764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59431982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50746154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48976850509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">5.50424480438232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5364146232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56858444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5106782913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40290975570679</t>
+    <t xml:space="preserve">5.53641414642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56858396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51067924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40291023254395</t>
   </si>
   <si>
     <t xml:space="preserve">5.44312238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33374547958374</t>
+    <t xml:space="preserve">5.33374500274658</t>
   </si>
   <si>
     <t xml:space="preserve">5.19219779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28388166427612</t>
+    <t xml:space="preserve">5.28388214111328</t>
   </si>
   <si>
     <t xml:space="preserve">5.22919368743896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16324520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0410008430481</t>
+    <t xml:space="preserve">5.163245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04100036621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.14394378662109</t>
@@ -3998,34 +3998,34 @@
     <t xml:space="preserve">5.12946748733521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00883054733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24688720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08121252059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18254709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19863271713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31766033172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53963136672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41577816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49459409713745</t>
+    <t xml:space="preserve">5.00883102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24688673019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08121299743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1825475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19863224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31766080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53963184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41577863693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49459362030029</t>
   </si>
   <si>
     <t xml:space="preserve">5.2887077331543</t>
@@ -4034,16 +4034,16 @@
     <t xml:space="preserve">5.25653743743896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3305287361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08925533294678</t>
+    <t xml:space="preserve">5.33052825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08925485610962</t>
   </si>
   <si>
     <t xml:space="preserve">5.15037727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1889820098877</t>
+    <t xml:space="preserve">5.18898153305054</t>
   </si>
   <si>
     <t xml:space="preserve">4.99596309661865</t>
@@ -4052,40 +4052,40 @@
     <t xml:space="preserve">5.16002893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08603858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13590097427368</t>
+    <t xml:space="preserve">5.08603811264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13590145111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.9879207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20345735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45920705795288</t>
+    <t xml:space="preserve">5.20345783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45920658111572</t>
   </si>
   <si>
     <t xml:space="preserve">5.39808464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37878274917603</t>
+    <t xml:space="preserve">5.37878322601318</t>
   </si>
   <si>
     <t xml:space="preserve">5.32409381866455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33696222305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28709840774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14555215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30961847305298</t>
+    <t xml:space="preserve">5.33696269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28709888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14555168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30961799621582</t>
   </si>
   <si>
     <t xml:space="preserve">5.35626363754272</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">5.47368383407593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54284811019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61362171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64579153060913</t>
+    <t xml:space="preserve">5.54284858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61362218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64579200744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.67152738571167</t>
@@ -4112,31 +4112,31 @@
     <t xml:space="preserve">5.90315008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92406034469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04308795928955</t>
+    <t xml:space="preserve">5.92405986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04308748245239</t>
   </si>
   <si>
     <t xml:space="preserve">6.11707830429077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09616804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02539491653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06560659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08651733398438</t>
+    <t xml:space="preserve">6.09616851806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02539539337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06560707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08651685714722</t>
   </si>
   <si>
     <t xml:space="preserve">6.21519660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27149343490601</t>
+    <t xml:space="preserve">6.27149295806885</t>
   </si>
   <si>
     <t xml:space="preserve">6.24897480010986</t>
@@ -4145,25 +4145,25 @@
     <t xml:space="preserve">6.26023435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35996007919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45968627929688</t>
+    <t xml:space="preserve">6.43716716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35996055603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45968580245972</t>
   </si>
   <si>
     <t xml:space="preserve">6.49668169021606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46451187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45646905899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50472402572632</t>
+    <t xml:space="preserve">6.46451234817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45646953582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50472450256348</t>
   </si>
   <si>
     <t xml:space="preserve">6.50969696044922</t>
@@ -4175,13 +4175,13 @@
     <t xml:space="preserve">6.56108522415161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47820138931274</t>
+    <t xml:space="preserve">6.47820091247559</t>
   </si>
   <si>
     <t xml:space="preserve">6.4931206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52958917617798</t>
+    <t xml:space="preserve">6.52958869934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.52461671829224</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">6.61413097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57434701919556</t>
+    <t xml:space="preserve">6.57434749603271</t>
   </si>
   <si>
     <t xml:space="preserve">6.51301193237305</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">6.46825551986694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54616594314575</t>
+    <t xml:space="preserve">6.54616546630859</t>
   </si>
   <si>
     <t xml:space="preserve">6.54948091506958</t>
@@ -4223,13 +4223,13 @@
     <t xml:space="preserve">6.39200210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55776977539062</t>
+    <t xml:space="preserve">6.55777025222778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51467037200928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49146223068237</t>
+    <t xml:space="preserve">6.49146270751953</t>
   </si>
   <si>
     <t xml:space="preserve">6.46328210830688</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">6.54450845718384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56274318695068</t>
+    <t xml:space="preserve">6.56274271011353</t>
   </si>
   <si>
     <t xml:space="preserve">6.68209600448608</t>
@@ -4259,25 +4259,25 @@
     <t xml:space="preserve">7.00202751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04015398025513</t>
+    <t xml:space="preserve">7.04015350341797</t>
   </si>
   <si>
     <t xml:space="preserve">7.11640739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11806440353394</t>
+    <t xml:space="preserve">7.11806488037109</t>
   </si>
   <si>
     <t xml:space="preserve">7.10646152496338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97218894958496</t>
+    <t xml:space="preserve">6.97218942642212</t>
   </si>
   <si>
     <t xml:space="preserve">6.98545122146606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07496452331543</t>
+    <t xml:space="preserve">7.07496404647827</t>
   </si>
   <si>
     <t xml:space="preserve">7.13464069366455</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">7.20757865905762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2672553062439</t>
+    <t xml:space="preserve">7.26725482940674</t>
   </si>
   <si>
     <t xml:space="preserve">7.26559734344482</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">7.34019327163696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40152740478516</t>
+    <t xml:space="preserve">7.40152788162231</t>
   </si>
   <si>
     <t xml:space="preserve">7.40484237670898</t>
@@ -4307,13 +4307,13 @@
     <t xml:space="preserve">7.45788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49767255783081</t>
+    <t xml:space="preserve">7.49767160415649</t>
   </si>
   <si>
     <t xml:space="preserve">7.54077243804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243040084839</t>
+    <t xml:space="preserve">7.54242944717407</t>
   </si>
   <si>
     <t xml:space="preserve">7.47446537017822</t>
@@ -4325,13 +4325,13 @@
     <t xml:space="preserve">7.62034177780151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6402325630188</t>
+    <t xml:space="preserve">7.64023351669312</t>
   </si>
   <si>
     <t xml:space="preserve">7.67504405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69327831268311</t>
+    <t xml:space="preserve">7.69327735900879</t>
   </si>
   <si>
     <t xml:space="preserve">7.52585315704346</t>
@@ -4355,13 +4355,13 @@
     <t xml:space="preserve">7.60210657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66675567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71814250946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72643184661865</t>
+    <t xml:space="preserve">7.66675472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71814346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72643089294434</t>
   </si>
   <si>
     <t xml:space="preserve">7.77781963348389</t>
@@ -4370,10 +4370,10 @@
     <t xml:space="preserve">7.45457363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87604379653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03518056869507</t>
+    <t xml:space="preserve">6.87604331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03518104553223</t>
   </si>
   <si>
     <t xml:space="preserve">6.66883373260498</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">6.76166391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00037050247192</t>
+    <t xml:space="preserve">7.00037002563477</t>
   </si>
   <si>
     <t xml:space="preserve">6.86941337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76663732528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76000642776489</t>
+    <t xml:space="preserve">6.76663684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76000595092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.67214965820312</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">6.83460283279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93406200408936</t>
+    <t xml:space="preserve">6.93406248092651</t>
   </si>
   <si>
     <t xml:space="preserve">6.92743158340454</t>
@@ -4427,19 +4427,19 @@
     <t xml:space="preserve">7.06999158859253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07993793487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15950584411621</t>
+    <t xml:space="preserve">7.07993841171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15950632095337</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18271350860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08656883239746</t>
+    <t xml:space="preserve">7.18271398544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08656930923462</t>
   </si>
   <si>
     <t xml:space="preserve">7.1429295539856</t>
@@ -6015,6 +6015,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.7299995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8700008392334</t>
   </si>
 </sst>
 </file>
@@ -71223,7 +71226,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6493634259</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>535974</v>
@@ -71244,6 +71247,32 @@
         <v>2000</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6495138889</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>645928</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>16.8700008392334</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>16.6299991607666</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>16.7900009155273</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>16.8700008392334</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>2001</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -38,82 +38,82 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446674346924</t>
+    <t xml:space="preserve">3.78446745872498</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49607443809509</t>
+    <t xml:space="preserve">3.73277449607849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49607515335083</t>
   </si>
   <si>
     <t xml:space="preserve">3.4144549369812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40901374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43349933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144311904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658294677734</t>
+    <t xml:space="preserve">3.40901231765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349885940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658199310303</t>
   </si>
   <si>
     <t xml:space="preserve">3.25937604904175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29202437400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41989612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.428058385849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187935829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276125907898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22672820091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13966655731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18863868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30562782287598</t>
+    <t xml:space="preserve">3.29202389717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157656669617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040415763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41989541053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805790901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077874183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3627622127533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2267279624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13966608047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18863844871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30562686920166</t>
   </si>
   <si>
     <t xml:space="preserve">3.03083872795105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89208340644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15598964691162</t>
+    <t xml:space="preserve">2.89208364486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1559898853302</t>
   </si>
   <si>
     <t xml:space="preserve">3.25393438339233</t>
@@ -122,64 +122,64 @@
     <t xml:space="preserve">3.3137891292572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40357184410095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36548280715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36820340156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46614742279053</t>
+    <t xml:space="preserve">3.40357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36548209190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36820316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46614718437195</t>
   </si>
   <si>
     <t xml:space="preserve">3.4362199306488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36004114151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49063348770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56681275367737</t>
+    <t xml:space="preserve">3.36004090309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49063420295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56681299209595</t>
   </si>
   <si>
     <t xml:space="preserve">3.56409239768982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69196391105652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71100902557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61850523948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652319908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380093574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79262852668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76542282104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70284605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181794166565</t>
+    <t xml:space="preserve">3.69196438789368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71100950241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61850571632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380212783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623245239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79262971878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76542186737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70284700393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181818008423</t>
   </si>
   <si>
     <t xml:space="preserve">3.7218918800354</t>
@@ -188,67 +188,67 @@
     <t xml:space="preserve">3.6946849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65387344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8143949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86608672142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71372961997986</t>
+    <t xml:space="preserve">3.65387439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81439518928528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84432196617126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86608815193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71372866630554</t>
   </si>
   <si>
     <t xml:space="preserve">3.63482975959778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54232597351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74637794494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77630519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821568489075</t>
+    <t xml:space="preserve">3.54232740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74637722969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77630496025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73821544647217</t>
   </si>
   <si>
     <t xml:space="preserve">3.87969160079956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91778063774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85248422622681</t>
+    <t xml:space="preserve">3.91777968406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85248470306396</t>
   </si>
   <si>
     <t xml:space="preserve">3.94407820701599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88579130172729</t>
+    <t xml:space="preserve">3.88579034805298</t>
   </si>
   <si>
     <t xml:space="preserve">3.94962930679321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97460985183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9662823677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88023924827576</t>
+    <t xml:space="preserve">3.974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96628212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88024020195007</t>
   </si>
   <si>
     <t xml:space="preserve">3.92464900016785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88856649398804</t>
+    <t xml:space="preserve">3.8885669708252</t>
   </si>
   <si>
     <t xml:space="preserve">4.00236463546753</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">4.04122304916382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93019962310791</t>
+    <t xml:space="preserve">3.93020057678223</t>
   </si>
   <si>
     <t xml:space="preserve">4.07730484008789</t>
@@ -269,25 +269,25 @@
     <t xml:space="preserve">3.99681353569031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96905851364136</t>
+    <t xml:space="preserve">3.9690580368042</t>
   </si>
   <si>
     <t xml:space="preserve">4.0606517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92742538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93575119972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9524040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91909718513489</t>
+    <t xml:space="preserve">3.92742443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93575096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92187333106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95240449905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9190981388092</t>
   </si>
   <si>
     <t xml:space="preserve">3.94130206108093</t>
@@ -296,292 +296,292 @@
     <t xml:space="preserve">4.08008050918579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29102277755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23551225662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1633472442627</t>
+    <t xml:space="preserve">4.29102373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23551273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16334772109985</t>
   </si>
   <si>
     <t xml:space="preserve">4.18832731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21608352661133</t>
+    <t xml:space="preserve">4.21608400344849</t>
   </si>
   <si>
     <t xml:space="preserve">4.18277645111084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13559198379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15502166748047</t>
+    <t xml:space="preserve">4.13559103012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15502119064331</t>
   </si>
   <si>
     <t xml:space="preserve">4.03289604187012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0523247718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09673357009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06342697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69427680969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5305187702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5527241230011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48888540267944</t>
+    <t xml:space="preserve">4.05232572555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09673404693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06342649459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69427752494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53051853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55272316932678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48888516426086</t>
   </si>
   <si>
     <t xml:space="preserve">3.6026828289032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78587055206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8247287273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80530023574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685316085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288286209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13916444778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26961493492126</t>
+    <t xml:space="preserve">3.78587102890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82472801208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80529999732971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288166999817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13916325569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26961541175842</t>
   </si>
   <si>
     <t xml:space="preserve">3.23630881309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40561819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41394472122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904461860657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19190001487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39174103736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47778296470642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59713220596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49721240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941561698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53884530067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55827403068542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54162096977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386475563049</t>
+    <t xml:space="preserve">3.40561842918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41394543647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19189977645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410465240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39174056053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47778248786926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59713196754456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941657066345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5388457775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55827450752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54162168502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386594772339</t>
   </si>
   <si>
     <t xml:space="preserve">3.63599061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58047890663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64154100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39451599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34455561637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949582099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54717206954956</t>
+    <t xml:space="preserve">3.58047914505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64154028892517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3945164680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34455633163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54717135429382</t>
   </si>
   <si>
     <t xml:space="preserve">3.56937623023987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4694561958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116881370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280265808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231135368347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4805588722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51664137840271</t>
+    <t xml:space="preserve">3.46945643424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4111692905426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280289649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231087684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48055791854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51664066314697</t>
   </si>
   <si>
     <t xml:space="preserve">3.45002770423889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47500729560852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51108980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56660175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58325481414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994750022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215166091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59990835189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49166083335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52219176292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50831460952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31402492523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37786293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30847334861755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36120915412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38896489143372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29737162590027</t>
+    <t xml:space="preserve">3.47500777244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51108956336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56660103797913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58325505256653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5499472618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264391899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59990787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49166107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52219271659851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50831365585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3140242099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37786269187927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3084728717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36120963096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38896441459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29737138748169</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745087623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23075699806213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29182028770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2668399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27516722679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39729189872742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46390509605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46112966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3223512172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38618969917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43059849739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43614912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50276303291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56382536888123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33900499343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835447311401</t>
+    <t xml:space="preserve">3.23075795173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29182052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26684021949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2751669883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337416648865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39729166030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46390438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839290618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4611291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32235097885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38618922233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43059873580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43614959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50276279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382513046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398434638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33900451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835375785828</t>
   </si>
   <si>
     <t xml:space="preserve">3.54439687728882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42227172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38341379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30014729499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28303289413452</t>
+    <t xml:space="preserve">3.42227149009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38341403007507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30014705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2830331325531</t>
   </si>
   <si>
     <t xml:space="preserve">3.37145471572876</t>
@@ -590,73 +590,73 @@
     <t xml:space="preserve">3.3914213180542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37715911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41423940658569</t>
+    <t xml:space="preserve">3.37716007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41423988342285</t>
   </si>
   <si>
     <t xml:space="preserve">3.45702505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48554873466492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118491172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256031990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73370146751404</t>
+    <t xml:space="preserve">3.48554849624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5311861038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256079673767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73370051383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.7993049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09309434890747</t>
+    <t xml:space="preserve">4.09309482574463</t>
   </si>
   <si>
     <t xml:space="preserve">3.95047855377197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89343214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95333051681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93906903266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93051218986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635137557983</t>
+    <t xml:space="preserve">3.89343118667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332956314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93906950950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93051171302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635089874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.92480659484863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90483975410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93621683120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9419207572937</t>
+    <t xml:space="preserve">3.90484070777893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93621587753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94192123413086</t>
   </si>
   <si>
     <t xml:space="preserve">3.92195439338684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89628386497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96474003791809</t>
+    <t xml:space="preserve">3.89628338813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477415084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96473908424377</t>
   </si>
   <si>
     <t xml:space="preserve">4.10735654830933</t>
@@ -668,133 +668,133 @@
     <t xml:space="preserve">4.04175281524658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2442684173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1501407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30131435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574449539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20433521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26708793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21289253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20718717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09879922866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23571109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18151760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17010688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1758131980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03319549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03890037536621</t>
+    <t xml:space="preserve">4.07883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426746368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15014123916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30131483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2043342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26708698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21289205551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20718812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09879970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23571157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18151712417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17010736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17581224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03319501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03890085220337</t>
   </si>
   <si>
     <t xml:space="preserve">4.08453798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07027626037598</t>
+    <t xml:space="preserve">4.07027673721313</t>
   </si>
   <si>
     <t xml:space="preserve">3.97044467926025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99326324462891</t>
+    <t xml:space="preserve">3.99326276779175</t>
   </si>
   <si>
     <t xml:space="preserve">3.981853723526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05886650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11306142807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06171894073486</t>
+    <t xml:space="preserve">4.05886697769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11306047439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06171846389771</t>
   </si>
   <si>
     <t xml:space="preserve">4.04745721817017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02749109268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75651955604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672137260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105036735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.519775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53689050674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.633868932724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6823582649231</t>
+    <t xml:space="preserve">4.02749156951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75651931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672113418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105108261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51977610588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688955307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692366600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68235898017883</t>
   </si>
   <si>
     <t xml:space="preserve">3.64242672920227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65098404884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091582298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7194390296936</t>
+    <t xml:space="preserve">3.65098261833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71943926811218</t>
   </si>
   <si>
     <t xml:space="preserve">3.73084878921509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81641888618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78789567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81071424484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779500961304</t>
+    <t xml:space="preserve">3.81641793251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78789448738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81071376800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779453277588</t>
   </si>
   <si>
     <t xml:space="preserve">3.76792931556702</t>
@@ -803,43 +803,43 @@
     <t xml:space="preserve">3.78219032287598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80215764045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83353209495544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90769290924072</t>
+    <t xml:space="preserve">3.80215668678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83353161811829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064649581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769338607788</t>
   </si>
   <si>
     <t xml:space="preserve">3.91625022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94762635231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97614908218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.927659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058017730713</t>
+    <t xml:space="preserve">3.94762587547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97614860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92765951156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89057922363281</t>
   </si>
   <si>
     <t xml:space="preserve">3.85349869728088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82212352752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87346601486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10278177261353</t>
+    <t xml:space="preserve">3.82212281227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8734655380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10278224945068</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869359970093</t>
@@ -848,106 +848,106 @@
     <t xml:space="preserve">4.17076730728149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11460542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1530327796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12938547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10573863983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16485691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23579835891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875331878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35107803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36290073394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35994577407837</t>
+    <t xml:space="preserve">4.11460638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15303230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12938594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1057391166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16485500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23579788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875379562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919370651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34516572952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35107755661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36290168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35994529724121</t>
   </si>
   <si>
     <t xml:space="preserve">4.39837169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28900384902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30082750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3717679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340227127075</t>
+    <t xml:space="preserve">4.2890043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30082702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37176847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340179443359</t>
   </si>
   <si>
     <t xml:space="preserve">4.51956367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46931314468384</t>
+    <t xml:space="preserve">4.46931266784668</t>
   </si>
   <si>
     <t xml:space="preserve">4.4752254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45453405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36881303787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33334159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41315174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30673933029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41906309127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43384218215942</t>
+    <t xml:space="preserve">4.45453357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.368812084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3333420753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41315126419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30673789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41906261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43384313583374</t>
   </si>
   <si>
     <t xml:space="preserve">4.38654804229736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30969572067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28604698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31856298446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39245939254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29491472244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3362979888916</t>
+    <t xml:space="preserve">4.30969476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28604793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31856250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39245986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29491519927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33629751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.25353336334229</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">4.37472486495972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3274302482605</t>
+    <t xml:space="preserve">4.32743072509766</t>
   </si>
   <si>
     <t xml:space="preserve">4.3392539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38063526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49296092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37768030166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40724039077759</t>
+    <t xml:space="preserve">4.38063669204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49295997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37768077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">4.38950443267822</t>
@@ -983,34 +983,34 @@
     <t xml:space="preserve">4.31560659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27126884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21510648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34220886230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32151794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25648880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28309154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057649612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23284101486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22101831436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16190052032471</t>
+    <t xml:space="preserve">4.27126789093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21510601043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34220933914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3215184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25648927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28309202194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23284196853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22101783752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16190004348755</t>
   </si>
   <si>
     <t xml:space="preserve">4.19737100601196</t>
@@ -1019,40 +1019,40 @@
     <t xml:space="preserve">4.24170970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17963600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22397470474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26831245422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29195976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35403347015381</t>
+    <t xml:space="preserve">4.1796350479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22397422790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26831197738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2919602394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35403299331665</t>
   </si>
   <si>
     <t xml:space="preserve">4.43679857254028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42201805114746</t>
+    <t xml:space="preserve">4.42201852798462</t>
   </si>
   <si>
     <t xml:space="preserve">4.26535606384277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1885027885437</t>
+    <t xml:space="preserve">4.18850326538086</t>
   </si>
   <si>
     <t xml:space="preserve">4.17372417449951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16781234741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24762105941772</t>
+    <t xml:space="preserve">4.16781091690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24762153625488</t>
   </si>
   <si>
     <t xml:space="preserve">4.21806240081787</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">4.28013610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23866891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1352858543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13832712173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1687331199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16569328308105</t>
+    <t xml:space="preserve">4.23866844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13528633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13832759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16873407363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1656928062439</t>
   </si>
   <si>
     <t xml:space="preserve">4.25083112716675</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">4.25995397567749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27211666107178</t>
+    <t xml:space="preserve">4.27211618423462</t>
   </si>
   <si>
     <t xml:space="preserve">4.36637592315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36941766738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117244720459</t>
+    <t xml:space="preserve">4.36941719055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509134292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117340087891</t>
   </si>
   <si>
     <t xml:space="preserve">4.32988834381104</t>
@@ -1112,73 +1112,73 @@
     <t xml:space="preserve">4.44543266296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50016498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54577493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4393515586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48800277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51232767105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44847440719604</t>
+    <t xml:space="preserve">4.50016450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54577445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43935203552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48800230026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51232719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44847393035889</t>
   </si>
   <si>
     <t xml:space="preserve">4.46367692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38766050338745</t>
+    <t xml:space="preserve">4.38766098022461</t>
   </si>
   <si>
     <t xml:space="preserve">4.30860376358032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29340076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3724570274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46063661575317</t>
+    <t xml:space="preserve">4.29340028762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37245750427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46063613891602</t>
   </si>
   <si>
     <t xml:space="preserve">4.45759534835815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55489587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57922172546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62179088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70084762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72517251968384</t>
+    <t xml:space="preserve">4.42718935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55489635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57922220230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62179040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70084810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72517347335815</t>
   </si>
   <si>
     <t xml:space="preserve">4.7403769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73429489135742</t>
+    <t xml:space="preserve">4.73429536819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.77078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81639242172241</t>
+    <t xml:space="preserve">4.8163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">4.81943368911743</t>
@@ -1193,103 +1193,103 @@
     <t xml:space="preserve">4.83463621139526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71301078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61570930480957</t>
+    <t xml:space="preserve">4.71300983428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61570978164673</t>
   </si>
   <si>
     <t xml:space="preserve">4.69172668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62787246704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53665256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25691223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29948234558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4059042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39374256134033</t>
+    <t xml:space="preserve">4.6278715133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53665351867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25691270828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2994818687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40590476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39374160766602</t>
   </si>
   <si>
     <t xml:space="preserve">4.43327045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42414903640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42110776901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43023014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52448987960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50320529937744</t>
+    <t xml:space="preserve">4.42414855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42110824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43023061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52449035644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50320625305176</t>
   </si>
   <si>
     <t xml:space="preserve">4.31468486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27819728851318</t>
+    <t xml:space="preserve">4.27819681167603</t>
   </si>
   <si>
     <t xml:space="preserve">4.32076692581177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38461923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41502666473389</t>
+    <t xml:space="preserve">4.38461971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41502618789673</t>
   </si>
   <si>
     <t xml:space="preserve">4.40894508361816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35725450515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3329291343689</t>
+    <t xml:space="preserve">4.35725402832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33292865753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.2690749168396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29644060134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30556344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23562860488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29035949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26603555679321</t>
+    <t xml:space="preserve">4.29644107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30556297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23562812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29036045074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26603507995605</t>
   </si>
   <si>
     <t xml:space="preserve">4.26299381256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22650623321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21738481521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28731966018677</t>
+    <t xml:space="preserve">4.22650575637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21738386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731918334961</t>
   </si>
   <si>
     <t xml:space="preserve">4.32380723953247</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">4.32702398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20500373840332</t>
+    <t xml:space="preserve">4.20500326156616</t>
   </si>
   <si>
     <t xml:space="preserve">4.11427021026611</t>
@@ -1313,43 +1313,43 @@
     <t xml:space="preserve">4.16745901107788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24567604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23003339767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2550630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2425479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16120195388794</t>
+    <t xml:space="preserve">4.24567651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2300329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25506353378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24254894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1612024307251</t>
   </si>
   <si>
     <t xml:space="preserve">4.21438980102539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17997407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17058801651001</t>
+    <t xml:space="preserve">4.17997455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17058753967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.08924055099487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02040815353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458660125732</t>
+    <t xml:space="preserve">4.02040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458707809448</t>
   </si>
   <si>
     <t xml:space="preserve">3.83581447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82329988479614</t>
+    <t xml:space="preserve">3.82329916954041</t>
   </si>
   <si>
     <t xml:space="preserve">3.77636861801147</t>
@@ -1358,97 +1358,97 @@
     <t xml:space="preserve">3.80765533447266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81704163551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79826974868774</t>
+    <t xml:space="preserve">3.81704115867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79826998710632</t>
   </si>
   <si>
     <t xml:space="preserve">3.73882436752319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63557624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195289611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262591362</t>
+    <t xml:space="preserve">3.63557600975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195313453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262543678284</t>
   </si>
   <si>
     <t xml:space="preserve">3.82642769813538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66060519218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72630953788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74508094787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6387050151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77011108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71692299842834</t>
+    <t xml:space="preserve">3.66060614585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72630906105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74508190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63870429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7701108455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71692252159119</t>
   </si>
   <si>
     <t xml:space="preserve">3.71379399299622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74820971488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69814991950989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68250679969788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72318053245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373419761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76072525978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183354377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60116028785706</t>
+    <t xml:space="preserve">3.74820923805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6981508731842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68250775337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72317981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76072549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64183378219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6011598110199</t>
   </si>
   <si>
     <t xml:space="preserve">3.57925915718079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6324474811554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68876481056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67624926567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70440793037415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56361556053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62931895256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686415672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61993265151978</t>
+    <t xml:space="preserve">3.63244700431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68876457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67624974250793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70440816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.629319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686367988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61993193626404</t>
   </si>
   <si>
     <t xml:space="preserve">3.62619042396545</t>
@@ -1457,91 +1457,91 @@
     <t xml:space="preserve">3.84520030021667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99537897109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88587379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91090297698975</t>
+    <t xml:space="preserve">3.99537968635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88587427139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9109046459198</t>
   </si>
   <si>
     <t xml:space="preserve">3.87023067474365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92341899871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961602210999</t>
+    <t xml:space="preserve">3.92341756820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961649894714</t>
   </si>
   <si>
     <t xml:space="preserve">3.84207129478455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78575539588928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79514050483704</t>
+    <t xml:space="preserve">3.78575444221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79514145851135</t>
   </si>
   <si>
     <t xml:space="preserve">3.77324032783508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70753645896912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698207855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452680587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81078481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80139827728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75446748733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73256683349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563652038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82017064094543</t>
+    <t xml:space="preserve">3.7075366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698231697083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078410148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80139851570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75446772575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73256635665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82017040252686</t>
   </si>
   <si>
     <t xml:space="preserve">3.75759625434875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81391286849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77949810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397337913513</t>
+    <t xml:space="preserve">3.81391334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77949738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397290229797</t>
   </si>
   <si>
     <t xml:space="preserve">3.87335920333862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89213156700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99225091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97660732269287</t>
+    <t xml:space="preserve">3.89213132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99225044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97660684585571</t>
   </si>
   <si>
     <t xml:space="preserve">3.9891209602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00163602828979</t>
+    <t xml:space="preserve">4.00163650512695</t>
   </si>
   <si>
     <t xml:space="preserve">3.4447238445282</t>
@@ -1550,82 +1550,82 @@
     <t xml:space="preserve">3.47288274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37276268005371</t>
+    <t xml:space="preserve">3.37276339530945</t>
   </si>
   <si>
     <t xml:space="preserve">3.375892162323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39466452598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4509813785553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39779281616211</t>
+    <t xml:space="preserve">3.3946647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098185539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39779233932495</t>
   </si>
   <si>
     <t xml:space="preserve">3.31018900871277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29141664505005</t>
+    <t xml:space="preserve">3.29141712188721</t>
   </si>
   <si>
     <t xml:space="preserve">3.24448561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22258472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16313934326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18504047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13498044013977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21006941795349</t>
+    <t xml:space="preserve">3.22258543968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313886642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18503952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13498020172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21006989479065</t>
   </si>
   <si>
     <t xml:space="preserve">3.20694136619568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26325798034668</t>
+    <t xml:space="preserve">3.26325821876526</t>
   </si>
   <si>
     <t xml:space="preserve">3.31644630432129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3070604801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31331729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28515887260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25387167930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27843809127808</t>
+    <t xml:space="preserve">3.30706024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28515934944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25387191772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25074291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2784378528595</t>
   </si>
   <si>
     <t xml:space="preserve">3.13193368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26541543006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890469551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727265357971</t>
+    <t xml:space="preserve">3.26541519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890445709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727313041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.48354387283325</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">3.45098757743835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44773173332214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44122099876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42494249343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41843104362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146122932434</t>
+    <t xml:space="preserve">3.44773149490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44122076034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494297027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843152046204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29146075248718</t>
   </si>
   <si>
     <t xml:space="preserve">3.27192735671997</t>
@@ -1655,115 +1655,115 @@
     <t xml:space="preserve">3.2335102558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28820538520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40866446495056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33378410339355</t>
+    <t xml:space="preserve">3.28820586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680676460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33378386497498</t>
   </si>
   <si>
     <t xml:space="preserve">3.31099486351013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3533182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30773854255676</t>
+    <t xml:space="preserve">3.35331892967224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30773901939392</t>
   </si>
   <si>
     <t xml:space="preserve">3.15537476539612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32076120376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28494954109192</t>
+    <t xml:space="preserve">3.32076168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31424999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28494930267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40215277671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36634135246277</t>
+    <t xml:space="preserve">3.40215253829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36634063720703</t>
   </si>
   <si>
     <t xml:space="preserve">3.44447636604309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46401047706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633358955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48679971694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075487136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331068992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726560592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45749855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50958871841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47052121162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5812132358551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71795105934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77655291557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70818400382996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83189845085144</t>
+    <t xml:space="preserve">3.46401000022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4867992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075510978699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331116676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726536750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4574990272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50958943367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4705216884613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58121371269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71795082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7765531539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70818376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83189940452576</t>
   </si>
   <si>
     <t xml:space="preserve">3.82864332199097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87096691131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92305660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87422227859497</t>
+    <t xml:space="preserve">3.87096619606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92305636405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87422156333923</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88724446296692</t>
+    <t xml:space="preserve">3.88724422454834</t>
   </si>
   <si>
     <t xml:space="preserve">3.99142551422119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95886850357056</t>
+    <t xml:space="preserve">3.95886898040771</t>
   </si>
   <si>
     <t xml:space="preserve">4.00770330429077</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">4.06304979324341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97189116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01747131347656</t>
+    <t xml:space="preserve">3.9718906879425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01746988296509</t>
   </si>
   <si>
     <t xml:space="preserve">4.0663046836853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06956005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258390426636</t>
+    <t xml:space="preserve">4.06956195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258247375488</t>
   </si>
   <si>
     <t xml:space="preserve">4.12165117263794</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">4.09235095977783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11514043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12816286087036</t>
+    <t xml:space="preserve">4.11513996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12816333770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.09886169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14118576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08583974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11188459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16071891784668</t>
+    <t xml:space="preserve">4.14118480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08583879470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11188411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16071796417236</t>
   </si>
   <si>
     <t xml:space="preserve">4.13141822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.261643409729</t>
+    <t xml:space="preserve">4.26164436340332</t>
   </si>
   <si>
     <t xml:space="preserve">4.24862146377563</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">4.24536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24211072921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23559904098511</t>
+    <t xml:space="preserve">4.24211025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23559951782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.2323431968689</t>
@@ -1844,25 +1844,25 @@
     <t xml:space="preserve">4.38210296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40489292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37569141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28844594955444</t>
+    <t xml:space="preserve">4.4048924446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233591079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37569236755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28844547271729</t>
   </si>
   <si>
     <t xml:space="preserve">4.32871341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33206939697266</t>
+    <t xml:space="preserve">4.33206844329834</t>
   </si>
   <si>
     <t xml:space="preserve">4.41260290145874</t>
@@ -1871,7 +1871,10 @@
     <t xml:space="preserve">4.39246988296509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36226987838745</t>
+    <t xml:space="preserve">4.36226940155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233638763428</t>
   </si>
   <si>
     <t xml:space="preserve">4.22804594039917</t>
@@ -1880,40 +1883,40 @@
     <t xml:space="preserve">4.238112449646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2515344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751195907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10388803482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16093444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10724353790283</t>
+    <t xml:space="preserve">4.25153493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10388851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10724496841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.1642894744873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1273775100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12402200698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06697750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07704401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08039903640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04684352874756</t>
+    <t xml:space="preserve">4.12737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12402248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06697702407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07704448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08039999008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04684448242188</t>
   </si>
   <si>
     <t xml:space="preserve">4.02671051025391</t>
@@ -1925,106 +1928,106 @@
     <t xml:space="preserve">4.03342199325562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09046697616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14415645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13408899307251</t>
+    <t xml:space="preserve">4.09046649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14415597915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13408946990967</t>
   </si>
   <si>
     <t xml:space="preserve">4.17435646057129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1575779914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13744449615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368850708008</t>
+    <t xml:space="preserve">4.15757942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11059951782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13744497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368898391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.19784593582153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21797895431519</t>
+    <t xml:space="preserve">4.21797943115234</t>
   </si>
   <si>
     <t xml:space="preserve">4.24482345581055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34213590621948</t>
+    <t xml:space="preserve">4.34213638305664</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28509092330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33877992630005</t>
+    <t xml:space="preserve">4.28509140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33878087997437</t>
   </si>
   <si>
     <t xml:space="preserve">4.34549140930176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34884786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47300338745117</t>
+    <t xml:space="preserve">4.34884643554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47300386428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.50991487503052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4629373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45622634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41931390762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48978185653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48307085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51662683486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5367603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49313831329346</t>
+    <t xml:space="preserve">4.46293830871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45622539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41931533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48978233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48307132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51662635803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53675985336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4931378364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.44280385971069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.426025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42266988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44951438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42938184738159</t>
+    <t xml:space="preserve">4.42602586746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42267036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44951486587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42938137054443</t>
   </si>
   <si>
     <t xml:space="preserve">4.5065598487854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4696478843689</t>
+    <t xml:space="preserve">4.46964836120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.40924835205078</t>
@@ -2033,40 +2036,40 @@
     <t xml:space="preserve">4.39582538604736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20120143890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455598831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21126794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14080095291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33542442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273735046387</t>
+    <t xml:space="preserve">4.20120096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21126747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14079999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273782730103</t>
   </si>
   <si>
     <t xml:space="preserve">4.38575839996338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46629333496094</t>
+    <t xml:space="preserve">4.46629285812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.41595888137817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50320482254028</t>
+    <t xml:space="preserve">4.50320386886597</t>
   </si>
   <si>
     <t xml:space="preserve">4.52333784103394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722684860229</t>
+    <t xml:space="preserve">4.60722780227661</t>
   </si>
   <si>
     <t xml:space="preserve">4.6172947883606</t>
@@ -2075,16 +2078,16 @@
     <t xml:space="preserve">4.59716081619263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70454025268555</t>
+    <t xml:space="preserve">4.70453977584839</t>
   </si>
   <si>
     <t xml:space="preserve">4.65756177902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67769527435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72467374801636</t>
+    <t xml:space="preserve">4.67769479751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7246732711792</t>
   </si>
   <si>
     <t xml:space="preserve">4.73138475418091</t>
@@ -2096,25 +2099,25 @@
     <t xml:space="preserve">4.61393880844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64078330993652</t>
+    <t xml:space="preserve">4.64078378677368</t>
   </si>
   <si>
     <t xml:space="preserve">4.60387229919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62736177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62400531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62064981460571</t>
+    <t xml:space="preserve">4.62736082077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6240062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62065029144287</t>
   </si>
   <si>
     <t xml:space="preserve">4.56024932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66762781143188</t>
+    <t xml:space="preserve">4.66762924194336</t>
   </si>
   <si>
     <t xml:space="preserve">4.66427278518677</t>
@@ -2126,28 +2129,28 @@
     <t xml:space="preserve">4.68105030059814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82534074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86560869216919</t>
+    <t xml:space="preserve">4.82534122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86560773849487</t>
   </si>
   <si>
     <t xml:space="preserve">4.90251970291138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.942786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98305416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04345512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.073655128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08707761764526</t>
+    <t xml:space="preserve">4.94278621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98305368423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04345464706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07365560531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08707714080811</t>
   </si>
   <si>
     <t xml:space="preserve">5.09714412689209</t>
@@ -2165,37 +2168,37 @@
     <t xml:space="preserve">5.15754508972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16425657272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17432260513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16761159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23472309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54343795776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6340389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89241933822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77161836624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7850399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87102508544922</t>
+    <t xml:space="preserve">5.16425609588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1743221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16761112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23472261428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54343748092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63403987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175138473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89241886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77161884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78504037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87102603912354</t>
   </si>
   <si>
     <t xml:space="preserve">6.02923679351807</t>
@@ -2204,64 +2207,64 @@
     <t xml:space="preserve">6.17025136947632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18400907516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2699933052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840381622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32846260070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909915924072</t>
+    <t xml:space="preserve">6.18400859832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26999378204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32846307754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909868240356</t>
   </si>
   <si>
     <t xml:space="preserve">6.40069007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33878183364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28031158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26311445236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33534145355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38349342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33190155029297</t>
+    <t xml:space="preserve">6.33878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2803111076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2631139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3353419303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38349199295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33190250396729</t>
   </si>
   <si>
     <t xml:space="preserve">6.21496343612671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23216009140015</t>
+    <t xml:space="preserve">6.23216104507446</t>
   </si>
   <si>
     <t xml:space="preserve">6.25967597961426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23559951782227</t>
+    <t xml:space="preserve">6.23559999465942</t>
   </si>
   <si>
     <t xml:space="preserve">6.30438709259033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28375101089478</t>
+    <t xml:space="preserve">6.28375053405762</t>
   </si>
   <si>
     <t xml:space="preserve">6.27687215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24935722351074</t>
+    <t xml:space="preserve">6.2493577003479</t>
   </si>
   <si>
     <t xml:space="preserve">6.1668119430542</t>
@@ -2270,31 +2273,31 @@
     <t xml:space="preserve">6.13585758209229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1461763381958</t>
+    <t xml:space="preserve">6.14617586135864</t>
   </si>
   <si>
     <t xml:space="preserve">6.09114503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11866092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91229820251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573810577393</t>
+    <t xml:space="preserve">6.11866188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0361156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91229867935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573715209961</t>
   </si>
   <si>
     <t xml:space="preserve">6.05331230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19088840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00860071182251</t>
+    <t xml:space="preserve">6.19088745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00860118865967</t>
   </si>
   <si>
     <t xml:space="preserve">6.00516128540039</t>
@@ -2303,34 +2306,31 @@
     <t xml:space="preserve">6.10490322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03267621994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92949390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95700931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90885782241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73001003265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85726833343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78504085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60619211196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61651134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249605178833</t>
+    <t xml:space="preserve">6.03267669677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92949438095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95700979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90885877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73001050949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8572678565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60619258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61651086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249462127686</t>
   </si>
   <si>
     <t xml:space="preserve">5.66810178756714</t>
@@ -2339,22 +2339,22 @@
     <t xml:space="preserve">5.71625328063965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77816104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81255531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80567646026611</t>
+    <t xml:space="preserve">5.77816152572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81255483627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80567693710327</t>
   </si>
   <si>
     <t xml:space="preserve">5.80911588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8779034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98108625411987</t>
+    <t xml:space="preserve">5.87790393829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98108530044556</t>
   </si>
   <si>
     <t xml:space="preserve">6.01547956466675</t>
@@ -2363,34 +2363,34 @@
     <t xml:space="preserve">5.8675856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70593452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40326881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35511827468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37231492996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505710601807</t>
+    <t xml:space="preserve">5.70593500137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40326929092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3551173210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37231540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505805969238</t>
   </si>
   <si>
     <t xml:space="preserve">5.0627703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00430059432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98366451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9492712020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69819593429565</t>
+    <t xml:space="preserve">5.00430107116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98366498947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94927072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6981954574585</t>
   </si>
   <si>
     <t xml:space="preserve">4.58813571929932</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">3.75580525398254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71453261375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36509203910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36784243583679</t>
+    <t xml:space="preserve">3.71453237533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36509108543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36784291267395</t>
   </si>
   <si>
     <t xml:space="preserve">3.08306193351746</t>
@@ -2417,22 +2417,22 @@
     <t xml:space="preserve">2.84092974662781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80516004562378</t>
+    <t xml:space="preserve">2.8051598072052</t>
   </si>
   <si>
     <t xml:space="preserve">2.91109299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90283823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25365543365479</t>
+    <t xml:space="preserve">2.90283846855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25365519523621</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133385658264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53568530082703</t>
+    <t xml:space="preserve">3.53568458557129</t>
   </si>
   <si>
     <t xml:space="preserve">3.41599416732788</t>
@@ -2444,55 +2444,55 @@
     <t xml:space="preserve">3.1986255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18899488449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20000123977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14359545707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25778269767761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43938231468201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59415435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76268339157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44970011711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4909725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5975935459137</t>
+    <t xml:space="preserve">3.18899512290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20000147819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14359521865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25778245925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43938279151917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.594153881073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76268434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44970035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49097323417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59759330749512</t>
   </si>
   <si>
     <t xml:space="preserve">3.52880597114563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36096382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48409414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56319999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5460033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68013834953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8555474281311</t>
+    <t xml:space="preserve">3.36096429824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48409366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56319952011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54600262641907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68013858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85554718971252</t>
   </si>
   <si>
     <t xml:space="preserve">4.01031923294067</t>
@@ -2501,145 +2501,145 @@
     <t xml:space="preserve">3.83147144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65950202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60447239875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64574503898621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68701767921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6904571056366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84866833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745686531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019951820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421481132507</t>
+    <t xml:space="preserve">3.65950226783752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60447192192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64574527740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68701839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69045662879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84866881370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745591163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421504974365</t>
   </si>
   <si>
     <t xml:space="preserve">3.80739593505859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81427478790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92089509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95529007911682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03439474105835</t>
+    <t xml:space="preserve">3.81427550315857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92089533805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95528960227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03439569473267</t>
   </si>
   <si>
     <t xml:space="preserve">4.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16853094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12037897109985</t>
+    <t xml:space="preserve">4.16853141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12037944793701</t>
   </si>
   <si>
     <t xml:space="preserve">4.08598566055298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23731803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28547048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44712114334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65348291397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76010417938232</t>
+    <t xml:space="preserve">4.23731899261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2854700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44712162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76010465621948</t>
   </si>
   <si>
     <t xml:space="preserve">4.57781744003296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33018207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34737920761108</t>
+    <t xml:space="preserve">4.33018255233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34737968444824</t>
   </si>
   <si>
     <t xml:space="preserve">4.49183368682861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44368124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42304515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46775770187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4539999961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49527215957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30266714096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33706045150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37489461898804</t>
+    <t xml:space="preserve">4.44368171691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42304468154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46775674819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45399951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49527263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30266666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29234838485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33706092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37489414215088</t>
   </si>
   <si>
     <t xml:space="preserve">4.39553022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32330274581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52622747421265</t>
+    <t xml:space="preserve">4.32330322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52622699737549</t>
   </si>
   <si>
     <t xml:space="preserve">4.41616678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52278709411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50215101242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31298542022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41960620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4711971282959</t>
+    <t xml:space="preserve">4.52278757095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50215148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31298494338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41960573196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47119665145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.53310585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.536545753479</t>
+    <t xml:space="preserve">4.53654479980469</t>
   </si>
   <si>
     <t xml:space="preserve">4.5571813583374</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">4.61221122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093858718872</t>
+    <t xml:space="preserve">4.57093906402588</t>
   </si>
   <si>
     <t xml:space="preserve">4.52966594696045</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">4.45743942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40928745269775</t>
+    <t xml:space="preserve">4.40928792953491</t>
   </si>
   <si>
     <t xml:space="preserve">4.39209127426147</t>
@@ -2669,46 +2669,46 @@
     <t xml:space="preserve">4.42648458480835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26139402389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42992448806763</t>
+    <t xml:space="preserve">4.26139497756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42992353439331</t>
   </si>
   <si>
     <t xml:space="preserve">4.43680286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63628721237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68443775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60877132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48839426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56406021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45056104660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5950140953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51590967178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5468635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40240955352783</t>
+    <t xml:space="preserve">4.56062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63628768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68443870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60877180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48839330673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5640606880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45056056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59501457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51590871810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54686307907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40240859985352</t>
   </si>
   <si>
     <t xml:space="preserve">4.2751522064209</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">4.35081815719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35425806045532</t>
+    <t xml:space="preserve">4.35425758361816</t>
   </si>
   <si>
     <t xml:space="preserve">4.55030202865601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33362150192261</t>
+    <t xml:space="preserve">4.33362197875977</t>
   </si>
   <si>
     <t xml:space="preserve">4.23043966293335</t>
@@ -2741,40 +2741,40 @@
     <t xml:space="preserve">4.50559043884277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43336343765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29922771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30610656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16165208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03783464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98968291282654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03095626831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25107669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73258924484253</t>
+    <t xml:space="preserve">4.43336391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29922723770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31986379623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30610609054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16165256500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03783512115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98968315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03095531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25107574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73259019851685</t>
   </si>
   <si>
     <t xml:space="preserve">4.81169557571411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93207359313965</t>
+    <t xml:space="preserve">4.93207406997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.81513500213623</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">4.96646738052368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20034551620483</t>
+    <t xml:space="preserve">5.20034599304199</t>
   </si>
   <si>
     <t xml:space="preserve">5.19346714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12467908859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22442054748535</t>
+    <t xml:space="preserve">5.12467861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22442150115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.24161815643311</t>
@@ -2801,40 +2801,40 @@
     <t xml:space="preserve">5.3791937828064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2656946182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3413610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23129987716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2966480255127</t>
+    <t xml:space="preserve">5.26569414138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34136009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23129940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29664850234985</t>
   </si>
   <si>
     <t xml:space="preserve">5.15563344955444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11092090606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10404300689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04557371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00774002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00086164474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91831684112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88736200332642</t>
+    <t xml:space="preserve">5.11092185974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10404253005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04557418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00774049758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00086116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91831636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88736152648926</t>
   </si>
   <si>
     <t xml:space="preserve">4.8942403793335</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">4.89768028259277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8839225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86672639846802</t>
+    <t xml:space="preserve">4.88392210006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8667254447937</t>
   </si>
   <si>
     <t xml:space="preserve">4.76698303222656</t>
@@ -2861,52 +2861,52 @@
     <t xml:space="preserve">4.89080142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91487789154053</t>
+    <t xml:space="preserve">4.91487693786621</t>
   </si>
   <si>
     <t xml:space="preserve">4.85984706878662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87016487121582</t>
+    <t xml:space="preserve">4.87016534805298</t>
   </si>
   <si>
     <t xml:space="preserve">5.05933141708374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03869533538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03181648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71539306640625</t>
+    <t xml:space="preserve">5.03869485855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03181552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71539211273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.59845352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53998470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61565113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6706805229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02837657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12811803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31728506088257</t>
+    <t xml:space="preserve">4.53998374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61565160751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67068147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02837705612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12811851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31728458404541</t>
   </si>
   <si>
     <t xml:space="preserve">5.25537586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27257299423218</t>
+    <t xml:space="preserve">5.27257251739502</t>
   </si>
   <si>
     <t xml:space="preserve">5.25881576538086</t>
@@ -2918,34 +2918,34 @@
     <t xml:space="preserve">5.07652807235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09028482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14875459671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493715286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05245208740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9699068069458</t>
+    <t xml:space="preserve">5.09028577804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14875555038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493762969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05245113372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96990728378296</t>
   </si>
   <si>
     <t xml:space="preserve">5.13499736785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14187574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23817920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29320907592773</t>
+    <t xml:space="preserve">5.16251277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14187669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23817825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29320859909058</t>
   </si>
   <si>
     <t xml:space="preserve">5.32760238647461</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">5.34479999542236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33104181289673</t>
+    <t xml:space="preserve">5.33104228973389</t>
   </si>
   <si>
     <t xml:space="preserve">5.33792114257812</t>
@@ -2963,37 +2963,37 @@
     <t xml:space="preserve">5.45142078399658</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58899593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708673477173</t>
+    <t xml:space="preserve">5.58899545669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50645065307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708625793457</t>
   </si>
   <si>
     <t xml:space="preserve">5.44454193115234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48237466812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48925399780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56491994857788</t>
+    <t xml:space="preserve">5.48237562179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48925352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56492042541504</t>
   </si>
   <si>
     <t xml:space="preserve">5.53740549087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51952075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55116271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47824811935425</t>
+    <t xml:space="preserve">5.51952028274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5511622428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47824716567993</t>
   </si>
   <si>
     <t xml:space="preserve">5.40258121490479</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">5.41221189498901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41496324539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36543560028076</t>
+    <t xml:space="preserve">5.414963722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36543703079224</t>
   </si>
   <si>
     <t xml:space="preserve">5.38332080841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43972730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39020013809204</t>
+    <t xml:space="preserve">5.43972682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39019966125488</t>
   </si>
   <si>
     <t xml:space="preserve">5.32553958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37644195556641</t>
+    <t xml:space="preserve">5.37644147872925</t>
   </si>
   <si>
     <t xml:space="preserve">5.39982986450195</t>
@@ -3032,103 +3032,103 @@
     <t xml:space="preserve">5.37506628036499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34617519378662</t>
+    <t xml:space="preserve">5.34617567062378</t>
   </si>
   <si>
     <t xml:space="preserve">5.46036291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37369108200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43697500228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5140175819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57730150222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55528926849365</t>
+    <t xml:space="preserve">5.37369012832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43697452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51401615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57730197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55528974533081</t>
   </si>
   <si>
     <t xml:space="preserve">5.42046642303467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42321729660034</t>
+    <t xml:space="preserve">5.4232177734375</t>
   </si>
   <si>
     <t xml:space="preserve">5.44247817993164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39845371246338</t>
+    <t xml:space="preserve">5.3984546661377</t>
   </si>
   <si>
     <t xml:space="preserve">5.47484111785889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43066740036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42928647994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44309091567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5949387550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58113479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56733083724976</t>
+    <t xml:space="preserve">5.43066644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42928600311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44309043884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59493970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58113527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56732988357544</t>
   </si>
   <si>
     <t xml:space="preserve">5.57837438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55766773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70813608169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74264669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63773345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69571161270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66948318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76473522186279</t>
+    <t xml:space="preserve">5.55766725540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60046148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70813655853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74264621734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6377329826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69571208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66948366165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76473426818848</t>
   </si>
   <si>
     <t xml:space="preserve">5.77715826034546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291833877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61288499832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6791467666626</t>
+    <t xml:space="preserve">5.6750054359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61288452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67914628982544</t>
   </si>
   <si>
     <t xml:space="preserve">5.83927774429321</t>
@@ -3137,25 +3137,25 @@
     <t xml:space="preserve">5.66120052337646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7923436164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66258144378662</t>
+    <t xml:space="preserve">5.79234313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66258192062378</t>
   </si>
   <si>
     <t xml:space="preserve">5.66534185409546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68466901779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68604850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65015745162964</t>
+    <t xml:space="preserve">5.68466854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328809738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68604898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65015697479248</t>
   </si>
   <si>
     <t xml:space="preserve">5.55352640151978</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">5.72746276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66810321807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68742990493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60460233688354</t>
+    <t xml:space="preserve">5.66810274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68742942810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6046028137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.59355926513672</t>
@@ -3188,19 +3188,19 @@
     <t xml:space="preserve">5.57975435256958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62392854690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362546920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81442928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81995153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79924535751343</t>
+    <t xml:space="preserve">5.62392902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81442975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81995105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79924583435059</t>
   </si>
   <si>
     <t xml:space="preserve">5.79510307312012</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">5.73160314559937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74540853500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71503829956055</t>
+    <t xml:space="preserve">5.7454080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71503782272339</t>
   </si>
   <si>
     <t xml:space="preserve">5.75507116317749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80752849578857</t>
+    <t xml:space="preserve">5.80752801895142</t>
   </si>
   <si>
     <t xml:space="preserve">5.88069200515747</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">5.95523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96351766586304</t>
+    <t xml:space="preserve">5.96351861953735</t>
   </si>
   <si>
     <t xml:space="preserve">6.04910564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03115940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981134414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03254079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07809448242188</t>
+    <t xml:space="preserve">6.03115892410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06981229782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07809495925903</t>
   </si>
   <si>
     <t xml:space="preserve">5.94695281982422</t>
@@ -3251,43 +3251,43 @@
     <t xml:space="preserve">5.92348480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98284482955933</t>
+    <t xml:space="preserve">5.98284387588501</t>
   </si>
   <si>
     <t xml:space="preserve">5.97318124771118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99802875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98560523986816</t>
+    <t xml:space="preserve">5.99802923202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98560476303101</t>
   </si>
   <si>
     <t xml:space="preserve">6.03668165206909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05048561096191</t>
+    <t xml:space="preserve">6.05048513412476</t>
   </si>
   <si>
     <t xml:space="preserve">6.06705141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06567049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08775758743286</t>
+    <t xml:space="preserve">6.06567096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0877571105957</t>
   </si>
   <si>
     <t xml:space="preserve">6.09051895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06014966964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04220247268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03944206237793</t>
+    <t xml:space="preserve">6.06014823913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04220294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03944301605225</t>
   </si>
   <si>
     <t xml:space="preserve">6.01045322418213</t>
@@ -3296,73 +3296,73 @@
     <t xml:space="preserve">6.15678024291992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19681262969971</t>
+    <t xml:space="preserve">6.19681310653687</t>
   </si>
   <si>
     <t xml:space="preserve">6.15125846862793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2023344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14573621749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95937585830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14849710464478</t>
+    <t xml:space="preserve">6.20233535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1457371711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95937633514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14849758148193</t>
   </si>
   <si>
     <t xml:space="preserve">6.3459005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3003454208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32519340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32243347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39835739135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4535756111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55710935592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57229423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343637466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542440414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6661639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71585941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420923233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72000122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245855331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80697011947632</t>
+    <t xml:space="preserve">6.30034685134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32519388198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32243299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39835786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45357513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55710887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57229471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6054253578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585988998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72000074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80696964263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.82739305496216</t>
@@ -3371,43 +3371,43 @@
     <t xml:space="preserve">6.70334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7093186378479</t>
+    <t xml:space="preserve">6.70931816101074</t>
   </si>
   <si>
     <t xml:space="preserve">6.62562131881714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6136646270752</t>
+    <t xml:space="preserve">6.61366415023804</t>
   </si>
   <si>
     <t xml:space="preserve">6.56284666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66149139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60917901992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56583642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50605201721191</t>
+    <t xml:space="preserve">6.66149091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60918045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56583595275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50605154037476</t>
   </si>
   <si>
     <t xml:space="preserve">6.58227682113647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49708461761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55387926101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68241596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65850210189819</t>
+    <t xml:space="preserve">6.49708318710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55387878417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68241548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65850162506104</t>
   </si>
   <si>
     <t xml:space="preserve">6.66448068618774</t>
@@ -3416,31 +3416,31 @@
     <t xml:space="preserve">6.73771619796753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77657651901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78404998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84532928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8318772315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74369478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66298580169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56434202194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70861291885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58429431915283</t>
+    <t xml:space="preserve">6.77657699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78404951095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84532880783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83187675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74369430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66298627853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56434154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70861196517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58429336547852</t>
   </si>
   <si>
     <t xml:space="preserve">6.7761435508728</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">6.38783931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43848848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32951688766479</t>
+    <t xml:space="preserve">6.4384880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32951736450195</t>
   </si>
   <si>
     <t xml:space="preserve">6.49374055862427</t>
@@ -3464,91 +3464,91 @@
     <t xml:space="preserve">6.44309186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47685718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54899311065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68405628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62112903594971</t>
+    <t xml:space="preserve">6.47685766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54899406433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6840558052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62112855911255</t>
   </si>
   <si>
     <t xml:space="preserve">6.56127166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51522731781006</t>
+    <t xml:space="preserve">6.51522779464722</t>
   </si>
   <si>
     <t xml:space="preserve">6.50601863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51062393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52443695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4446268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2451024055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42927885055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48299741744995</t>
+    <t xml:space="preserve">6.51062297821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52443647384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44462633132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24510288238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42927932739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48299694061279</t>
   </si>
   <si>
     <t xml:space="preserve">6.58889865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64568567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74391269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79456186294556</t>
+    <t xml:space="preserve">6.65335988998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64568519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74391222000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79456090927124</t>
   </si>
   <si>
     <t xml:space="preserve">6.85288429260254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66410303115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78688669204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84981441497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97566699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10612630844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13221645355225</t>
+    <t xml:space="preserve">6.66410350799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78688812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84981393814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97566843032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10612678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1322169303894</t>
   </si>
   <si>
     <t xml:space="preserve">6.99255132675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96185398101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79763126373291</t>
+    <t xml:space="preserve">6.96185493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79763078689575</t>
   </si>
   <si>
     <t xml:space="preserve">6.7914924621582</t>
@@ -3557,58 +3557,58 @@
     <t xml:space="preserve">6.70554256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40779161453247</t>
+    <t xml:space="preserve">6.40779209136963</t>
   </si>
   <si>
     <t xml:space="preserve">6.41700077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55052804946899</t>
+    <t xml:space="preserve">6.55052852630615</t>
   </si>
   <si>
     <t xml:space="preserve">6.51829719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46611404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57201623916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67177820205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76386642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69786834716797</t>
+    <t xml:space="preserve">6.46611356735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57201480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76386547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69786930084229</t>
   </si>
   <si>
     <t xml:space="preserve">6.45844030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54438877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69940376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79916572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56894588470459</t>
+    <t xml:space="preserve">6.54438781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69940280914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79916477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56894540786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.34486484527588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5229024887085</t>
+    <t xml:space="preserve">6.52290153503418</t>
   </si>
   <si>
     <t xml:space="preserve">6.47225332260132</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38476991653442</t>
+    <t xml:space="preserve">6.38476943969727</t>
   </si>
   <si>
     <t xml:space="preserve">6.36328220367432</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">5.75089693069458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8874945640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64960050582886</t>
+    <t xml:space="preserve">5.88749408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6496000289917</t>
   </si>
   <si>
     <t xml:space="preserve">5.43933200836182</t>
@@ -3638,43 +3638,43 @@
     <t xml:space="preserve">5.46388912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33650159835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98810195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0709810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62657785415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29966640472412</t>
+    <t xml:space="preserve">5.33650064468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98810148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977857589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07098054885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62657833099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29966592788696</t>
   </si>
   <si>
     <t xml:space="preserve">5.41938066482544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50993299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62811326980591</t>
+    <t xml:space="preserve">5.50993347167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62811279296875</t>
   </si>
   <si>
     <t xml:space="preserve">5.92125988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88135528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86447191238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82149791717529</t>
+    <t xml:space="preserve">5.88135576248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86447286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82149744033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.97190809249878</t>
@@ -3686,28 +3686,28 @@
     <t xml:space="preserve">5.87214612960815</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92586374282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96116495132446</t>
+    <t xml:space="preserve">5.92586421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96116542816162</t>
   </si>
   <si>
     <t xml:space="preserve">6.12538814544678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06860113143921</t>
+    <t xml:space="preserve">6.06860065460205</t>
   </si>
   <si>
     <t xml:space="preserve">5.95195627212524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05325269699097</t>
+    <t xml:space="preserve">6.05325317382812</t>
   </si>
   <si>
     <t xml:space="preserve">5.98879146575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93353843688965</t>
+    <t xml:space="preserve">5.93353796005249</t>
   </si>
   <si>
     <t xml:space="preserve">5.72787523269653</t>
@@ -3716,97 +3716,97 @@
     <t xml:space="preserve">5.71559619903564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85679817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82303285598755</t>
+    <t xml:space="preserve">5.85679864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82303237915039</t>
   </si>
   <si>
     <t xml:space="preserve">5.77084922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81842803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86293792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79859828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89671564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87097978591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78090524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65865993499756</t>
+    <t xml:space="preserve">5.81842851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79859781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89671611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87098026275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78090476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6586594581604</t>
   </si>
   <si>
     <t xml:space="preserve">5.56536722183228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60397052764893</t>
+    <t xml:space="preserve">5.60397100448608</t>
   </si>
   <si>
     <t xml:space="preserve">5.55089092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61040449142456</t>
+    <t xml:space="preserve">5.61040592193604</t>
   </si>
   <si>
     <t xml:space="preserve">5.56375932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59271192550659</t>
+    <t xml:space="preserve">5.59271144866943</t>
   </si>
   <si>
     <t xml:space="preserve">5.55732488632202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62166452407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58788633346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50263690948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56054258346558</t>
+    <t xml:space="preserve">5.62166404724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58788681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50263643264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56054210662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.81146574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66348457336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7085223197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74069213867188</t>
+    <t xml:space="preserve">5.66348552703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70852327346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74069261550903</t>
   </si>
   <si>
     <t xml:space="preserve">5.76321172714233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6892204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510822296143</t>
+    <t xml:space="preserve">5.68922090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510774612427</t>
   </si>
   <si>
     <t xml:space="preserve">5.75516891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76803636550903</t>
+    <t xml:space="preserve">5.76803684234619</t>
   </si>
   <si>
     <t xml:space="preserve">5.9514045715332</t>
@@ -3815,46 +3815,46 @@
     <t xml:space="preserve">5.94175386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91280126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84685230255127</t>
+    <t xml:space="preserve">5.91280078887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84685325622559</t>
   </si>
   <si>
     <t xml:space="preserve">5.75034332275391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8870644569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80503177642822</t>
+    <t xml:space="preserve">5.88706541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80503225326538</t>
   </si>
   <si>
     <t xml:space="preserve">5.72299909591675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55249977111816</t>
+    <t xml:space="preserve">5.55249929428101</t>
   </si>
   <si>
     <t xml:space="preserve">5.17450475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13107585906982</t>
+    <t xml:space="preserve">4.93323087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13107538223267</t>
   </si>
   <si>
     <t xml:space="preserve">5.20828294754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01043891906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11820793151855</t>
+    <t xml:space="preserve">5.0104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225992202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1182074546814</t>
   </si>
   <si>
     <t xml:space="preserve">5.11981630325317</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">5.15198612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30157518386841</t>
+    <t xml:space="preserve">5.30157470703125</t>
   </si>
   <si>
     <t xml:space="preserve">5.16807126998901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17933082580566</t>
+    <t xml:space="preserve">5.17933034896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.14876890182495</t>
@@ -3878,25 +3878,25 @@
     <t xml:space="preserve">5.04904270172119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07156229019165</t>
+    <t xml:space="preserve">5.07156181335449</t>
   </si>
   <si>
     <t xml:space="preserve">5.05386829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80294418334961</t>
+    <t xml:space="preserve">4.80294466018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.88819408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03456687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17611312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295850753784</t>
+    <t xml:space="preserve">5.03456735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17611360549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03295755386353</t>
   </si>
   <si>
     <t xml:space="preserve">5.10855722427368</t>
@@ -3905,52 +3905,52 @@
     <t xml:space="preserve">5.03778314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85924053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98631191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12142515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93484020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01848173141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0152645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96379232406616</t>
+    <t xml:space="preserve">4.85924100875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9123215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98631143569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12142467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93483972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01848125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01526403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96379280090332</t>
   </si>
   <si>
     <t xml:space="preserve">4.99274587631226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1873722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21150064468384</t>
+    <t xml:space="preserve">5.18737268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21150016784668</t>
   </si>
   <si>
     <t xml:space="preserve">5.15842056274414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45598983764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59431982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50746154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48976850509644</t>
+    <t xml:space="preserve">5.45599031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59432029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50746250152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48976898193359</t>
   </si>
   <si>
     <t xml:space="preserve">5.46242380142212</t>
@@ -3959,13 +3959,13 @@
     <t xml:space="preserve">5.50424480438232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53641414642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56858396530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51067924499512</t>
+    <t xml:space="preserve">5.5364146232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56858348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51067876815796</t>
   </si>
   <si>
     <t xml:space="preserve">5.40291023254395</t>
@@ -3974,10 +3974,10 @@
     <t xml:space="preserve">5.44312238693237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33374500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19219779968262</t>
+    <t xml:space="preserve">5.33374452590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19219827651978</t>
   </si>
   <si>
     <t xml:space="preserve">5.28388214111328</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">5.14394378662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12946748733521</t>
+    <t xml:space="preserve">5.12946701049805</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883102416992</t>
@@ -4004,28 +4004,28 @@
     <t xml:space="preserve">5.24688673019409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08121299743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1825475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19863224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31766080856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53963184356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41577863693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49459362030029</t>
+    <t xml:space="preserve">5.08121252059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659955978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18254709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19863176345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31765985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53963136672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41577816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49459409713745</t>
   </si>
   <si>
     <t xml:space="preserve">5.2887077331543</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">5.33052825927734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08925485610962</t>
+    <t xml:space="preserve">5.08925533294678</t>
   </si>
   <si>
     <t xml:space="preserve">5.15037727355957</t>
@@ -4052,43 +4052,43 @@
     <t xml:space="preserve">5.16002893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08603811264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13590145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9879207611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20345783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45920658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39808464050293</t>
+    <t xml:space="preserve">5.08603763580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.135901927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98792028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20345735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45920705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39808416366577</t>
   </si>
   <si>
     <t xml:space="preserve">5.37878322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32409381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33696269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28709888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14555168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30961799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35626363754272</t>
+    <t xml:space="preserve">5.32409429550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33696222305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28709936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14555215835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30961847305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35626411437988</t>
   </si>
   <si>
     <t xml:space="preserve">5.47368383407593</t>
@@ -4106,40 +4106,40 @@
     <t xml:space="preserve">5.67152738571167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73908472061157</t>
+    <t xml:space="preserve">5.73908424377441</t>
   </si>
   <si>
     <t xml:space="preserve">5.90315008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92405986785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04308748245239</t>
+    <t xml:space="preserve">5.92406034469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04308795928955</t>
   </si>
   <si>
     <t xml:space="preserve">6.11707830429077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09616851806641</t>
+    <t xml:space="preserve">6.09616804122925</t>
   </si>
   <si>
     <t xml:space="preserve">6.02539539337158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06560707092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08651685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21519660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27149295806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24897480010986</t>
+    <t xml:space="preserve">6.06560659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08651733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21519708633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24897432327271</t>
   </si>
   <si>
     <t xml:space="preserve">6.26023435592651</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">6.35996055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45968580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49668169021606</t>
+    <t xml:space="preserve">6.45968627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49668216705322</t>
   </si>
   <si>
     <t xml:space="preserve">6.46451234817505</t>
@@ -4163,28 +4163,28 @@
     <t xml:space="preserve">6.45646953582764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50472450256348</t>
+    <t xml:space="preserve">6.50472497940063</t>
   </si>
   <si>
     <t xml:space="preserve">6.50969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53290414810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56108522415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47820091247559</t>
+    <t xml:space="preserve">6.53290462493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56108570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47820138931274</t>
   </si>
   <si>
     <t xml:space="preserve">6.4931206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52958869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52461671829224</t>
+    <t xml:space="preserve">6.52958917617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52461624145508</t>
   </si>
   <si>
     <t xml:space="preserve">6.67877960205078</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">6.53124666213989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61413097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57434749603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51301193237305</t>
+    <t xml:space="preserve">6.61413049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57434606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51301240921021</t>
   </si>
   <si>
     <t xml:space="preserve">6.47488594055176</t>
@@ -4208,22 +4208,22 @@
     <t xml:space="preserve">6.52627372741699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46825551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54616546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54948091506958</t>
+    <t xml:space="preserve">6.46825504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54616594314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5494818687439</t>
   </si>
   <si>
     <t xml:space="preserve">6.4400749206543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39200210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55777025222778</t>
+    <t xml:space="preserve">6.39200258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55776977539062</t>
   </si>
   <si>
     <t xml:space="preserve">6.51467037200928</t>
@@ -4235,28 +4235,28 @@
     <t xml:space="preserve">6.46328210830688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54450845718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56274271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68209600448608</t>
+    <t xml:space="preserve">6.54450798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56274318695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68209552764893</t>
   </si>
   <si>
     <t xml:space="preserve">6.64728498458862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73514175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86609792709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87935924530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00202751159668</t>
+    <t xml:space="preserve">6.73514223098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86609840393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87935876846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00202703475952</t>
   </si>
   <si>
     <t xml:space="preserve">7.04015350341797</t>
@@ -4268,28 +4268,28 @@
     <t xml:space="preserve">7.11806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10646152496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97218942642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98545122146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07496404647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13464069366455</t>
+    <t xml:space="preserve">7.10646104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9721884727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98545074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07496547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13464117050171</t>
   </si>
   <si>
     <t xml:space="preserve">7.19100189208984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20757865905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26725482940674</t>
+    <t xml:space="preserve">7.20758008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2672553062439</t>
   </si>
   <si>
     <t xml:space="preserve">7.26559734344482</t>
@@ -4301,79 +4301,79 @@
     <t xml:space="preserve">7.40152788162231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40484237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45788812637329</t>
+    <t xml:space="preserve">7.40484285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45788764953613</t>
   </si>
   <si>
     <t xml:space="preserve">7.49767160415649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54077243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54242944717407</t>
+    <t xml:space="preserve">7.54077100753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54242992401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.47446537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58884477615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62034177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64023351669312</t>
+    <t xml:space="preserve">7.58884525299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62034130096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64023303985596</t>
   </si>
   <si>
     <t xml:space="preserve">7.67504405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69327735900879</t>
+    <t xml:space="preserve">7.69327783584595</t>
   </si>
   <si>
     <t xml:space="preserve">7.52585315704346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49435710906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.559006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6054220199585</t>
+    <t xml:space="preserve">7.46286058425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49435663223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55900621414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60542154312134</t>
   </si>
   <si>
     <t xml:space="preserve">7.59713363647461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60210657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66675472259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71814346313477</t>
+    <t xml:space="preserve">7.60210704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66675567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71814489364624</t>
   </si>
   <si>
     <t xml:space="preserve">7.72643089294434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77781963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45457363128662</t>
+    <t xml:space="preserve">7.77781915664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45457410812378</t>
   </si>
   <si>
     <t xml:space="preserve">6.87604331970215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03518104553223</t>
+    <t xml:space="preserve">7.03518056869507</t>
   </si>
   <si>
     <t xml:space="preserve">6.66883373260498</t>
@@ -4382,40 +4382,40 @@
     <t xml:space="preserve">6.73348331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51135444641113</t>
+    <t xml:space="preserve">6.51135492324829</t>
   </si>
   <si>
     <t xml:space="preserve">6.76166391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00037002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86941337585449</t>
+    <t xml:space="preserve">7.00037050247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86941289901733</t>
   </si>
   <si>
     <t xml:space="preserve">6.76663684844971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76000595092773</t>
+    <t xml:space="preserve">6.76000642776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.67214965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83460283279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93406248092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92743158340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01363039016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96887397766113</t>
+    <t xml:space="preserve">6.83460187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93406200408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92743110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01363086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96887350082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.89262056350708</t>
@@ -4424,37 +4424,37 @@
     <t xml:space="preserve">7.05341529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06999158859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07993841171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15950632095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16282176971436</t>
+    <t xml:space="preserve">7.06999206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07993793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15950584411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16282224655151</t>
   </si>
   <si>
     <t xml:space="preserve">7.18271398544312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08656930923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1429295539856</t>
+    <t xml:space="preserve">7.08656883239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14293050765991</t>
   </si>
   <si>
     <t xml:space="preserve">7.1634407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05917692184448</t>
+    <t xml:space="preserve">7.05917739868164</t>
   </si>
   <si>
     <t xml:space="preserve">7.01473665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05746793746948</t>
+    <t xml:space="preserve">7.05746841430664</t>
   </si>
   <si>
     <t xml:space="preserve">7.00277233123779</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">6.85406827926636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72245597839355</t>
+    <t xml:space="preserve">6.72245645523071</t>
   </si>
   <si>
     <t xml:space="preserve">6.92414712905884</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92585563659668</t>
+    <t xml:space="preserve">6.92585611343384</t>
   </si>
   <si>
     <t xml:space="preserve">6.92072772979736</t>
@@ -4481,85 +4481,85 @@
     <t xml:space="preserve">6.77031469345093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65921401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76005840301514</t>
+    <t xml:space="preserve">6.65921354293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76005887985229</t>
   </si>
   <si>
     <t xml:space="preserve">6.71049118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71220064163208</t>
+    <t xml:space="preserve">6.71220016479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.79937171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78569841384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9549126625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98738813400269</t>
+    <t xml:space="preserve">6.78569793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491313934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98738861083984</t>
   </si>
   <si>
     <t xml:space="preserve">6.93782091140747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74638557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86774158477783</t>
+    <t xml:space="preserve">6.74638509750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86774206161499</t>
   </si>
   <si>
     <t xml:space="preserve">6.86261367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79082536697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73100233078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84894037246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0301194190979</t>
+    <t xml:space="preserve">6.79082584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73100185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84893989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011989593506</t>
   </si>
   <si>
     <t xml:space="preserve">6.96858739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98397064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00619029998779</t>
+    <t xml:space="preserve">6.98397016525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00619077682495</t>
   </si>
   <si>
     <t xml:space="preserve">6.99422550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99593496322632</t>
+    <t xml:space="preserve">6.99593448638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.0232834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06259536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09678030014038</t>
+    <t xml:space="preserve">7.06259489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09677982330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.12583780288696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14634847640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15660381317139</t>
+    <t xml:space="preserve">7.14634895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15660333633423</t>
   </si>
   <si>
     <t xml:space="preserve">7.11045408248901</t>
@@ -4577,13 +4577,13 @@
     <t xml:space="preserve">6.87116003036499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94636726379395</t>
+    <t xml:space="preserve">6.94636678695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.97029638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07797861099243</t>
+    <t xml:space="preserve">7.07797813415527</t>
   </si>
   <si>
     <t xml:space="preserve">7.09165334701538</t>
@@ -4595,88 +4595,88 @@
     <t xml:space="preserve">6.90534496307373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72587442398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88825273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123888015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06088590621948</t>
+    <t xml:space="preserve">6.72587394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84039354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8882532119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123935699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06088638305664</t>
   </si>
   <si>
     <t xml:space="preserve">7.13096475601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12925624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14976644515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30530881881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34291172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34974908828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38393306732178</t>
+    <t xml:space="preserve">7.12925577163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14976692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30530834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34291124343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34974813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38393354415894</t>
   </si>
   <si>
     <t xml:space="preserve">7.38564252853394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41982746124268</t>
+    <t xml:space="preserve">7.41982698440552</t>
   </si>
   <si>
     <t xml:space="preserve">7.44033861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46768617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57536888122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55485773086548</t>
+    <t xml:space="preserve">7.46768522262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57536935806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55485820770264</t>
   </si>
   <si>
     <t xml:space="preserve">7.27112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21813678741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20446300506592</t>
+    <t xml:space="preserve">7.21813726425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20446348190308</t>
   </si>
   <si>
     <t xml:space="preserve">7.20788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19249773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76347827911377</t>
+    <t xml:space="preserve">7.19249820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76347732543945</t>
   </si>
   <si>
     <t xml:space="preserve">6.94465827941895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03182888031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13609266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97200536727905</t>
+    <t xml:space="preserve">7.0318284034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13609313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97200584411621</t>
   </si>
   <si>
     <t xml:space="preserve">6.91047286987305</t>
@@ -4685,31 +4685,31 @@
     <t xml:space="preserve">6.92756509780884</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97371435165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95662212371826</t>
+    <t xml:space="preserve">6.97371482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95662307739258</t>
   </si>
   <si>
     <t xml:space="preserve">6.94978523254395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02157354354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15318584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17027854919434</t>
+    <t xml:space="preserve">7.02157306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15318536758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17027807235718</t>
   </si>
   <si>
     <t xml:space="preserve">7.21300840377808</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19078826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03695678710938</t>
+    <t xml:space="preserve">7.19078874588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03695726394653</t>
   </si>
   <si>
     <t xml:space="preserve">7.17882347106934</t>
@@ -4727,10 +4727,10 @@
     <t xml:space="preserve">7.08139705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11558198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19933414459229</t>
+    <t xml:space="preserve">7.11558246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19933462142944</t>
   </si>
   <si>
     <t xml:space="preserve">7.04037523269653</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">7.0284104347229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97884321212769</t>
+    <t xml:space="preserve">6.97884273529053</t>
   </si>
   <si>
     <t xml:space="preserve">6.87799692153931</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">6.83697509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80279016494751</t>
+    <t xml:space="preserve">6.80279064178467</t>
   </si>
   <si>
     <t xml:space="preserve">6.8916711807251</t>
@@ -4757,22 +4757,22 @@
     <t xml:space="preserve">6.76860570907593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86090469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88312482833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76518678665161</t>
+    <t xml:space="preserve">6.86090421676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88312530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76518726348877</t>
   </si>
   <si>
     <t xml:space="preserve">6.78740739822388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77715110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72416543960571</t>
+    <t xml:space="preserve">6.77715158462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72416496276855</t>
   </si>
   <si>
     <t xml:space="preserve">6.66946935653687</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">6.60109949111938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55153179168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48999881744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49854469299316</t>
+    <t xml:space="preserve">6.55153131484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48999834060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49854516983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.49341726303101</t>
@@ -4799,10 +4799,10 @@
     <t xml:space="preserve">6.53443908691406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58571577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61819219589233</t>
+    <t xml:space="preserve">6.58571624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61819171905518</t>
   </si>
   <si>
     <t xml:space="preserve">6.74980354309082</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">6.82842874526978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84552145004272</t>
+    <t xml:space="preserve">6.84552192687988</t>
   </si>
   <si>
     <t xml:space="preserve">7.00789928436279</t>
@@ -4826,46 +4826,46 @@
     <t xml:space="preserve">6.99080753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1668586730957</t>
+    <t xml:space="preserve">7.16685914993286</t>
   </si>
   <si>
     <t xml:space="preserve">7.29847097396851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28137969970703</t>
+    <t xml:space="preserve">7.28137874603271</t>
   </si>
   <si>
     <t xml:space="preserve">7.17198705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19420766830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29675388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26316118240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23487234115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1959753036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24194526672363</t>
+    <t xml:space="preserve">7.1942081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29675436019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26316070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23487281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19597578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24194478988647</t>
   </si>
   <si>
     <t xml:space="preserve">7.15531015396118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17475938796997</t>
+    <t xml:space="preserve">7.17475891113281</t>
   </si>
   <si>
     <t xml:space="preserve">7.19243907928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21896076202393</t>
+    <t xml:space="preserve">7.21896028518677</t>
   </si>
   <si>
     <t xml:space="preserve">7.26669788360596</t>
@@ -4874,22 +4874,22 @@
     <t xml:space="preserve">7.25785732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24901676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30029058456421</t>
+    <t xml:space="preserve">7.24901628494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30029106140137</t>
   </si>
   <si>
     <t xml:space="preserve">7.2773060798645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31973934173584</t>
+    <t xml:space="preserve">7.31973886489868</t>
   </si>
   <si>
     <t xml:space="preserve">7.40637397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47532796859741</t>
+    <t xml:space="preserve">7.47532749176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.44527053833008</t>
@@ -4898,13 +4898,13 @@
     <t xml:space="preserve">7.551353931427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61853981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5407452583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51952886581421</t>
+    <t xml:space="preserve">7.61854028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54074573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51952791213989</t>
   </si>
   <si>
     <t xml:space="preserve">7.54781818389893</t>
@@ -4913,22 +4913,22 @@
     <t xml:space="preserve">7.48239994049072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47886323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53897762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49654340744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54428195953369</t>
+    <t xml:space="preserve">7.47886371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53897714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49654388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">7.58671474456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58141136169434</t>
+    <t xml:space="preserve">7.58141088485718</t>
   </si>
   <si>
     <t xml:space="preserve">7.67511796951294</t>
@@ -4937,64 +4937,64 @@
     <t xml:space="preserve">7.65390110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7971134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80241727828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81832933425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72815942764282</t>
+    <t xml:space="preserve">7.79711246490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80241775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72815895080566</t>
   </si>
   <si>
     <t xml:space="preserve">7.8625316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04640960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11182689666748</t>
+    <t xml:space="preserve">8.04640865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11182594299316</t>
   </si>
   <si>
     <t xml:space="preserve">8.11005878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21967887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28509616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27625560760498</t>
+    <t xml:space="preserve">8.21967792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28509521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2762565612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.37880229949951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43361282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41946887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26741600036621</t>
+    <t xml:space="preserve">8.43361186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41946792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26741504669189</t>
   </si>
   <si>
     <t xml:space="preserve">8.36642646789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39294815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33106517791748</t>
+    <t xml:space="preserve">8.39294719696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33106422424316</t>
   </si>
   <si>
     <t xml:space="preserve">8.33813762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4636697769165</t>
+    <t xml:space="preserve">8.46366882324219</t>
   </si>
   <si>
     <t xml:space="preserve">8.44952487945557</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">8.5732889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67583656311035</t>
+    <t xml:space="preserve">8.67583560943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.75009346008301</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">8.61572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62456130981445</t>
+    <t xml:space="preserve">8.62456226348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.57152080535889</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">8.59273719787598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.628098487854</t>
+    <t xml:space="preserve">8.62809753417969</t>
   </si>
   <si>
     <t xml:space="preserve">8.737717628479</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">8.79783058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78722190856934</t>
+    <t xml:space="preserve">8.78722286224365</t>
   </si>
   <si>
     <t xml:space="preserve">8.7695426940918</t>
@@ -5048,16 +5048,16 @@
     <t xml:space="preserve">8.79959964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7819185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84026527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88888549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86236381530762</t>
+    <t xml:space="preserve">8.78191947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84026432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88888645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86236476898193</t>
   </si>
   <si>
     <t xml:space="preserve">8.76070213317871</t>
@@ -5066,19 +5066,19 @@
     <t xml:space="preserve">8.73064613342285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62986660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77661609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82258415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97286891937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87120532989502</t>
+    <t xml:space="preserve">8.6298656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77661418914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82258319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97286796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87120628356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.07011127471924</t>
@@ -5087,13 +5087,13 @@
     <t xml:space="preserve">9.10547256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11431312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1496753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13199234008789</t>
+    <t xml:space="preserve">9.11431407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14967441558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13199329376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.06127166748047</t>
@@ -5108,10 +5108,10 @@
     <t xml:space="preserve">9.07895183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03475093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9551887512207</t>
+    <t xml:space="preserve">9.03474998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95518779754639</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910488128662</t>
@@ -5120,16 +5120,16 @@
     <t xml:space="preserve">8.85794544219971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91982650756836</t>
+    <t xml:space="preserve">8.91982746124268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74744129180908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83142375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99054908752441</t>
+    <t xml:space="preserve">8.83142471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9905481338501</t>
   </si>
   <si>
     <t xml:space="preserve">9.00899124145508</t>
@@ -5138,28 +5138,28 @@
     <t xml:space="preserve">9.12886428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24873828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14269733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30406475067139</t>
+    <t xml:space="preserve">9.24873924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14269638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3040657043457</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705539703369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41471862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47926616668701</t>
+    <t xml:space="preserve">9.41471767425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4792652130127</t>
   </si>
   <si>
     <t xml:space="preserve">9.62680244445801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66368770599365</t>
+    <t xml:space="preserve">9.66368675231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.70057201385498</t>
@@ -5168,13 +5168,13 @@
     <t xml:space="preserve">9.94954013824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0601940155029</t>
+    <t xml:space="preserve">10.0601930618286</t>
   </si>
   <si>
     <t xml:space="preserve">10.0509719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99564647674561</t>
+    <t xml:space="preserve">9.99564552307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.95876216888428</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">9.7651195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97720336914062</t>
+    <t xml:space="preserve">9.97720432281494</t>
   </si>
   <si>
     <t xml:space="preserve">10.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98642444610596</t>
+    <t xml:space="preserve">9.98642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901416778564</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">9.49770832061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55303382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79278182983398</t>
+    <t xml:space="preserve">9.55303478240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7927827835083</t>
   </si>
   <si>
     <t xml:space="preserve">9.68212985992432</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">9.57147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50692939758301</t>
+    <t xml:space="preserve">9.50693035125732</t>
   </si>
   <si>
     <t xml:space="preserve">9.69135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667644500732</t>
+    <t xml:space="preserve">9.74667739868164</t>
   </si>
   <si>
     <t xml:space="preserve">9.82044506072998</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">9.86655044555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9126558303833</t>
+    <t xml:space="preserve">9.91265678405762</t>
   </si>
   <si>
     <t xml:space="preserve">9.96798324584961</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">10.0233097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90343570709229</t>
+    <t xml:space="preserve">9.90343475341797</t>
   </si>
   <si>
     <t xml:space="preserve">10.1062994003296</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">10.2077302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48848628997803</t>
+    <t xml:space="preserve">9.48848724365234</t>
   </si>
   <si>
     <t xml:space="preserve">9.25796031951904</t>
@@ -5282,10 +5282,10 @@
     <t xml:space="preserve">8.99515914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96749591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31328678131104</t>
+    <t xml:space="preserve">8.96749687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31328773498535</t>
   </si>
   <si>
     <t xml:space="preserve">9.43315982818604</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">9.58991813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82966613769531</t>
+    <t xml:space="preserve">9.82966709136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.84810924530029</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">10.0878562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1892881393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2446155548096</t>
+    <t xml:space="preserve">10.1892890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2446146011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.014087677002</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">10.0970773696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0694141387939</t>
+    <t xml:space="preserve">10.0694150924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.1247415542603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1800680160522</t>
+    <t xml:space="preserve">10.1800670623779</t>
   </si>
   <si>
     <t xml:space="preserve">10.3737096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198160171509</t>
+    <t xml:space="preserve">10.4198150634766</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907199859619</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">10.3552675247192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183832168579</t>
+    <t xml:space="preserve">10.3183841705322</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765743255615</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">10.2999420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3091621398926</t>
+    <t xml:space="preserve">10.3091630935669</t>
   </si>
   <si>
     <t xml:space="preserve">10.2169523239136</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">10.2722787857056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276052474976</t>
+    <t xml:space="preserve">10.3276042938232</t>
   </si>
   <si>
     <t xml:space="preserve">10.4567003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4935836791992</t>
+    <t xml:space="preserve">10.4935846328735</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042375564575</t>
@@ -5396,22 +5396,22 @@
     <t xml:space="preserve">10.4474792480469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5581312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134586334229</t>
+    <t xml:space="preserve">10.5581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134576797485</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4843635559082</t>
+    <t xml:space="preserve">10.4843626022339</t>
   </si>
   <si>
     <t xml:space="preserve">10.6226797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7517738342285</t>
+    <t xml:space="preserve">10.7517747879028</t>
   </si>
   <si>
     <t xml:space="preserve">10.9177541732788</t>
@@ -28396,7 +28396,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28422,7 +28422,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G849" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28448,7 +28448,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G850" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28474,7 +28474,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28500,7 +28500,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28526,7 +28526,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G853" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28552,7 +28552,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G854" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28578,7 +28578,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28604,7 +28604,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G856" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28630,7 +28630,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G857" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28656,7 +28656,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G858" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28682,7 +28682,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G859" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28708,7 +28708,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G860" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28734,7 +28734,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28760,7 +28760,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G862" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28786,7 +28786,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28812,7 +28812,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28838,7 +28838,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G865" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28864,7 +28864,7 @@
         <v>6</v>
       </c>
       <c r="G866" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28890,7 +28890,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G867" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28916,7 +28916,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G868" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28942,7 +28942,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G869" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28968,7 +28968,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G870" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28994,7 +28994,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G871" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29020,7 +29020,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G872" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29046,7 +29046,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29072,7 +29072,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G874" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29098,7 +29098,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29124,7 +29124,7 @@
         <v>6.125</v>
       </c>
       <c r="G876" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29150,7 +29150,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G877" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -29176,7 +29176,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G878" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -29202,7 +29202,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29228,7 +29228,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -29254,7 +29254,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G881" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -29280,7 +29280,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G882" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -29306,7 +29306,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G883" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -29332,7 +29332,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G884" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -29358,7 +29358,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G885" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -29384,7 +29384,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G886" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29410,7 +29410,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G887" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29436,7 +29436,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G888" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -29462,7 +29462,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G889" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -29488,7 +29488,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G890" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -29514,7 +29514,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G891" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29540,7 +29540,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29566,7 +29566,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29592,7 +29592,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G894" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29618,7 +29618,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29644,7 +29644,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G896" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29670,7 +29670,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G897" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29696,7 +29696,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G898" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29722,7 +29722,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29748,7 +29748,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G900" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29774,7 +29774,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G901" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29800,7 +29800,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G902" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29826,7 +29826,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29852,7 +29852,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29878,7 +29878,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G905" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29904,7 +29904,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29930,7 +29930,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G907" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29956,7 +29956,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G908" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29982,7 +29982,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G909" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30034,7 +30034,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G911" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -30060,7 +30060,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G912" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -30086,7 +30086,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -30112,7 +30112,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G914" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -30138,7 +30138,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G915" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -30164,7 +30164,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G916" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -30190,7 +30190,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G917" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -30216,7 +30216,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G918" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30242,7 +30242,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G919" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30268,7 +30268,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G920" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30294,7 +30294,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30320,7 +30320,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30372,7 +30372,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G924" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30398,7 +30398,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30424,7 +30424,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G926" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30450,7 +30450,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G927" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30476,7 +30476,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G928" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30502,7 +30502,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G929" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30528,7 +30528,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G930" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30554,7 +30554,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G931" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30580,7 +30580,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30606,7 +30606,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G933" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30632,7 +30632,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G934" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30658,7 +30658,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30684,7 +30684,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G936" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30710,7 +30710,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G937" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30736,7 +30736,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G938" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30762,7 +30762,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30788,7 +30788,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G940" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30814,7 +30814,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G941" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30840,7 +30840,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G942" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30866,7 +30866,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G943" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30892,7 +30892,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G944" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30918,7 +30918,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30944,7 +30944,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G946" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30970,7 +30970,7 @@
         <v>7</v>
       </c>
       <c r="G947" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30996,7 +30996,7 @@
         <v>6.875</v>
       </c>
       <c r="G948" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31022,7 +31022,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31048,7 +31048,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G950" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31074,7 +31074,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G951" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31100,7 +31100,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31126,7 +31126,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G953" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31152,7 +31152,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G954" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31178,7 +31178,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31204,7 +31204,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G956" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31230,7 +31230,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G957" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31256,7 +31256,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G958" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31282,7 +31282,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G959" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31308,7 +31308,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G960" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31334,7 +31334,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G961" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31360,7 +31360,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G962" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31386,7 +31386,7 @@
         <v>7.25</v>
       </c>
       <c r="G963" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31412,7 +31412,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G964" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31438,7 +31438,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G965" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31464,7 +31464,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31490,7 +31490,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G967" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31516,7 +31516,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G968" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31542,7 +31542,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G969" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31568,7 +31568,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G970" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31594,7 +31594,7 @@
         <v>7.625</v>
       </c>
       <c r="G971" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31620,7 +31620,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G972" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31646,7 +31646,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G973" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31672,7 +31672,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31698,7 +31698,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G975" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31724,7 +31724,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G976" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31750,7 +31750,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G977" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31776,7 +31776,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G978" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31802,7 +31802,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G979" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31828,7 +31828,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G980" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31854,7 +31854,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G981" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31880,7 +31880,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G982" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31906,7 +31906,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G983" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31932,7 +31932,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G984" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31958,7 +31958,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G985" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31984,7 +31984,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G986" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -32010,7 +32010,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G987" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32036,7 +32036,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G988" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32062,7 +32062,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G989" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32088,7 +32088,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G990" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32114,7 +32114,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G991" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32140,7 +32140,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G992" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -32166,7 +32166,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G993" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -32192,7 +32192,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32218,7 +32218,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G995" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32244,7 +32244,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G996" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32270,7 +32270,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G997" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32296,7 +32296,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G998" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32322,7 +32322,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G999" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32348,7 +32348,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32374,7 +32374,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1001" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -32400,7 +32400,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32426,7 +32426,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G1003" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32452,7 +32452,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1004" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -32478,7 +32478,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1005" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32504,7 +32504,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1006" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32530,7 +32530,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1007" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32556,7 +32556,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32582,7 +32582,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G1009" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32608,7 +32608,7 @@
         <v>9.125</v>
       </c>
       <c r="G1010" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32634,7 +32634,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32660,7 +32660,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G1012" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32686,7 +32686,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1013" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32712,7 +32712,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1014" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32738,7 +32738,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1015" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32764,7 +32764,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G1016" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32790,7 +32790,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G1017" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32816,7 +32816,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1018" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32842,7 +32842,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1019" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32868,7 +32868,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1020" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32894,7 +32894,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G1021" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32920,7 +32920,7 @@
         <v>9</v>
       </c>
       <c r="G1022" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32946,7 +32946,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1023" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32972,7 +32972,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1024" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32998,7 +32998,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1025" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -33024,7 +33024,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1026" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -33050,7 +33050,7 @@
         <v>8.875</v>
       </c>
       <c r="G1027" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -33076,7 +33076,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1028" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -33102,7 +33102,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1029" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -33128,7 +33128,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1030" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -33154,7 +33154,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1031" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -33180,7 +33180,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1032" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -33206,7 +33206,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33232,7 +33232,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1034" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33258,7 +33258,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1035" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33284,7 +33284,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1036" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33388,7 +33388,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33544,7 +33544,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1046" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -71252,7 +71252,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6495138889</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>645928</v>
@@ -71273,6 +71273,32 @@
         <v>2001</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912847222</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>772236</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>17.0599994659424</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>16.9200000762939</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>17.0200004577637</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="2004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="2005">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,109 +44,109 @@
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277449607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49607539176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4144549369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43349981307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144383430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937581062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29202389717102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157585144043</t>
+    <t xml:space="preserve">3.73277401924133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49607467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41445541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901303291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144335746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688549995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29202437400818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157608985901</t>
   </si>
   <si>
     <t xml:space="preserve">3.21040344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41989541053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22672724723816</t>
+    <t xml:space="preserve">3.41989588737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077826499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276125907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2267279624939</t>
   </si>
   <si>
     <t xml:space="preserve">3.1396656036377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18863868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30562734603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8920841217041</t>
+    <t xml:space="preserve">3.18863749504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30562710762024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89208364486694</t>
   </si>
   <si>
     <t xml:space="preserve">3.15599012374878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25393486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31379008293152</t>
+    <t xml:space="preserve">3.25393414497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3137891292572</t>
   </si>
   <si>
     <t xml:space="preserve">3.40357160568237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36548280715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36820268630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46614861488342</t>
+    <t xml:space="preserve">3.36548256874084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36820316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46614742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.43621945381165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36004066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49063420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56681299209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409192085266</t>
+    <t xml:space="preserve">3.36004137992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49063444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56681275367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409215927124</t>
   </si>
   <si>
     <t xml:space="preserve">3.69196391105652</t>
@@ -155,106 +155,106 @@
     <t xml:space="preserve">3.71100902557373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61850571632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68652200698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380236625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093651771545</t>
+    <t xml:space="preserve">3.61850523948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68652319908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380212783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093627929688</t>
   </si>
   <si>
     <t xml:space="preserve">3.80623292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79262948036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76542234420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70284676551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181913375854</t>
+    <t xml:space="preserve">3.7926287651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76542258262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70284724235535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181865692139</t>
   </si>
   <si>
     <t xml:space="preserve">3.72189140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69468450546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387415885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439518928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432291984558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86608719825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71372961997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63482928276062</t>
+    <t xml:space="preserve">3.69468402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387463569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81439423561096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84432244300842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8660876750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7137291431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6348295211792</t>
   </si>
   <si>
     <t xml:space="preserve">3.54232668876648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637770652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77630543708801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821520805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87969088554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91778087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85248398780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88579058647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9496283531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97460913658142</t>
+    <t xml:space="preserve">3.74637746810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77630519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73821496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87969183921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91778016090393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85248422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407773017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88579106330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94962882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97460865974426</t>
   </si>
   <si>
     <t xml:space="preserve">3.9662823677063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88023972511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92464804649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88856601715088</t>
+    <t xml:space="preserve">3.88023948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92464876174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88856625556946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00236511230469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98848628997803</t>
+    <t xml:space="preserve">3.98848676681519</t>
   </si>
   <si>
     <t xml:space="preserve">4.04122304916382</t>
@@ -266,103 +266,103 @@
     <t xml:space="preserve">4.07730484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99681401252747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96905827522278</t>
+    <t xml:space="preserve">3.99681305885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96905755996704</t>
   </si>
   <si>
     <t xml:space="preserve">4.06065130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92742466926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93575119972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187404632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95240378379822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91909790039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130206108093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08008050918579</t>
+    <t xml:space="preserve">3.92742443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93575096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92187333106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95240426063538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91909766197205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130301475525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08008098602295</t>
   </si>
   <si>
     <t xml:space="preserve">4.29102277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23551225662231</t>
+    <t xml:space="preserve">4.23551273345947</t>
   </si>
   <si>
     <t xml:space="preserve">4.16334772109985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883282661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21608400344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.182776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559103012085</t>
+    <t xml:space="preserve">4.18832731246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21608352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18277645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559246063232</t>
   </si>
   <si>
     <t xml:space="preserve">4.15502071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03289651870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05232524871826</t>
+    <t xml:space="preserve">4.0328950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05232429504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.09673452377319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06342697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69427680969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53051900863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55272340774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48888468742371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60268330574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78587079048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82472825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80529952049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685387611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288286209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13916349411011</t>
+    <t xml:space="preserve">4.06342792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69427728652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53051829338074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55272364616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48888516426086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60268378257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78587031364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82472896575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80529999732971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685411453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288262367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13916420936584</t>
   </si>
   <si>
     <t xml:space="preserve">3.26961541175842</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">3.40561819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4139449596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904485702515</t>
+    <t xml:space="preserve">3.41394472122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904461860657</t>
   </si>
   <si>
     <t xml:space="preserve">3.24463510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19189953804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21410369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39174008369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47778248786926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59713220596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49721264839172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941633224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53884506225586</t>
+    <t xml:space="preserve">3.19189977645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21410393714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39174056053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47778296470642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59713196754456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721217155457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53884553909302</t>
   </si>
   <si>
     <t xml:space="preserve">3.55827450752258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54162096977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386475563049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63599014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58047914505005</t>
+    <t xml:space="preserve">3.5416214466095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386523246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63599038124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58047938346863</t>
   </si>
   <si>
     <t xml:space="preserve">3.64154124259949</t>
@@ -428,58 +428,58 @@
     <t xml:space="preserve">3.39451575279236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34455633163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54717206954956</t>
+    <t xml:space="preserve">3.34455585479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5471715927124</t>
   </si>
   <si>
     <t xml:space="preserve">3.56937670707703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4694561958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116905212402</t>
+    <t xml:space="preserve">3.46945571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41116976737976</t>
   </si>
   <si>
     <t xml:space="preserve">3.45280241966248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37231159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48055791854858</t>
+    <t xml:space="preserve">3.37231135368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48055863380432</t>
   </si>
   <si>
     <t xml:space="preserve">3.51664090156555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45002722740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47500705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51108956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56660151481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58325362205505</t>
+    <t xml:space="preserve">3.45002698898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47500801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51108932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56660103797913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58325409889221</t>
   </si>
   <si>
     <t xml:space="preserve">3.54994702339172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57215261459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264344215393</t>
+    <t xml:space="preserve">3.57215189933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264415740967</t>
   </si>
   <si>
     <t xml:space="preserve">3.59990835189819</t>
@@ -488,79 +488,79 @@
     <t xml:space="preserve">3.49166107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52219152450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50831437110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31402373313904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37786221504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30847358703613</t>
+    <t xml:space="preserve">3.52219176292419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50831365585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31402444839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37786245346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30847382545471</t>
   </si>
   <si>
     <t xml:space="preserve">3.36120915412903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38896512985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29737091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19745111465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23075699806213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29181981086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26683974266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27516674995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39729261398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46390509605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839433670044</t>
+    <t xml:space="preserve">3.38896489143372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29737210273743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19745087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23075819015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29182004928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26684021949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27516651153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337297439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39729166030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46390533447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">3.46112942695618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32235097885132</t>
+    <t xml:space="preserve">3.32235145568848</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618898391724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43059825897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43614912033081</t>
+    <t xml:space="preserve">3.43059897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43615031242371</t>
   </si>
   <si>
     <t xml:space="preserve">3.50276350975037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56382513046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398530006409</t>
+    <t xml:space="preserve">3.56382584571838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398506164551</t>
   </si>
   <si>
     <t xml:space="preserve">3.33900475502014</t>
@@ -569,100 +569,100 @@
     <t xml:space="preserve">3.45835471153259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54439663887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42227220535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38341355323792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30014634132385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28303241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37145447731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39142179489136</t>
+    <t xml:space="preserve">3.54439687728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4222719669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38341331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30014705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2830331325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37145519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3914213180542</t>
   </si>
   <si>
     <t xml:space="preserve">3.37715983390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41424036026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45702457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48554849624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5311861038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256079673767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73370146751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09309434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95047903060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89343166351318</t>
+    <t xml:space="preserve">3.41423940658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45702481269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48554825782776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118586540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7993049621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09309482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95047831535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89343118667603</t>
   </si>
   <si>
     <t xml:space="preserve">3.95333003997803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93906831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93051242828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92480659484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90484118461609</t>
+    <t xml:space="preserve">3.93906879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93051171302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635232925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92480778694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90484070777893</t>
   </si>
   <si>
     <t xml:space="preserve">3.93621635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94192123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92195510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89628410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96473932266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10735654830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12447118759155</t>
+    <t xml:space="preserve">3.94192051887512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92195534706116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89628434181213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477415084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96474027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10735607147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12447023391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.04175233840942</t>
@@ -671,46 +671,46 @@
     <t xml:space="preserve">4.07883358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24426889419556</t>
+    <t xml:space="preserve">4.2442684173584</t>
   </si>
   <si>
     <t xml:space="preserve">4.15014123916626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30131483078003</t>
+    <t xml:space="preserve">4.30131435394287</t>
   </si>
   <si>
     <t xml:space="preserve">4.21574449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20433664321899</t>
+    <t xml:space="preserve">4.20433521270752</t>
   </si>
   <si>
     <t xml:space="preserve">4.26708650588989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21289205551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20718765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09879922866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2357120513916</t>
+    <t xml:space="preserve">4.21289253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20718812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09879875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23571109771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.18151712417603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17010736465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17581224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03319501876831</t>
+    <t xml:space="preserve">4.1701078414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17581129074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03319597244263</t>
   </si>
   <si>
     <t xml:space="preserve">4.03890037536621</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">4.07027578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9704442024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99326324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98185348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05886650085449</t>
+    <t xml:space="preserve">3.97044467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99326300621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98185253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05886697769165</t>
   </si>
   <si>
     <t xml:space="preserve">4.11306047439575</t>
@@ -740,112 +740,112 @@
     <t xml:space="preserve">4.06171894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04745674133301</t>
+    <t xml:space="preserve">4.04745769500732</t>
   </si>
   <si>
     <t xml:space="preserve">4.02749061584473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75651979446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672184944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61104989051819</t>
+    <t xml:space="preserve">3.75651931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105036735535</t>
   </si>
   <si>
     <t xml:space="preserve">3.51977610588074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53689026832581</t>
+    <t xml:space="preserve">3.53688955307007</t>
   </si>
   <si>
     <t xml:space="preserve">3.51692366600037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63386940956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68235945701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64242577552795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65098309516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091629981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71943950653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73084926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81641864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7878954410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81071376800537</t>
+    <t xml:space="preserve">3.633868932724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68235874176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64242625236511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6509838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71943926811218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73084807395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81641840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78789496421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81071305274963</t>
   </si>
   <si>
     <t xml:space="preserve">3.84779405593872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7679283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8021559715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83353233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90769243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91624927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9476261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.976149559021</t>
+    <t xml:space="preserve">3.7679295539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78219056129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80215764045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83353328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769267082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91625046730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94762563705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97614932060242</t>
   </si>
   <si>
     <t xml:space="preserve">3.92765998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89057993888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349798202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212328910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87346506118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10278177261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1086950302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17076778411865</t>
+    <t xml:space="preserve">3.89057946205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349869728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87346458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10278224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10869455337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17076826095581</t>
   </si>
   <si>
     <t xml:space="preserve">4.11460542678833</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">4.15303230285645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12938642501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1057391166687</t>
+    <t xml:space="preserve">4.12938547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10573816299438</t>
   </si>
   <si>
     <t xml:space="preserve">4.16485595703125</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">4.23579788208008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2387523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34516572952271</t>
+    <t xml:space="preserve">4.23875284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919513702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34516525268555</t>
   </si>
   <si>
     <t xml:space="preserve">4.35107707977295</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">4.36290073394775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35994529724121</t>
+    <t xml:space="preserve">4.35994577407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.39837169647217</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">4.28900384902954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30082750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37176895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340179443359</t>
+    <t xml:space="preserve">4.30082702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37176847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340227127075</t>
   </si>
   <si>
     <t xml:space="preserve">4.51956367492676</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">4.47522497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45453357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36881160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33334159851074</t>
+    <t xml:space="preserve">4.45453405380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36881351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3333420753479</t>
   </si>
   <si>
     <t xml:space="preserve">4.41315078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30673933029175</t>
+    <t xml:space="preserve">4.30673837661743</t>
   </si>
   <si>
     <t xml:space="preserve">4.41906261444092</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">4.43384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38654851913452</t>
+    <t xml:space="preserve">4.38654804229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.30969476699829</t>
@@ -941,133 +941,133 @@
     <t xml:space="preserve">4.31856250762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39246034622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29491472244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3362979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25353288650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32447385787964</t>
+    <t xml:space="preserve">4.39245891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29491519927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33629846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25353384017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32447481155396</t>
   </si>
   <si>
     <t xml:space="preserve">4.37472534179688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33925342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38063716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49296045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37768077850342</t>
+    <t xml:space="preserve">4.3274302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3392539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38063621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49295997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37768125534058</t>
   </si>
   <si>
     <t xml:space="preserve">4.40723943710327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38950347900391</t>
+    <t xml:space="preserve">4.38950490951538</t>
   </si>
   <si>
     <t xml:space="preserve">4.31560659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27126884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21510601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.342209815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32151889801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25648927688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28309059143066</t>
+    <t xml:space="preserve">4.27126789093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21510648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34220886230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3215184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25648880004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28309297561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.25057744979858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23284149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22101831436157</t>
+    <t xml:space="preserve">4.23284196853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22101783752441</t>
   </si>
   <si>
     <t xml:space="preserve">4.16190052032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19737148284912</t>
+    <t xml:space="preserve">4.1973705291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.24170923233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1796350479126</t>
+    <t xml:space="preserve">4.17963552474976</t>
   </si>
   <si>
     <t xml:space="preserve">4.22397375106812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26831245422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29195928573608</t>
+    <t xml:space="preserve">4.26831197738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29195976257324</t>
   </si>
   <si>
     <t xml:space="preserve">4.35403299331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43679857254028</t>
+    <t xml:space="preserve">4.43679809570312</t>
   </si>
   <si>
     <t xml:space="preserve">4.42201900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26535701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18850326538086</t>
+    <t xml:space="preserve">4.26535606384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18850374221802</t>
   </si>
   <si>
     <t xml:space="preserve">4.17372369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16781187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24762010574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21806240081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23866891860962</t>
+    <t xml:space="preserve">4.16781234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24762153625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2180609703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28013563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23866844177246</t>
   </si>
   <si>
     <t xml:space="preserve">4.13528633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13832759857178</t>
+    <t xml:space="preserve">4.13832664489746</t>
   </si>
   <si>
     <t xml:space="preserve">4.16873407363892</t>
@@ -1076,25 +1076,25 @@
     <t xml:space="preserve">4.1656928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25083160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25995349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27211570739746</t>
+    <t xml:space="preserve">4.25083065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25995302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2721152305603</t>
   </si>
   <si>
     <t xml:space="preserve">4.3663763999939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36941623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117292404175</t>
+    <t xml:space="preserve">4.3694167137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117340087891</t>
   </si>
   <si>
     <t xml:space="preserve">4.32988834381104</t>
@@ -1103,37 +1103,37 @@
     <t xml:space="preserve">4.38157939910889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3359694480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39678239822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44543313980103</t>
+    <t xml:space="preserve">4.33597040176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39678287506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44543266296387</t>
   </si>
   <si>
     <t xml:space="preserve">4.5001654624939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54577398300171</t>
+    <t xml:space="preserve">4.54577445983887</t>
   </si>
   <si>
     <t xml:space="preserve">4.4393515586853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48800230026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51232671737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44847440719604</t>
+    <t xml:space="preserve">4.48800182342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51232719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44847345352173</t>
   </si>
   <si>
     <t xml:space="preserve">4.46367692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38766098022461</t>
+    <t xml:space="preserve">4.38766002655029</t>
   </si>
   <si>
     <t xml:space="preserve">4.30860424041748</t>
@@ -1145,58 +1145,58 @@
     <t xml:space="preserve">4.37245798110962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46063709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45759582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55489587783813</t>
+    <t xml:space="preserve">4.46063661575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45759534835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55489683151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.57922267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62178993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70084762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.725172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74037599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73429536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77078247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81639242172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7647008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80423021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83463668823242</t>
+    <t xml:space="preserve">4.62179088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70084810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72517347335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7403769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73429441452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77078199386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81639289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76470232009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80422973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83463621139526</t>
   </si>
   <si>
     <t xml:space="preserve">4.71300983428955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61571025848389</t>
+    <t xml:space="preserve">4.61570930480957</t>
   </si>
   <si>
     <t xml:space="preserve">4.691725730896</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">4.53665256500244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25691223144531</t>
+    <t xml:space="preserve">4.25691366195679</t>
   </si>
   <si>
     <t xml:space="preserve">4.2994818687439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4059042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39374256134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43326997756958</t>
+    <t xml:space="preserve">4.40590524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39374160766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4332709312439</t>
   </si>
   <si>
     <t xml:space="preserve">4.42414855957031</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">4.43022966384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52449083328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5032057762146</t>
+    <t xml:space="preserve">4.52448987960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50320625305176</t>
   </si>
   <si>
     <t xml:space="preserve">4.31468486785889</t>
@@ -1244,43 +1244,43 @@
     <t xml:space="preserve">4.27819728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32076597213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38461971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41502618789673</t>
+    <t xml:space="preserve">4.32076644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38462018966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4150276184082</t>
   </si>
   <si>
     <t xml:space="preserve">4.40894508361816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35725450515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3329291343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26907539367676</t>
+    <t xml:space="preserve">4.35725402832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33292865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2690749168396</t>
   </si>
   <si>
     <t xml:space="preserve">4.29644155502319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30556344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23562860488892</t>
+    <t xml:space="preserve">4.30556297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2356276512146</t>
   </si>
   <si>
     <t xml:space="preserve">4.29035949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26603412628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26299428939819</t>
+    <t xml:space="preserve">4.26603507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26299381256104</t>
   </si>
   <si>
     <t xml:space="preserve">4.22650623321533</t>
@@ -1289,64 +1289,64 @@
     <t xml:space="preserve">4.21738433837891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28731918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32380723953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38646841049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32702350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20500373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11427021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14555788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16745853424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23003339767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25506353378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254846572876</t>
+    <t xml:space="preserve">4.28731966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32380628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38646984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32702445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20500421524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11427116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14555740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16745901107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24567747116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23003387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2550630569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24254751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.16120100021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21438980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17997407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17058849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08924150466919</t>
+    <t xml:space="preserve">4.21438932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17997360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17058753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08924007415771</t>
   </si>
   <si>
     <t xml:space="preserve">4.02040910720825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85458588600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83581376075745</t>
+    <t xml:space="preserve">3.85458707809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83581399917603</t>
   </si>
   <si>
     <t xml:space="preserve">3.82329940795898</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">3.7763683795929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80765604972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81704235076904</t>
+    <t xml:space="preserve">3.80765628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81704163551331</t>
   </si>
   <si>
     <t xml:space="preserve">3.79826974868774</t>
@@ -1367,64 +1367,64 @@
     <t xml:space="preserve">3.73882365226746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63557577133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195218086243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262615203857</t>
+    <t xml:space="preserve">3.63557648658752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195265769958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262543678284</t>
   </si>
   <si>
     <t xml:space="preserve">3.8264274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66060590744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72630929946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7450807094574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63870525360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7701108455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71692252159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74821019172668</t>
+    <t xml:space="preserve">3.66060614585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72630906105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74508142471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6387050151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77011132240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71692299842834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379423141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74821043014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.69815039634705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68250727653503</t>
+    <t xml:space="preserve">3.68250703811646</t>
   </si>
   <si>
     <t xml:space="preserve">3.72318077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66373443603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183378219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6011598110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57925844192505</t>
+    <t xml:space="preserve">3.66373419761658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7607250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64183402061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60116052627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57925915718079</t>
   </si>
   <si>
     <t xml:space="preserve">3.63244676589966</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">3.68876433372498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67624950408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70440816879272</t>
+    <t xml:space="preserve">3.67624998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70440769195557</t>
   </si>
   <si>
     <t xml:space="preserve">3.56361556053162</t>
@@ -1445,58 +1445,58 @@
     <t xml:space="preserve">3.62931823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66686367988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6199324131012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62619042396545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84520077705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99537944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88587379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91090393066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87023019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341876029968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87961602210999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84207153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78575491905212</t>
+    <t xml:space="preserve">3.66686344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61993265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62618947029114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8452000617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99537897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88587427139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91090369224548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87022972106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9234185218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87961578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84207105636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78575420379639</t>
   </si>
   <si>
     <t xml:space="preserve">3.79514074325562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77323985099792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70753693580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698207855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8107852935791</t>
+    <t xml:space="preserve">3.7732400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7075366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698279380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452752113342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078481674194</t>
   </si>
   <si>
     <t xml:space="preserve">3.80139827728271</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">3.75446724891663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73256587982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563532829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82017016410828</t>
+    <t xml:space="preserve">3.73256731033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82017135620117</t>
   </si>
   <si>
     <t xml:space="preserve">3.75759625434875</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">3.81391334533691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77949714660645</t>
+    <t xml:space="preserve">3.77949738502502</t>
   </si>
   <si>
     <t xml:space="preserve">3.86397290229797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87335920333862</t>
+    <t xml:space="preserve">3.87335896492004</t>
   </si>
   <si>
     <t xml:space="preserve">3.89213109016418</t>
@@ -1535,49 +1535,49 @@
     <t xml:space="preserve">3.99225044250488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97660660743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912119865417</t>
+    <t xml:space="preserve">3.97660732269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912167549133</t>
   </si>
   <si>
     <t xml:space="preserve">4.00163698196411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44472336769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47288179397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37276315689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37589168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39466500282288</t>
+    <t xml:space="preserve">3.44472432136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47288250923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37276339530945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37589192390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39466428756714</t>
   </si>
   <si>
     <t xml:space="preserve">3.45098114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39779233932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31018877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29141640663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24448561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22258472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1631383895874</t>
+    <t xml:space="preserve">3.39779281616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31018853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29141712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24448537826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22258448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313886642456</t>
   </si>
   <si>
     <t xml:space="preserve">3.18504023551941</t>
@@ -1589,22 +1589,22 @@
     <t xml:space="preserve">3.21007013320923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20694088935852</t>
+    <t xml:space="preserve">3.20694136619568</t>
   </si>
   <si>
     <t xml:space="preserve">3.26325798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31644654273987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3070604801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3133180141449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28515911102295</t>
+    <t xml:space="preserve">3.31644582748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30705976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331777572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28515887260437</t>
   </si>
   <si>
     <t xml:space="preserve">3.25387191772461</t>
@@ -1613,112 +1613,112 @@
     <t xml:space="preserve">3.25074315071106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2784378528595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13193416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727384567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48354387283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4477322101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44122076034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4249427318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41843128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146075248718</t>
+    <t xml:space="preserve">3.27843832969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13193440437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890469551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727265357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48354458808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45098757743835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44773173332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4412202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494320869446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29146099090576</t>
   </si>
   <si>
     <t xml:space="preserve">3.27192711830139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23351001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28820538520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680724143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4086639881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33378481864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31099486351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3533182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30773878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1553750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076144218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31425046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2849497795105</t>
+    <t xml:space="preserve">3.23351073265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28820443153381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4086651802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33378410339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31099438667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30773901939392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15537476539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31425070762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28494906425476</t>
   </si>
   <si>
     <t xml:space="preserve">3.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40215301513672</t>
+    <t xml:space="preserve">3.4021520614624</t>
   </si>
   <si>
     <t xml:space="preserve">3.36634111404419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44447636604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46401000022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633358955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48679971694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075463294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331092834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726584434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45749855041504</t>
+    <t xml:space="preserve">3.44447588920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46401047706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633406639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48679995536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075415611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331116676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45749878883362</t>
   </si>
   <si>
     <t xml:space="preserve">3.50958895683289</t>
@@ -1727,82 +1727,82 @@
     <t xml:space="preserve">3.47052121162415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58121395111084</t>
+    <t xml:space="preserve">3.58121347427368</t>
   </si>
   <si>
     <t xml:space="preserve">3.71795082092285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77655291557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70818400382996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83189845085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864308357239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8709671497345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92305612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87422132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8872447013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99142551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95886850357056</t>
+    <t xml:space="preserve">3.77655220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83189868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864332199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87096667289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92305684089661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87422204017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8807327747345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99142527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95886874198914</t>
   </si>
   <si>
     <t xml:space="preserve">4.00770378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99793553352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06304979324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9718918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01747035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06630563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0825834274292</t>
+    <t xml:space="preserve">3.9979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0174708366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0663046836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956052780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258390426636</t>
   </si>
   <si>
     <t xml:space="preserve">4.12165117263794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09235000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11514043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12816286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09886121749878</t>
+    <t xml:space="preserve">4.09235048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11513996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1281623840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09886264801025</t>
   </si>
   <si>
     <t xml:space="preserve">4.14118528366089</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">4.08583927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11188459396362</t>
+    <t xml:space="preserve">4.11188364028931</t>
   </si>
   <si>
     <t xml:space="preserve">4.16071891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13141775131226</t>
+    <t xml:space="preserve">4.13141822814941</t>
   </si>
   <si>
     <t xml:space="preserve">4.26164436340332</t>
@@ -1826,19 +1826,19 @@
     <t xml:space="preserve">4.24862194061279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24536466598511</t>
+    <t xml:space="preserve">4.24536514282227</t>
   </si>
   <si>
     <t xml:space="preserve">4.24211025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23559904098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2323431968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3235011100769</t>
+    <t xml:space="preserve">4.23559808731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23234367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32350158691406</t>
   </si>
   <si>
     <t xml:space="preserve">4.38210296630859</t>
@@ -1847,73 +1847,70 @@
     <t xml:space="preserve">4.4048924446106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37884759902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2884464263916</t>
+    <t xml:space="preserve">4.37884712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233591079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37569141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28844690322876</t>
   </si>
   <si>
     <t xml:space="preserve">4.32871294021606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3320689201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41260290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39246988296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36226940155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233591079712</t>
+    <t xml:space="preserve">4.33206844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41260385513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39247035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36226987838745</t>
   </si>
   <si>
     <t xml:space="preserve">4.22804546356201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.238112449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2515344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10388851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16093349456787</t>
+    <t xml:space="preserve">4.23811340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25153398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751195907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10388898849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16093397140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.10724401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16428995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12737798690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12402248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06697750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07704401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08039999008179</t>
+    <t xml:space="preserve">4.1642894744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12402296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06697702407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07704448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">4.04684400558472</t>
@@ -1922,49 +1919,49 @@
     <t xml:space="preserve">4.02671003341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0065770149231</t>
+    <t xml:space="preserve">4.00657749176025</t>
   </si>
   <si>
     <t xml:space="preserve">4.03342199325562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09046649932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14415645599365</t>
+    <t xml:space="preserve">4.0904655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14415597915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.13408899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17435646057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15757894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13744497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368850708008</t>
+    <t xml:space="preserve">4.17435598373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15757846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11059999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13744449615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368898391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.19784545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21797895431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24482393264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34213542938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28173494338989</t>
+    <t xml:space="preserve">4.21797847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24482440948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34213590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28173542022705</t>
   </si>
   <si>
     <t xml:space="preserve">4.28509140014648</t>
@@ -1973,40 +1970,40 @@
     <t xml:space="preserve">4.33878087997437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3454909324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34884691238403</t>
+    <t xml:space="preserve">4.34549140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34884786605835</t>
   </si>
   <si>
     <t xml:space="preserve">4.47300434112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50991487503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46293687820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41931390762329</t>
+    <t xml:space="preserve">4.50991535186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4629373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45622634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41931438446045</t>
   </si>
   <si>
     <t xml:space="preserve">4.48978185653687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48307085037231</t>
+    <t xml:space="preserve">4.48307037353516</t>
   </si>
   <si>
     <t xml:space="preserve">4.51662683486938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53676080703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49313735961914</t>
+    <t xml:space="preserve">4.5367603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49313688278198</t>
   </si>
   <si>
     <t xml:space="preserve">4.44280385971069</t>
@@ -2015,22 +2012,22 @@
     <t xml:space="preserve">4.42602491378784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42266988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44951486587524</t>
+    <t xml:space="preserve">4.42267036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44951438903809</t>
   </si>
   <si>
     <t xml:space="preserve">4.42938137054443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5065598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4696478843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40924787521362</t>
+    <t xml:space="preserve">4.50656032562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46964883804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40924882888794</t>
   </si>
   <si>
     <t xml:space="preserve">4.39582586288452</t>
@@ -2039,22 +2036,22 @@
     <t xml:space="preserve">4.20120143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20455646514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21126794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14080047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33542490005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38575887680054</t>
+    <t xml:space="preserve">4.20455598831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21126842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14079999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33542537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273687362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38575839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.46629285812378</t>
@@ -2063,40 +2060,40 @@
     <t xml:space="preserve">4.41595935821533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50320434570312</t>
+    <t xml:space="preserve">4.50320482254028</t>
   </si>
   <si>
     <t xml:space="preserve">4.52333736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61729431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59716081619263</t>
+    <t xml:space="preserve">4.60722827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61729383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59716129302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.70453977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65756273269653</t>
+    <t xml:space="preserve">4.65756130218506</t>
   </si>
   <si>
     <t xml:space="preserve">4.67769527435303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72467279434204</t>
+    <t xml:space="preserve">4.7246732711792</t>
   </si>
   <si>
     <t xml:space="preserve">4.73138475418091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69782876968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.613938331604</t>
+    <t xml:space="preserve">4.697829246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61393880844116</t>
   </si>
   <si>
     <t xml:space="preserve">4.64078378677368</t>
@@ -2105,25 +2102,25 @@
     <t xml:space="preserve">4.60387229919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62736129760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62400531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62064981460571</t>
+    <t xml:space="preserve">4.62736177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62400579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62065029144287</t>
   </si>
   <si>
     <t xml:space="preserve">4.56024980545044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66762828826904</t>
+    <t xml:space="preserve">4.66762781143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.66427230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66091680526733</t>
+    <t xml:space="preserve">4.66091728210449</t>
   </si>
   <si>
     <t xml:space="preserve">4.68105030059814</t>
@@ -2132,133 +2129,133 @@
     <t xml:space="preserve">4.82534122467041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86560869216919</t>
+    <t xml:space="preserve">4.86560821533203</t>
   </si>
   <si>
     <t xml:space="preserve">4.90251970291138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94278764724731</t>
+    <t xml:space="preserve">4.94278621673584</t>
   </si>
   <si>
     <t xml:space="preserve">4.98305416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04345512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.073655128479</t>
+    <t xml:space="preserve">5.04345417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07365465164185</t>
   </si>
   <si>
     <t xml:space="preserve">5.08707761764526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09714412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11727714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15083408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16090059280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15754461288452</t>
+    <t xml:space="preserve">5.09714365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1172776222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15083456039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1609001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">5.16425609588623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17432308197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16761112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23472356796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54343795776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63403844833374</t>
+    <t xml:space="preserve">5.17432260513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16761159896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23472309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54343748092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6340389251709</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89241933822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7716178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78504037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87102508544922</t>
+    <t xml:space="preserve">5.89241886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77161836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7850399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87102460861206</t>
   </si>
   <si>
     <t xml:space="preserve">6.02923679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17025184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18400859832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26999282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32846307754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909963607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40069103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878231048584</t>
+    <t xml:space="preserve">6.17025136947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18400812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2699933052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840381622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32846212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40068960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878135681152</t>
   </si>
   <si>
     <t xml:space="preserve">6.28031158447266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2631139755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33534145355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38349342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33190155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496343612671</t>
+    <t xml:space="preserve">6.26311540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3353419303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38349390029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33190298080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496391296387</t>
   </si>
   <si>
     <t xml:space="preserve">6.2321605682373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2596755027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23559999465942</t>
+    <t xml:space="preserve">6.25967502593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23559904098511</t>
   </si>
   <si>
     <t xml:space="preserve">6.30438756942749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28375196456909</t>
+    <t xml:space="preserve">6.28375148773193</t>
   </si>
   <si>
     <t xml:space="preserve">6.27687215805054</t>
@@ -2267,46 +2264,46 @@
     <t xml:space="preserve">6.2493577003479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16681146621704</t>
+    <t xml:space="preserve">6.16681241989136</t>
   </si>
   <si>
     <t xml:space="preserve">6.13585758209229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1461763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11866044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91229820251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573762893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05331230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00860071182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00516128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10490322113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267621994019</t>
+    <t xml:space="preserve">6.14617586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09114503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91229772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05331182479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00859928131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00516080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10490274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03267669677734</t>
   </si>
   <si>
     <t xml:space="preserve">5.92949438095093</t>
@@ -2315,25 +2312,28 @@
     <t xml:space="preserve">5.95700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90885782241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73000955581665</t>
+    <t xml:space="preserve">5.90885877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73001050949097</t>
   </si>
   <si>
     <t xml:space="preserve">5.85726737976074</t>
   </si>
   <si>
+    <t xml:space="preserve">5.78504085540771</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.60619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61651086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6681022644043</t>
+    <t xml:space="preserve">5.61651134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66810178756714</t>
   </si>
   <si>
     <t xml:space="preserve">5.71625328063965</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">5.77816152572632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81255578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80567693710327</t>
+    <t xml:space="preserve">5.81255531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80567598342896</t>
   </si>
   <si>
     <t xml:space="preserve">5.80911636352539</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">5.87790393829346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98108625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01547861099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86758613586426</t>
+    <t xml:space="preserve">5.98108434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01548004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86758470535278</t>
   </si>
   <si>
     <t xml:space="preserve">5.70593500137329</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">5.40326929092407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3551173210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37231397628784</t>
+    <t xml:space="preserve">5.35511779785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37231492996216</t>
   </si>
   <si>
     <t xml:space="preserve">5.24505758285522</t>
@@ -2381,79 +2381,79 @@
     <t xml:space="preserve">5.0627703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00430107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98366451263428</t>
+    <t xml:space="preserve">5.00430011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98366498947144</t>
   </si>
   <si>
     <t xml:space="preserve">4.94927072525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69819593429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58813524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26483345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75580477714539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71453309059143</t>
+    <t xml:space="preserve">4.69819641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58813571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26483392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75580501556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71453332901001</t>
   </si>
   <si>
     <t xml:space="preserve">3.36509156227112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36784291267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08306217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8051598072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91109299659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90283846855164</t>
+    <t xml:space="preserve">3.36784267425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092950820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516004562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91109275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90283799171448</t>
   </si>
   <si>
     <t xml:space="preserve">3.25365543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3513343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53568506240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41599416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24815273284912</t>
+    <t xml:space="preserve">3.35133385658264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53568434715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41599440574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2481529712677</t>
   </si>
   <si>
     <t xml:space="preserve">3.19862508773804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18899536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20000123977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14359521865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25778269767761</t>
+    <t xml:space="preserve">3.18899488449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20000100135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14359569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25778245925903</t>
   </si>
   <si>
     <t xml:space="preserve">3.43938231468201</t>
@@ -2465,112 +2465,112 @@
     <t xml:space="preserve">3.7626838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44969964027405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4909725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59759378433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52880620956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56319999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54600286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68013882637024</t>
+    <t xml:space="preserve">3.44970059394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49097275733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5975935459137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52880644798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096429824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48409414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56319952011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54600358009338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68013858795166</t>
   </si>
   <si>
     <t xml:space="preserve">3.85554718971252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01031970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83147215843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65950202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60447263717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64574480056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68701767921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69045662879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84866833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421481132507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80739569664001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81427502632141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92089486122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95528960227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03439521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07222747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16853189468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12037944793701</t>
+    <t xml:space="preserve">4.01031923294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83147120475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65950298309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60447239875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64574503898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6870174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6904571056366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84866809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745638847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019856452942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421433448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80739641189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81427478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92089557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95528936386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03439474105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16853094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12037992477417</t>
   </si>
   <si>
     <t xml:space="preserve">4.08598613739014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23731899261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28546953201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44712209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65348434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76010417938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57781791687012</t>
+    <t xml:space="preserve">4.23731851577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2854700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44712114334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76010513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57781744003296</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018255233765</t>
@@ -2579,25 +2579,25 @@
     <t xml:space="preserve">4.34737920761108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4918327331543</t>
+    <t xml:space="preserve">4.49183320999146</t>
   </si>
   <si>
     <t xml:space="preserve">4.4436821937561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42304563522339</t>
+    <t xml:space="preserve">4.42304515838623</t>
   </si>
   <si>
     <t xml:space="preserve">4.46775722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4539999961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49527168273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30266714096069</t>
+    <t xml:space="preserve">4.45399951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49527215957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30266666412354</t>
   </si>
   <si>
     <t xml:space="preserve">4.29234838485718</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">4.37489414215088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39552974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32330322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52622604370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41616678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52278709411621</t>
+    <t xml:space="preserve">4.39553070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32330274581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52622699737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41616630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52278757095337</t>
   </si>
   <si>
     <t xml:space="preserve">4.50215196609497</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">4.31298542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41960620880127</t>
+    <t xml:space="preserve">4.41960573196411</t>
   </si>
   <si>
     <t xml:space="preserve">4.47119665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53310632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53654527664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55718088150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66380214691162</t>
+    <t xml:space="preserve">4.53310585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53654432296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5571813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66380262374878</t>
   </si>
   <si>
     <t xml:space="preserve">4.61221170425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093811035156</t>
+    <t xml:space="preserve">4.57093906402588</t>
   </si>
   <si>
     <t xml:space="preserve">4.52966594696045</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">4.45743989944458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40928745269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39209079742432</t>
+    <t xml:space="preserve">4.40928792953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39209127426147</t>
   </si>
   <si>
     <t xml:space="preserve">4.42648506164551</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">4.26139450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42992401123047</t>
+    <t xml:space="preserve">4.42992353439331</t>
   </si>
   <si>
     <t xml:space="preserve">4.43680238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56062078475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63628768920898</t>
+    <t xml:space="preserve">4.56062030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63628625869751</t>
   </si>
   <si>
     <t xml:space="preserve">4.68443775177002</t>
@@ -2690,88 +2690,88 @@
     <t xml:space="preserve">4.60877132415771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48839330673218</t>
+    <t xml:space="preserve">4.48839378356934</t>
   </si>
   <si>
     <t xml:space="preserve">4.56406021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45056056976318</t>
+    <t xml:space="preserve">4.45056009292603</t>
   </si>
   <si>
     <t xml:space="preserve">4.5950140953064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51590871810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54686307907104</t>
+    <t xml:space="preserve">4.51590824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54686212539673</t>
   </si>
   <si>
     <t xml:space="preserve">4.40240907669067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27515172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081768035889</t>
+    <t xml:space="preserve">4.27515268325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3508186340332</t>
   </si>
   <si>
     <t xml:space="preserve">4.35425758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55030202865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33362197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23044061660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32674169540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20636367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27859163284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50559043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4333643913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29922771453857</t>
+    <t xml:space="preserve">4.55030298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33362150192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23044013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32674217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20636415481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2785906791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50559091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43336343765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29922723770142</t>
   </si>
   <si>
     <t xml:space="preserve">4.31986379623413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30610704421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16165208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03783416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9896833896637</t>
+    <t xml:space="preserve">4.30610656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16165161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03783464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98968362808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.03095579147339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25107622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73259019851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81169509887695</t>
+    <t xml:space="preserve">4.25107669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73258924484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81169462203979</t>
   </si>
   <si>
     <t xml:space="preserve">4.93207406997681</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">4.81513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96646785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20034503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1934666633606</t>
+    <t xml:space="preserve">4.96646738052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20034551620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19346618652344</t>
   </si>
   <si>
     <t xml:space="preserve">5.12467956542969</t>
@@ -2801,73 +2801,73 @@
     <t xml:space="preserve">5.3791937828064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2656946182251</t>
+    <t xml:space="preserve">5.26569414138794</t>
   </si>
   <si>
     <t xml:space="preserve">5.34136056900024</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23129940032959</t>
+    <t xml:space="preserve">5.23130035400391</t>
   </si>
   <si>
     <t xml:space="preserve">5.29664850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11092185974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10404348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04557418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00774002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00086164474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91831636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88736152648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89423942565918</t>
+    <t xml:space="preserve">5.1556339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11092138290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10404300689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04557323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00774049758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00086116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91831588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88736248016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89423990249634</t>
   </si>
   <si>
     <t xml:space="preserve">4.89767980575562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88392210006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86672592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76698350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83577156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85296773910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89080142974854</t>
+    <t xml:space="preserve">4.8839225769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8667254447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76698303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83577060699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85296821594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89080047607422</t>
   </si>
   <si>
     <t xml:space="preserve">4.91487693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85984706878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87016582489014</t>
+    <t xml:space="preserve">4.85984659194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87016487121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.05933094024658</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">5.03869438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03181600570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71539211273193</t>
+    <t xml:space="preserve">5.03181648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71539258956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.59845399856567</t>
@@ -2888,43 +2888,43 @@
     <t xml:space="preserve">4.53998422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61565065383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67068099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02837562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12811899185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31728458404541</t>
+    <t xml:space="preserve">4.61565113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6706805229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12811851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31728506088257</t>
   </si>
   <si>
     <t xml:space="preserve">5.25537586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27257299423218</t>
+    <t xml:space="preserve">5.27257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">5.2588152885437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15219354629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07652807235718</t>
+    <t xml:space="preserve">5.15219449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07652854919434</t>
   </si>
   <si>
     <t xml:space="preserve">5.0902853012085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14875507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493667602539</t>
+    <t xml:space="preserve">5.14875555038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493715286255</t>
   </si>
   <si>
     <t xml:space="preserve">5.05245208740234</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">4.96990728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13499689102173</t>
+    <t xml:space="preserve">5.13499736785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.16251230239868</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">5.29320955276489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32760238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34479951858521</t>
+    <t xml:space="preserve">5.32760286331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34479999542236</t>
   </si>
   <si>
     <t xml:space="preserve">5.33104228973389</t>
@@ -2960,34 +2960,34 @@
     <t xml:space="preserve">5.33792114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45142030715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58899593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50645065307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708768844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44454193115234</t>
+    <t xml:space="preserve">5.45142078399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58899641036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50645112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44454145431519</t>
   </si>
   <si>
     <t xml:space="preserve">5.4823751449585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48925399780273</t>
+    <t xml:space="preserve">5.48925304412842</t>
   </si>
   <si>
     <t xml:space="preserve">5.56491994857788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53740549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51952028274536</t>
+    <t xml:space="preserve">5.53740501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">5.5511622428894</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">5.47824811935425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40258121490479</t>
+    <t xml:space="preserve">5.40258073806763</t>
   </si>
   <si>
     <t xml:space="preserve">5.45898723602295</t>
@@ -3008,22 +3008,22 @@
     <t xml:space="preserve">5.41496324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3654351234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3833212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43972635269165</t>
+    <t xml:space="preserve">5.36543607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38332033157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43972730636597</t>
   </si>
   <si>
     <t xml:space="preserve">5.39019966125488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32553863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37644195556641</t>
+    <t xml:space="preserve">5.32554006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37644147872925</t>
   </si>
   <si>
     <t xml:space="preserve">5.39983034133911</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">5.37506675720215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34617519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46036291122437</t>
+    <t xml:space="preserve">5.34617471694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46036338806152</t>
   </si>
   <si>
     <t xml:space="preserve">5.37369060516357</t>
@@ -3044,154 +3044,154 @@
     <t xml:space="preserve">5.43697500228882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5140175819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57730197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55528974533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42321729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4424786567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39845514297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47484111785889</t>
+    <t xml:space="preserve">5.51401662826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57730150222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55529022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44247817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39845418930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47484064102173</t>
   </si>
   <si>
     <t xml:space="preserve">5.43066692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42928552627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44309043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5949387550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58113479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5673303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57837390899658</t>
+    <t xml:space="preserve">5.42928695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44309139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59493970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58113527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56733083724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57837343215942</t>
   </si>
   <si>
     <t xml:space="preserve">5.55766773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60046100616455</t>
+    <t xml:space="preserve">5.60046148300171</t>
   </si>
   <si>
     <t xml:space="preserve">5.70813608169556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74264669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63773345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69571256637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66948270797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76473379135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77715826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291786193848</t>
+    <t xml:space="preserve">5.74264717102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63773393630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69571113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66948318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76473426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7771577835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6750054359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291738510132</t>
   </si>
   <si>
     <t xml:space="preserve">5.61288547515869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67914628982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83927774429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66120052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79234313964844</t>
+    <t xml:space="preserve">5.67914724349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83927869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66120004653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79234266281128</t>
   </si>
   <si>
     <t xml:space="preserve">5.66258144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328762054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68604850769043</t>
+    <t xml:space="preserve">5.66534185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68466901779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328809738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68604898452759</t>
   </si>
   <si>
     <t xml:space="preserve">5.65015697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55352544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63635301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72746276855469</t>
+    <t xml:space="preserve">5.55352640151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63635349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72746229171753</t>
   </si>
   <si>
     <t xml:space="preserve">5.66810274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68742990493774</t>
+    <t xml:space="preserve">5.68742895126343</t>
   </si>
   <si>
     <t xml:space="preserve">5.60460233688354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59355926513672</t>
+    <t xml:space="preserve">5.59355878829956</t>
   </si>
   <si>
     <t xml:space="preserve">5.36164474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40443849563599</t>
+    <t xml:space="preserve">5.40443801879883</t>
   </si>
   <si>
     <t xml:space="preserve">5.57975482940674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62392854690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67362451553345</t>
+    <t xml:space="preserve">5.62392902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67362499237061</t>
   </si>
   <si>
     <t xml:space="preserve">5.81442928314209</t>
@@ -3200,25 +3200,25 @@
     <t xml:space="preserve">5.8199520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79924488067627</t>
+    <t xml:space="preserve">5.79924583435059</t>
   </si>
   <si>
     <t xml:space="preserve">5.79510354995728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73160362243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7454080581665</t>
+    <t xml:space="preserve">5.73160314559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74540853500366</t>
   </si>
   <si>
     <t xml:space="preserve">5.71503829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75507116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80752801895142</t>
+    <t xml:space="preserve">5.75507211685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80752754211426</t>
   </si>
   <si>
     <t xml:space="preserve">5.88069200515747</t>
@@ -3227,49 +3227,49 @@
     <t xml:space="preserve">5.95523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04910564422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0311598777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981134414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0325403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94695329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92348527908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98284482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97318172454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99802923202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98560523986816</t>
+    <t xml:space="preserve">5.96351861953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04910516738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03116035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06981182098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03254079818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07809543609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94695281982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92348480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98284387588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97318029403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99802875518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98560571670532</t>
   </si>
   <si>
     <t xml:space="preserve">6.03668212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05048656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06705093383789</t>
+    <t xml:space="preserve">6.05048561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06705141067505</t>
   </si>
   <si>
     <t xml:space="preserve">6.06567096710205</t>
@@ -3278,16 +3278,16 @@
     <t xml:space="preserve">6.08775758743286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09051942825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06014919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04220294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03944253921509</t>
+    <t xml:space="preserve">6.09051847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0601487159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04220342636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03944158554077</t>
   </si>
   <si>
     <t xml:space="preserve">6.01045370101929</t>
@@ -3296,16 +3296,16 @@
     <t xml:space="preserve">6.15678024291992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19681215286255</t>
+    <t xml:space="preserve">6.19681262969971</t>
   </si>
   <si>
     <t xml:space="preserve">6.15125846862793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2023344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1457371711731</t>
+    <t xml:space="preserve">6.20233488082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14573669433594</t>
   </si>
   <si>
     <t xml:space="preserve">5.95937633514404</t>
@@ -3314,31 +3314,31 @@
     <t xml:space="preserve">6.14849758148193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34590101242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30034637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32519340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32243347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39835834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4535756111145</t>
+    <t xml:space="preserve">6.34590148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30034685134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32519435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32243299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39835786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45357513427734</t>
   </si>
   <si>
     <t xml:space="preserve">6.55710887908936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57229471206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343542098999</t>
+    <t xml:space="preserve">6.57229375839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343589782715</t>
   </si>
   <si>
     <t xml:space="preserve">6.60542392730713</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">6.72690439224243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66616487503052</t>
+    <t xml:space="preserve">6.6661639213562</t>
   </si>
   <si>
     <t xml:space="preserve">6.71585988998413</t>
@@ -3356,64 +3356,64 @@
     <t xml:space="preserve">6.80420875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72000122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245855331421</t>
+    <t xml:space="preserve">6.72000217437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245759963989</t>
   </si>
   <si>
     <t xml:space="preserve">6.80696964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82739305496216</t>
+    <t xml:space="preserve">6.827392578125</t>
   </si>
   <si>
     <t xml:space="preserve">6.70334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7093186378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62562036514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6136646270752</t>
+    <t xml:space="preserve">6.70931816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61366415023804</t>
   </si>
   <si>
     <t xml:space="preserve">6.56284666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66149139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60917949676514</t>
+    <t xml:space="preserve">6.66149091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60918045043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.56583595275879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50605249404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58227682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49708461761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.553879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68241596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65850162506104</t>
+    <t xml:space="preserve">6.50605154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58227586746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49708318710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55387926101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6824164390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65850210189819</t>
   </si>
   <si>
     <t xml:space="preserve">6.66448068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73771667480469</t>
+    <t xml:space="preserve">6.737717628479</t>
   </si>
   <si>
     <t xml:space="preserve">6.77657651901245</t>
@@ -3422,25 +3422,25 @@
     <t xml:space="preserve">6.78404998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84532928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8318772315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74369525909424</t>
+    <t xml:space="preserve">6.84532833099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83187675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7436957359314</t>
   </si>
   <si>
     <t xml:space="preserve">6.66298580169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56434202194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7086124420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58429384231567</t>
+    <t xml:space="preserve">6.56434106826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70861148834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58429336547852</t>
   </si>
   <si>
     <t xml:space="preserve">6.77614402770996</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">6.68865966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38783979415894</t>
+    <t xml:space="preserve">6.38783931732178</t>
   </si>
   <si>
     <t xml:space="preserve">6.4384880065918</t>
@@ -3464,136 +3464,136 @@
     <t xml:space="preserve">6.44309234619141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47685718536377</t>
+    <t xml:space="preserve">6.47685670852661</t>
   </si>
   <si>
     <t xml:space="preserve">6.5489935874939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68405628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62112903594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56127166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51522779464722</t>
+    <t xml:space="preserve">6.6840558052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62112951278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56127262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51522731781006</t>
   </si>
   <si>
     <t xml:space="preserve">6.50601863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51062393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52443695068359</t>
+    <t xml:space="preserve">6.51062345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52443647384644</t>
   </si>
   <si>
     <t xml:space="preserve">6.44462633132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2451024055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42927885055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48299741744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58889865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65336084365845</t>
+    <t xml:space="preserve">6.24510288238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42927980422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48299694061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58889818191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65335941314697</t>
   </si>
   <si>
     <t xml:space="preserve">6.64568567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66103363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74391269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79456186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85288429260254</t>
+    <t xml:space="preserve">6.66103458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7439136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7945613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85288381576538</t>
   </si>
   <si>
     <t xml:space="preserve">6.66410350799561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78688716888428</t>
+    <t xml:space="preserve">6.78688812255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.84981441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97566747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.106125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1322169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99255084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96185398101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79763174057007</t>
+    <t xml:space="preserve">6.97566795349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10612487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13221740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99254989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96185445785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79763078689575</t>
   </si>
   <si>
     <t xml:space="preserve">6.7914924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70554256439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40779161453247</t>
+    <t xml:space="preserve">6.70554304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40779209136963</t>
   </si>
   <si>
     <t xml:space="preserve">6.41700077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55052757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51829719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46611356735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5720157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67177820205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76386594772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69786834716797</t>
+    <t xml:space="preserve">6.55052804946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51829767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46611404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57201528549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67177724838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76386547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69786930084229</t>
   </si>
   <si>
     <t xml:space="preserve">6.45844030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54438877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69940328598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79916524887085</t>
+    <t xml:space="preserve">6.54438924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69940376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79916572570801</t>
   </si>
   <si>
     <t xml:space="preserve">6.56894636154175</t>
@@ -3605,16 +3605,16 @@
     <t xml:space="preserve">6.52290201187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47225332260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38476943969727</t>
+    <t xml:space="preserve">6.47225379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38476991653442</t>
   </si>
   <si>
     <t xml:space="preserve">6.36328220367432</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29575109481812</t>
+    <t xml:space="preserve">6.29575157165527</t>
   </si>
   <si>
     <t xml:space="preserve">6.23435878753662</t>
@@ -3626,16 +3626,16 @@
     <t xml:space="preserve">5.75089693069458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88749408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64960050582886</t>
+    <t xml:space="preserve">5.8874945640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6496000289917</t>
   </si>
   <si>
     <t xml:space="preserve">5.43933200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46388864517212</t>
+    <t xml:space="preserve">5.46388959884644</t>
   </si>
   <si>
     <t xml:space="preserve">5.336501121521</t>
@@ -3656,34 +3656,34 @@
     <t xml:space="preserve">5.29966592788696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41938018798828</t>
+    <t xml:space="preserve">5.41938066482544</t>
   </si>
   <si>
     <t xml:space="preserve">5.50993299484253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62811326980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92125988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88135528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86447238922119</t>
+    <t xml:space="preserve">5.62811279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92126035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88135480880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86447286605835</t>
   </si>
   <si>
     <t xml:space="preserve">5.82149791717529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97190809249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9089822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87214660644531</t>
+    <t xml:space="preserve">5.9719090461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90898132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87214612960815</t>
   </si>
   <si>
     <t xml:space="preserve">5.92586421966553</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">5.96116495132446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12538814544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06860065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95195627212524</t>
+    <t xml:space="preserve">6.12538909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06860113143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95195579528809</t>
   </si>
   <si>
     <t xml:space="preserve">6.05325317382812</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">5.98879146575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93353843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72787570953369</t>
+    <t xml:space="preserve">5.93353796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72787523269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.71559619903564</t>
@@ -3719,19 +3719,19 @@
     <t xml:space="preserve">5.85679864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82303285598755</t>
+    <t xml:space="preserve">5.82303237915039</t>
   </si>
   <si>
     <t xml:space="preserve">5.77084970474243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81842803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86293745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79859828948975</t>
+    <t xml:space="preserve">5.81842851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86293697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7985987663269</t>
   </si>
   <si>
     <t xml:space="preserve">5.89671564102173</t>
@@ -3740,31 +3740,31 @@
     <t xml:space="preserve">5.87098026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78090476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65865993499756</t>
+    <t xml:space="preserve">5.78090524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65865898132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.56536769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60397052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55089092254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61040449142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56375932693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59271144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55732440948486</t>
+    <t xml:space="preserve">5.60397100448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55089139938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61040544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56375885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59271192550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55732536315918</t>
   </si>
   <si>
     <t xml:space="preserve">5.62166452407837</t>
@@ -3773,31 +3773,31 @@
     <t xml:space="preserve">5.58788585662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50263643264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56054210662842</t>
+    <t xml:space="preserve">5.50263595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56054258346558</t>
   </si>
   <si>
     <t xml:space="preserve">5.81146574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66348505020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7085223197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74069261550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76321172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68922090530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817398071289</t>
+    <t xml:space="preserve">5.66348552703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70852279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74069213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76321125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68922138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817350387573</t>
   </si>
   <si>
     <t xml:space="preserve">5.89510726928711</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">5.75516939163208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76803636550903</t>
+    <t xml:space="preserve">5.76803684234619</t>
   </si>
   <si>
     <t xml:space="preserve">5.9514045715332</t>
@@ -3815,22 +3815,22 @@
     <t xml:space="preserve">5.94175338745117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91280078887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84685230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75034379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8870644569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80503225326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72299909591675</t>
+    <t xml:space="preserve">5.91280126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84685277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75034332275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80503177642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72299957275391</t>
   </si>
   <si>
     <t xml:space="preserve">5.55249977111816</t>
@@ -3845,16 +3845,16 @@
     <t xml:space="preserve">5.13107585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20828294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01043939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1182074546814</t>
+    <t xml:space="preserve">5.20828342437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01043891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225992202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11820793151855</t>
   </si>
   <si>
     <t xml:space="preserve">5.11981630325317</t>
@@ -3863,25 +3863,25 @@
     <t xml:space="preserve">5.15198612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30157566070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16807079315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17933082580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14876890182495</t>
+    <t xml:space="preserve">5.30157518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16807126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17933034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14876842498779</t>
   </si>
   <si>
     <t xml:space="preserve">5.04904270172119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07156229019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05386829376221</t>
+    <t xml:space="preserve">5.07156181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05386877059937</t>
   </si>
   <si>
     <t xml:space="preserve">4.80294466018677</t>
@@ -3890,43 +3890,43 @@
     <t xml:space="preserve">4.88819408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03456687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17611312866211</t>
+    <t xml:space="preserve">5.0345664024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17611360549927</t>
   </si>
   <si>
     <t xml:space="preserve">5.03295803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10855722427368</t>
+    <t xml:space="preserve">5.10855674743652</t>
   </si>
   <si>
     <t xml:space="preserve">5.0377836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85924100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98631191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12142467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93484020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01848173141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0152645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96379280090332</t>
+    <t xml:space="preserve">4.8592414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9123215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98631143569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12142515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93483972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01848077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01526498794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96379327774048</t>
   </si>
   <si>
     <t xml:space="preserve">4.99274587631226</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">5.21150016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15842056274414</t>
+    <t xml:space="preserve">5.15842008590698</t>
   </si>
   <si>
     <t xml:space="preserve">5.45599031448364</t>
@@ -3950,22 +3950,22 @@
     <t xml:space="preserve">5.50746154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48976898193359</t>
+    <t xml:space="preserve">5.48976850509644</t>
   </si>
   <si>
     <t xml:space="preserve">5.46242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50424528121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5364146232605</t>
+    <t xml:space="preserve">5.50424480438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53641414642334</t>
   </si>
   <si>
     <t xml:space="preserve">5.56858444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51067972183228</t>
+    <t xml:space="preserve">5.51067876815796</t>
   </si>
   <si>
     <t xml:space="preserve">5.40291023254395</t>
@@ -3983,25 +3983,25 @@
     <t xml:space="preserve">5.28388214111328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22919368743896</t>
+    <t xml:space="preserve">5.22919321060181</t>
   </si>
   <si>
     <t xml:space="preserve">5.163245677948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04100036621094</t>
+    <t xml:space="preserve">5.0410008430481</t>
   </si>
   <si>
     <t xml:space="preserve">5.14394378662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12946796417236</t>
+    <t xml:space="preserve">5.12946748733521</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883054733276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24688720703125</t>
+    <t xml:space="preserve">5.24688673019409</t>
   </si>
   <si>
     <t xml:space="preserve">5.08121252059937</t>
@@ -4019,10 +4019,10 @@
     <t xml:space="preserve">5.31766033172607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53963184356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41577816009521</t>
+    <t xml:space="preserve">5.53963088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41577863693237</t>
   </si>
   <si>
     <t xml:space="preserve">5.49459362030029</t>
@@ -4031,40 +4031,40 @@
     <t xml:space="preserve">5.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25653791427612</t>
+    <t xml:space="preserve">5.25653743743896</t>
   </si>
   <si>
     <t xml:space="preserve">5.33052825927734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08925485610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15037727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18898153305054</t>
+    <t xml:space="preserve">5.08925533294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15037775039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18898105621338</t>
   </si>
   <si>
     <t xml:space="preserve">4.99596309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16002893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08603858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13590097427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98792123794556</t>
+    <t xml:space="preserve">5.1600284576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08603763580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13590145111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9879207611084</t>
   </si>
   <si>
     <t xml:space="preserve">5.20345783233643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45920658111572</t>
+    <t xml:space="preserve">5.4592080116272</t>
   </si>
   <si>
     <t xml:space="preserve">5.39808464050293</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">5.32409429550171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33696269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28709888458252</t>
+    <t xml:space="preserve">5.33696222305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28709936141968</t>
   </si>
   <si>
     <t xml:space="preserve">5.14555215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30961799621582</t>
+    <t xml:space="preserve">5.30961751937866</t>
   </si>
   <si>
     <t xml:space="preserve">5.35626411437988</t>
@@ -4094,34 +4094,34 @@
     <t xml:space="preserve">5.47368383407593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54284811019897</t>
+    <t xml:space="preserve">5.54284906387329</t>
   </si>
   <si>
     <t xml:space="preserve">5.61362218856812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64579248428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67152738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73908376693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90315055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92405986785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04308748245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11707878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09616851806641</t>
+    <t xml:space="preserve">5.64579200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67152786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73908472061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90315008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92406034469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04308795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11707830429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09616804122925</t>
   </si>
   <si>
     <t xml:space="preserve">6.02539491653442</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">6.08651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21519708633423</t>
+    <t xml:space="preserve">6.21519756317139</t>
   </si>
   <si>
     <t xml:space="preserve">6.27149343490601</t>
@@ -4142,25 +4142,25 @@
     <t xml:space="preserve">6.24897480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26023435592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43716716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35996007919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45968580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49668121337891</t>
+    <t xml:space="preserve">6.26023387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43716764450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35996055603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45968675613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49668216705322</t>
   </si>
   <si>
     <t xml:space="preserve">6.46451187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45647001266479</t>
+    <t xml:space="preserve">6.45646905899048</t>
   </si>
   <si>
     <t xml:space="preserve">6.50472450256348</t>
@@ -4172,13 +4172,13 @@
     <t xml:space="preserve">6.53290462493896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56108522415161</t>
+    <t xml:space="preserve">6.56108474731445</t>
   </si>
   <si>
     <t xml:space="preserve">6.47820091247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4931206703186</t>
+    <t xml:space="preserve">6.49312019348145</t>
   </si>
   <si>
     <t xml:space="preserve">6.52958917617798</t>
@@ -4187,34 +4187,34 @@
     <t xml:space="preserve">6.52461671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67877960205078</t>
+    <t xml:space="preserve">6.67878007888794</t>
   </si>
   <si>
     <t xml:space="preserve">6.53124713897705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61413097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57434701919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51301240921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4748854637146</t>
+    <t xml:space="preserve">6.61413049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5743465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51301193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47488594055176</t>
   </si>
   <si>
     <t xml:space="preserve">6.52627372741699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46825504302979</t>
+    <t xml:space="preserve">6.46825551986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.54616594314575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54948091506958</t>
+    <t xml:space="preserve">6.54948139190674</t>
   </si>
   <si>
     <t xml:space="preserve">6.4400749206543</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">6.51467037200928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49146223068237</t>
+    <t xml:space="preserve">6.49146270751953</t>
   </si>
   <si>
     <t xml:space="preserve">6.46328210830688</t>
@@ -4244,31 +4244,31 @@
     <t xml:space="preserve">6.68209552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64728498458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73514127731323</t>
+    <t xml:space="preserve">6.64728450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73514175415039</t>
   </si>
   <si>
     <t xml:space="preserve">6.86609792709351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87935972213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00202798843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04015350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11640739440918</t>
+    <t xml:space="preserve">6.87935924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00202703475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04015398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11640691757202</t>
   </si>
   <si>
     <t xml:space="preserve">7.11806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10646200180054</t>
+    <t xml:space="preserve">7.10646152496338</t>
   </si>
   <si>
     <t xml:space="preserve">6.97218894958496</t>
@@ -4277,49 +4277,49 @@
     <t xml:space="preserve">6.98545122146606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07496452331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13464069366455</t>
+    <t xml:space="preserve">7.07496500015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13464164733887</t>
   </si>
   <si>
     <t xml:space="preserve">7.19100189208984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20757865905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2672553062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26559734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34019374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40152788162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40484237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49767208099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54077196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54242944717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47446584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58884525299072</t>
+    <t xml:space="preserve">7.20757961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26725482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26559829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34019327163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40152740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40484285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45788764953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49767160415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54077291488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54242992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47446489334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58884477615356</t>
   </si>
   <si>
     <t xml:space="preserve">7.6203408241272</t>
@@ -4328,70 +4328,70 @@
     <t xml:space="preserve">7.64023303985596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67504405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69327783584595</t>
+    <t xml:space="preserve">7.6750431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69327831268311</t>
   </si>
   <si>
     <t xml:space="preserve">7.5258526802063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49435806274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55900716781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6054220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59713411331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60210609436035</t>
+    <t xml:space="preserve">7.46286153793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49435758590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55900573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60542058944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59713363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60210704803467</t>
   </si>
   <si>
     <t xml:space="preserve">7.66675519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71814346313477</t>
+    <t xml:space="preserve">7.71814441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.72643136978149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77781915664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45457410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87604379653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03518104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66883373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73348331451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51135444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76166439056396</t>
+    <t xml:space="preserve">7.77782011032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45457363128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87604331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03518056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66883420944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.733482837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51135492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76166391372681</t>
   </si>
   <si>
     <t xml:space="preserve">7.00037002563477</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86941289901733</t>
+    <t xml:space="preserve">6.86941337585449</t>
   </si>
   <si>
     <t xml:space="preserve">6.76663684844971</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">6.76000642776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67214965820312</t>
+    <t xml:space="preserve">6.67214918136597</t>
   </si>
   <si>
     <t xml:space="preserve">6.83460235595703</t>
@@ -4409,19 +4409,19 @@
     <t xml:space="preserve">6.93406248092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9274320602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01363039016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96887397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89262104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05341529846191</t>
+    <t xml:space="preserve">6.92743110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01363086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96887302398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89262056350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05341577529907</t>
   </si>
   <si>
     <t xml:space="preserve">7.06999158859253</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">7.16282176971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18271350860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08656883239746</t>
+    <t xml:space="preserve">7.18271398544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08656930923462</t>
   </si>
   <si>
     <t xml:space="preserve">7.14293003082275</t>
@@ -4451,16 +4451,16 @@
     <t xml:space="preserve">7.05917692184448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01473617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05746793746948</t>
+    <t xml:space="preserve">7.01473665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05746841430664</t>
   </si>
   <si>
     <t xml:space="preserve">7.00277233123779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78057050704956</t>
+    <t xml:space="preserve">6.7805700302124</t>
   </si>
   <si>
     <t xml:space="preserve">6.85406827926636</t>
@@ -4469,13 +4469,13 @@
     <t xml:space="preserve">6.72245597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92414712905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92585611343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92072772979736</t>
+    <t xml:space="preserve">6.92414665222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92585563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92072820663452</t>
   </si>
   <si>
     <t xml:space="preserve">6.77031469345093</t>
@@ -4490,22 +4490,22 @@
     <t xml:space="preserve">6.71049118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71220016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79937124252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78569841384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491218566895</t>
+    <t xml:space="preserve">6.71220064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79937171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78569793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9549126625061</t>
   </si>
   <si>
     <t xml:space="preserve">6.98738813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93782043457031</t>
+    <t xml:space="preserve">6.93782091140747</t>
   </si>
   <si>
     <t xml:space="preserve">6.74638557434082</t>
@@ -4517,10 +4517,10 @@
     <t xml:space="preserve">6.86261367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79082536697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73100185394287</t>
+    <t xml:space="preserve">6.79082584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73100233078003</t>
   </si>
   <si>
     <t xml:space="preserve">6.84893989562988</t>
@@ -4529,13 +4529,13 @@
     <t xml:space="preserve">7.0301194190979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96858739852905</t>
+    <t xml:space="preserve">6.96858692169189</t>
   </si>
   <si>
     <t xml:space="preserve">6.98397016525269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00619029998779</t>
+    <t xml:space="preserve">7.00618982315063</t>
   </si>
   <si>
     <t xml:space="preserve">6.99422597885132</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">6.99593448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0232834815979</t>
+    <t xml:space="preserve">7.02328300476074</t>
   </si>
   <si>
     <t xml:space="preserve">7.0625958442688</t>
@@ -4559,19 +4559,19 @@
     <t xml:space="preserve">7.14634895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15660381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11045408248901</t>
+    <t xml:space="preserve">7.15660333633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11045455932617</t>
   </si>
   <si>
     <t xml:space="preserve">7.12754678726196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04208374023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98226070404053</t>
+    <t xml:space="preserve">7.04208469390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98226118087769</t>
   </si>
   <si>
     <t xml:space="preserve">6.87116003036499</t>
@@ -4583,13 +4583,13 @@
     <t xml:space="preserve">6.97029638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07797861099243</t>
+    <t xml:space="preserve">7.07797813415527</t>
   </si>
   <si>
     <t xml:space="preserve">7.09165334701538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96345901489258</t>
+    <t xml:space="preserve">6.96345853805542</t>
   </si>
   <si>
     <t xml:space="preserve">6.90534496307373</t>
@@ -4601,13 +4601,13 @@
     <t xml:space="preserve">6.84039354324341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8882532119751</t>
+    <t xml:space="preserve">6.88825273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06088638305664</t>
+    <t xml:space="preserve">7.06088590621948</t>
   </si>
   <si>
     <t xml:space="preserve">7.13096523284912</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">7.12925624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14976644515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30530834197998</t>
+    <t xml:space="preserve">7.14976692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30530786514282</t>
   </si>
   <si>
     <t xml:space="preserve">7.34291124343872</t>
@@ -4628,37 +4628,37 @@
     <t xml:space="preserve">7.3497486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38393402099609</t>
+    <t xml:space="preserve">7.38393354415894</t>
   </si>
   <si>
     <t xml:space="preserve">7.38564252853394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41982650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44033908843994</t>
+    <t xml:space="preserve">7.41982793807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44033861160278</t>
   </si>
   <si>
     <t xml:space="preserve">7.46768617630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57536840438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55485725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21813726425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20446300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788097381592</t>
+    <t xml:space="preserve">7.57536888122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55485820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2711238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20446252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788192749023</t>
   </si>
   <si>
     <t xml:space="preserve">7.19249820709229</t>
@@ -4673,16 +4673,16 @@
     <t xml:space="preserve">7.03182888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13609266281128</t>
+    <t xml:space="preserve">7.13609313964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.97200536727905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91047286987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92756462097168</t>
+    <t xml:space="preserve">6.91047334671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92756509780884</t>
   </si>
   <si>
     <t xml:space="preserve">6.97371482849121</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">6.95662260055542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94978523254395</t>
+    <t xml:space="preserve">6.9497857093811</t>
   </si>
   <si>
     <t xml:space="preserve">7.02157306671143</t>
@@ -4700,31 +4700,31 @@
     <t xml:space="preserve">7.15318536758423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17027854919434</t>
+    <t xml:space="preserve">7.17027807235718</t>
   </si>
   <si>
     <t xml:space="preserve">7.21300792694092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19078874588013</t>
+    <t xml:space="preserve">7.19078826904297</t>
   </si>
   <si>
     <t xml:space="preserve">7.03695726394653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17882299423218</t>
+    <t xml:space="preserve">7.17882347106934</t>
   </si>
   <si>
     <t xml:space="preserve">7.18737030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1685676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22497415542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08139753341675</t>
+    <t xml:space="preserve">7.16856813430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22497367858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08139705657959</t>
   </si>
   <si>
     <t xml:space="preserve">7.11558198928833</t>
@@ -4733,28 +4733,28 @@
     <t xml:space="preserve">7.19933462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04037475585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0284104347229</t>
+    <t xml:space="preserve">7.04037523269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841091156006</t>
   </si>
   <si>
     <t xml:space="preserve">6.97884321212769</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87799692153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83697557449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80279064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8916711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76860570907593</t>
+    <t xml:space="preserve">6.87799739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83697509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80279016494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89167165756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76860523223877</t>
   </si>
   <si>
     <t xml:space="preserve">6.86090421676636</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">6.77715158462524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72416543960571</t>
+    <t xml:space="preserve">6.72416496276855</t>
   </si>
   <si>
     <t xml:space="preserve">6.66946935653687</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">6.57887935638428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60109949111938</t>
+    <t xml:space="preserve">6.60109996795654</t>
   </si>
   <si>
     <t xml:space="preserve">6.55153131484985</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">6.49854469299316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49341773986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53443908691406</t>
+    <t xml:space="preserve">6.49341726303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5344386100769</t>
   </si>
   <si>
     <t xml:space="preserve">6.58571624755859</t>
@@ -4811,7 +4811,7 @@
     <t xml:space="preserve">6.88483381271362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80449962615967</t>
+    <t xml:space="preserve">6.80450010299683</t>
   </si>
   <si>
     <t xml:space="preserve">6.82842922210693</t>
@@ -4823,49 +4823,49 @@
     <t xml:space="preserve">7.00789976119995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.990807056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1668586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29847097396851</t>
+    <t xml:space="preserve">6.99080753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16685914993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29847049713135</t>
   </si>
   <si>
     <t xml:space="preserve">7.28137922286987</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17198753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19420719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29675388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26316070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23487234115601</t>
+    <t xml:space="preserve">7.17198657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19420766830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29675436019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26316118240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23487281799316</t>
   </si>
   <si>
     <t xml:space="preserve">7.19597578048706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24194526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15530967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17475938796997</t>
+    <t xml:space="preserve">7.24194478988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15531015396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17475891113281</t>
   </si>
   <si>
     <t xml:space="preserve">7.19243907928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21896076202393</t>
+    <t xml:space="preserve">7.21896028518677</t>
   </si>
   <si>
     <t xml:space="preserve">7.26669788360596</t>
@@ -4874,10 +4874,10 @@
     <t xml:space="preserve">7.25785732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24901723861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30029106140137</t>
+    <t xml:space="preserve">7.24901676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30029058456421</t>
   </si>
   <si>
     <t xml:space="preserve">7.2773060798645</t>
@@ -4889,7 +4889,7 @@
     <t xml:space="preserve">7.40637397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47532749176025</t>
+    <t xml:space="preserve">7.47532796859741</t>
   </si>
   <si>
     <t xml:space="preserve">7.44527053833008</t>
@@ -4898,37 +4898,37 @@
     <t xml:space="preserve">7.551353931427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61853981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5407452583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51952886581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54781818389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48240041732788</t>
+    <t xml:space="preserve">7.61854028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54074573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51952838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54781770706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48239994049072</t>
   </si>
   <si>
     <t xml:space="preserve">7.47886371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53897762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49654340744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54428148269653</t>
+    <t xml:space="preserve">7.53897714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49654388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54428291320801</t>
   </si>
   <si>
     <t xml:space="preserve">7.58671474456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58141136169434</t>
+    <t xml:space="preserve">7.58141088485718</t>
   </si>
   <si>
     <t xml:space="preserve">7.67511796951294</t>
@@ -4937,22 +4937,22 @@
     <t xml:space="preserve">7.65390110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79711294174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80241775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81832981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72815895080566</t>
+    <t xml:space="preserve">7.79711246490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80241727828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81833028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72815847396851</t>
   </si>
   <si>
     <t xml:space="preserve">7.8625316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04640865325928</t>
+    <t xml:space="preserve">8.04640960693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.11182689666748</t>
@@ -4961,10 +4961,10 @@
     <t xml:space="preserve">8.11005878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21967792510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28509616851807</t>
+    <t xml:space="preserve">8.21967887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28509521484375</t>
   </si>
   <si>
     <t xml:space="preserve">8.27625560760498</t>
@@ -4973,43 +4973,43 @@
     <t xml:space="preserve">8.37880229949951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43361282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41946887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26741600036621</t>
+    <t xml:space="preserve">8.43361186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41946792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26741504669189</t>
   </si>
   <si>
     <t xml:space="preserve">8.36642646789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39294719696045</t>
+    <t xml:space="preserve">8.39294815063477</t>
   </si>
   <si>
     <t xml:space="preserve">8.33106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33813858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46367073059082</t>
+    <t xml:space="preserve">8.33813762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46366882324219</t>
   </si>
   <si>
     <t xml:space="preserve">8.44952487945557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57328796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67583560943604</t>
+    <t xml:space="preserve">8.5732889175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67583656311035</t>
   </si>
   <si>
     <t xml:space="preserve">8.75009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50079917907715</t>
+    <t xml:space="preserve">8.50079822540283</t>
   </si>
   <si>
     <t xml:space="preserve">8.68644428253174</t>
@@ -5021,10 +5021,10 @@
     <t xml:space="preserve">8.62456130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57152080535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54500102996826</t>
+    <t xml:space="preserve">8.5715217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54499912261963</t>
   </si>
   <si>
     <t xml:space="preserve">8.59273719787598</t>
@@ -5036,73 +5036,73 @@
     <t xml:space="preserve">8.737717628479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783153533936</t>
+    <t xml:space="preserve">8.79783058166504</t>
   </si>
   <si>
     <t xml:space="preserve">8.78722286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76954174041748</t>
+    <t xml:space="preserve">8.7695426940918</t>
   </si>
   <si>
     <t xml:space="preserve">8.79959964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7819185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84026432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88888645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86236381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76070308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73064613342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62986660003662</t>
+    <t xml:space="preserve">8.78191947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84026527404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88888549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86236476898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76070117950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73064517974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6298656463623</t>
   </si>
   <si>
     <t xml:space="preserve">8.77661514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82258415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97286796569824</t>
+    <t xml:space="preserve">8.82258319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97286891937256</t>
   </si>
   <si>
     <t xml:space="preserve">8.87120532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07011222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10547351837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11431217193604</t>
+    <t xml:space="preserve">9.07011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10547256469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11431407928467</t>
   </si>
   <si>
     <t xml:space="preserve">9.14967441558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13199329376221</t>
+    <t xml:space="preserve">9.13199234008789</t>
   </si>
   <si>
     <t xml:space="preserve">9.06127166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99938869476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87562656402588</t>
+    <t xml:space="preserve">8.9993896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87562561035156</t>
   </si>
   <si>
     <t xml:space="preserve">9.07895183563232</t>
@@ -5111,7 +5111,7 @@
     <t xml:space="preserve">9.03475093841553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95518779754639</t>
+    <t xml:space="preserve">8.9551887512207</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910488128662</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">8.85794544219971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91982650756836</t>
+    <t xml:space="preserve">8.91982746124268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74744129180908</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">8.83142471313477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99055004119873</t>
+    <t xml:space="preserve">8.99054908752441</t>
   </si>
   <si>
     <t xml:space="preserve">9.00899124145508</t>
@@ -5138,28 +5138,28 @@
     <t xml:space="preserve">9.12886428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24873828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14269733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30406475067139</t>
+    <t xml:space="preserve">9.24873924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14269638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3040657043457</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705539703369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41471862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47926616668701</t>
+    <t xml:space="preserve">9.41471767425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4792652130127</t>
   </si>
   <si>
     <t xml:space="preserve">9.62680244445801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66368770599365</t>
+    <t xml:space="preserve">9.66368675231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.70057201385498</t>
@@ -5168,13 +5168,13 @@
     <t xml:space="preserve">9.94954013824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0601940155029</t>
+    <t xml:space="preserve">10.0601930618286</t>
   </si>
   <si>
     <t xml:space="preserve">10.0509719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99564647674561</t>
+    <t xml:space="preserve">9.99564552307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.95876216888428</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">9.7651195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97720336914062</t>
+    <t xml:space="preserve">9.97720432281494</t>
   </si>
   <si>
     <t xml:space="preserve">10.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98642444610596</t>
+    <t xml:space="preserve">9.98642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901416778564</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">9.49770832061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55303382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79278182983398</t>
+    <t xml:space="preserve">9.55303478240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7927827835083</t>
   </si>
   <si>
     <t xml:space="preserve">9.68212985992432</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">9.57147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50692939758301</t>
+    <t xml:space="preserve">9.50693035125732</t>
   </si>
   <si>
     <t xml:space="preserve">9.69135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667644500732</t>
+    <t xml:space="preserve">9.74667739868164</t>
   </si>
   <si>
     <t xml:space="preserve">9.82044506072998</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">9.86655044555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9126558303833</t>
+    <t xml:space="preserve">9.91265678405762</t>
   </si>
   <si>
     <t xml:space="preserve">9.96798324584961</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">10.0233097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90343570709229</t>
+    <t xml:space="preserve">9.90343475341797</t>
   </si>
   <si>
     <t xml:space="preserve">10.1062994003296</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">10.2077302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48848628997803</t>
+    <t xml:space="preserve">9.48848724365234</t>
   </si>
   <si>
     <t xml:space="preserve">9.25796031951904</t>
@@ -5282,10 +5282,10 @@
     <t xml:space="preserve">8.99515914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96749591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31328678131104</t>
+    <t xml:space="preserve">8.96749687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31328773498535</t>
   </si>
   <si>
     <t xml:space="preserve">9.43315982818604</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">9.58991813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82966613769531</t>
+    <t xml:space="preserve">9.82966709136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.84810924530029</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">10.0878562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1892881393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2446155548096</t>
+    <t xml:space="preserve">10.1892890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2446146011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.014087677002</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">10.0970773696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0694141387939</t>
+    <t xml:space="preserve">10.0694150924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.1247415542603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1800680160522</t>
+    <t xml:space="preserve">10.1800670623779</t>
   </si>
   <si>
     <t xml:space="preserve">10.3737096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198160171509</t>
+    <t xml:space="preserve">10.4198150634766</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907199859619</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">10.3552675247192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183832168579</t>
+    <t xml:space="preserve">10.3183841705322</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765743255615</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">10.2999420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3091621398926</t>
+    <t xml:space="preserve">10.3091630935669</t>
   </si>
   <si>
     <t xml:space="preserve">10.2169523239136</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">10.2722787857056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276052474976</t>
+    <t xml:space="preserve">10.3276042938232</t>
   </si>
   <si>
     <t xml:space="preserve">10.4567003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4935836791992</t>
+    <t xml:space="preserve">10.4935846328735</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042375564575</t>
@@ -5396,22 +5396,22 @@
     <t xml:space="preserve">10.4474792480469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5581312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134586334229</t>
+    <t xml:space="preserve">10.5581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134576797485</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4843635559082</t>
+    <t xml:space="preserve">10.4843626022339</t>
   </si>
   <si>
     <t xml:space="preserve">10.6226797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7517738342285</t>
+    <t xml:space="preserve">10.7517747879028</t>
   </si>
   <si>
     <t xml:space="preserve">10.9177541732788</t>
@@ -6024,6 +6024,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.3700008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4099998474121</t>
   </si>
 </sst>
 </file>
@@ -28402,7 +28405,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28428,7 +28431,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G849" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28454,7 +28457,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G850" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28480,7 +28483,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28506,7 +28509,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28532,7 +28535,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G853" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28558,7 +28561,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G854" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28584,7 +28587,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28610,7 +28613,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G856" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28636,7 +28639,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G857" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28662,7 +28665,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G858" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28688,7 +28691,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G859" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28714,7 +28717,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G860" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28740,7 +28743,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28766,7 +28769,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G862" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28792,7 +28795,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28818,7 +28821,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28844,7 +28847,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G865" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28870,7 +28873,7 @@
         <v>6</v>
       </c>
       <c r="G866" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28896,7 +28899,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G867" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28922,7 +28925,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G868" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28948,7 +28951,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G869" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28974,7 +28977,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G870" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -29000,7 +29003,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G871" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29026,7 +29029,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G872" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29052,7 +29055,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29078,7 +29081,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G874" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29104,7 +29107,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29130,7 +29133,7 @@
         <v>6.125</v>
       </c>
       <c r="G876" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29156,7 +29159,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G877" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -29182,7 +29185,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G878" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -29208,7 +29211,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29234,7 +29237,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -29260,7 +29263,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G881" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -29286,7 +29289,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G882" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -29312,7 +29315,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G883" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -29338,7 +29341,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G884" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -29364,7 +29367,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G885" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -29390,7 +29393,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G886" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29416,7 +29419,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G887" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29442,7 +29445,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G888" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -29468,7 +29471,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G889" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -29494,7 +29497,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G890" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -29520,7 +29523,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G891" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29546,7 +29549,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29572,7 +29575,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29598,7 +29601,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G894" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29624,7 +29627,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29650,7 +29653,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G896" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29676,7 +29679,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G897" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29702,7 +29705,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G898" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29728,7 +29731,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29754,7 +29757,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G900" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29780,7 +29783,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G901" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29806,7 +29809,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G902" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29832,7 +29835,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29858,7 +29861,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29884,7 +29887,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G905" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29910,7 +29913,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29936,7 +29939,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G907" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29962,7 +29965,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G908" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29988,7 +29991,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G909" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30040,7 +30043,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G911" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -30066,7 +30069,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G912" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -30092,7 +30095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -30118,7 +30121,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G914" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -30144,7 +30147,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G915" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -30170,7 +30173,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G916" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -30196,7 +30199,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G917" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -30222,7 +30225,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G918" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30248,7 +30251,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G919" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30274,7 +30277,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G920" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30300,7 +30303,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30326,7 +30329,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30378,7 +30381,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G924" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30404,7 +30407,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30430,7 +30433,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G926" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30456,7 +30459,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G927" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30482,7 +30485,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G928" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30508,7 +30511,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G929" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30534,7 +30537,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G930" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30560,7 +30563,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G931" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30586,7 +30589,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30612,7 +30615,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G933" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30638,7 +30641,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G934" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30664,7 +30667,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30690,7 +30693,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G936" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30716,7 +30719,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G937" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30742,7 +30745,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G938" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30768,7 +30771,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30794,7 +30797,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G940" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30820,7 +30823,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G941" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30846,7 +30849,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G942" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30872,7 +30875,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G943" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30898,7 +30901,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G944" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30924,7 +30927,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30950,7 +30953,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G946" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30976,7 +30979,7 @@
         <v>7</v>
       </c>
       <c r="G947" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -31002,7 +31005,7 @@
         <v>6.875</v>
       </c>
       <c r="G948" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31028,7 +31031,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31054,7 +31057,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G950" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31080,7 +31083,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G951" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31106,7 +31109,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31132,7 +31135,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G953" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31158,7 +31161,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G954" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31184,7 +31187,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31210,7 +31213,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G956" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31236,7 +31239,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G957" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31262,7 +31265,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G958" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31288,7 +31291,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G959" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31314,7 +31317,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G960" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31340,7 +31343,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G961" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31366,7 +31369,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G962" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31392,7 +31395,7 @@
         <v>7.25</v>
       </c>
       <c r="G963" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31418,7 +31421,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G964" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31444,7 +31447,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G965" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31470,7 +31473,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31496,7 +31499,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G967" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31522,7 +31525,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G968" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31548,7 +31551,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G969" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31574,7 +31577,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G970" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31600,7 +31603,7 @@
         <v>7.625</v>
       </c>
       <c r="G971" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31626,7 +31629,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G972" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31652,7 +31655,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G973" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31678,7 +31681,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31704,7 +31707,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G975" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31730,7 +31733,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G976" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31756,7 +31759,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G977" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31782,7 +31785,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G978" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31808,7 +31811,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G979" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31834,7 +31837,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G980" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31860,7 +31863,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G981" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31886,7 +31889,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G982" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31912,7 +31915,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G983" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31938,7 +31941,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G984" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31964,7 +31967,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G985" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31990,7 +31993,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G986" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -32016,7 +32019,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G987" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32042,7 +32045,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G988" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32068,7 +32071,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G989" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32094,7 +32097,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G990" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32120,7 +32123,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G991" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32146,7 +32149,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G992" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -32172,7 +32175,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G993" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -32198,7 +32201,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32224,7 +32227,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G995" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32250,7 +32253,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G996" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32276,7 +32279,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G997" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32302,7 +32305,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G998" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32328,7 +32331,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G999" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32354,7 +32357,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32380,7 +32383,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1001" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -32406,7 +32409,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32432,7 +32435,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G1003" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32458,7 +32461,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1004" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -32484,7 +32487,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1005" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32510,7 +32513,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1006" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32536,7 +32539,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1007" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32562,7 +32565,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32588,7 +32591,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G1009" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32614,7 +32617,7 @@
         <v>9.125</v>
       </c>
       <c r="G1010" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32640,7 +32643,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32666,7 +32669,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G1012" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32692,7 +32695,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1013" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32718,7 +32721,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1014" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32744,7 +32747,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1015" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32770,7 +32773,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G1016" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32796,7 +32799,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G1017" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32822,7 +32825,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1018" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32848,7 +32851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1019" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32874,7 +32877,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1020" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32900,7 +32903,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G1021" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32926,7 +32929,7 @@
         <v>9</v>
       </c>
       <c r="G1022" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32952,7 +32955,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1023" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32978,7 +32981,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1024" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -33004,7 +33007,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1025" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -33030,7 +33033,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1026" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -33056,7 +33059,7 @@
         <v>8.875</v>
       </c>
       <c r="G1027" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -33082,7 +33085,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1028" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -33108,7 +33111,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1029" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -33134,7 +33137,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1030" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -33160,7 +33163,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1031" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -33186,7 +33189,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1032" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -33212,7 +33215,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33238,7 +33241,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1034" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33264,7 +33267,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1035" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33290,7 +33293,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1036" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33394,7 +33397,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33550,7 +33553,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1046" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -71362,7 +71365,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6910416667</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>904722</v>
@@ -71383,6 +71386,32 @@
         <v>2003</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6910185185</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>1121260</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>17.5200004577637</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>17.2600002288818</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>17.3700008392334</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>17.4099998474121</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>2004</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="2007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="2010">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,115 +47,115 @@
     <t xml:space="preserve">3.73277378082275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49607491493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4144549369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901303291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43349957466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144383430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937628746033</t>
+    <t xml:space="preserve">3.49607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41445446014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901327133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349885940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144311904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937533378601</t>
   </si>
   <si>
     <t xml:space="preserve">3.29202389717102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10157561302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4198956489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805814743042</t>
+    <t xml:space="preserve">3.10157537460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040296554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41989588737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805767059326</t>
   </si>
   <si>
     <t xml:space="preserve">3.43077874183655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35187911987305</t>
+    <t xml:space="preserve">3.35187864303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.36276173591614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22672772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13966608047485</t>
+    <t xml:space="preserve">3.22672748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13966584205627</t>
   </si>
   <si>
     <t xml:space="preserve">3.18863797187805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30562663078308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03083848953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89208364486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15599036216736</t>
+    <t xml:space="preserve">3.30562734603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03083872795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89208436012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15599012374878</t>
   </si>
   <si>
     <t xml:space="preserve">3.25393438339233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31378984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40357136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36548256874084</t>
+    <t xml:space="preserve">3.31378865242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40357184410095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36548161506653</t>
   </si>
   <si>
     <t xml:space="preserve">3.36820268630981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46614694595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43622088432312</t>
+    <t xml:space="preserve">3.46614789962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4362199306488</t>
   </si>
   <si>
     <t xml:space="preserve">3.36004066467285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49063372612</t>
+    <t xml:space="preserve">3.49063348770142</t>
   </si>
   <si>
     <t xml:space="preserve">3.56681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5640914440155</t>
+    <t xml:space="preserve">3.56409215927124</t>
   </si>
   <si>
     <t xml:space="preserve">3.69196391105652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71100974082947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61850523948669</t>
+    <t xml:space="preserve">3.71100950241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61850643157959</t>
   </si>
   <si>
     <t xml:space="preserve">3.68652296066284</t>
@@ -164,97 +164,97 @@
     <t xml:space="preserve">3.68380188941956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7409360408783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80623292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7926299571991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76542210578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70284605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181937217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7218918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69468522071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387558937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439566612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432196617126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8660876750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71372938156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63482999801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54232668876648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74637770652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77630496025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821544647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87969160079956</t>
+    <t xml:space="preserve">3.74093675613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80623149871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79262924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76542282104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70284652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181889533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69468474388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387415885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8143949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84432315826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86608791351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71372890472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63482904434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54232621192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74637794494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77630543708801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73821568489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8796911239624</t>
   </si>
   <si>
     <t xml:space="preserve">3.91778063774109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85248374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407773017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88579130172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94962978363037</t>
+    <t xml:space="preserve">3.85248422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407820701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88579082489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94962859153748</t>
   </si>
   <si>
     <t xml:space="preserve">3.97460889816284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9662823677063</t>
+    <t xml:space="preserve">3.96628260612488</t>
   </si>
   <si>
     <t xml:space="preserve">3.88023900985718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92464923858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88856744766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00236463546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98848700523376</t>
+    <t xml:space="preserve">3.92464971542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88856673240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00236415863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98848652839661</t>
   </si>
   <si>
     <t xml:space="preserve">4.04122257232666</t>
@@ -263,106 +263,106 @@
     <t xml:space="preserve">3.93020009994507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07730436325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99681329727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9690580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06065082550049</t>
+    <t xml:space="preserve">4.07730484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99681377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96905755996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0606517791748</t>
   </si>
   <si>
     <t xml:space="preserve">3.92742466926575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93575024604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187356948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95240497589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91909766197205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130182266235</t>
+    <t xml:space="preserve">3.93575143814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92187428474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95240449905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91909742355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130277633667</t>
   </si>
   <si>
     <t xml:space="preserve">4.08008098602295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29102373123169</t>
+    <t xml:space="preserve">4.29102325439453</t>
   </si>
   <si>
     <t xml:space="preserve">4.23551225662231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16334819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1883282661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21608352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18277645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15502119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03289651870728</t>
+    <t xml:space="preserve">4.1633472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21608400344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.182776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559198379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15502071380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03289604187012</t>
   </si>
   <si>
     <t xml:space="preserve">4.0523247718811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09673404693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06342744827271</t>
+    <t xml:space="preserve">4.09673357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06342792510986</t>
   </si>
   <si>
     <t xml:space="preserve">3.69427752494812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53051853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55272269248962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48888492584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60268306732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78587198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8247287273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80529999732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685339927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288310050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13916325569153</t>
+    <t xml:space="preserve">3.53051900863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55272316932678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48888516426086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60268259048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7858715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82472825050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80529952049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685411453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288190841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13916373252869</t>
   </si>
   <si>
     <t xml:space="preserve">3.26961541175842</t>
@@ -371,16 +371,16 @@
     <t xml:space="preserve">3.23630905151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40561842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4139449596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904509544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463582038879</t>
+    <t xml:space="preserve">3.40561866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41394543647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2890453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463510513306</t>
   </si>
   <si>
     <t xml:space="preserve">3.19189953804016</t>
@@ -389,97 +389,97 @@
     <t xml:space="preserve">3.21410417556763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39174056053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47778272628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5971314907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49721193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941657066345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53884506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.558274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54162073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63598990440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58047842979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64154171943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39451622962952</t>
+    <t xml:space="preserve">3.39174008369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47778296470642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59713172912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721169471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941633224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53884530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55827403068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54162168502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386475563049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63599038124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58047866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64154148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39451599121094</t>
   </si>
   <si>
     <t xml:space="preserve">3.34455537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4194962978363</t>
+    <t xml:space="preserve">3.41949582099915</t>
   </si>
   <si>
     <t xml:space="preserve">3.54717230796814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56937670707703</t>
+    <t xml:space="preserve">3.56937646865845</t>
   </si>
   <si>
     <t xml:space="preserve">3.46945667266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41116952896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280313491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48055863380432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51664018630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45002746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47500705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51108932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56660103797913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58325409889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994750022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57215237617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65264272689819</t>
+    <t xml:space="preserve">3.4111692905426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280289649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48055815696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51664113998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45002770423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47500658035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51108956336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56660127639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58325457572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994797706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57215213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65264368057251</t>
   </si>
   <si>
     <t xml:space="preserve">3.59990787506104</t>
@@ -491,112 +491,112 @@
     <t xml:space="preserve">3.52219200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50831413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31402397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37786245346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30847382545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36120891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38896465301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29737091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19745063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23075842857361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29182028770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26683974266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27516746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337392807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39729189872742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46390509605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839409828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4611291885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3223512172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3861882686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43059825897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43614935874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50276327133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56382584571838</t>
+    <t xml:space="preserve">3.50831389427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31402492523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37786221504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30847311019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36120963096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38896489143372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29737162590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19745111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23075747489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29182004928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26684045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27516627311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337321281433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3972909450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46390461921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839433670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46112895011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32235050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38618898391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43059849739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43614912033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50276255607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382513046265</t>
   </si>
   <si>
     <t xml:space="preserve">3.36398506164551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3390052318573</t>
+    <t xml:space="preserve">3.33900427818298</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835423469543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54439663887024</t>
+    <t xml:space="preserve">3.54439640045166</t>
   </si>
   <si>
     <t xml:space="preserve">3.42227149009705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38341355323792</t>
+    <t xml:space="preserve">3.38341283798218</t>
   </si>
   <si>
     <t xml:space="preserve">3.30014634132385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28303289413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3714554309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39142107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37715983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41423988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45702528953552</t>
+    <t xml:space="preserve">3.28303337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37145471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39142179489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37716007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41423916816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45702481269836</t>
   </si>
   <si>
     <t xml:space="preserve">3.48554825782776</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">3.56256079673767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73370099067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930448532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09309434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95047855377197</t>
+    <t xml:space="preserve">3.73370122909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79930400848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09309387207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95047926902771</t>
   </si>
   <si>
     <t xml:space="preserve">3.89343166351318</t>
@@ -629,40 +629,40 @@
     <t xml:space="preserve">3.93906927108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93051171302795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635113716125</t>
+    <t xml:space="preserve">3.9305112361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635137557983</t>
   </si>
   <si>
     <t xml:space="preserve">3.92480659484863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90484118461609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93621706962585</t>
+    <t xml:space="preserve">3.90484094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93621635437012</t>
   </si>
   <si>
     <t xml:space="preserve">3.9419207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92195391654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89628338813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477391242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96473979949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10735654830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12447023391724</t>
+    <t xml:space="preserve">3.92195510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89628386497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477343559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96473956108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10735607147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12446975708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.04175233840942</t>
@@ -671,37 +671,37 @@
     <t xml:space="preserve">4.07883358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24426746368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1501407623291</t>
+    <t xml:space="preserve">4.2442684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15014123916626</t>
   </si>
   <si>
     <t xml:space="preserve">4.30131483078003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21574401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20433473587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26708650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21289205551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20718812942505</t>
+    <t xml:space="preserve">4.215744972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20433521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26708745956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21289300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20718717575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.09879922866821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23571157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18151760101318</t>
+    <t xml:space="preserve">4.23571109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18151664733887</t>
   </si>
   <si>
     <t xml:space="preserve">4.17010736465454</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.17581224441528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03319597244263</t>
+    <t xml:space="preserve">4.03319644927979</t>
   </si>
   <si>
     <t xml:space="preserve">4.03890037536621</t>
@@ -719,22 +719,22 @@
     <t xml:space="preserve">4.08453798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07027578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9704442024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99326324462891</t>
+    <t xml:space="preserve">4.07027530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97044444084167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99326276779175</t>
   </si>
   <si>
     <t xml:space="preserve">3.98185420036316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05886745452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11306095123291</t>
+    <t xml:space="preserve">4.05886697769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11305999755859</t>
   </si>
   <si>
     <t xml:space="preserve">4.06171941757202</t>
@@ -743,61 +743,61 @@
     <t xml:space="preserve">4.04745721817017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02749061584473</t>
+    <t xml:space="preserve">4.02749109268188</t>
   </si>
   <si>
     <t xml:space="preserve">3.75651931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63672113418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105060577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51977682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688979148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.633868932724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68235874176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64242649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65098261833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091534614563</t>
+    <t xml:space="preserve">3.63672161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105036735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5197765827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53689002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51692390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68235921859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64242625236511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65098357200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091582298279</t>
   </si>
   <si>
     <t xml:space="preserve">3.7194390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73084855079651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81641864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78789496421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81071424484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779477119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76792931556702</t>
+    <t xml:space="preserve">3.73084831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81641817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78789567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81071352958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84779381752014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7679283618927</t>
   </si>
   <si>
     <t xml:space="preserve">3.78219079971313</t>
@@ -806,130 +806,130 @@
     <t xml:space="preserve">3.80215620994568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8335325717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064721107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9076931476593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91625022888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94762563705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97614884376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92765927314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058041572571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212352752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87346577644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10278177261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10869359970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17076778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11460590362549</t>
+    <t xml:space="preserve">3.83353233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064625740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91624999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94762587547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97614908218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92765998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89057898521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349869728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87346529960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10278224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10869312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17076826095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11460638046265</t>
   </si>
   <si>
     <t xml:space="preserve">4.1530327796936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12938594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1057391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16485643386841</t>
+    <t xml:space="preserve">4.12938451766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10573863983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">4.23579740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23875331878662</t>
+    <t xml:space="preserve">4.23875379562378</t>
   </si>
   <si>
     <t xml:space="preserve">4.20919466018677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35107707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36290121078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35994529724121</t>
+    <t xml:space="preserve">4.34516620635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35107755661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36290073394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35994434356689</t>
   </si>
   <si>
     <t xml:space="preserve">4.39837217330933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28900289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30082702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37176895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340227127075</t>
+    <t xml:space="preserve">4.28900384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30082750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37176942825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340179443359</t>
   </si>
   <si>
     <t xml:space="preserve">4.51956367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46931409835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47522401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45453357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36881303787231</t>
+    <t xml:space="preserve">4.46931314468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47522497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45453310012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.368812084198</t>
   </si>
   <si>
     <t xml:space="preserve">4.3333420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41315174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30673885345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41906309127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43384265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38654851913452</t>
+    <t xml:space="preserve">4.41315126419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30673933029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41906261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43384218215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38654708862305</t>
   </si>
   <si>
     <t xml:space="preserve">4.30969524383545</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">4.28604793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31856250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39245986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29491519927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3362979888916</t>
+    <t xml:space="preserve">4.31856203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39246034622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2949161529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33629751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.25353288650513</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">4.32447385787964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37472486495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3274302482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33925342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38063716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49296092987061</t>
+    <t xml:space="preserve">4.3747239112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32743072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3392539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3806357383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49296045303345</t>
   </si>
   <si>
     <t xml:space="preserve">4.37768030166626</t>
@@ -977,52 +977,52 @@
     <t xml:space="preserve">4.40723991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38950443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31560659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27126741409302</t>
+    <t xml:space="preserve">4.38950347900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31560707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27126836776733</t>
   </si>
   <si>
     <t xml:space="preserve">4.21510648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34220933914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32151889801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25648927688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28309202194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057649612427</t>
+    <t xml:space="preserve">4.342209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3215184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25648832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2830924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057792663574</t>
   </si>
   <si>
     <t xml:space="preserve">4.23284196853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22101783752441</t>
+    <t xml:space="preserve">4.22101831436157</t>
   </si>
   <si>
     <t xml:space="preserve">4.16190004348755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19737100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24170923233032</t>
+    <t xml:space="preserve">4.19737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24170875549316</t>
   </si>
   <si>
     <t xml:space="preserve">4.17963600158691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22397375106812</t>
+    <t xml:space="preserve">4.22397422790527</t>
   </si>
   <si>
     <t xml:space="preserve">4.26831245422363</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">4.26535654067993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18850231170654</t>
+    <t xml:space="preserve">4.18850326538086</t>
   </si>
   <si>
     <t xml:space="preserve">4.17372369766235</t>
@@ -1055,34 +1055,34 @@
     <t xml:space="preserve">4.24762105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21806192398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28013610839844</t>
+    <t xml:space="preserve">4.21806144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28013515472412</t>
   </si>
   <si>
     <t xml:space="preserve">4.23866844177246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13528633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13832712173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16873407363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16569328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25083160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25995349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27211666107178</t>
+    <t xml:space="preserve">4.13528728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13832664489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16873359680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16569375991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25083065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25995302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27211618423462</t>
   </si>
   <si>
     <t xml:space="preserve">4.36637592315674</t>
@@ -1091,115 +1091,115 @@
     <t xml:space="preserve">4.3694167137146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34509134292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35117340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32988882064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38157892227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33596992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39678239822388</t>
+    <t xml:space="preserve">4.34509181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35117292404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32988834381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38157987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3359694480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39678192138672</t>
   </si>
   <si>
     <t xml:space="preserve">4.44543313980103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50016498565674</t>
+    <t xml:space="preserve">4.50016450881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.54577445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4393515586853</t>
+    <t xml:space="preserve">4.43935203552246</t>
   </si>
   <si>
     <t xml:space="preserve">4.48800182342529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51232814788818</t>
+    <t xml:space="preserve">4.51232671737671</t>
   </si>
   <si>
     <t xml:space="preserve">4.44847345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46367645263672</t>
+    <t xml:space="preserve">4.46367692947388</t>
   </si>
   <si>
     <t xml:space="preserve">4.38766098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30860328674316</t>
+    <t xml:space="preserve">4.30860376358032</t>
   </si>
   <si>
     <t xml:space="preserve">4.29340076446533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37245750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46063661575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45759582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55489635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57922124862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62179136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70084762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72517347335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74037599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73429584503174</t>
+    <t xml:space="preserve">4.37245798110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46063613891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45759534835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55489683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57922172546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62179088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70084857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.725172996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7403769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73429489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.77078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8163914680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81943273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7647008895874</t>
+    <t xml:space="preserve">4.81639289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76470136642456</t>
   </si>
   <si>
     <t xml:space="preserve">4.80423021316528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83463621139526</t>
+    <t xml:space="preserve">4.83463573455811</t>
   </si>
   <si>
     <t xml:space="preserve">4.71301031112671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61570978164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69172668457031</t>
+    <t xml:space="preserve">4.61570882797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69172620773315</t>
   </si>
   <si>
     <t xml:space="preserve">4.62787199020386</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">4.29948234558105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40590476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39374113082886</t>
+    <t xml:space="preserve">4.40590524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39374208450317</t>
   </si>
   <si>
     <t xml:space="preserve">4.4332709312439</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">4.42414855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42110776901245</t>
+    <t xml:space="preserve">4.42110824584961</t>
   </si>
   <si>
     <t xml:space="preserve">4.43022966384888</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">4.52449035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5032057762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31468486785889</t>
+    <t xml:space="preserve">4.50320529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31468534469604</t>
   </si>
   <si>
     <t xml:space="preserve">4.27819728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32076692581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38462018966675</t>
+    <t xml:space="preserve">4.32076644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38461923599243</t>
   </si>
   <si>
     <t xml:space="preserve">4.41502666473389</t>
@@ -1259,82 +1259,82 @@
     <t xml:space="preserve">4.35725402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33292865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26907587051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29644203186035</t>
+    <t xml:space="preserve">4.3329291343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26907539367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29644107818604</t>
   </si>
   <si>
     <t xml:space="preserve">4.3055624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23562860488892</t>
+    <t xml:space="preserve">4.2356276512146</t>
   </si>
   <si>
     <t xml:space="preserve">4.29035997390747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26603412628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26299476623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22650623321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21738433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28732013702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32380771636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38646984100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32702445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20500373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11426973342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14555740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16745853424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23003387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2550630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16120147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21438932418823</t>
+    <t xml:space="preserve">4.26603507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26299428939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22650527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21738338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32380723953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38647031784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32702350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20500326156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11427068710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14555788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16745805740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24567747116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23003339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25506401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2425479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16120195388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21438980102539</t>
   </si>
   <si>
     <t xml:space="preserve">4.17997407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17058801651001</t>
+    <t xml:space="preserve">4.17058706283569</t>
   </si>
   <si>
     <t xml:space="preserve">4.08924055099487</t>
@@ -1346,244 +1346,244 @@
     <t xml:space="preserve">3.85458636283875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83581376075745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82329964637756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77636909484863</t>
+    <t xml:space="preserve">3.83581471443176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82329940795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77636861801147</t>
   </si>
   <si>
     <t xml:space="preserve">3.80765581130981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81704187393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79826998710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73882365226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63557624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195265769958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262686729431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82642817497253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66060566902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72630906105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74508118629456</t>
+    <t xml:space="preserve">3.81704115867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79826927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73882389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63557648658752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195313453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262543678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82642865180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66060590744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72630858421326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7450807094574</t>
   </si>
   <si>
     <t xml:space="preserve">3.63870477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77011132240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71692252159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379399299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74820995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69815015792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68250751495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72317981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66373467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183354377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6011598110199</t>
+    <t xml:space="preserve">3.77011108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71692323684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379446983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69815039634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68250775337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72318005561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373372077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7607250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64183330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60116076469421</t>
   </si>
   <si>
     <t xml:space="preserve">3.57925891876221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63244676589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68876361846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67624926567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7044084072113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62931823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686320304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61993265151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62618970870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84520053863525</t>
+    <t xml:space="preserve">3.63244700431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68876457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6762490272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70440816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56361556053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62931847572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61993217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62618923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84520077705383</t>
   </si>
   <si>
     <t xml:space="preserve">3.99537920951843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88587355613708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9109034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87023043632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341876029968</t>
+    <t xml:space="preserve">3.88587379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91090393066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87022972106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341828346252</t>
   </si>
   <si>
     <t xml:space="preserve">3.87961649894714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8420717716217</t>
+    <t xml:space="preserve">3.84207224845886</t>
   </si>
   <si>
     <t xml:space="preserve">3.78575491905212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79514050483704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77324080467224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70753693580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698184013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81078457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80139875411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75446772575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73256659507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82017087936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75759696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81391310691833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77949786186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335896492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89213156700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99225091934204</t>
+    <t xml:space="preserve">3.79514074325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77324056625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70753788948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698279380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452609062195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078386306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80139803886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75446796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73256683349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563580513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82017064094543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75759601593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81391286849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77949714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397290229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335848808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89213109016418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9922513961792</t>
   </si>
   <si>
     <t xml:space="preserve">3.97660684585571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98912262916565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00163698196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4447238445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47288250923157</t>
+    <t xml:space="preserve">3.98912167549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00163745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472432136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47288274765015</t>
   </si>
   <si>
     <t xml:space="preserve">3.37276363372803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37589192390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39466547966003</t>
+    <t xml:space="preserve">3.37589168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39466428756714</t>
   </si>
   <si>
     <t xml:space="preserve">3.45098161697388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39779353141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31018853187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29141640663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24448561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22258424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16313862800598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18504023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13498044013977</t>
+    <t xml:space="preserve">3.39779305458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31018900871277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29141712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24448537826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22258448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313886642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18503975868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13498067855835</t>
   </si>
   <si>
     <t xml:space="preserve">3.21006989479065</t>
@@ -1592,22 +1592,22 @@
     <t xml:space="preserve">3.2069411277771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26325798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31644630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30706024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31331777572632</t>
+    <t xml:space="preserve">3.26325821876526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31644654273987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30705976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331729888916</t>
   </si>
   <si>
     <t xml:space="preserve">3.28515911102295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25387120246887</t>
+    <t xml:space="preserve">3.25387144088745</t>
   </si>
   <si>
     <t xml:space="preserve">3.2507426738739</t>
@@ -1616,223 +1616,223 @@
     <t xml:space="preserve">3.27843809127808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13193440437317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541543006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890421867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727265357971</t>
+    <t xml:space="preserve">3.13193416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541590690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727313041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.48354387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45098781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4477322101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44122076034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42494249343872</t>
+    <t xml:space="preserve">3.45098829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44773149490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4412202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4249427318573</t>
   </si>
   <si>
     <t xml:space="preserve">3.41843128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29146075248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192759513855</t>
+    <t xml:space="preserve">3.29146099090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192735671997</t>
   </si>
   <si>
     <t xml:space="preserve">3.23351073265076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28820514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4086639881134</t>
+    <t xml:space="preserve">3.28820538520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40866446495056</t>
   </si>
   <si>
     <t xml:space="preserve">3.33378434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31099486351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1553750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076168060303</t>
+    <t xml:space="preserve">3.31099534034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30773878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15537476539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076120376587</t>
   </si>
   <si>
     <t xml:space="preserve">3.31425070762634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2849497795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41517543792725</t>
+    <t xml:space="preserve">3.28494954109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41517519950867</t>
   </si>
   <si>
     <t xml:space="preserve">3.40215277671814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634159088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44447612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46401023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633406639099</t>
+    <t xml:space="preserve">3.36634039878845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44447636604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46401000022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633358955383</t>
   </si>
   <si>
     <t xml:space="preserve">3.48680019378662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46075439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331068992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4574990272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50958967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47052121162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5812132358551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71795034408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7765519618988</t>
+    <t xml:space="preserve">3.46075487136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726560592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45749950408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50958943367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47052097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58121371269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71795105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77655220031738</t>
   </si>
   <si>
     <t xml:space="preserve">3.70818376541138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83189916610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864308357239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87096571922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92305684089661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87422156333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073396682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99142456054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95886898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00770378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99793672561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06304836273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97189116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01747035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0663046836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0825834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12165117263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09235048294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11513948440552</t>
+    <t xml:space="preserve">3.83189868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864284515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87096643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92305707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87422180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88724398612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99142575263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95886874198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00770425796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99793696403503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06304979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97188997268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01746988296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12165069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09235000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11513996124268</t>
   </si>
   <si>
     <t xml:space="preserve">4.12816286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09886169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14118576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08583879470825</t>
+    <t xml:space="preserve">4.0988621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14118528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08583927154541</t>
   </si>
   <si>
     <t xml:space="preserve">4.11188411712646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16071891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13141822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26164436340332</t>
+    <t xml:space="preserve">4.16071844100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13141870498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26164388656616</t>
   </si>
   <si>
     <t xml:space="preserve">4.24862146377563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24536609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24210977554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23559904098511</t>
+    <t xml:space="preserve">4.24536561965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24211025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23559999465942</t>
   </si>
   <si>
     <t xml:space="preserve">4.2323431968689</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">4.32350063323975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38210296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40489292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884759902954</t>
+    <t xml:space="preserve">4.38210344314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4048924446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3788480758667</t>
   </si>
   <si>
     <t xml:space="preserve">4.37233591079712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37569189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2884464263916</t>
+    <t xml:space="preserve">4.37569236755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28844690322876</t>
   </si>
   <si>
     <t xml:space="preserve">4.32871341705322</t>
@@ -1865,28 +1865,28 @@
     <t xml:space="preserve">4.3320689201355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41260290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39246988296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36226940155029</t>
+    <t xml:space="preserve">4.4126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39246940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36226844787598</t>
   </si>
   <si>
     <t xml:space="preserve">4.22804641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.238112449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25153493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14751195907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10388898849487</t>
+    <t xml:space="preserve">4.23811197280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25153541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14751148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10388946533203</t>
   </si>
   <si>
     <t xml:space="preserve">4.16093397140503</t>
@@ -1895,40 +1895,40 @@
     <t xml:space="preserve">4.10724449157715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1642894744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12737798690796</t>
+    <t xml:space="preserve">4.16428899765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12737846374512</t>
   </si>
   <si>
     <t xml:space="preserve">4.12402248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06697797775269</t>
+    <t xml:space="preserve">4.06697702407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.07704448699951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08039999008179</t>
+    <t xml:space="preserve">4.08039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">4.04684495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02671051025391</t>
+    <t xml:space="preserve">4.02671098709106</t>
   </si>
   <si>
     <t xml:space="preserve">4.00657653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03342247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09046649932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14415645599365</t>
+    <t xml:space="preserve">4.03342151641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0904655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14415597915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.13408899307251</t>
@@ -1937,79 +1937,79 @@
     <t xml:space="preserve">4.17435646057129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1575779914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11059999465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13744449615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368898391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19784545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21797895431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24482345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34213542938232</t>
+    <t xml:space="preserve">4.15757894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13744497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368850708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19784593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21797847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24482440948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34213590621948</t>
   </si>
   <si>
     <t xml:space="preserve">4.28173589706421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28509092330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33877992630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3454909324646</t>
+    <t xml:space="preserve">4.28509044647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34549140930176</t>
   </si>
   <si>
     <t xml:space="preserve">4.34884691238403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47300434112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50991582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4629373550415</t>
+    <t xml:space="preserve">4.47300386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50991535186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46293783187866</t>
   </si>
   <si>
     <t xml:space="preserve">4.45622539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41931438446045</t>
+    <t xml:space="preserve">4.41931533813477</t>
   </si>
   <si>
     <t xml:space="preserve">4.48978185653687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48307085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51662635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53676080703735</t>
+    <t xml:space="preserve">4.48307037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51662683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53675985336304</t>
   </si>
   <si>
     <t xml:space="preserve">4.4931378364563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44280290603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42602586746216</t>
+    <t xml:space="preserve">4.44280385971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.426025390625</t>
   </si>
   <si>
     <t xml:space="preserve">4.42267036437988</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">4.4495153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42938137054443</t>
+    <t xml:space="preserve">4.42938184738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.5065598487854</t>
@@ -2033,22 +2033,22 @@
     <t xml:space="preserve">4.39582586288452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20120143890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21126747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14080047607422</t>
+    <t xml:space="preserve">4.20120096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21126794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14080095291138</t>
   </si>
   <si>
     <t xml:space="preserve">4.33542442321777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43273639678955</t>
+    <t xml:space="preserve">4.43273687362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.38575839996338</t>
@@ -2057,34 +2057,34 @@
     <t xml:space="preserve">4.46629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41595840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50320434570312</t>
+    <t xml:space="preserve">4.41595888137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">4.52333784103394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60722684860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61729431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70454025268555</t>
+    <t xml:space="preserve">4.60722827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6172947883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59716033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70453977584839</t>
   </si>
   <si>
     <t xml:space="preserve">4.65756177902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67769432067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72467374801636</t>
+    <t xml:space="preserve">4.67769479751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72467279434204</t>
   </si>
   <si>
     <t xml:space="preserve">4.73138523101807</t>
@@ -2093,61 +2093,61 @@
     <t xml:space="preserve">4.69782876968384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61393880844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64078426361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60387134552002</t>
+    <t xml:space="preserve">4.61393928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64078330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60387182235718</t>
   </si>
   <si>
     <t xml:space="preserve">4.62736129760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62400531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62064933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56024885177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6676287651062</t>
+    <t xml:space="preserve">4.62400579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62065029144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56024980545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66762828826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.66427278518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66091775894165</t>
+    <t xml:space="preserve">4.66091728210449</t>
   </si>
   <si>
     <t xml:space="preserve">4.6810507774353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82534074783325</t>
+    <t xml:space="preserve">4.82534122467041</t>
   </si>
   <si>
     <t xml:space="preserve">4.86560869216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90251970291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.942786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98305463790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04345464706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07365560531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08707666397095</t>
+    <t xml:space="preserve">4.90252017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94278621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98305368423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04345417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.073655128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08707761764526</t>
   </si>
   <si>
     <t xml:space="preserve">5.09714412689209</t>
@@ -2156,31 +2156,31 @@
     <t xml:space="preserve">5.1172776222229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15083456039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16090059280396</t>
+    <t xml:space="preserve">5.15083408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16090106964111</t>
   </si>
   <si>
     <t xml:space="preserve">5.15754461288452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16425609588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17432308197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16761064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2347240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63403940200806</t>
+    <t xml:space="preserve">5.16425561904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17432260513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16761207580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23472309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54343795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6340389251709</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175186157227</t>
@@ -2192,40 +2192,40 @@
     <t xml:space="preserve">5.77161836624146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78504037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8710241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02923631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17025136947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18400907516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2699933052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840238571167</t>
+    <t xml:space="preserve">5.78504085540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87102460861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02923679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17025184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18400859832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26999282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840190887451</t>
   </si>
   <si>
     <t xml:space="preserve">6.32846260070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34909868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40068912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878183364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2803111076355</t>
+    <t xml:space="preserve">6.34909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40069007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878087997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28031253814697</t>
   </si>
   <si>
     <t xml:space="preserve">6.26311445236206</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">6.33190202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21496152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2321605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25967645645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23559904098511</t>
+    <t xml:space="preserve">6.21496248245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23216009140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2596755027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23559951782227</t>
   </si>
   <si>
     <t xml:space="preserve">6.30438756942749</t>
@@ -2258,40 +2258,40 @@
     <t xml:space="preserve">6.28375101089478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2768726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24935722351074</t>
+    <t xml:space="preserve">6.27687215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2493577003479</t>
   </si>
   <si>
     <t xml:space="preserve">6.16681241989136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13585710525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14617538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09114503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11866140365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91229820251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573810577393</t>
+    <t xml:space="preserve">6.13585758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14617586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09114551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0361156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91229772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573762893677</t>
   </si>
   <si>
     <t xml:space="preserve">6.0533127784729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19088792800903</t>
+    <t xml:space="preserve">6.19088745117188</t>
   </si>
   <si>
     <t xml:space="preserve">6.00860071182251</t>
@@ -2300,103 +2300,103 @@
     <t xml:space="preserve">6.00516128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10490369796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267621994019</t>
+    <t xml:space="preserve">6.10490274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03267669677734</t>
   </si>
   <si>
     <t xml:space="preserve">5.92949485778809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95700931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90885877609253</t>
+    <t xml:space="preserve">5.95700979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90885829925537</t>
   </si>
   <si>
     <t xml:space="preserve">5.73001003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85726737976074</t>
+    <t xml:space="preserve">5.85726690292358</t>
   </si>
   <si>
     <t xml:space="preserve">5.60619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61651134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70249557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66810131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71625328063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77816104888916</t>
+    <t xml:space="preserve">5.61651086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70249509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66810178756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71625375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77816152572632</t>
   </si>
   <si>
     <t xml:space="preserve">5.81255483627319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80567598342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80911588668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8779034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98108577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01547956466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86758613586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70593547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40326929092407</t>
+    <t xml:space="preserve">5.80567646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80911636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87790393829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98108434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01547908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86758518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70593452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40326881408691</t>
   </si>
   <si>
     <t xml:space="preserve">5.35511779785156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37231492996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505758285522</t>
+    <t xml:space="preserve">5.372314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505805969238</t>
   </si>
   <si>
     <t xml:space="preserve">5.0627703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00430107116699</t>
+    <t xml:space="preserve">5.00430059432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.98366498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9492712020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6981954574585</t>
+    <t xml:space="preserve">4.94927072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69819593429565</t>
   </si>
   <si>
     <t xml:space="preserve">4.58813571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26483345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75580525398254</t>
+    <t xml:space="preserve">4.26483392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7558057308197</t>
   </si>
   <si>
     <t xml:space="preserve">3.71453261375427</t>
@@ -2405,34 +2405,34 @@
     <t xml:space="preserve">3.36509203910828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36784291267395</t>
+    <t xml:space="preserve">3.36784338951111</t>
   </si>
   <si>
     <t xml:space="preserve">3.08306193351746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84092974662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80515956878662</t>
+    <t xml:space="preserve">2.84092950820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516004562378</t>
   </si>
   <si>
     <t xml:space="preserve">2.91109299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90283799171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25365543365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35133385658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53568458557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41599440574646</t>
+    <t xml:space="preserve">2.90283823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25365567207336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35133409500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53568506240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41599416732788</t>
   </si>
   <si>
     <t xml:space="preserve">3.24815225601196</t>
@@ -2441,100 +2441,100 @@
     <t xml:space="preserve">3.1986255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18899512290955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20000100135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14359545707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25778317451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43938255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59415435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76268410682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44970059394836</t>
+    <t xml:space="preserve">3.18899536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20000123977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14359521865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25778293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43938183784485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59415411949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7626838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44970035552979</t>
   </si>
   <si>
     <t xml:space="preserve">3.4909725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59759402275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52880668640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096405982971</t>
+    <t xml:space="preserve">3.5975935459137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52880597114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.48409414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56320023536682</t>
+    <t xml:space="preserve">3.56319975852966</t>
   </si>
   <si>
     <t xml:space="preserve">3.54600310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68013858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85554718971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01031970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83147215843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65950202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60447192192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64574527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68701672554016</t>
+    <t xml:space="preserve">3.68013882637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8555474281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01031923294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83147144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65950274467468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60447239875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64574575424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68701767921448</t>
   </si>
   <si>
     <t xml:space="preserve">3.69045686721802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84866881370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91745591163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79019904136658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70421504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80739545822144</t>
+    <t xml:space="preserve">3.84866857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91745638847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79019951820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70421409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80739617347717</t>
   </si>
   <si>
     <t xml:space="preserve">3.81427478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92089533805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95528888702393</t>
+    <t xml:space="preserve">3.92089581489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95528960227966</t>
   </si>
   <si>
     <t xml:space="preserve">4.03439474105835</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">4.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.168532371521</t>
+    <t xml:space="preserve">4.16853094100952</t>
   </si>
   <si>
     <t xml:space="preserve">4.12037944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08598518371582</t>
+    <t xml:space="preserve">4.08598566055298</t>
   </si>
   <si>
     <t xml:space="preserve">4.23731899261475</t>
@@ -2558,28 +2558,28 @@
     <t xml:space="preserve">4.28546953201294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44712018966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65348386764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76010465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57781839370728</t>
+    <t xml:space="preserve">4.44712066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76010513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57781744003296</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34737920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49183368682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44368124008179</t>
+    <t xml:space="preserve">4.34737873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4918327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44368171691895</t>
   </si>
   <si>
     <t xml:space="preserve">4.42304515838623</t>
@@ -2591,19 +2591,19 @@
     <t xml:space="preserve">4.45399951934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49527215957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30266666412354</t>
+    <t xml:space="preserve">4.49527168273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30266714096069</t>
   </si>
   <si>
     <t xml:space="preserve">4.29234838485718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33706045150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37489461898804</t>
+    <t xml:space="preserve">4.33706140518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37489414215088</t>
   </si>
   <si>
     <t xml:space="preserve">4.39553022384644</t>
@@ -2612,109 +2612,109 @@
     <t xml:space="preserve">4.32330322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52622652053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41616630554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52278709411621</t>
+    <t xml:space="preserve">4.52622699737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52278804779053</t>
   </si>
   <si>
     <t xml:space="preserve">4.50215148925781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31298542022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41960620880127</t>
+    <t xml:space="preserve">4.31298494338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41960525512695</t>
   </si>
   <si>
     <t xml:space="preserve">4.47119665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53310632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53654432296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55718088150024</t>
+    <t xml:space="preserve">4.53310537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53654527664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55718183517456</t>
   </si>
   <si>
     <t xml:space="preserve">4.66380214691162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61221170425415</t>
+    <t xml:space="preserve">4.61221122741699</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093858718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52966594696045</t>
+    <t xml:space="preserve">4.52966547012329</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743894577026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40928792953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39209079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42648458480835</t>
+    <t xml:space="preserve">4.4092869758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39209127426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42648506164551</t>
   </si>
   <si>
     <t xml:space="preserve">4.26139450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42992305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43680238723755</t>
+    <t xml:space="preserve">4.42992401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43680334091187</t>
   </si>
   <si>
     <t xml:space="preserve">4.56062126159668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63628625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68443822860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60877132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48839378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56405973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45055961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5950140953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51590871810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5468635559082</t>
+    <t xml:space="preserve">4.63628721237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68443870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60877227783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48839330673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5640606880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45056009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59501361846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51590919494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54686307907104</t>
   </si>
   <si>
     <t xml:space="preserve">4.40240955352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2751522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081768035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35425710678101</t>
+    <t xml:space="preserve">4.27515268325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3508186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35425758361816</t>
   </si>
   <si>
     <t xml:space="preserve">4.55030250549316</t>
@@ -2723,25 +2723,25 @@
     <t xml:space="preserve">4.33362150192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23044013977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32674312591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20636367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27859115600586</t>
+    <t xml:space="preserve">4.23044061660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32674217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20636463165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27859163284302</t>
   </si>
   <si>
     <t xml:space="preserve">4.50559091567993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43336391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29922676086426</t>
+    <t xml:space="preserve">4.43336343765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29922771453857</t>
   </si>
   <si>
     <t xml:space="preserve">4.31986379623413</t>
@@ -2750,16 +2750,16 @@
     <t xml:space="preserve">4.30610656738281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16165256500244</t>
+    <t xml:space="preserve">4.16165208816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.03783464431763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9896833896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03095579147339</t>
+    <t xml:space="preserve">3.98968362808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03095626831055</t>
   </si>
   <si>
     <t xml:space="preserve">4.25107622146606</t>
@@ -2768,40 +2768,40 @@
     <t xml:space="preserve">4.73258972167969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81169509887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93207359313965</t>
+    <t xml:space="preserve">4.81169557571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93207454681396</t>
   </si>
   <si>
     <t xml:space="preserve">4.81513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96646738052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20034646987915</t>
+    <t xml:space="preserve">4.966468334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20034503936768</t>
   </si>
   <si>
     <t xml:space="preserve">5.19346761703491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12467908859253</t>
+    <t xml:space="preserve">5.12467861175537</t>
   </si>
   <si>
     <t xml:space="preserve">5.22442102432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24161863327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37919330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569414138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34136056900024</t>
+    <t xml:space="preserve">5.24161815643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37919425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3413610458374</t>
   </si>
   <si>
     <t xml:space="preserve">5.23129987716675</t>
@@ -2810,79 +2810,79 @@
     <t xml:space="preserve">5.29664754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15563344955444</t>
+    <t xml:space="preserve">5.1556339263916</t>
   </si>
   <si>
     <t xml:space="preserve">5.11092090606689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10404348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04557323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00774049758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00086164474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91831684112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88736200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8942403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89768028259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8839225769043</t>
+    <t xml:space="preserve">5.10404253005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04557371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00774097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00086116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91831588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88736152648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89424085617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89768123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88392305374146</t>
   </si>
   <si>
     <t xml:space="preserve">4.8667254447937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76698350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8357720375061</t>
+    <t xml:space="preserve">4.76698303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83577108383179</t>
   </si>
   <si>
     <t xml:space="preserve">4.85296821594238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89080142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91487741470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85984659194946</t>
+    <t xml:space="preserve">4.89080095291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91487646102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85984754562378</t>
   </si>
   <si>
     <t xml:space="preserve">4.87016487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05933046340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03869438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03181505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71539258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59845352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53998374938965</t>
+    <t xml:space="preserve">5.05933141708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03869390487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03181648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71539163589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59845399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53998422622681</t>
   </si>
   <si>
     <t xml:space="preserve">4.61565065383911</t>
@@ -2891,91 +2891,91 @@
     <t xml:space="preserve">4.67068099975586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02837705612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12811851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31728410720825</t>
+    <t xml:space="preserve">5.02837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12811899185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31728506088257</t>
   </si>
   <si>
     <t xml:space="preserve">5.25537586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27257347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25881576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15219402313232</t>
+    <t xml:space="preserve">5.27257251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2588152885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15219449996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.07652759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09028577804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14875459671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02493715286255</t>
+    <t xml:space="preserve">5.09028482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14875507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02493667602539</t>
   </si>
   <si>
     <t xml:space="preserve">5.05245208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96990633010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13499736785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16251277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14187526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23817920684814</t>
+    <t xml:space="preserve">4.96990728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13499784469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16251230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14187622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23817777633667</t>
   </si>
   <si>
     <t xml:space="preserve">5.29320907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32760238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34479999542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33104228973389</t>
+    <t xml:space="preserve">5.32760286331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34479951858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33104181289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.33792114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45142078399658</t>
+    <t xml:space="preserve">5.45142030715942</t>
   </si>
   <si>
     <t xml:space="preserve">5.58899593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50645017623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44454145431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48237419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48925352096558</t>
+    <t xml:space="preserve">5.50645065307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708673477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44454193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48237466812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48925399780273</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492042541504</t>
@@ -2987,31 +2987,31 @@
     <t xml:space="preserve">5.51952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5511622428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47824811935425</t>
+    <t xml:space="preserve">5.55116271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47824764251709</t>
   </si>
   <si>
     <t xml:space="preserve">5.40258169174194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45898675918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41221141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41496324539185</t>
+    <t xml:space="preserve">5.45898723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41221189498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.414963722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.36543607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3833212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43972635269165</t>
+    <t xml:space="preserve">5.38332080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43972682952881</t>
   </si>
   <si>
     <t xml:space="preserve">5.39019918441772</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">5.32553911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37644243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39982986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37506675720215</t>
+    <t xml:space="preserve">5.37644195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39982891082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37506628036499</t>
   </si>
   <si>
     <t xml:space="preserve">5.34617567062378</t>
@@ -3038,61 +3038,61 @@
     <t xml:space="preserve">5.37369012832642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43697452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51401805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57730102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55529022216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046642303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4232177734375</t>
+    <t xml:space="preserve">5.43697547912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51401662826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5773024559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55528974533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42321729660034</t>
   </si>
   <si>
     <t xml:space="preserve">5.44247770309448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39845418930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47484111785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43066644668579</t>
+    <t xml:space="preserve">5.39845371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47484064102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43066692352295</t>
   </si>
   <si>
     <t xml:space="preserve">5.42928647994995</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44309043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59493923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58113574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56733083724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57837438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55766773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70813655853271</t>
+    <t xml:space="preserve">5.44308996200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59493970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58113527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56732988357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57837390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55766725540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70813608169556</t>
   </si>
   <si>
     <t xml:space="preserve">5.74264621734619</t>
@@ -3104,85 +3104,85 @@
     <t xml:space="preserve">5.67224407196045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69571256637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66948318481445</t>
+    <t xml:space="preserve">5.69571208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66948413848877</t>
   </si>
   <si>
     <t xml:space="preserve">5.76473426818848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77715826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291738510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61288547515869</t>
+    <t xml:space="preserve">5.77715730667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6750054359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291833877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61288499832153</t>
   </si>
   <si>
     <t xml:space="preserve">5.67914628982544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83927774429321</t>
+    <t xml:space="preserve">5.83927822113037</t>
   </si>
   <si>
     <t xml:space="preserve">5.66120052337646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79234313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66258144378662</t>
+    <t xml:space="preserve">5.7923436164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66258096694946</t>
   </si>
   <si>
     <t xml:space="preserve">5.66534185409546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68328857421875</t>
+    <t xml:space="preserve">5.68466806411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68328809738159</t>
   </si>
   <si>
     <t xml:space="preserve">5.68604850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65015697479248</t>
+    <t xml:space="preserve">5.65015745162964</t>
   </si>
   <si>
     <t xml:space="preserve">5.55352592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63635349273682</t>
+    <t xml:space="preserve">5.63635301589966</t>
   </si>
   <si>
     <t xml:space="preserve">5.72746276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66810274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68742895126343</t>
+    <t xml:space="preserve">5.66810369491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68742942810059</t>
   </si>
   <si>
     <t xml:space="preserve">5.60460233688354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59355926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36164474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40443801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57975387573242</t>
+    <t xml:space="preserve">5.59355974197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36164426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40443754196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57975435256958</t>
   </si>
   <si>
     <t xml:space="preserve">5.62392807006836</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">5.8199520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79924583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79510402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73160362243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7454080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71503829956055</t>
+    <t xml:space="preserve">5.79924488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79510354995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73160314559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74540853500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71503734588623</t>
   </si>
   <si>
     <t xml:space="preserve">5.75507116317749</t>
@@ -3218,67 +3218,67 @@
     <t xml:space="preserve">5.80752754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88069152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95523548126221</t>
+    <t xml:space="preserve">5.88069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95523595809937</t>
   </si>
   <si>
     <t xml:space="preserve">5.9635181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04910659790039</t>
+    <t xml:space="preserve">6.04910516738892</t>
   </si>
   <si>
     <t xml:space="preserve">6.0311598777771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0698127746582</t>
+    <t xml:space="preserve">6.06981134414673</t>
   </si>
   <si>
     <t xml:space="preserve">6.0325403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07809495925903</t>
+    <t xml:space="preserve">6.07809448242188</t>
   </si>
   <si>
     <t xml:space="preserve">5.94695329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92348527908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98284435272217</t>
+    <t xml:space="preserve">5.92348480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98284482955933</t>
   </si>
   <si>
     <t xml:space="preserve">5.97318077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99802827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98560476303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03668212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05048608779907</t>
+    <t xml:space="preserve">5.99802875518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98560428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03668165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05048561096191</t>
   </si>
   <si>
     <t xml:space="preserve">6.06705141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06567096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08775806427002</t>
+    <t xml:space="preserve">6.06567144393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08775758743286</t>
   </si>
   <si>
     <t xml:space="preserve">6.09051895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06014966964722</t>
+    <t xml:space="preserve">6.06014919281006</t>
   </si>
   <si>
     <t xml:space="preserve">6.04220342636108</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">6.03944253921509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01045274734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15677976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19681358337402</t>
+    <t xml:space="preserve">6.01045322418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15678024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19681215286255</t>
   </si>
   <si>
     <t xml:space="preserve">6.15125846862793</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">5.95937585830688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14849758148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34590101242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30034637451172</t>
+    <t xml:space="preserve">6.14849710464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3459005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30034685134888</t>
   </si>
   <si>
     <t xml:space="preserve">6.32519388198853</t>
@@ -3323,85 +3323,85 @@
     <t xml:space="preserve">6.32243347167969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3983588218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45357608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5571084022522</t>
+    <t xml:space="preserve">6.39835834503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45357513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55710887908936</t>
   </si>
   <si>
     <t xml:space="preserve">6.57229423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70343637466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690439224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616344451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71586036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72000169754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.806969165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82739305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70334100723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70931911468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62562036514282</t>
+    <t xml:space="preserve">6.70343685150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6054253578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71585988998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420827865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72000122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245950698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80696964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.827392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7093186378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62562084197998</t>
   </si>
   <si>
     <t xml:space="preserve">6.61366415023804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56284618377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66149139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60917854309082</t>
+    <t xml:space="preserve">6.56284713745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66148996353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60917997360229</t>
   </si>
   <si>
     <t xml:space="preserve">6.56583595275879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50605154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58227682113647</t>
+    <t xml:space="preserve">6.50605058670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58227586746216</t>
   </si>
   <si>
     <t xml:space="preserve">6.49708366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.553879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68241739273071</t>
+    <t xml:space="preserve">6.55388021469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68241548538208</t>
   </si>
   <si>
     <t xml:space="preserve">6.65850210189819</t>
@@ -3410,64 +3410,64 @@
     <t xml:space="preserve">6.6644811630249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73771667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77657556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78404951095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84532737731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8318772315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74369525909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66298627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56434106826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70861148834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58429384231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77614450454712</t>
+    <t xml:space="preserve">6.73771619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77657508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78404998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84532976150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83187675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74369478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66298675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56434202194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7086124420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58429336547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77614402770996</t>
   </si>
   <si>
     <t xml:space="preserve">6.68865966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38783979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43848752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32951688766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49374103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44309282302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47685718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54899454116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68405628204346</t>
+    <t xml:space="preserve">6.38783931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43848848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32951736450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49374055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44309186935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47685766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54899311065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68405532836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.62112951278687</t>
@@ -3479,19 +3479,19 @@
     <t xml:space="preserve">6.51522731781006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50601863861084</t>
+    <t xml:space="preserve">6.506019115448</t>
   </si>
   <si>
     <t xml:space="preserve">6.51062345504761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52443599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44462633132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24510192871094</t>
+    <t xml:space="preserve">6.52443647384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4446268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2451024055481</t>
   </si>
   <si>
     <t xml:space="preserve">6.42927885055542</t>
@@ -3500,97 +3500,97 @@
     <t xml:space="preserve">6.48299741744995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58889865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65335988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74391269683838</t>
+    <t xml:space="preserve">6.58889818191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65335893630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64568471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103458404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7439136505127</t>
   </si>
   <si>
     <t xml:space="preserve">6.7945613861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85288429260254</t>
+    <t xml:space="preserve">6.85288381576538</t>
   </si>
   <si>
     <t xml:space="preserve">6.66410303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78688716888428</t>
+    <t xml:space="preserve">6.78688764572144</t>
   </si>
   <si>
     <t xml:space="preserve">6.84981393814087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97566795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.106125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13221740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99255132675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96185398101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79763031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79149198532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70554351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40779256820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41700077056885</t>
+    <t xml:space="preserve">6.97566747665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10612630844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13221788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99254989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96185445785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79763126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7914924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70554256439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40779209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41700124740601</t>
   </si>
   <si>
     <t xml:space="preserve">6.55052804946899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51829814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46611452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57201623916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76386547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69786882400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45844078063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54438781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69940328598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79916667938232</t>
+    <t xml:space="preserve">6.51829767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46611404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57201480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67177724838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76386594772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69786787033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45843982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54438877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69940280914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79916524887085</t>
   </si>
   <si>
     <t xml:space="preserve">6.56894636154175</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">6.34486436843872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52290201187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47225284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38476991653442</t>
+    <t xml:space="preserve">6.52290153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47225332260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38476943969727</t>
   </si>
   <si>
     <t xml:space="preserve">6.36328220367432</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">6.29575157165527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23435926437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2850079536438</t>
+    <t xml:space="preserve">6.23435878753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28500747680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.75089740753174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88749408721924</t>
+    <t xml:space="preserve">5.8874945640564</t>
   </si>
   <si>
     <t xml:space="preserve">5.6496000289917</t>
@@ -3647,58 +3647,58 @@
     <t xml:space="preserve">5.07098054885864</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62657785415649</t>
+    <t xml:space="preserve">5.62657880783081</t>
   </si>
   <si>
     <t xml:space="preserve">5.29966592788696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41938018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50993394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62811374664307</t>
+    <t xml:space="preserve">5.41937971115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50993299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62811326980591</t>
   </si>
   <si>
     <t xml:space="preserve">5.92126035690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88135480880737</t>
+    <t xml:space="preserve">5.88135576248169</t>
   </si>
   <si>
     <t xml:space="preserve">5.86447286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82149839401245</t>
+    <t xml:space="preserve">5.82149791717529</t>
   </si>
   <si>
     <t xml:space="preserve">5.97190856933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90898084640503</t>
+    <t xml:space="preserve">5.90898132324219</t>
   </si>
   <si>
     <t xml:space="preserve">5.87214660644531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92586421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96116495132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12538814544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06860113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95195579528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05325269699097</t>
+    <t xml:space="preserve">5.92586469650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96116542816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12538862228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06860065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95195627212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05325317382812</t>
   </si>
   <si>
     <t xml:space="preserve">5.98879098892212</t>
@@ -3713,19 +3713,19 @@
     <t xml:space="preserve">5.7155966758728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85679864883423</t>
+    <t xml:space="preserve">5.85679912567139</t>
   </si>
   <si>
     <t xml:space="preserve">5.82303237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77084922790527</t>
+    <t xml:space="preserve">5.77084970474243</t>
   </si>
   <si>
     <t xml:space="preserve">5.81842803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86293792724609</t>
+    <t xml:space="preserve">5.86293745040894</t>
   </si>
   <si>
     <t xml:space="preserve">5.79859828948975</t>
@@ -3734,22 +3734,22 @@
     <t xml:space="preserve">5.89671564102173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87098073959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78090524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65865993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56536769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60397052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55089139938354</t>
+    <t xml:space="preserve">5.87098026275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7809042930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6586594581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56536722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60397148132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55089044570923</t>
   </si>
   <si>
     <t xml:space="preserve">5.61040449142456</t>
@@ -3758,28 +3758,28 @@
     <t xml:space="preserve">5.56375932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59271192550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55732440948486</t>
+    <t xml:space="preserve">5.59271144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55732488632202</t>
   </si>
   <si>
     <t xml:space="preserve">5.62166452407837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58788633346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50263595581055</t>
+    <t xml:space="preserve">5.58788585662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50263690948486</t>
   </si>
   <si>
     <t xml:space="preserve">5.56054210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81146669387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66348457336426</t>
+    <t xml:space="preserve">5.81146621704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66348552703857</t>
   </si>
   <si>
     <t xml:space="preserve">5.7085223197937</t>
@@ -3788,19 +3788,19 @@
     <t xml:space="preserve">5.74069261550903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76321172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68922138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75516939163208</t>
+    <t xml:space="preserve">5.76321125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68922090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75516891479492</t>
   </si>
   <si>
     <t xml:space="preserve">5.76803636550903</t>
@@ -3812,64 +3812,64 @@
     <t xml:space="preserve">5.94175338745117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91280078887939</t>
+    <t xml:space="preserve">5.91280031204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.84685277938843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75034379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8870644569397</t>
+    <t xml:space="preserve">5.75034332275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706493377686</t>
   </si>
   <si>
     <t xml:space="preserve">5.80503177642822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72299909591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55249881744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17450475692749</t>
+    <t xml:space="preserve">5.72299957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55249929428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17450523376465</t>
   </si>
   <si>
     <t xml:space="preserve">4.93323230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13107585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2082839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01043891906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225992202759</t>
+    <t xml:space="preserve">5.13107538223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20828342437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01043939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05226039886475</t>
   </si>
   <si>
     <t xml:space="preserve">5.1182074546814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11981630325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15198659896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30157566070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1680703163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17933034896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14876937866211</t>
+    <t xml:space="preserve">5.11981582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15198612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30157518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16807126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17933082580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14876890182495</t>
   </si>
   <si>
     <t xml:space="preserve">5.04904270172119</t>
@@ -3881,34 +3881,34 @@
     <t xml:space="preserve">5.05386829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88819408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03456687927246</t>
+    <t xml:space="preserve">4.80294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88819456100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03456735610962</t>
   </si>
   <si>
     <t xml:space="preserve">5.17611312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03295803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10855722427368</t>
+    <t xml:space="preserve">5.03295755386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10855674743652</t>
   </si>
   <si>
     <t xml:space="preserve">5.0377836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8592414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98631191253662</t>
+    <t xml:space="preserve">4.85924100875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9123215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98631143569946</t>
   </si>
   <si>
     <t xml:space="preserve">5.12142467498779</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">4.96379280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99274635314941</t>
+    <t xml:space="preserve">4.99274587631226</t>
   </si>
   <si>
     <t xml:space="preserve">5.18737268447876</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">5.21149969100952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15841960906982</t>
+    <t xml:space="preserve">5.15842008590698</t>
   </si>
   <si>
     <t xml:space="preserve">5.45599031448364</t>
@@ -3944,31 +3944,31 @@
     <t xml:space="preserve">5.59432029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50746154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48976850509644</t>
+    <t xml:space="preserve">5.50746250152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48976898193359</t>
   </si>
   <si>
     <t xml:space="preserve">5.46242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50424528121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5364146232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56858396530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51067876815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40290975570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44312286376953</t>
+    <t xml:space="preserve">5.50424480438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53641414642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56858444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51067924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40291023254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44312238693237</t>
   </si>
   <si>
     <t xml:space="preserve">5.33374500274658</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">5.22919321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16324520111084</t>
+    <t xml:space="preserve">5.163245677948</t>
   </si>
   <si>
     <t xml:space="preserve">5.0410008430481</t>
@@ -3992,10 +3992,10 @@
     <t xml:space="preserve">5.14394330978394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12946748733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00883054733276</t>
+    <t xml:space="preserve">5.12946701049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00883102416992</t>
   </si>
   <si>
     <t xml:space="preserve">5.24688720703125</t>
@@ -4007,43 +4007,43 @@
     <t xml:space="preserve">5.11659955978394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1825475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19863224029541</t>
+    <t xml:space="preserve">5.18254709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19863271713257</t>
   </si>
   <si>
     <t xml:space="preserve">5.31766033172607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53963184356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41577816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49459362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28870820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25653791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33052778244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08925533294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15037775039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18898105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99596214294434</t>
+    <t xml:space="preserve">5.53963136672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41577863693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49459409713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25653743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33052825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08925485610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15037727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18898153305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99596309661865</t>
   </si>
   <si>
     <t xml:space="preserve">5.1600284576416</t>
@@ -4052,16 +4052,16 @@
     <t xml:space="preserve">5.08603811264038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13590145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98792123794556</t>
+    <t xml:space="preserve">5.135901927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98792028427124</t>
   </si>
   <si>
     <t xml:space="preserve">5.20345783233643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45920753479004</t>
+    <t xml:space="preserve">5.45920705795288</t>
   </si>
   <si>
     <t xml:space="preserve">5.39808464050293</t>
@@ -4073,31 +4073,31 @@
     <t xml:space="preserve">5.32409429550171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33696174621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28709840774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14555215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30961799621582</t>
+    <t xml:space="preserve">5.33696222305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28709888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1455512046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30961751937866</t>
   </si>
   <si>
     <t xml:space="preserve">5.35626459121704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47368431091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54284858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61362171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64579248428345</t>
+    <t xml:space="preserve">5.47368383407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54284906387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61362218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64579200744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.67152738571167</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">5.92405986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04308843612671</t>
+    <t xml:space="preserve">6.04308795928955</t>
   </si>
   <si>
     <t xml:space="preserve">6.11707878112793</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">6.08651781082153</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21519613265991</t>
+    <t xml:space="preserve">6.21519660949707</t>
   </si>
   <si>
     <t xml:space="preserve">6.27149343490601</t>
@@ -4139,28 +4139,28 @@
     <t xml:space="preserve">6.24897527694702</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26023387908936</t>
+    <t xml:space="preserve">6.26023435592651</t>
   </si>
   <si>
     <t xml:space="preserve">6.43716764450073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35996055603027</t>
+    <t xml:space="preserve">6.35996007919312</t>
   </si>
   <si>
     <t xml:space="preserve">6.45968627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49668216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46451234817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45646953582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50472402572632</t>
+    <t xml:space="preserve">6.49668169021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46451187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45646905899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50472450256348</t>
   </si>
   <si>
     <t xml:space="preserve">6.50969743728638</t>
@@ -4172,22 +4172,22 @@
     <t xml:space="preserve">6.56108522415161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47820138931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49312019348145</t>
+    <t xml:space="preserve">6.47820091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4931206703186</t>
   </si>
   <si>
     <t xml:space="preserve">6.52958917617798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52461624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67878007888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53124666213989</t>
+    <t xml:space="preserve">6.52461671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67877960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53124713897705</t>
   </si>
   <si>
     <t xml:space="preserve">6.61413049697876</t>
@@ -4199,19 +4199,19 @@
     <t xml:space="preserve">6.51301240921021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47488594055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52627420425415</t>
+    <t xml:space="preserve">6.4748854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52627468109131</t>
   </si>
   <si>
     <t xml:space="preserve">6.46825504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54616594314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494818687439</t>
+    <t xml:space="preserve">6.54616641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54948139190674</t>
   </si>
   <si>
     <t xml:space="preserve">6.4400749206543</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">6.39200258255005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55776977539062</t>
+    <t xml:space="preserve">6.55777025222778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51467037200928</t>
@@ -4244,43 +4244,43 @@
     <t xml:space="preserve">6.64728498458862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73514127731323</t>
+    <t xml:space="preserve">6.73514175415039</t>
   </si>
   <si>
     <t xml:space="preserve">6.86609792709351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87935972213745</t>
+    <t xml:space="preserve">6.87935924530029</t>
   </si>
   <si>
     <t xml:space="preserve">7.00202751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04015445709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11640739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11806440353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10646057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97218942642212</t>
+    <t xml:space="preserve">7.04015398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11640691757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11806488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10646104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97218894958496</t>
   </si>
   <si>
     <t xml:space="preserve">6.98545122146606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07496547698975</t>
+    <t xml:space="preserve">7.07496500015259</t>
   </si>
   <si>
     <t xml:space="preserve">7.13464069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19100189208984</t>
+    <t xml:space="preserve">7.19100141525269</t>
   </si>
   <si>
     <t xml:space="preserve">7.20757913589478</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">7.26559782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34019327163696</t>
+    <t xml:space="preserve">7.34019374847412</t>
   </si>
   <si>
     <t xml:space="preserve">7.40152788162231</t>
@@ -4304,34 +4304,34 @@
     <t xml:space="preserve">7.45788860321045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54077243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54243040084839</t>
+    <t xml:space="preserve">7.49767208099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.540771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54242944717407</t>
   </si>
   <si>
     <t xml:space="preserve">7.47446537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58884525299072</t>
+    <t xml:space="preserve">7.58884477615356</t>
   </si>
   <si>
     <t xml:space="preserve">7.6203408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64023303985596</t>
+    <t xml:space="preserve">7.64023399353027</t>
   </si>
   <si>
     <t xml:space="preserve">7.67504405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69327783584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5258526802063</t>
+    <t xml:space="preserve">7.69327878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52585315704346</t>
   </si>
   <si>
     <t xml:space="preserve">7.46286153793335</t>
@@ -4358,37 +4358,37 @@
     <t xml:space="preserve">7.71814346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72643232345581</t>
+    <t xml:space="preserve">7.72643136978149</t>
   </si>
   <si>
     <t xml:space="preserve">7.77782011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45457410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87604331970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03518152236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66883373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73348379135132</t>
+    <t xml:space="preserve">7.45457363128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87604379653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03518104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66883420944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73348331451416</t>
   </si>
   <si>
     <t xml:space="preserve">6.51135492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76166439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00036907196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86941289901733</t>
+    <t xml:space="preserve">6.76166391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00036954879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86941337585449</t>
   </si>
   <si>
     <t xml:space="preserve">6.76663684844971</t>
@@ -4400,43 +4400,43 @@
     <t xml:space="preserve">6.67214965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83460187911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93406295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92743110656738</t>
+    <t xml:space="preserve">6.83460235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93406248092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92743158340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.01363134384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96887397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89262056350708</t>
+    <t xml:space="preserve">6.96887302398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89262104034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.05341529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06999206542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15950632095337</t>
+    <t xml:space="preserve">7.06999158859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07993793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15950536727905</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18271398544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08656930923462</t>
+    <t xml:space="preserve">7.18271446228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0865683555603</t>
   </si>
   <si>
     <t xml:space="preserve">7.1429295539856</t>
@@ -4454,13 +4454,13 @@
     <t xml:space="preserve">7.05746793746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00277233123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78057050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85406827926636</t>
+    <t xml:space="preserve">7.00277185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7805700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85406875610352</t>
   </si>
   <si>
     <t xml:space="preserve">6.7224555015564</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">6.92072725296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77031469345093</t>
+    <t xml:space="preserve">6.77031421661377</t>
   </si>
   <si>
     <t xml:space="preserve">6.65921354293823</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">6.76005935668945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71049118041992</t>
+    <t xml:space="preserve">6.71049165725708</t>
   </si>
   <si>
     <t xml:space="preserve">6.71220064163208</t>
@@ -4508,22 +4508,22 @@
     <t xml:space="preserve">6.74638509750366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86774158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86261367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79082584381104</t>
+    <t xml:space="preserve">6.86774206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86261415481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79082536697388</t>
   </si>
   <si>
     <t xml:space="preserve">6.73100185394287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84893941879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011989593506</t>
+    <t xml:space="preserve">6.84893989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0301194190979</t>
   </si>
   <si>
     <t xml:space="preserve">6.96858692169189</t>
@@ -4538,10 +4538,10 @@
     <t xml:space="preserve">6.99422550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99593496322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02328300476074</t>
+    <t xml:space="preserve">6.99593448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02328252792358</t>
   </si>
   <si>
     <t xml:space="preserve">7.06259536743164</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">7.11045360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1275463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04208421707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98226118087769</t>
+    <t xml:space="preserve">7.12754678726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04208374023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98226070404053</t>
   </si>
   <si>
     <t xml:space="preserve">6.87116050720215</t>
@@ -4595,16 +4595,16 @@
     <t xml:space="preserve">6.72587442398071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84039354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88825273513794</t>
+    <t xml:space="preserve">6.84039402008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8882532119751</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06088638305664</t>
+    <t xml:space="preserve">7.0608868598938</t>
   </si>
   <si>
     <t xml:space="preserve">7.13096523284912</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">7.14976739883423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30530786514282</t>
+    <t xml:space="preserve">7.30530834197998</t>
   </si>
   <si>
     <t xml:space="preserve">7.34291124343872</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">7.34974908828735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38393306732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38564252853394</t>
+    <t xml:space="preserve">7.38393354415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38564300537109</t>
   </si>
   <si>
     <t xml:space="preserve">7.41982746124268</t>
@@ -4655,13 +4655,13 @@
     <t xml:space="preserve">7.20446252822876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788145065308</t>
+    <t xml:space="preserve">7.20788097381592</t>
   </si>
   <si>
     <t xml:space="preserve">7.19249868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76347780227661</t>
+    <t xml:space="preserve">6.76347732543945</t>
   </si>
   <si>
     <t xml:space="preserve">6.94465780258179</t>
@@ -4706,13 +4706,13 @@
     <t xml:space="preserve">7.19078826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03695726394653</t>
+    <t xml:space="preserve">7.03695678710938</t>
   </si>
   <si>
     <t xml:space="preserve">7.17882299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18736982345581</t>
+    <t xml:space="preserve">7.18736934661865</t>
   </si>
   <si>
     <t xml:space="preserve">7.16856813430786</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">7.04037475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02841091156006</t>
+    <t xml:space="preserve">7.0284104347229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97884273529053</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">6.76860570907593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86090421676636</t>
+    <t xml:space="preserve">6.86090469360352</t>
   </si>
   <si>
     <t xml:space="preserve">6.88312482833862</t>
@@ -4766,19 +4766,19 @@
     <t xml:space="preserve">6.78740692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7771520614624</t>
+    <t xml:space="preserve">6.77715158462524</t>
   </si>
   <si>
     <t xml:space="preserve">6.72416543960571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66946887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57887983322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60109949111938</t>
+    <t xml:space="preserve">6.66946935653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57887935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60109996795654</t>
   </si>
   <si>
     <t xml:space="preserve">6.55153131484985</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">6.48999834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49854469299316</t>
+    <t xml:space="preserve">6.49854516983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.49341726303101</t>
@@ -4808,10 +4808,10 @@
     <t xml:space="preserve">6.88483381271362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80449962615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82842874526978</t>
+    <t xml:space="preserve">6.80449914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82842922210693</t>
   </si>
   <si>
     <t xml:space="preserve">6.84552192687988</t>
@@ -4826,16 +4826,16 @@
     <t xml:space="preserve">7.16685914993286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29847097396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28137922286987</t>
+    <t xml:space="preserve">7.29847145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28137874603271</t>
   </si>
   <si>
     <t xml:space="preserve">7.17198705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19420766830444</t>
+    <t xml:space="preserve">7.19420719146729</t>
   </si>
   <si>
     <t xml:space="preserve">7.29675436019897</t>
@@ -6032,7 +6032,16 @@
     <t xml:space="preserve">17.6900005340576</t>
   </si>
   <si>
+    <t xml:space="preserve">17.4500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8500003814697</t>
+  </si>
+  <si>
     <t xml:space="preserve">18.0300006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6399993896484</t>
   </si>
 </sst>
 </file>
@@ -71475,27 +71484,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6915509259</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>1465148</v>
+        <v>1931279</v>
       </c>
       <c r="C2505" t="n">
-        <v>18.1599998474121</v>
+        <v>17.6100006103516</v>
       </c>
       <c r="D2505" t="n">
-        <v>17.75</v>
+        <v>17.3500003814697</v>
       </c>
       <c r="E2505" t="n">
-        <v>17.9400005340576</v>
+        <v>17.5400009155273</v>
       </c>
       <c r="F2505" t="n">
-        <v>18.0300006866455</v>
+        <v>17.4500007629395</v>
       </c>
       <c r="G2505" t="s">
         <v>2006</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>3101806</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>18.1700000762939</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>17.1900005340576</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>17.4699993133545</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>17.8500003814697</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>2007</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>1465148</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>18.1599998474121</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>17.9400005340576</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>18.0300006866455</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6911111111</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>1965537</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>18.3099994659424</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>18.4400005340576</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>18.6399993896484</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>2009</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="2017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="2018">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446698188782</t>
+    <t xml:space="preserve">3.78446626663208</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
@@ -50,472 +50,472 @@
     <t xml:space="preserve">3.49607539176941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41445446014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901327133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43349862098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5368857383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658270835876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937533378601</t>
+    <t xml:space="preserve">3.41445469856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349981307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144311904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688502311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937581062317</t>
   </si>
   <si>
     <t xml:space="preserve">3.2920241355896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10157585144043</t>
+    <t xml:space="preserve">3.10157608985901</t>
   </si>
   <si>
     <t xml:space="preserve">3.21040344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41989517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187888145447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276125907898</t>
+    <t xml:space="preserve">3.4198956489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.428058385849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077850341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187840461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276173591614</t>
   </si>
   <si>
     <t xml:space="preserve">3.22672772407532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13966608047485</t>
+    <t xml:space="preserve">3.13966584205627</t>
   </si>
   <si>
     <t xml:space="preserve">3.18863844871521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30562686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03083896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89208388328552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15599012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393438339233</t>
+    <t xml:space="preserve">3.30562710762024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03083848953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89208340644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15599060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393486022949</t>
   </si>
   <si>
     <t xml:space="preserve">3.31378960609436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40357184410095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36548256874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36820316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46614742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43622040748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36004090309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49063324928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56681323051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409192085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6919641494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71100878715515</t>
+    <t xml:space="preserve">3.40357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36548233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36820268630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46614694595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43622016906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36004137992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49063301086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56681227684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409239768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69196367263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71100926399231</t>
   </si>
   <si>
     <t xml:space="preserve">3.61850571632385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68652248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68380188941956</t>
+    <t xml:space="preserve">3.6865222454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68380212783813</t>
   </si>
   <si>
     <t xml:space="preserve">3.74093627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80623316764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7926287651062</t>
+    <t xml:space="preserve">3.80623292922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79262948036194</t>
   </si>
   <si>
     <t xml:space="preserve">3.76542186737061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70284700393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181889533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72189116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69468474388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439423561096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432220458984</t>
+    <t xml:space="preserve">3.70284628868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181913375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72189211845398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6946849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387415885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81439447402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84432244300842</t>
   </si>
   <si>
     <t xml:space="preserve">3.86608695983887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71372890472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6348295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54232668876648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74637818336487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77630567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821520805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87969064712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91777896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85248398780823</t>
+    <t xml:space="preserve">3.71373009681702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63482880592346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54232621192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74637770652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77630543708801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73821473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87969088554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91778111457825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85248446464539</t>
   </si>
   <si>
     <t xml:space="preserve">3.94407725334167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88579130172729</t>
+    <t xml:space="preserve">3.88579082489014</t>
   </si>
   <si>
     <t xml:space="preserve">3.94962859153748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97460842132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96628260612488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88023948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92464900016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88856720924377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00236463546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9884877204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0412220954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93019986152649</t>
+    <t xml:space="preserve">3.97460889816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96628308296204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88023972511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92464876174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88856625556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00236558914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98848700523376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04122304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93020057678223</t>
   </si>
   <si>
     <t xml:space="preserve">4.07730484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99681258201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96905851364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0606517791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93575167655945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92187309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95240521430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9190981388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94130206108093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08008098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29102373123169</t>
+    <t xml:space="preserve">3.99681377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9690580368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06065130233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742419242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93575143814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92187333106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95240497589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91909790039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94130182266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08008003234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29102468490601</t>
   </si>
   <si>
     <t xml:space="preserve">4.23551225662231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1633472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18832778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21608352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18277645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13559103012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15502071380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03289556503296</t>
+    <t xml:space="preserve">4.16334772109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1883282661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21608257293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18277597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13559150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15502166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03289604187012</t>
   </si>
   <si>
     <t xml:space="preserve">4.05232524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09673309326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06342649459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6942765712738</t>
+    <t xml:space="preserve">4.09673357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06342744827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69427800178528</t>
   </si>
   <si>
     <t xml:space="preserve">3.5305187702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55272340774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48888468742371</t>
+    <t xml:space="preserve">3.55272364616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48888516426086</t>
   </si>
   <si>
     <t xml:space="preserve">3.6026828289032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78587055206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82472848892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80530023574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94685387611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35288286209106</t>
+    <t xml:space="preserve">3.78587126731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82472896575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80529952049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94685411453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35288238525391</t>
   </si>
   <si>
     <t xml:space="preserve">3.13916420936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26961541175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23630905151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40561866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4139449596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28904438018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24463510513306</t>
+    <t xml:space="preserve">3.26961517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23630857467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4056179523468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41394519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28904485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24463558197021</t>
   </si>
   <si>
     <t xml:space="preserve">3.19189977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21410465240479</t>
+    <t xml:space="preserve">3.21410393714905</t>
   </si>
   <si>
     <t xml:space="preserve">3.39174056053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47778296470642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59713196754456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49721169471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51941704750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53884625434875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55827498435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54162120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386475563049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63599014282227</t>
+    <t xml:space="preserve">3.47778344154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59713172912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49721240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51941609382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53884601593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55827450752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54162096977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63599038124084</t>
   </si>
   <si>
     <t xml:space="preserve">3.58047890663147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64154100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39451622962952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34455537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949605941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54717254638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56937670707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41116952896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45280265808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37231111526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48055863380432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51664113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45002698898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47500729560852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51108956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56660127639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58325409889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54994750022888</t>
+    <t xml:space="preserve">3.64154195785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39451551437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34455585479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54717230796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56937646865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46945691108704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4111692905426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45280313491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37231135368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48055815696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51664137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45002722740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47500705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51108932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56660151481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58325386047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54994821548462</t>
   </si>
   <si>
     <t xml:space="preserve">3.57215189933777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65264415740967</t>
+    <t xml:space="preserve">3.65264391899109</t>
   </si>
   <si>
     <t xml:space="preserve">3.59990811347961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4916615486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52219247817993</t>
+    <t xml:space="preserve">3.49166059494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52219152450562</t>
   </si>
   <si>
     <t xml:space="preserve">3.50831460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31402468681335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37786245346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30847382545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36120891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38896417617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29737091064453</t>
+    <t xml:space="preserve">3.3140242099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37786293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30847334861755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36120963096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38896489143372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29737114906311</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745111465454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23075771331787</t>
+    <t xml:space="preserve">3.23075795173645</t>
   </si>
   <si>
     <t xml:space="preserve">3.29182028770447</t>
@@ -524,58 +524,58 @@
     <t xml:space="preserve">3.2668399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2751669883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43337392807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3972909450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46390509605408</t>
+    <t xml:space="preserve">3.27516674995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43337368965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39729142189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46390533447266</t>
   </si>
   <si>
     <t xml:space="preserve">3.40839385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46112966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32235145568848</t>
+    <t xml:space="preserve">3.46112942695618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3223512172699</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618946075439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43059802055359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43614912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50276231765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56382536888123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36398506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33900475502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835399627686</t>
+    <t xml:space="preserve">3.43059849739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43614935874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50276350975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382513046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36398482322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33900499343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835375785828</t>
   </si>
   <si>
     <t xml:space="preserve">3.54439687728882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42227125167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38341331481934</t>
+    <t xml:space="preserve">3.4222719669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38341403007507</t>
   </si>
   <si>
     <t xml:space="preserve">3.30014729499817</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">3.28303289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37145471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39142155647278</t>
+    <t xml:space="preserve">3.37145495414734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39142203330994</t>
   </si>
   <si>
     <t xml:space="preserve">3.3771595954895</t>
@@ -596,295 +596,295 @@
     <t xml:space="preserve">3.41423964500427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45702505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48554873466492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53118586540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56256103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73370099067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79930543899536</t>
+    <t xml:space="preserve">3.45702409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48554849624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53118538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56256151199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73370170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79930472373962</t>
   </si>
   <si>
     <t xml:space="preserve">4.09309530258179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95047855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8934314250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95333075523376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93906855583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93051195144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85635137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92480731010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90484046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9362165927887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94192147254944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92195439338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89628386497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94477248191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96473932266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10735607147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12447071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04175329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2442684173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15014171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30131435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574449539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20433568954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26708650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21289205551147</t>
+    <t xml:space="preserve">3.95047831535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89343166351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95333003997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93906879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9305112361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85635161399841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92480707168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90483999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93621635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9419207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92195463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89628338813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94477343559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96473956108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10735654830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12446975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04175233840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426889419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1501407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30131483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574544906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20433664321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26708698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21289300918579</t>
   </si>
   <si>
     <t xml:space="preserve">4.20718812942505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09879970550537</t>
+    <t xml:space="preserve">4.09879875183105</t>
   </si>
   <si>
     <t xml:space="preserve">4.23571109771729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18151617050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17010736465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17581272125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03319549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03890085220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07027673721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97044444084167</t>
+    <t xml:space="preserve">4.18151807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1701078414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17581224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03319501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03889989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08453845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07027626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97044491767883</t>
   </si>
   <si>
     <t xml:space="preserve">3.99326324462891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98185324668884</t>
+    <t xml:space="preserve">3.98185420036316</t>
   </si>
   <si>
     <t xml:space="preserve">4.05886697769165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11306095123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06171846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04745674133301</t>
+    <t xml:space="preserve">4.11306190490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06171941757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04745721817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.02749109268188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75651907920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63672208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61105060577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51977634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688955307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51692366600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386940956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68235874176025</t>
+    <t xml:space="preserve">3.75651979446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63672184944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61105108261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51977610588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53689050674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5169243812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386845588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68235898017883</t>
   </si>
   <si>
     <t xml:space="preserve">3.64242649078369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65098404884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71943998336792</t>
+    <t xml:space="preserve">3.6509838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69091606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71943926811218</t>
   </si>
   <si>
     <t xml:space="preserve">3.73084855079651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81641840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7878954410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81071400642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84779381752014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76792883872986</t>
+    <t xml:space="preserve">3.81641888618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78789520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81071352958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8477942943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76792907714844</t>
   </si>
   <si>
     <t xml:space="preserve">3.78219032287598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80215668678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83353161811829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85064721107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9076931476593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91624975204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94762516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97614908218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9276602268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89057874679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349917411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212281227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8734655380249</t>
+    <t xml:space="preserve">3.80215716362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83353233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85064673423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90769290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9162495136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94762587547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97614860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92765927314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89057922363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349893569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87346529960632</t>
   </si>
   <si>
     <t xml:space="preserve">4.10278224945068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17076730728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11460542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15303230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12938499450684</t>
+    <t xml:space="preserve">4.10869359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17076826095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1146068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1530327796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12938547134399</t>
   </si>
   <si>
     <t xml:space="preserve">4.10573816299438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16485643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23579788208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875331878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20919466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35107803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36290168762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35994482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39837169647217</t>
+    <t xml:space="preserve">4.16485500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23579835891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875379562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20919370651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34516620635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35107755661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36290121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35994529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39837217330933</t>
   </si>
   <si>
     <t xml:space="preserve">4.28900384902954</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">4.30082750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37176847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46340227127075</t>
+    <t xml:space="preserve">4.37176942825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46340179443359</t>
   </si>
   <si>
     <t xml:space="preserve">4.51956415176392</t>
@@ -905,139 +905,139 @@
     <t xml:space="preserve">4.46931266784668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4752254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45453310012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.368812084198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33334159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41315174102783</t>
+    <t xml:space="preserve">4.47522592544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45453357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36881256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3333420753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41315126419067</t>
   </si>
   <si>
     <t xml:space="preserve">4.30673885345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41906309127808</t>
+    <t xml:space="preserve">4.41906261444092</t>
   </si>
   <si>
     <t xml:space="preserve">4.43384218215942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38654851913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30969524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28604745864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31856298446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39245986938477</t>
+    <t xml:space="preserve">4.38654899597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30969429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28604698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31856250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39246034622192</t>
   </si>
   <si>
     <t xml:space="preserve">4.29491519927979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33629846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25353240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3244743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37472486495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3392539024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38063716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49295997619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37768030166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40723896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38950395584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31560659408569</t>
+    <t xml:space="preserve">4.3362979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25353288650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32447338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37472438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3274302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33925342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38063621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49296092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37768077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40724039077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38950490951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31560754776001</t>
   </si>
   <si>
     <t xml:space="preserve">4.27126836776733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21510553359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.342209815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3215184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25648880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28309154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23284149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22101879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16190004348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1973705291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24170970916748</t>
+    <t xml:space="preserve">4.21510601043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34221029281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32151746749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25648832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28309202194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057744979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23284244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22101831436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16189956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19737100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24171018600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.17963552474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22397375106812</t>
+    <t xml:space="preserve">4.22397422790527</t>
   </si>
   <si>
     <t xml:space="preserve">4.26831197738647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2919602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35403251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43679904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42201852798462</t>
+    <t xml:space="preserve">4.29195928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35403394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43679809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42201900482178</t>
   </si>
   <si>
     <t xml:space="preserve">4.26535701751709</t>
@@ -1049,49 +1049,49 @@
     <t xml:space="preserve">4.17372369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16781282424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24762153625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21806240081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23866939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13528633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13832712173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16873407363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16569375991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25083065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25995302200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27211666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3663763999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36941623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34509181976318</t>
+    <t xml:space="preserve">4.16781187057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24762105941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21806192398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2801365852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23866891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13528680801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13832664489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16873359680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1656928062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25083112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25995349884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27211618423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36637592315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3694167137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34509134292603</t>
   </si>
   <si>
     <t xml:space="preserve">4.35117292404175</t>
@@ -1100,40 +1100,40 @@
     <t xml:space="preserve">4.32988786697388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38157939910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3359694480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39678287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44543313980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50016498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54577445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43935203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48800182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51232767105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44847393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46367740631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38766050338745</t>
+    <t xml:space="preserve">4.38157987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33596897125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39678192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44543266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50016450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54577398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43935251235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48800277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51232814788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44847297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46367645263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38766145706177</t>
   </si>
   <si>
     <t xml:space="preserve">4.30860376358032</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">4.29340028762817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3724570274353</t>
+    <t xml:space="preserve">4.37245845794678</t>
   </si>
   <si>
     <t xml:space="preserve">4.46063661575317</t>
@@ -1151,31 +1151,31 @@
     <t xml:space="preserve">4.45759534835815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55489587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57922172546387</t>
+    <t xml:space="preserve">4.42718982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55489683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57922220230103</t>
   </si>
   <si>
     <t xml:space="preserve">4.62179136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70084762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72517395019531</t>
+    <t xml:space="preserve">4.70084857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.725172996521</t>
   </si>
   <si>
     <t xml:space="preserve">4.74037647247314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73429393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77078199386597</t>
+    <t xml:space="preserve">4.73429489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77078247070312</t>
   </si>
   <si>
     <t xml:space="preserve">4.81639289855957</t>
@@ -1184,52 +1184,52 @@
     <t xml:space="preserve">4.81943368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76470232009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80422925949097</t>
+    <t xml:space="preserve">4.76470136642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80422973632812</t>
   </si>
   <si>
     <t xml:space="preserve">4.83463621139526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71301078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61571073532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69172620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62787199020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5366530418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25691270828247</t>
+    <t xml:space="preserve">4.71301031112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61570882797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.691725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62787246704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53665208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25691318511963</t>
   </si>
   <si>
     <t xml:space="preserve">4.29948234558105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40590524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39374160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43327045440674</t>
+    <t xml:space="preserve">4.40590476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39374208450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43326950073242</t>
   </si>
   <si>
     <t xml:space="preserve">4.42414855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42110776901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43022966384888</t>
+    <t xml:space="preserve">4.42110824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43022918701172</t>
   </si>
   <si>
     <t xml:space="preserve">4.52449035644531</t>
@@ -1238,70 +1238,70 @@
     <t xml:space="preserve">4.5032057762146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31468534469604</t>
+    <t xml:space="preserve">4.31468439102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.27819681167603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32076644897461</t>
+    <t xml:space="preserve">4.32076692581177</t>
   </si>
   <si>
     <t xml:space="preserve">4.38461971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41502666473389</t>
+    <t xml:space="preserve">4.41502714157104</t>
   </si>
   <si>
     <t xml:space="preserve">4.40894460678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35725450515747</t>
+    <t xml:space="preserve">4.35725402832031</t>
   </si>
   <si>
     <t xml:space="preserve">4.3329291343689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26907539367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29644107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30556344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2356276512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29035949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26603507995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26299428939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22650671005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21738433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28731918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32380723953247</t>
+    <t xml:space="preserve">4.26907444000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29644155502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30556297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23562812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29035997390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26603412628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26299381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22650575637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21738386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28731966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32380771636963</t>
   </si>
   <si>
     <t xml:space="preserve">4.38646936416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32702302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20500421524048</t>
+    <t xml:space="preserve">4.32702350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20500326156616</t>
   </si>
   <si>
     <t xml:space="preserve">4.11427068710327</t>
@@ -1310,298 +1310,298 @@
     <t xml:space="preserve">4.14555788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16745901107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24567651748657</t>
+    <t xml:space="preserve">4.16745805740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24567747116089</t>
   </si>
   <si>
     <t xml:space="preserve">4.23003339767456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25506258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254751205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16120195388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21438980102539</t>
+    <t xml:space="preserve">4.25506353378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24254894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16120100021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21439027786255</t>
   </si>
   <si>
     <t xml:space="preserve">4.17997360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17058801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08924007415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85458660125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83581399917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82329988479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77636885643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80765628814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81704187393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79826974868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73882412910461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63557600975037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74195241928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262567520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82642841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66060590744019</t>
+    <t xml:space="preserve">4.17058753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08924055099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85458636283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8358142375946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82329869270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77636861801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80765557289124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81704211235046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79827046394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73882341384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63557577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74195265769958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262662887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82642817497253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66060543060303</t>
   </si>
   <si>
     <t xml:space="preserve">3.72630882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74508237838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63870429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77011156082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71692323684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71379375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74820995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69814991950989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6825065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72318005561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.663733959198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76072549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64183306694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60116028785706</t>
+    <t xml:space="preserve">3.74508142471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6387050151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77011132240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71692276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71379351615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74821019172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69815063476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68250727653503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72317957878113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66373467445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76072525978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6418342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6011598110199</t>
   </si>
   <si>
     <t xml:space="preserve">3.57925915718079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6324474811554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68876481056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67624950408936</t>
+    <t xml:space="preserve">3.63244771957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68876433372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67624974250793</t>
   </si>
   <si>
     <t xml:space="preserve">3.70440793037415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56361508369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62931871414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66686296463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61993265151978</t>
+    <t xml:space="preserve">3.56361556053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62931942939758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66686272621155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6199324131012</t>
   </si>
   <si>
     <t xml:space="preserve">3.62619018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84520053863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99537944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88587355613708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91090321540833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87023091316223</t>
+    <t xml:space="preserve">3.84520125389099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99537873268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88587379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91090393066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87022948265076</t>
   </si>
   <si>
     <t xml:space="preserve">3.92341876029968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87961649894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84207248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78575444221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79514074325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7732400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70753693580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76698184013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452799797058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81078481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80139756202698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75446772575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73256587982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68563580513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82017040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75759649276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81391286849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77949714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86397242546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335896492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8921320438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99225044250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97660684585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912286758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00163602828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4447238445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47288203239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37276268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37589168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39466428756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098185539246</t>
+    <t xml:space="preserve">3.87961626052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84207153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7857551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79514193534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77323961257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70753598213196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76698279380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81078433990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80139899253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75446724891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73256635665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68563556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82017087936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75759601593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81391358375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77949786186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86397337913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335848808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89213109016418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99224948883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97660660743713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912119865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00163698196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4728832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37276387214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.375892162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3946647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4509813785553</t>
   </si>
   <si>
     <t xml:space="preserve">3.39779305458069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31018829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29141616821289</t>
+    <t xml:space="preserve">3.31018853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29141640663147</t>
   </si>
   <si>
     <t xml:space="preserve">3.24448561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22258472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16313886642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18503952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13498091697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21006965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20694160461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26325845718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31644678115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3070604801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3133180141449</t>
+    <t xml:space="preserve">3.22258448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16313862800598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18504047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13498044013977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21006989479065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2069411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2632577419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31644606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30705976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31331729888916</t>
   </si>
   <si>
     <t xml:space="preserve">3.28515934944153</t>
@@ -1610,76 +1610,76 @@
     <t xml:space="preserve">3.25387191772461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25074315071106</t>
+    <t xml:space="preserve">3.25074362754822</t>
   </si>
   <si>
     <t xml:space="preserve">3.27843809127808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13193368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26541566848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25890493392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32727336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48354363441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45098757743835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44773197174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44122076034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42494201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41843104362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29146099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27192759513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2335102558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28820610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34680676460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40866374969482</t>
+    <t xml:space="preserve">3.13193416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26541543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25890421867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32727360725403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48354387283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4509871006012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44773149490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44121980667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42494225502014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41843128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29146075248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27192687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23351049423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28820514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34680700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40866422653198</t>
   </si>
   <si>
     <t xml:space="preserve">3.33378458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31099438667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331845283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30773949623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15537548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32076144218445</t>
+    <t xml:space="preserve">3.31099462509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30773878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1553750038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32076168060303</t>
   </si>
   <si>
     <t xml:space="preserve">3.31425094604492</t>
@@ -1688,127 +1688,127 @@
     <t xml:space="preserve">3.2849497795105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41517472267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40215229988098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36634111404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44447565078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4640097618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633358955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48679995536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46075463294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49331068992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46726536750793</t>
+    <t xml:space="preserve">3.4151759147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40215253829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36634135246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44447612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46401023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633382797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48679971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46075415611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49331116676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46726584434509</t>
   </si>
   <si>
     <t xml:space="preserve">3.45749831199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50958871841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47052121162415</t>
+    <t xml:space="preserve">3.50958967208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47052216529846</t>
   </si>
   <si>
     <t xml:space="preserve">3.58121347427368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71795082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77655220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70818400382996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8318977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82864284515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87096571922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92305684089661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87422180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073301315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88724446296692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99142551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95886898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00770378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99793696403503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97189164161682</t>
+    <t xml:space="preserve">3.71795105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77655291557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70818448066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8318989276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82864308357239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87096619606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92305707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87422108650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99142527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95886874198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00770425796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99793648719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06305027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97189140319824</t>
   </si>
   <si>
     <t xml:space="preserve">4.01747035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06630563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06956052780151</t>
+    <t xml:space="preserve">4.06630516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06956100463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12165069580078</t>
+    <t xml:space="preserve">4.12165117263794</t>
   </si>
   <si>
     <t xml:space="preserve">4.09235000610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11514043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12816190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09886264801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14118576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08583879470825</t>
+    <t xml:space="preserve">4.11513996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12816286087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09886169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14118480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08583927154541</t>
   </si>
   <si>
     <t xml:space="preserve">4.11188459396362</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">4.13141870498657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26164484024048</t>
+    <t xml:space="preserve">4.26164388656616</t>
   </si>
   <si>
     <t xml:space="preserve">4.24862194061279</t>
@@ -1829,28 +1829,28 @@
     <t xml:space="preserve">4.24536609649658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24210977554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23559951782227</t>
+    <t xml:space="preserve">4.24211072921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23559808731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.23234367370605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32350063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38210391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40489292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37233591079712</t>
+    <t xml:space="preserve">4.3235011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38210344314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4048924446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37233638763428</t>
   </si>
   <si>
     <t xml:space="preserve">4.37569236755371</t>
@@ -1862,25 +1862,28 @@
     <t xml:space="preserve">4.32871341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33206939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4126033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39246892929077</t>
+    <t xml:space="preserve">4.3320689201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41260290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39246940612793</t>
   </si>
   <si>
     <t xml:space="preserve">4.36226940155029</t>
   </si>
   <si>
+    <t xml:space="preserve">4.37233686447144</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.22804594039917</t>
   </si>
   <si>
     <t xml:space="preserve">4.238112449646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25153493881226</t>
+    <t xml:space="preserve">4.25153541564941</t>
   </si>
   <si>
     <t xml:space="preserve">4.14751148223877</t>
@@ -1892,46 +1895,46 @@
     <t xml:space="preserve">4.16093349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10724401473999</t>
+    <t xml:space="preserve">4.10724496841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.1642894744873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1273775100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12402248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06697750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07704401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08039951324463</t>
+    <t xml:space="preserve">4.12737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12402296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06697654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07704496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08039999008179</t>
   </si>
   <si>
     <t xml:space="preserve">4.04684400558472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02671003341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00657606124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03342199325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09046649932861</t>
+    <t xml:space="preserve">4.02671051025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00657653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03342247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09046745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.14415597915649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13408946990967</t>
+    <t xml:space="preserve">4.13408899307251</t>
   </si>
   <si>
     <t xml:space="preserve">4.17435598373413</t>
@@ -1940,31 +1943,31 @@
     <t xml:space="preserve">4.15757846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11060047149658</t>
+    <t xml:space="preserve">4.11059951782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.13744449615479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07368803024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19784545898438</t>
+    <t xml:space="preserve">4.07368898391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19784593582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.21797895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24482345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34213590621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28173542022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28509092330933</t>
+    <t xml:space="preserve">4.24482393264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34213638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28173494338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28509044647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.33878040313721</t>
@@ -1973,13 +1976,13 @@
     <t xml:space="preserve">4.34549140930176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34884691238403</t>
+    <t xml:space="preserve">4.34884738922119</t>
   </si>
   <si>
     <t xml:space="preserve">4.47300386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50991487503052</t>
+    <t xml:space="preserve">4.50991582870483</t>
   </si>
   <si>
     <t xml:space="preserve">4.46293687820435</t>
@@ -2000,91 +2003,91 @@
     <t xml:space="preserve">4.51662683486938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53675985336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49313735961914</t>
+    <t xml:space="preserve">4.5367603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4931378364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.44280338287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42602491378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42266988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4495153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42938184738159</t>
+    <t xml:space="preserve">4.426025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42267036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44951438903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42938137054443</t>
   </si>
   <si>
     <t xml:space="preserve">4.5065598487854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4696478843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40924882888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39582538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20120096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20455646514893</t>
+    <t xml:space="preserve">4.46964836120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40924787521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39582586288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20120143890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20455741882324</t>
   </si>
   <si>
     <t xml:space="preserve">4.21126794815063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14079999923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33542537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43273687362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38575792312622</t>
+    <t xml:space="preserve">4.14080047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43273735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38575887680054</t>
   </si>
   <si>
     <t xml:space="preserve">4.46629285812378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41595888137817</t>
+    <t xml:space="preserve">4.41595840454102</t>
   </si>
   <si>
     <t xml:space="preserve">4.50320434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52333879470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60722732543945</t>
+    <t xml:space="preserve">4.52333736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60722780227661</t>
   </si>
   <si>
     <t xml:space="preserve">4.6172947883606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59716129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70454025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65756177902222</t>
+    <t xml:space="preserve">4.59716081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70453929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65756225585938</t>
   </si>
   <si>
     <t xml:space="preserve">4.67769527435303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72467374801636</t>
+    <t xml:space="preserve">4.7246732711792</t>
   </si>
   <si>
     <t xml:space="preserve">4.73138475418091</t>
@@ -2093,40 +2096,40 @@
     <t xml:space="preserve">4.69782876968384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.613938331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64078330993652</t>
+    <t xml:space="preserve">4.61393880844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64078378677368</t>
   </si>
   <si>
     <t xml:space="preserve">4.60387229919434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62736225128174</t>
+    <t xml:space="preserve">4.62736129760742</t>
   </si>
   <si>
     <t xml:space="preserve">4.62400579452515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62065076828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56024980545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6676287651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66427278518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66091823577881</t>
+    <t xml:space="preserve">4.62065029144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5602502822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66762828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66427230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66091728210449</t>
   </si>
   <si>
     <t xml:space="preserve">4.6810507774353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82534122467041</t>
+    <t xml:space="preserve">4.82534170150757</t>
   </si>
   <si>
     <t xml:space="preserve">4.86560821533203</t>
@@ -2135,34 +2138,34 @@
     <t xml:space="preserve">4.90251970291138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94278621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98305416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04345512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.073655128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08707761764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09714365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1172776222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15083360671997</t>
+    <t xml:space="preserve">4.942786693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98305368423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04345464706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07365417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08707714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09714412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11727809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15083408355713</t>
   </si>
   <si>
     <t xml:space="preserve">5.16090059280396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15754461288452</t>
+    <t xml:space="preserve">5.15754413604736</t>
   </si>
   <si>
     <t xml:space="preserve">5.16425609588623</t>
@@ -2171,7 +2174,7 @@
     <t xml:space="preserve">5.17432260513306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16761112213135</t>
+    <t xml:space="preserve">5.16761207580566</t>
   </si>
   <si>
     <t xml:space="preserve">5.23472356796265</t>
@@ -2180,10 +2183,10 @@
     <t xml:space="preserve">5.54343795776367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6340389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175233840942</t>
+    <t xml:space="preserve">5.63403940200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175186157227</t>
   </si>
   <si>
     <t xml:space="preserve">5.89241933822632</t>
@@ -2192,10 +2195,10 @@
     <t xml:space="preserve">5.77161836624146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7850399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87102508544922</t>
+    <t xml:space="preserve">5.78504037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87102460861206</t>
   </si>
   <si>
     <t xml:space="preserve">6.02923727035522</t>
@@ -2204,49 +2207,49 @@
     <t xml:space="preserve">6.17025184631348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18400859832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26999425888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840238571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32846212387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40069007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33878040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28031253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26311492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33534240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38349199295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33190202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23216104507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25967597961426</t>
+    <t xml:space="preserve">6.18401002883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2699933052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32846307754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40069055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33878087997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2803111076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26311445236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33534097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38349342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33190250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2321605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25967502593994</t>
   </si>
   <si>
     <t xml:space="preserve">6.23559999465942</t>
@@ -2255,10 +2258,10 @@
     <t xml:space="preserve">6.30438709259033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28375148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27687215805054</t>
+    <t xml:space="preserve">6.28375053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27687168121338</t>
   </si>
   <si>
     <t xml:space="preserve">6.2493577003479</t>
@@ -2270,37 +2273,37 @@
     <t xml:space="preserve">6.13585710525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14617586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09114599227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11866140365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91229772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91573715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0533127784729</t>
+    <t xml:space="preserve">6.1461763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09114503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11866044998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611516952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91229724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91573762893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05331230163574</t>
   </si>
   <si>
     <t xml:space="preserve">6.19088792800903</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00859975814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10490274429321</t>
+    <t xml:space="preserve">6.00860071182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00516080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10490322113037</t>
   </si>
   <si>
     <t xml:space="preserve">6.03267621994019</t>
@@ -2309,19 +2312,16 @@
     <t xml:space="preserve">5.92949438095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95700931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90885925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73001003265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85726737976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78504037857056</t>
+    <t xml:space="preserve">5.95700979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90885829925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73001146316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85726833343506</t>
   </si>
   <si>
     <t xml:space="preserve">5.60619258880615</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">5.61651086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70249557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66810178756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71625280380249</t>
+    <t xml:space="preserve">5.70249509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66810131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71625375747681</t>
   </si>
   <si>
     <t xml:space="preserve">5.77816104888916</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">5.80567693710327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80911540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8779034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98108577728271</t>
+    <t xml:space="preserve">5.80911636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87790441513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9810848236084</t>
   </si>
   <si>
     <t xml:space="preserve">6.01547908782959</t>
@@ -2363,31 +2363,31 @@
     <t xml:space="preserve">5.86758518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70593452453613</t>
+    <t xml:space="preserve">5.70593500137329</t>
   </si>
   <si>
     <t xml:space="preserve">5.40326929092407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35511779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.372314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24505758285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0627703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00430107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98366355895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9492712020874</t>
+    <t xml:space="preserve">5.3551173210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37231492996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24505853652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06277084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00430059432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98366498947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94927072525024</t>
   </si>
   <si>
     <t xml:space="preserve">4.69819593429565</t>
@@ -2399,25 +2399,25 @@
     <t xml:space="preserve">4.26483345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75580453872681</t>
+    <t xml:space="preserve">3.75580477714539</t>
   </si>
   <si>
     <t xml:space="preserve">3.71453237533569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36509132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36784315109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08306169509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092974662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8051598072052</t>
+    <t xml:space="preserve">3.36509156227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36784291267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08306217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092950820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516052246094</t>
   </si>
   <si>
     <t xml:space="preserve">2.91109275817871</t>
@@ -2429,88 +2429,88 @@
     <t xml:space="preserve">3.25365567207336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35133457183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53568458557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41599464416504</t>
+    <t xml:space="preserve">3.35133409500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53568482398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41599440574646</t>
   </si>
   <si>
     <t xml:space="preserve">3.24815225601196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19862508773804</t>
+    <t xml:space="preserve">3.1986255645752</t>
   </si>
   <si>
     <t xml:space="preserve">3.18899512290955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20000147819519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14359569549561</t>
+    <t xml:space="preserve">3.20000076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14359545707703</t>
   </si>
   <si>
     <t xml:space="preserve">3.25778269767761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43938231468201</t>
+    <t xml:space="preserve">3.43938183784485</t>
   </si>
   <si>
     <t xml:space="preserve">3.59415411949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76268339157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44970035552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49097275733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59759378433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52880597114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36096453666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56319999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54600405693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68013882637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85554695129395</t>
+    <t xml:space="preserve">3.76268362998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44969964027405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49097299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59759330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52880620956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36096405982971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48409366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56319975852966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54600286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68013858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85554766654968</t>
   </si>
   <si>
     <t xml:space="preserve">4.01031923294067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83147096633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65950226783752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60447239875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64574527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6870174407959</t>
+    <t xml:space="preserve">3.83147168159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6595025062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60447263717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64574456214905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68701767921448</t>
   </si>
   <si>
     <t xml:space="preserve">3.6904571056366</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">3.84866833686829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91745638847351</t>
+    <t xml:space="preserve">3.91745686531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.79019904136658</t>
@@ -2528,46 +2528,46 @@
     <t xml:space="preserve">3.70421481132507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80739617347717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81427478790283</t>
+    <t xml:space="preserve">3.80739521980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81427454948425</t>
   </si>
   <si>
     <t xml:space="preserve">3.92089533805847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95529007911682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03439521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0722279548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16853094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12037992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08598518371582</t>
+    <t xml:space="preserve">3.95528960227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03439474105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16853046417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12037897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08598613739014</t>
   </si>
   <si>
     <t xml:space="preserve">4.23731851577759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28547048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44712114334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65348386764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76010417938232</t>
+    <t xml:space="preserve">4.2854700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44712066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65348339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76010465621948</t>
   </si>
   <si>
     <t xml:space="preserve">4.57781744003296</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">4.33018207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34737920761108</t>
+    <t xml:space="preserve">4.34737873077393</t>
   </si>
   <si>
     <t xml:space="preserve">4.49183320999146</t>
@@ -2585,28 +2585,28 @@
     <t xml:space="preserve">4.4436821937561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42304563522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4677562713623</t>
+    <t xml:space="preserve">4.42304515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46775722503662</t>
   </si>
   <si>
     <t xml:space="preserve">4.4539999961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49527168273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30266666412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29234886169434</t>
+    <t xml:space="preserve">4.49527263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30266714096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29234933853149</t>
   </si>
   <si>
     <t xml:space="preserve">4.33706045150757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37489414215088</t>
+    <t xml:space="preserve">4.37489366531372</t>
   </si>
   <si>
     <t xml:space="preserve">4.39553022384644</t>
@@ -2615,19 +2615,19 @@
     <t xml:space="preserve">4.32330322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52622699737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41616678237915</t>
+    <t xml:space="preserve">4.52622604370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41616725921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.52278709411621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5021505355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31298542022705</t>
+    <t xml:space="preserve">4.50215101242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31298494338989</t>
   </si>
   <si>
     <t xml:space="preserve">4.41960620880127</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">4.47119665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53310489654541</t>
+    <t xml:space="preserve">4.53310537338257</t>
   </si>
   <si>
     <t xml:space="preserve">4.53654432296753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5571813583374</t>
+    <t xml:space="preserve">4.55718183517456</t>
   </si>
   <si>
     <t xml:space="preserve">4.66380214691162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61221122741699</t>
+    <t xml:space="preserve">4.61221218109131</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093906402588</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">4.52966594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45743894577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40928792953491</t>
+    <t xml:space="preserve">4.45743942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40928745269775</t>
   </si>
   <si>
     <t xml:space="preserve">4.39209079742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42648410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26139450073242</t>
+    <t xml:space="preserve">4.42648363113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26139402389526</t>
   </si>
   <si>
     <t xml:space="preserve">4.42992401123047</t>
@@ -2678,58 +2678,58 @@
     <t xml:space="preserve">4.43680286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56062078475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63628768920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68443870544434</t>
+    <t xml:space="preserve">4.56062030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63628673553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68443822860718</t>
   </si>
   <si>
     <t xml:space="preserve">4.60877227783203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48839330673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56405973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45056009292603</t>
+    <t xml:space="preserve">4.48839378356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56406021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45056056976318</t>
   </si>
   <si>
     <t xml:space="preserve">4.5950140953064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51590919494629</t>
+    <t xml:space="preserve">4.51590871810913</t>
   </si>
   <si>
     <t xml:space="preserve">4.54686307907104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40240907669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2751522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081815719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35425806045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55030250549316</t>
+    <t xml:space="preserve">4.40240859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27515172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3508186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35425758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55030298233032</t>
   </si>
   <si>
     <t xml:space="preserve">4.33362150192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23043966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32674264907837</t>
+    <t xml:space="preserve">4.23044013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32674312591553</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636463165283</t>
@@ -2738,28 +2738,28 @@
     <t xml:space="preserve">4.27859115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50559043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43336391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29922723770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31986379623413</t>
+    <t xml:space="preserve">4.50559139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43336343765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29922771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31986427307129</t>
   </si>
   <si>
     <t xml:space="preserve">4.30610656738281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16165208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03783416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9896833896637</t>
+    <t xml:space="preserve">4.16165256500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03783512115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98968410491943</t>
   </si>
   <si>
     <t xml:space="preserve">4.03095579147339</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">4.73259019851685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81169605255127</t>
+    <t xml:space="preserve">4.81169557571411</t>
   </si>
   <si>
     <t xml:space="preserve">4.93207406997681</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">4.96646785736084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20034599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19346714019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12467956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22442102432251</t>
+    <t xml:space="preserve">5.20034503936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1934666633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12467908859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22442150115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.24161815643311</t>
@@ -2801,43 +2801,43 @@
     <t xml:space="preserve">5.3791937828064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569414138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34136056900024</t>
+    <t xml:space="preserve">5.26569366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34136009216309</t>
   </si>
   <si>
     <t xml:space="preserve">5.23130035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2966480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1556339263916</t>
+    <t xml:space="preserve">5.29664850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15563344955444</t>
   </si>
   <si>
     <t xml:space="preserve">5.11092185974121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10404300689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04557418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00774097442627</t>
+    <t xml:space="preserve">5.10404348373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04557371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00774002075195</t>
   </si>
   <si>
     <t xml:space="preserve">5.00086164474487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91831636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88736152648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89424133300781</t>
+    <t xml:space="preserve">4.91831731796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8873610496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8942403793335</t>
   </si>
   <si>
     <t xml:space="preserve">4.89767980575562</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">4.8839225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86672592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76698398590088</t>
+    <t xml:space="preserve">4.8667254447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76698303222656</t>
   </si>
   <si>
     <t xml:space="preserve">4.83577108383179</t>
@@ -2861,67 +2861,67 @@
     <t xml:space="preserve">4.89080142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91487646102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85984754562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87016534805298</t>
+    <t xml:space="preserve">4.91487693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85984706878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87016487121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.05933046340942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03869438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03181600570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71539258956909</t>
+    <t xml:space="preserve">5.03869533538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03181552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71539211273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.59845352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53998470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61565065383911</t>
+    <t xml:space="preserve">4.53998422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61565113067627</t>
   </si>
   <si>
     <t xml:space="preserve">4.67068099975586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02837657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12811851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31728458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25537538528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27257299423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2588152885437</t>
+    <t xml:space="preserve">5.02837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12811899185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31728506088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25537586212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27257204055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25881576538086</t>
   </si>
   <si>
     <t xml:space="preserve">5.15219449996948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07652807235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09028625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14875555038452</t>
+    <t xml:space="preserve">5.07652854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09028577804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14875507354736</t>
   </si>
   <si>
     <t xml:space="preserve">5.02493715286255</t>
@@ -2930,13 +2930,13 @@
     <t xml:space="preserve">5.05245208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96990728378296</t>
+    <t xml:space="preserve">4.9699068069458</t>
   </si>
   <si>
     <t xml:space="preserve">5.13499784469604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16251277923584</t>
+    <t xml:space="preserve">5.16251230239868</t>
   </si>
   <si>
     <t xml:space="preserve">5.14187574386597</t>
@@ -2948,70 +2948,70 @@
     <t xml:space="preserve">5.29320907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32760286331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34479999542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33104228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33792161941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45142030715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5889949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52708673477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44454145431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48237419128418</t>
+    <t xml:space="preserve">5.32760238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34479951858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33104181289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33792114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45142126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58899593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50645065307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52708625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44454193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48237466812134</t>
   </si>
   <si>
     <t xml:space="preserve">5.48925352096558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56492042541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53740501403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51952123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5511622428894</t>
+    <t xml:space="preserve">5.56491994857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53740549087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51952028274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55116319656372</t>
   </si>
   <si>
     <t xml:space="preserve">5.47824811935425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40258121490479</t>
+    <t xml:space="preserve">5.40258169174194</t>
   </si>
   <si>
     <t xml:space="preserve">5.45898723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4122109413147</t>
+    <t xml:space="preserve">5.41221141815186</t>
   </si>
   <si>
     <t xml:space="preserve">5.414963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36543607711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38332033157349</t>
+    <t xml:space="preserve">5.36543655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38332080841064</t>
   </si>
   <si>
     <t xml:space="preserve">5.43972682952881</t>
@@ -3020,49 +3020,49 @@
     <t xml:space="preserve">5.39019966125488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32553911209106</t>
+    <t xml:space="preserve">5.32553863525391</t>
   </si>
   <si>
     <t xml:space="preserve">5.37644243240356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39982891082764</t>
+    <t xml:space="preserve">5.39982938766479</t>
   </si>
   <si>
     <t xml:space="preserve">5.37506628036499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34617519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46036338806152</t>
+    <t xml:space="preserve">5.34617567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46036386489868</t>
   </si>
   <si>
     <t xml:space="preserve">5.37369060516357</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43697595596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5140175819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57730197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55528926849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42046642303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42321681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44247913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39845371246338</t>
+    <t xml:space="preserve">5.43697500228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51401710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57730150222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55528974533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42046594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44247817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39845418930054</t>
   </si>
   <si>
     <t xml:space="preserve">5.47484064102173</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">5.43066644668579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42928695678711</t>
+    <t xml:space="preserve">5.42928552627563</t>
   </si>
   <si>
     <t xml:space="preserve">5.44309091567993</t>
@@ -3080,46 +3080,46 @@
     <t xml:space="preserve">5.59493923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58113574981689</t>
+    <t xml:space="preserve">5.58113527297974</t>
   </si>
   <si>
     <t xml:space="preserve">5.56733083724976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57837438583374</t>
+    <t xml:space="preserve">5.57837390899658</t>
   </si>
   <si>
     <t xml:space="preserve">5.55766773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60046052932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70813655853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74264717102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63773393630981</t>
+    <t xml:space="preserve">5.60046148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70813608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74264621734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63773345947266</t>
   </si>
   <si>
     <t xml:space="preserve">5.67224454879761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69571208953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66948318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76473426818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7771577835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500495910645</t>
+    <t xml:space="preserve">5.69571161270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66948366165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76473474502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77715826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6750054359436</t>
   </si>
   <si>
     <t xml:space="preserve">5.65291786193848</t>
@@ -3134,43 +3134,43 @@
     <t xml:space="preserve">5.83927774429321</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66120052337646</t>
+    <t xml:space="preserve">5.66120004653931</t>
   </si>
   <si>
     <t xml:space="preserve">5.79234313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66258096694946</t>
+    <t xml:space="preserve">5.66258192062378</t>
   </si>
   <si>
     <t xml:space="preserve">5.66534233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68466854095459</t>
+    <t xml:space="preserve">5.68466901779175</t>
   </si>
   <si>
     <t xml:space="preserve">5.68328857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68604898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65015602111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55352544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6363525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72746276855469</t>
+    <t xml:space="preserve">5.68604850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65015745162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55352592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63635349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72746229171753</t>
   </si>
   <si>
     <t xml:space="preserve">5.66810274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68742942810059</t>
+    <t xml:space="preserve">5.68742895126343</t>
   </si>
   <si>
     <t xml:space="preserve">5.60460233688354</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">5.59355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36164474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40443801879883</t>
+    <t xml:space="preserve">5.36164379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40443849563599</t>
   </si>
   <si>
     <t xml:space="preserve">5.57975435256958</t>
@@ -3191,16 +3191,16 @@
     <t xml:space="preserve">5.62392902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67362451553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81442975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81995153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79924535751343</t>
+    <t xml:space="preserve">5.67362499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8199520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79924488067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.79510307312012</t>
@@ -3215,256 +3215,256 @@
     <t xml:space="preserve">5.71503782272339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75507164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8075270652771</t>
+    <t xml:space="preserve">5.75507211685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80752801895142</t>
   </si>
   <si>
     <t xml:space="preserve">5.88069200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95523595809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96351861953735</t>
+    <t xml:space="preserve">5.95523548126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96351766586304</t>
   </si>
   <si>
     <t xml:space="preserve">6.04910564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0311598777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06981229782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0325403213501</t>
+    <t xml:space="preserve">6.03115940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0698127746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03254079818726</t>
   </si>
   <si>
     <t xml:space="preserve">6.07809448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94695234298706</t>
+    <t xml:space="preserve">5.94695329666138</t>
   </si>
   <si>
     <t xml:space="preserve">5.92348480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98284530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97318124771118</t>
+    <t xml:space="preserve">5.98284387588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97318172454834</t>
   </si>
   <si>
     <t xml:space="preserve">5.99802923202515</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98560476303101</t>
+    <t xml:space="preserve">5.98560428619385</t>
   </si>
   <si>
     <t xml:space="preserve">6.03668165206909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05048561096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06705141067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06567096710205</t>
+    <t xml:space="preserve">6.05048513412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06705188751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06567144393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.08775758743286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09051990509033</t>
+    <t xml:space="preserve">6.09051895141602</t>
   </si>
   <si>
     <t xml:space="preserve">6.06014919281006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04220294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03944301605225</t>
+    <t xml:space="preserve">6.04220342636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03944253921509</t>
   </si>
   <si>
     <t xml:space="preserve">6.01045322418213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15677928924561</t>
+    <t xml:space="preserve">6.15677976608276</t>
   </si>
   <si>
     <t xml:space="preserve">6.19681310653687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15125799179077</t>
+    <t xml:space="preserve">6.15125846862793</t>
   </si>
   <si>
     <t xml:space="preserve">6.20233535766602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14573621749878</t>
+    <t xml:space="preserve">6.14573764801025</t>
   </si>
   <si>
     <t xml:space="preserve">5.9593768119812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14849710464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34590101242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30034685134888</t>
+    <t xml:space="preserve">6.14849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34590148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30034637451172</t>
   </si>
   <si>
     <t xml:space="preserve">6.32519388198853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32243394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3983588218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45357704162598</t>
+    <t xml:space="preserve">6.32243299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39835786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4535756111145</t>
   </si>
   <si>
     <t xml:space="preserve">6.55710887908936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57229328155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70343589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60542440414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72690343856812</t>
+    <t xml:space="preserve">6.57229471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70343637466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60542392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72690439224243</t>
   </si>
   <si>
     <t xml:space="preserve">6.66616487503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71585941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80420875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72000217437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77245950698853</t>
+    <t xml:space="preserve">6.71586036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80420780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72000122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77245903015137</t>
   </si>
   <si>
     <t xml:space="preserve">6.80697011947632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82739305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70334100723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70931911468506</t>
+    <t xml:space="preserve">6.827392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70931816101074</t>
   </si>
   <si>
     <t xml:space="preserve">6.62562036514282</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61366367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56284713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66149044036865</t>
+    <t xml:space="preserve">6.6136646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56284618377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66149091720581</t>
   </si>
   <si>
     <t xml:space="preserve">6.60918045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56583642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50605201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58227682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49708318710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.553879737854</t>
+    <t xml:space="preserve">6.56583595275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5060510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58227634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49708414077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55387926101685</t>
   </si>
   <si>
     <t xml:space="preserve">6.68241548538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65850162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6644811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73771715164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77657556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78404951095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84532928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83187675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7436957359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66298675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56434202194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70861196517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58429384231567</t>
+    <t xml:space="preserve">6.65850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66448068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73771619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77657699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78404998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84532880783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8318772315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74369478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66298532485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56434106826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7086124420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58429431915283</t>
   </si>
   <si>
     <t xml:space="preserve">6.7761435508728</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68865919113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38783979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43848752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32951688766479</t>
+    <t xml:space="preserve">6.68865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38783931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4384880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32951641082764</t>
   </si>
   <si>
     <t xml:space="preserve">6.49374055862427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44309186935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47685766220093</t>
+    <t xml:space="preserve">6.44309139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47685813903809</t>
   </si>
   <si>
     <t xml:space="preserve">6.54899406433105</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">6.6840558052063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62112951278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56127166748047</t>
+    <t xml:space="preserve">6.62112903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56127262115479</t>
   </si>
   <si>
     <t xml:space="preserve">6.51522779464722</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">6.50601863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51062345504761</t>
+    <t xml:space="preserve">6.51062393188477</t>
   </si>
   <si>
     <t xml:space="preserve">6.52443599700928</t>
@@ -3494,79 +3494,79 @@
     <t xml:space="preserve">6.4446268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24510192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42927932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48299694061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58889865875244</t>
+    <t xml:space="preserve">6.2451024055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42927885055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48299646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5888991355896</t>
   </si>
   <si>
     <t xml:space="preserve">6.65335941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66103410720825</t>
+    <t xml:space="preserve">6.64568567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66103458404541</t>
   </si>
   <si>
     <t xml:space="preserve">6.74391317367554</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7945613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85288381576538</t>
+    <t xml:space="preserve">6.79456186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8528847694397</t>
   </si>
   <si>
     <t xml:space="preserve">6.66410350799561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78688764572144</t>
+    <t xml:space="preserve">6.78688812255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.84981441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97566795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.106125831604</t>
+    <t xml:space="preserve">6.97566843032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10612630844116</t>
   </si>
   <si>
     <t xml:space="preserve">7.13221788406372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99255180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96185445785522</t>
+    <t xml:space="preserve">6.99255132675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96185398101807</t>
   </si>
   <si>
     <t xml:space="preserve">6.79763078689575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79149198532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70554256439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40779209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41700124740601</t>
+    <t xml:space="preserve">6.79149293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70554304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40779161453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41700077056885</t>
   </si>
   <si>
     <t xml:space="preserve">6.55052804946899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51829719543457</t>
+    <t xml:space="preserve">6.51829767227173</t>
   </si>
   <si>
     <t xml:space="preserve">6.46611356735229</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">6.57201528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67177677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76386499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69786930084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45843982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54438877105713</t>
+    <t xml:space="preserve">6.67177772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76386594772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69786787033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45844078063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54438972473145</t>
   </si>
   <si>
     <t xml:space="preserve">6.69940328598022</t>
@@ -3596,25 +3596,25 @@
     <t xml:space="preserve">6.79916524887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56894588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34486532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52290105819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47225284576416</t>
+    <t xml:space="preserve">6.56894540786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52290201187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47225379943848</t>
   </si>
   <si>
     <t xml:space="preserve">6.38476943969727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36328268051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29575157165527</t>
+    <t xml:space="preserve">6.36328172683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29575204849243</t>
   </si>
   <si>
     <t xml:space="preserve">6.23435878753662</t>
@@ -3623,10 +3623,10 @@
     <t xml:space="preserve">6.28500747680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75089693069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88749408721924</t>
+    <t xml:space="preserve">5.75089645385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8874945640564</t>
   </si>
   <si>
     <t xml:space="preserve">5.6496000289917</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">5.336501121521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9881010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977857589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07098054885864</t>
+    <t xml:space="preserve">4.98810195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07098007202148</t>
   </si>
   <si>
     <t xml:space="preserve">5.62657833099365</t>
@@ -3659,46 +3659,46 @@
     <t xml:space="preserve">5.41937971115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50993394851685</t>
+    <t xml:space="preserve">5.50993299484253</t>
   </si>
   <si>
     <t xml:space="preserve">5.62811279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92125940322876</t>
+    <t xml:space="preserve">5.92125988006592</t>
   </si>
   <si>
     <t xml:space="preserve">5.88135528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86447334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82149839401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97190809249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90898084640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87214612960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92586421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9611644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12538862228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06860113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95195627212524</t>
+    <t xml:space="preserve">5.86447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82149791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97190856933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87214660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92586517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96116495132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12538814544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06860065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95195579528809</t>
   </si>
   <si>
     <t xml:space="preserve">6.05325317382812</t>
@@ -3713,10 +3713,10 @@
     <t xml:space="preserve">5.72787523269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7155966758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85679769515991</t>
+    <t xml:space="preserve">5.71559619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85679864883423</t>
   </si>
   <si>
     <t xml:space="preserve">5.82303237915039</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">5.77084970474243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81842851638794</t>
+    <t xml:space="preserve">5.81842803955078</t>
   </si>
   <si>
     <t xml:space="preserve">5.86293697357178</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">5.87098073959351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78090476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65865993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56536722183228</t>
+    <t xml:space="preserve">5.78090524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6586594581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56536769866943</t>
   </si>
   <si>
     <t xml:space="preserve">5.60397148132324</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">5.56375932693481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59271192550659</t>
+    <t xml:space="preserve">5.59271144866943</t>
   </si>
   <si>
     <t xml:space="preserve">5.55732488632202</t>
@@ -3770,61 +3770,61 @@
     <t xml:space="preserve">5.62166452407837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58788585662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50263595581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56054162979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66348552703857</t>
+    <t xml:space="preserve">5.58788633346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50263643264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56054210662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81146621704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66348505020142</t>
   </si>
   <si>
     <t xml:space="preserve">5.70852279663086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74069261550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76321125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68922138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71817398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510774612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75516939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76803684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95140504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91280126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84685277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75034379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706541061401</t>
+    <t xml:space="preserve">5.74069213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76321172714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68922090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75516891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76803731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95140409469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94175338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91280078887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84685325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75034332275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706493377686</t>
   </si>
   <si>
     <t xml:space="preserve">5.80503177642822</t>
@@ -3833,28 +3833,28 @@
     <t xml:space="preserve">5.72299909591675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55249929428101</t>
+    <t xml:space="preserve">5.55249977111816</t>
   </si>
   <si>
     <t xml:space="preserve">5.17450475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323230743408</t>
   </si>
   <si>
     <t xml:space="preserve">5.13107585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20828294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01043891906738</t>
+    <t xml:space="preserve">5.20828342437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01043939590454</t>
   </si>
   <si>
     <t xml:space="preserve">5.05225992202759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11820793151855</t>
+    <t xml:space="preserve">5.1182074546814</t>
   </si>
   <si>
     <t xml:space="preserve">5.11981630325317</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">5.15198612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30157518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16807174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17933034896851</t>
+    <t xml:space="preserve">5.30157566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16807079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17933082580566</t>
   </si>
   <si>
     <t xml:space="preserve">5.14876890182495</t>
@@ -3878,25 +3878,25 @@
     <t xml:space="preserve">5.04904317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07156133651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05386877059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88819360733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0345664024353</t>
+    <t xml:space="preserve">5.07156181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05386829376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88819456100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03456687927246</t>
   </si>
   <si>
     <t xml:space="preserve">5.17611360549927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03295850753784</t>
+    <t xml:space="preserve">5.03295755386353</t>
   </si>
   <si>
     <t xml:space="preserve">5.10855674743652</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">5.0377836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85924100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91232109069824</t>
+    <t xml:space="preserve">4.8592414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9123215675354</t>
   </si>
   <si>
     <t xml:space="preserve">4.98631143569946</t>
@@ -3920,28 +3920,28 @@
     <t xml:space="preserve">4.93483972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01848173141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0152645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96379375457764</t>
+    <t xml:space="preserve">5.01848125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01526498794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96379280090332</t>
   </si>
   <si>
     <t xml:space="preserve">4.99274587631226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18737316131592</t>
+    <t xml:space="preserve">5.1873722076416</t>
   </si>
   <si>
     <t xml:space="preserve">5.21150016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15842008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45598983764648</t>
+    <t xml:space="preserve">5.15841960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45599031448364</t>
   </si>
   <si>
     <t xml:space="preserve">5.59432029724121</t>
@@ -3950,16 +3950,16 @@
     <t xml:space="preserve">5.50746154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48976898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46242380142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50424480438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53641510009766</t>
+    <t xml:space="preserve">5.48976850509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46242427825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50424528121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53641414642334</t>
   </si>
   <si>
     <t xml:space="preserve">5.56858444213867</t>
@@ -3971,16 +3971,16 @@
     <t xml:space="preserve">5.40291023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44312238693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33374452590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19219827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28388261795044</t>
+    <t xml:space="preserve">5.44312286376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33374500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19219779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28388214111328</t>
   </si>
   <si>
     <t xml:space="preserve">5.22919321060181</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">5.0410008430481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14394283294678</t>
+    <t xml:space="preserve">5.14394330978394</t>
   </si>
   <si>
     <t xml:space="preserve">5.12946748733521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00883054733276</t>
+    <t xml:space="preserve">5.00883102416992</t>
   </si>
   <si>
     <t xml:space="preserve">5.24688720703125</t>
@@ -4007,19 +4007,19 @@
     <t xml:space="preserve">5.08121252059937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1825475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19863271713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31766033172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53963136672974</t>
+    <t xml:space="preserve">5.11660003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18254709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19863224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31765985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53963184356689</t>
   </si>
   <si>
     <t xml:space="preserve">5.41577816009521</t>
@@ -4028,43 +4028,43 @@
     <t xml:space="preserve">5.49459362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25653791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33052825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08925533294678</t>
+    <t xml:space="preserve">5.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25653743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33052778244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08925485610962</t>
   </si>
   <si>
     <t xml:space="preserve">5.15037727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18898153305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99596309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16002798080444</t>
+    <t xml:space="preserve">5.1889820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99596261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1600284576416</t>
   </si>
   <si>
     <t xml:space="preserve">5.08603763580322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13590145111084</t>
+    <t xml:space="preserve">5.135901927948</t>
   </si>
   <si>
     <t xml:space="preserve">4.9879207611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20345783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45920753479004</t>
+    <t xml:space="preserve">5.20345735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45920705795288</t>
   </si>
   <si>
     <t xml:space="preserve">5.39808464050293</t>
@@ -4082,22 +4082,22 @@
     <t xml:space="preserve">5.28709936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14555215835571</t>
+    <t xml:space="preserve">5.14555168151855</t>
   </si>
   <si>
     <t xml:space="preserve">5.30961751937866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35626411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47368383407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54284906387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61362171173096</t>
+    <t xml:space="preserve">5.35626459121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47368335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54284811019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61362218856812</t>
   </si>
   <si>
     <t xml:space="preserve">5.64579200744629</t>
@@ -4106,43 +4106,43 @@
     <t xml:space="preserve">5.67152738571167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73908472061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90315008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92406034469604</t>
+    <t xml:space="preserve">5.73908376693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90315055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9240608215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.04308795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11707878112793</t>
+    <t xml:space="preserve">6.11707830429077</t>
   </si>
   <si>
     <t xml:space="preserve">6.09616804122925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02539491653442</t>
+    <t xml:space="preserve">6.02539539337158</t>
   </si>
   <si>
     <t xml:space="preserve">6.06560659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08651733398438</t>
+    <t xml:space="preserve">6.08651685714722</t>
   </si>
   <si>
     <t xml:space="preserve">6.21519708633423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27149391174316</t>
+    <t xml:space="preserve">6.27149343490601</t>
   </si>
   <si>
     <t xml:space="preserve">6.24897480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26023387908936</t>
+    <t xml:space="preserve">6.26023435592651</t>
   </si>
   <si>
     <t xml:space="preserve">6.43716716766357</t>
@@ -4154,22 +4154,22 @@
     <t xml:space="preserve">6.45968675613403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49668216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46451234817505</t>
+    <t xml:space="preserve">6.49668169021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46451187133789</t>
   </si>
   <si>
     <t xml:space="preserve">6.45646905899048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50472450256348</t>
+    <t xml:space="preserve">6.50472402572632</t>
   </si>
   <si>
     <t xml:space="preserve">6.50969743728638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53290414810181</t>
+    <t xml:space="preserve">6.53290462493896</t>
   </si>
   <si>
     <t xml:space="preserve">6.56108474731445</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">6.47820091247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49312019348145</t>
+    <t xml:space="preserve">6.4931206703186</t>
   </si>
   <si>
     <t xml:space="preserve">6.52958917617798</t>
@@ -4187,31 +4187,31 @@
     <t xml:space="preserve">6.52461671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67878007888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53124761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61413097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57434606552124</t>
+    <t xml:space="preserve">6.67877912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53124713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61413049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5743465423584</t>
   </si>
   <si>
     <t xml:space="preserve">6.51301240921021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47488594055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46825551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54616546630859</t>
+    <t xml:space="preserve">6.4748854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52627420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46825504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">6.54948139190674</t>
@@ -4220,19 +4220,19 @@
     <t xml:space="preserve">6.4400749206543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39200210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55777025222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51466989517212</t>
+    <t xml:space="preserve">6.39200258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55776977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51467037200928</t>
   </si>
   <si>
     <t xml:space="preserve">6.49146270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46328258514404</t>
+    <t xml:space="preserve">6.46328210830688</t>
   </si>
   <si>
     <t xml:space="preserve">6.54450845718384</t>
@@ -4241,16 +4241,16 @@
     <t xml:space="preserve">6.56274318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68209552764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64728450775146</t>
+    <t xml:space="preserve">6.68209600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64728498458862</t>
   </si>
   <si>
     <t xml:space="preserve">6.73514175415039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86609840393066</t>
+    <t xml:space="preserve">6.86609792709351</t>
   </si>
   <si>
     <t xml:space="preserve">6.87935924530029</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">6.97218894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98545074462891</t>
+    <t xml:space="preserve">6.98545122146606</t>
   </si>
   <si>
     <t xml:space="preserve">7.07496500015259</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">7.13464117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19100189208984</t>
+    <t xml:space="preserve">7.191002368927</t>
   </si>
   <si>
     <t xml:space="preserve">7.20757961273193</t>
@@ -4292,34 +4292,34 @@
     <t xml:space="preserve">7.2672553062439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26559782028198</t>
+    <t xml:space="preserve">7.26559734344482</t>
   </si>
   <si>
     <t xml:space="preserve">7.34019374847412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40152740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40484237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49767255783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.540771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54243040084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47446489334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58884477615356</t>
+    <t xml:space="preserve">7.40152788162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40484285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45788860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49767208099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54077243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54242944717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47446537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58884572982788</t>
   </si>
   <si>
     <t xml:space="preserve">7.6203408241272</t>
@@ -4328,34 +4328,34 @@
     <t xml:space="preserve">7.64023303985596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67504405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69327831268311</t>
+    <t xml:space="preserve">7.67504358291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69327783584595</t>
   </si>
   <si>
     <t xml:space="preserve">7.52585220336914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46286010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49435615539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.559006690979</t>
+    <t xml:space="preserve">7.46286058425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49435710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55900621414185</t>
   </si>
   <si>
     <t xml:space="preserve">7.60542154312134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59713363647461</t>
+    <t xml:space="preserve">7.59713411331177</t>
   </si>
   <si>
     <t xml:space="preserve">7.60210657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66675567626953</t>
+    <t xml:space="preserve">7.66675519943237</t>
   </si>
   <si>
     <t xml:space="preserve">7.71814441680908</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">7.72643136978149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77781915664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45457315444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87604284286499</t>
+    <t xml:space="preserve">7.77782011032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45457363128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87604379653931</t>
   </si>
   <si>
     <t xml:space="preserve">7.03518056869507</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">6.66883373260498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73348331451416</t>
+    <t xml:space="preserve">6.733482837677</t>
   </si>
   <si>
     <t xml:space="preserve">6.51135492324829</t>
@@ -4388,37 +4388,37 @@
     <t xml:space="preserve">6.76166439056396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00037050247192</t>
+    <t xml:space="preserve">7.00036954879761</t>
   </si>
   <si>
     <t xml:space="preserve">6.86941289901733</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76663637161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76000595092773</t>
+    <t xml:space="preserve">6.76663684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76000642776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.67214965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83460187911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93406248092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92743110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01363134384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96887397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89262056350708</t>
+    <t xml:space="preserve">6.83460235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93406200408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92743158340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01363086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96887302398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89262104034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.05341529846191</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">7.06999158859253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07993793487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15950632095337</t>
+    <t xml:space="preserve">7.07993841171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15950584411621</t>
   </si>
   <si>
     <t xml:space="preserve">7.16282176971436</t>
@@ -4439,13 +4439,13 @@
     <t xml:space="preserve">7.18271398544312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0865683555603</t>
+    <t xml:space="preserve">7.08656883239746</t>
   </si>
   <si>
     <t xml:space="preserve">7.1429295539856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16344022750854</t>
+    <t xml:space="preserve">7.1634407043457</t>
   </si>
   <si>
     <t xml:space="preserve">7.05917692184448</t>
@@ -4457,43 +4457,43 @@
     <t xml:space="preserve">7.05746793746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00277233123779</t>
+    <t xml:space="preserve">7.00277185440063</t>
   </si>
   <si>
     <t xml:space="preserve">6.7805700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85406827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72245645523071</t>
+    <t xml:space="preserve">6.85406875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72245597839355</t>
   </si>
   <si>
     <t xml:space="preserve">6.92414712905884</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92585611343384</t>
+    <t xml:space="preserve">6.92585563659668</t>
   </si>
   <si>
     <t xml:space="preserve">6.92072772979736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77031517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65921401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76005887985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71049118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71220064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79937171936035</t>
+    <t xml:space="preserve">6.77031469345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65921354293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76005935668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71049165725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71220016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79937124252319</t>
   </si>
   <si>
     <t xml:space="preserve">6.78569793701172</t>
@@ -4502,31 +4502,31 @@
     <t xml:space="preserve">6.9549126625061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98738861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93782091140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74638605117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86774158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86261415481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79082584381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73100137710571</t>
+    <t xml:space="preserve">6.98738813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93782043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74638509750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86774206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86261367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79082536697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73100185394287</t>
   </si>
   <si>
     <t xml:space="preserve">6.84893989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03011989593506</t>
+    <t xml:space="preserve">7.0301194190979</t>
   </si>
   <si>
     <t xml:space="preserve">6.96858739852905</t>
@@ -4535,22 +4535,22 @@
     <t xml:space="preserve">6.98397016525269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00619077682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99422597885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99593496322632</t>
+    <t xml:space="preserve">7.00618982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99422550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99593448638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.02328300476074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06259536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09678030014038</t>
+    <t xml:space="preserve">7.0625958442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09678077697754</t>
   </si>
   <si>
     <t xml:space="preserve">7.12583780288696</t>
@@ -4568,16 +4568,16 @@
     <t xml:space="preserve">7.12754678726196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04208469390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98226118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87116003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94636726379395</t>
+    <t xml:space="preserve">7.04208421707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98226070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87116050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94636678695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.97029638290405</t>
@@ -4589,43 +4589,43 @@
     <t xml:space="preserve">7.09165287017822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96345901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90534496307373</t>
+    <t xml:space="preserve">6.96345853805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90534543991089</t>
   </si>
   <si>
     <t xml:space="preserve">6.72587442398071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88825273513794</t>
+    <t xml:space="preserve">6.84039354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8882532119751</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13096475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12925624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14976739883423</t>
+    <t xml:space="preserve">7.0608868598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13096570968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12925577163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14976692199707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30530834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34291124343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3497486114502</t>
+    <t xml:space="preserve">7.34291172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34974908828735</t>
   </si>
   <si>
     <t xml:space="preserve">7.38393354415894</t>
@@ -4634,40 +4634,40 @@
     <t xml:space="preserve">7.38564300537109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41982793807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44033908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46768617630005</t>
+    <t xml:space="preserve">7.41982746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44033861160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46768665313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.57536888122559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55485773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21813726425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20446300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19249773025513</t>
+    <t xml:space="preserve">7.55485820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2711238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20446252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788145065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19249820709229</t>
   </si>
   <si>
     <t xml:space="preserve">6.76347780227661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94465827941895</t>
+    <t xml:space="preserve">6.94465780258179</t>
   </si>
   <si>
     <t xml:space="preserve">7.0318284034729</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">6.91047334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92756462097168</t>
+    <t xml:space="preserve">6.92756509780884</t>
   </si>
   <si>
     <t xml:space="preserve">6.97371482849121</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">6.95662260055542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9497857093811</t>
+    <t xml:space="preserve">6.94978523254395</t>
   </si>
   <si>
     <t xml:space="preserve">7.02157306671143</t>
@@ -4700,28 +4700,28 @@
     <t xml:space="preserve">7.15318536758423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17027854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19078874588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03695726394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17882394790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18736982345581</t>
+    <t xml:space="preserve">7.17027759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21300792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19078826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03695678710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17882299423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18737030029297</t>
   </si>
   <si>
     <t xml:space="preserve">7.16856813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22497367858887</t>
+    <t xml:space="preserve">7.22497415542603</t>
   </si>
   <si>
     <t xml:space="preserve">7.08139705657959</t>
@@ -4730,10 +4730,10 @@
     <t xml:space="preserve">7.11558198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04037523269653</t>
+    <t xml:space="preserve">7.19933462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04037475585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.0284104347229</t>
@@ -4745,25 +4745,25 @@
     <t xml:space="preserve">6.87799739837646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83697509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80279064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8916711807251</t>
+    <t xml:space="preserve">6.83697557449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80279016494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89167165756226</t>
   </si>
   <si>
     <t xml:space="preserve">6.76860523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86090421676636</t>
+    <t xml:space="preserve">6.86090469360352</t>
   </si>
   <si>
     <t xml:space="preserve">6.88312482833862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76518726348877</t>
+    <t xml:space="preserve">6.76518630981445</t>
   </si>
   <si>
     <t xml:space="preserve">6.78740692138672</t>
@@ -4772,16 +4772,16 @@
     <t xml:space="preserve">6.77715158462524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72416496276855</t>
+    <t xml:space="preserve">6.72416543960571</t>
   </si>
   <si>
     <t xml:space="preserve">6.66946935653687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57887983322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60109949111938</t>
+    <t xml:space="preserve">6.57887935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60109996795654</t>
   </si>
   <si>
     <t xml:space="preserve">6.55153131484985</t>
@@ -4790,13 +4790,13 @@
     <t xml:space="preserve">6.48999834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49854516983032</t>
+    <t xml:space="preserve">6.49854469299316</t>
   </si>
   <si>
     <t xml:space="preserve">6.49341726303101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53443956375122</t>
+    <t xml:space="preserve">6.53443908691406</t>
   </si>
   <si>
     <t xml:space="preserve">6.58571624755859</t>
@@ -4808,13 +4808,13 @@
     <t xml:space="preserve">6.74980354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88483333587646</t>
+    <t xml:space="preserve">6.88483381271362</t>
   </si>
   <si>
     <t xml:space="preserve">6.80449962615967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82842874526978</t>
+    <t xml:space="preserve">6.82842922210693</t>
   </si>
   <si>
     <t xml:space="preserve">6.84552192687988</t>
@@ -4829,16 +4829,16 @@
     <t xml:space="preserve">7.16685914993286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29847145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28137922286987</t>
+    <t xml:space="preserve">7.29847049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28137874603271</t>
   </si>
   <si>
     <t xml:space="preserve">7.17198705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1942081451416</t>
+    <t xml:space="preserve">7.19420766830444</t>
   </si>
   <si>
     <t xml:space="preserve">7.29675436019897</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">7.26316118240356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23487281799316</t>
+    <t xml:space="preserve">7.23487234115601</t>
   </si>
   <si>
     <t xml:space="preserve">7.19597578048706</t>
@@ -4862,13 +4862,13 @@
     <t xml:space="preserve">7.17475891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19243907928467</t>
+    <t xml:space="preserve">7.19243860244751</t>
   </si>
   <si>
     <t xml:space="preserve">7.21896028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26669788360596</t>
+    <t xml:space="preserve">7.2666974067688</t>
   </si>
   <si>
     <t xml:space="preserve">7.25785732269287</t>
@@ -4877,7 +4877,7 @@
     <t xml:space="preserve">7.24901676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30029058456421</t>
+    <t xml:space="preserve">7.30029106140137</t>
   </si>
   <si>
     <t xml:space="preserve">7.2773060798645</t>
@@ -4889,25 +4889,25 @@
     <t xml:space="preserve">7.40637397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47532796859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44527053833008</t>
+    <t xml:space="preserve">7.47532749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44527101516724</t>
   </si>
   <si>
     <t xml:space="preserve">7.551353931427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61854028701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54074573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51952838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54781770706177</t>
+    <t xml:space="preserve">7.61853981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5407452583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51952886581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54781723022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.48239994049072</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">7.49654388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54428291320801</t>
+    <t xml:space="preserve">7.54428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">7.58671474456787</t>
@@ -4937,22 +4937,22 @@
     <t xml:space="preserve">7.65390110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79711246490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80241727828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81833028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72815847396851</t>
+    <t xml:space="preserve">7.79711294174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80241775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72815895080566</t>
   </si>
   <si>
     <t xml:space="preserve">7.8625316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04640960693359</t>
+    <t xml:space="preserve">8.04640865325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.11182689666748</t>
@@ -4961,25 +4961,25 @@
     <t xml:space="preserve">8.11005878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21967887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28509521484375</t>
+    <t xml:space="preserve">8.21967792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28509616851807</t>
   </si>
   <si>
     <t xml:space="preserve">8.27625560760498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37880229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43361186981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41946792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26741504669189</t>
+    <t xml:space="preserve">8.37880325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43361282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41946887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26741600036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.36642646789551</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">8.33106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33813762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46366882324219</t>
+    <t xml:space="preserve">8.33813858032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4636697769165</t>
   </si>
   <si>
     <t xml:space="preserve">8.44952487945557</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">8.5732889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67583656311035</t>
+    <t xml:space="preserve">8.67583560943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.75009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50079822540283</t>
+    <t xml:space="preserve">8.50079917907715</t>
   </si>
   <si>
     <t xml:space="preserve">8.68644428253174</t>
@@ -5021,10 +5021,10 @@
     <t xml:space="preserve">8.62456130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5715217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54499912261963</t>
+    <t xml:space="preserve">8.57152080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54500102996826</t>
   </si>
   <si>
     <t xml:space="preserve">8.59273719787598</t>
@@ -5036,37 +5036,37 @@
     <t xml:space="preserve">8.737717628479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783058166504</t>
+    <t xml:space="preserve">8.79783153533936</t>
   </si>
   <si>
     <t xml:space="preserve">8.78722286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7695426940918</t>
+    <t xml:space="preserve">8.76954174041748</t>
   </si>
   <si>
     <t xml:space="preserve">8.79959964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78191947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84026527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88888549804688</t>
+    <t xml:space="preserve">8.7819185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84026432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88888645172119</t>
   </si>
   <si>
     <t xml:space="preserve">8.86236476898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76070117950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73064517974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6298656463623</t>
+    <t xml:space="preserve">8.76070213317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73064613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62986660003662</t>
   </si>
   <si>
     <t xml:space="preserve">8.77661514282227</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">8.82258319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97286891937256</t>
+    <t xml:space="preserve">8.97286701202393</t>
   </si>
   <si>
     <t xml:space="preserve">8.87120532989502</t>
@@ -5084,34 +5084,34 @@
     <t xml:space="preserve">9.07011127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10547256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11431407928467</t>
+    <t xml:space="preserve">9.10547351837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11431312561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.14967441558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13199234008789</t>
+    <t xml:space="preserve">9.13199329376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.06127166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9993896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87562561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07895183563232</t>
+    <t xml:space="preserve">8.99938869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87562656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07895278930664</t>
   </si>
   <si>
     <t xml:space="preserve">9.03475093841553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9551887512207</t>
+    <t xml:space="preserve">8.95518779754639</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910488128662</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">8.91982746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74744129180908</t>
+    <t xml:space="preserve">8.7474422454834</t>
   </si>
   <si>
     <t xml:space="preserve">8.83142471313477</t>
@@ -5138,28 +5138,28 @@
     <t xml:space="preserve">9.12886428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24873924255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14269638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3040657043457</t>
+    <t xml:space="preserve">9.24873828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14269733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30406475067139</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705539703369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41471767425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4792652130127</t>
+    <t xml:space="preserve">9.41471862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47926616668701</t>
   </si>
   <si>
     <t xml:space="preserve">9.62680244445801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66368675231934</t>
+    <t xml:space="preserve">9.66368770599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.70057201385498</t>
@@ -5168,13 +5168,13 @@
     <t xml:space="preserve">9.94954013824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0601930618286</t>
+    <t xml:space="preserve">10.0601940155029</t>
   </si>
   <si>
     <t xml:space="preserve">10.0509719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99564552307129</t>
+    <t xml:space="preserve">9.99564647674561</t>
   </si>
   <si>
     <t xml:space="preserve">9.95876216888428</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">9.7651195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97720432281494</t>
+    <t xml:space="preserve">9.97720336914062</t>
   </si>
   <si>
     <t xml:space="preserve">10.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98642539978027</t>
+    <t xml:space="preserve">9.98642444610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901416778564</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">9.49770832061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55303478240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7927827835083</t>
+    <t xml:space="preserve">9.55303382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79278182983398</t>
   </si>
   <si>
     <t xml:space="preserve">9.68212985992432</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">9.57147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50693035125732</t>
+    <t xml:space="preserve">9.50692939758301</t>
   </si>
   <si>
     <t xml:space="preserve">9.69135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667739868164</t>
+    <t xml:space="preserve">9.74667644500732</t>
   </si>
   <si>
     <t xml:space="preserve">9.82044506072998</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">9.86655044555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91265678405762</t>
+    <t xml:space="preserve">9.9126558303833</t>
   </si>
   <si>
     <t xml:space="preserve">9.96798324584961</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">10.0233097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90343475341797</t>
+    <t xml:space="preserve">9.90343570709229</t>
   </si>
   <si>
     <t xml:space="preserve">10.1062994003296</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">10.2077302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48848724365234</t>
+    <t xml:space="preserve">9.48848628997803</t>
   </si>
   <si>
     <t xml:space="preserve">9.25796031951904</t>
@@ -5282,10 +5282,10 @@
     <t xml:space="preserve">8.99515914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96749687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31328773498535</t>
+    <t xml:space="preserve">8.96749591827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31328678131104</t>
   </si>
   <si>
     <t xml:space="preserve">9.43315982818604</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">9.58991813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82966709136963</t>
+    <t xml:space="preserve">9.82966613769531</t>
   </si>
   <si>
     <t xml:space="preserve">9.84810924530029</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">10.0878562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1892890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2446146011353</t>
+    <t xml:space="preserve">10.1892881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2446155548096</t>
   </si>
   <si>
     <t xml:space="preserve">10.014087677002</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">10.0970773696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0694150924683</t>
+    <t xml:space="preserve">10.0694141387939</t>
   </si>
   <si>
     <t xml:space="preserve">10.1247415542603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1800670623779</t>
+    <t xml:space="preserve">10.1800680160522</t>
   </si>
   <si>
     <t xml:space="preserve">10.3737096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198150634766</t>
+    <t xml:space="preserve">10.4198160171509</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907199859619</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">10.3552675247192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183841705322</t>
+    <t xml:space="preserve">10.3183832168579</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765743255615</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">10.2999420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3091630935669</t>
+    <t xml:space="preserve">10.3091621398926</t>
   </si>
   <si>
     <t xml:space="preserve">10.2169523239136</t>
@@ -5372,13 +5372,13 @@
     <t xml:space="preserve">10.2722787857056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276042938232</t>
+    <t xml:space="preserve">10.3276052474976</t>
   </si>
   <si>
     <t xml:space="preserve">10.4567003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4935846328735</t>
+    <t xml:space="preserve">10.4935836791992</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042375564575</t>
@@ -5396,22 +5396,22 @@
     <t xml:space="preserve">10.4474792480469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5581321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134576797485</t>
+    <t xml:space="preserve">10.5581312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134586334229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4843626022339</t>
+    <t xml:space="preserve">10.4843635559082</t>
   </si>
   <si>
     <t xml:space="preserve">10.6226797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7517747879028</t>
+    <t xml:space="preserve">10.7517738342285</t>
   </si>
   <si>
     <t xml:space="preserve">10.9177541732788</t>
@@ -6063,6 +6063,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.4300003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5799999237061</t>
   </si>
 </sst>
 </file>
@@ -28441,7 +28444,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28467,7 +28470,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G849" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28493,7 +28496,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G850" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28519,7 +28522,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28545,7 +28548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G852" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28571,7 +28574,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G853" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28597,7 +28600,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G854" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28623,7 +28626,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28649,7 +28652,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G856" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28675,7 +28678,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G857" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28701,7 +28704,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G858" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28727,7 +28730,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G859" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28753,7 +28756,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G860" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28779,7 +28782,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28805,7 +28808,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G862" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28831,7 +28834,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28857,7 +28860,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28883,7 +28886,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G865" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28909,7 +28912,7 @@
         <v>6</v>
       </c>
       <c r="G866" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28935,7 +28938,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G867" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28961,7 +28964,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G868" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28987,7 +28990,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G869" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -29013,7 +29016,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G870" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -29039,7 +29042,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G871" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29065,7 +29068,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G872" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29091,7 +29094,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29117,7 +29120,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G874" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29143,7 +29146,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29169,7 +29172,7 @@
         <v>6.125</v>
       </c>
       <c r="G876" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29195,7 +29198,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G877" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -29221,7 +29224,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G878" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -29247,7 +29250,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29273,7 +29276,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -29299,7 +29302,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G881" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -29325,7 +29328,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G882" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -29351,7 +29354,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G883" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -29377,7 +29380,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G884" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -29403,7 +29406,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G885" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -29429,7 +29432,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G886" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29455,7 +29458,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G887" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29481,7 +29484,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G888" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -29507,7 +29510,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G889" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -29533,7 +29536,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G890" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -29559,7 +29562,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G891" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29585,7 +29588,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29611,7 +29614,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29637,7 +29640,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G894" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29663,7 +29666,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29689,7 +29692,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G896" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29715,7 +29718,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G897" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29741,7 +29744,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G898" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29767,7 +29770,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29793,7 +29796,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G900" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29819,7 +29822,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G901" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29845,7 +29848,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G902" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29871,7 +29874,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29897,7 +29900,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29923,7 +29926,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G905" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29949,7 +29952,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29975,7 +29978,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G907" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -30001,7 +30004,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G908" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -30027,7 +30030,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G909" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30079,7 +30082,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G911" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -30105,7 +30108,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G912" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -30131,7 +30134,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -30157,7 +30160,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G914" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -30183,7 +30186,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G915" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -30209,7 +30212,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G916" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -30235,7 +30238,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G917" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -30261,7 +30264,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G918" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30287,7 +30290,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G919" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30313,7 +30316,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G920" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30339,7 +30342,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30365,7 +30368,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30417,7 +30420,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G924" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30443,7 +30446,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30469,7 +30472,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G926" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30495,7 +30498,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G927" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30521,7 +30524,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G928" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30547,7 +30550,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G929" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30573,7 +30576,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G930" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30599,7 +30602,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G931" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30625,7 +30628,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30651,7 +30654,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G933" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30677,7 +30680,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G934" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30703,7 +30706,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30729,7 +30732,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G936" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30755,7 +30758,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G937" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30781,7 +30784,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G938" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30807,7 +30810,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30833,7 +30836,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G940" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30859,7 +30862,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G941" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30885,7 +30888,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G942" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30911,7 +30914,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G943" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30937,7 +30940,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G944" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30963,7 +30966,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30989,7 +30992,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G946" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -31015,7 +31018,7 @@
         <v>7</v>
       </c>
       <c r="G947" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -31041,7 +31044,7 @@
         <v>6.875</v>
       </c>
       <c r="G948" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31067,7 +31070,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31093,7 +31096,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G950" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31119,7 +31122,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G951" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31145,7 +31148,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31171,7 +31174,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G953" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31197,7 +31200,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G954" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31223,7 +31226,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31249,7 +31252,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G956" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31275,7 +31278,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G957" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31301,7 +31304,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G958" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31327,7 +31330,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G959" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31353,7 +31356,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G960" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31379,7 +31382,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G961" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31405,7 +31408,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G962" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31431,7 +31434,7 @@
         <v>7.25</v>
       </c>
       <c r="G963" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31457,7 +31460,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G964" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31483,7 +31486,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G965" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31509,7 +31512,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31535,7 +31538,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G967" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31561,7 +31564,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G968" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31587,7 +31590,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G969" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31613,7 +31616,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G970" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31639,7 +31642,7 @@
         <v>7.625</v>
       </c>
       <c r="G971" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31665,7 +31668,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G972" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31691,7 +31694,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G973" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31717,7 +31720,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31743,7 +31746,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G975" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31769,7 +31772,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G976" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31795,7 +31798,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G977" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31821,7 +31824,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G978" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31847,7 +31850,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G979" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31873,7 +31876,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G980" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31899,7 +31902,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G981" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31925,7 +31928,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G982" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31951,7 +31954,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G983" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31977,7 +31980,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G984" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -32003,7 +32006,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G985" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -32029,7 +32032,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G986" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -32055,7 +32058,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G987" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32081,7 +32084,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G988" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32107,7 +32110,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G989" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32133,7 +32136,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G990" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32159,7 +32162,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G991" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32185,7 +32188,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G992" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -32211,7 +32214,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G993" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -32237,7 +32240,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32263,7 +32266,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G995" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32289,7 +32292,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G996" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32315,7 +32318,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G997" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32341,7 +32344,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G998" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32367,7 +32370,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G999" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32393,7 +32396,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32419,7 +32422,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1001" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -32445,7 +32448,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32471,7 +32474,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G1003" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32497,7 +32500,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1004" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -32523,7 +32526,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1005" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32549,7 +32552,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1006" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32575,7 +32578,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1007" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32601,7 +32604,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32627,7 +32630,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G1009" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32653,7 +32656,7 @@
         <v>9.125</v>
       </c>
       <c r="G1010" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32679,7 +32682,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32705,7 +32708,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G1012" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32731,7 +32734,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1013" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32757,7 +32760,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1014" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32783,7 +32786,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1015" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32809,7 +32812,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G1016" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32835,7 +32838,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G1017" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32861,7 +32864,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1018" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32887,7 +32890,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1019" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32913,7 +32916,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1020" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32939,7 +32942,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G1021" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32965,7 +32968,7 @@
         <v>9</v>
       </c>
       <c r="G1022" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32991,7 +32994,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G1023" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -33017,7 +33020,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1024" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -33043,7 +33046,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G1025" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -33069,7 +33072,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1026" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -33095,7 +33098,7 @@
         <v>8.875</v>
       </c>
       <c r="G1027" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -33121,7 +33124,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1028" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -33147,7 +33150,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1029" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -33173,7 +33176,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1030" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -33199,7 +33202,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1031" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -33225,7 +33228,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1032" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -33251,7 +33254,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33277,7 +33280,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1034" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33303,7 +33306,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1035" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33329,7 +33332,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1036" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33433,7 +33436,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33589,7 +33592,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1046" t="s">
-        <v>769</v>
+        <v>727</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -71739,7 +71742,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6912384259</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>1274860</v>
@@ -71760,6 +71763,32 @@
         <v>2016</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6911689815</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>924262</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>18.1800003051758</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>18.4500007629395</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>18.5799999237061</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMED.MI.xlsx
+++ b/data/BMED.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="2018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="2019">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,124 +38,124 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78446626663208</t>
+    <t xml:space="preserve">3.78446769714355</t>
   </si>
   <si>
     <t xml:space="preserve">BMED.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73277425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49607539176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41445469856262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40901374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43349981307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53144311904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53688502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28658223152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25937581062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920241355896</t>
+    <t xml:space="preserve">3.73277306556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41445398330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40901327133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43349957466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53144359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53688549995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28658294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25937604904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29202389717102</t>
   </si>
   <si>
     <t xml:space="preserve">3.10157608985901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21040344238281</t>
+    <t xml:space="preserve">3.21040415763855</t>
   </si>
   <si>
     <t xml:space="preserve">3.4198956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.428058385849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43077850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35187840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36276173591614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22672772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13966584205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18863844871521</t>
+    <t xml:space="preserve">3.42805814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43077874183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35187888145447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36276197433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22672748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13966536521912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">3.30562710762024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03083848953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89208340644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15599060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31378960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40357208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36548233032227</t>
+    <t xml:space="preserve">3.03083920478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89208388328552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15599036216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393438339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31378936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40357232093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36548256874084</t>
   </si>
   <si>
     <t xml:space="preserve">3.36820268630981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46614694595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43622016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36004137992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49063301086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56681227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56409239768982</t>
+    <t xml:space="preserve">3.46614789962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43622088432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36004114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49063396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56681275367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56409311294556</t>
   </si>
   <si>
     <t xml:space="preserve">3.69196367263794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71100926399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61850571632385</t>
+    <t xml:space="preserve">3.71100831031799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61850452423096</t>
   </si>
   <si>
     <t xml:space="preserve">3.6865222454071</t>
@@ -170,106 +170,106 @@
     <t xml:space="preserve">3.80623292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79262948036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76542186737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70284628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181913375854</t>
+    <t xml:space="preserve">3.79262852668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76542234420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70284676551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181937217712</t>
   </si>
   <si>
     <t xml:space="preserve">3.72189211845398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6946849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65387415885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81439447402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84432244300842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86608695983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71373009681702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63482880592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54232621192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74637770652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77630543708801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73821473121643</t>
+    <t xml:space="preserve">3.69468426704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65387